--- a/assets/tvm/Time Value of Money.xlsx
+++ b/assets/tvm/Time Value of Money.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pdwho\Dropbox (Personal)\Courses\Teaching\Financial Analytics\Course\1 - Time Value of Money\Async\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pdwho\Dropbox\Courses\Teaching\Financial Analytics\Course\1 - Time Value of Money\Async\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB48BC55-3E52-4356-A425-BA2B2E6AF316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3149E89A-9D9F-4A8D-BA4E-14DEA6FBA824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3188" yWindow="3067" windowWidth="16200" windowHeight="10613" xr2:uid="{4B9245ED-29C9-4BFA-B4BC-EEE18C2BBC8A}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10876" firstSheet="16" activeTab="16" xr2:uid="{A866A9DF-D953-4036-93AA-C66DC42DF8F3}"/>
   </bookViews>
   <sheets>
     <sheet name="PV" sheetId="2" r:id="rId1"/>
@@ -20,17 +20,18 @@
     <sheet name="Solution 1" sheetId="6" r:id="rId5"/>
     <sheet name="Annuity" sheetId="7" r:id="rId6"/>
     <sheet name="Annuity Challenge" sheetId="8" r:id="rId7"/>
-    <sheet name="Perpetuity" sheetId="9" r:id="rId8"/>
-    <sheet name="Perpetuity Challenge" sheetId="10" r:id="rId9"/>
-    <sheet name="Solutions 2" sheetId="11" r:id="rId10"/>
-    <sheet name="NPV" sheetId="12" r:id="rId11"/>
-    <sheet name="IRR" sheetId="13" r:id="rId12"/>
-    <sheet name="Challenge Problems 3" sheetId="14" r:id="rId13"/>
-    <sheet name="Solutions 3" sheetId="15" r:id="rId14"/>
-    <sheet name="TVM Functions" sheetId="16" r:id="rId15"/>
-    <sheet name="PV with PMT &amp; FV" sheetId="17" r:id="rId16"/>
-    <sheet name="Challenge Problems 4" sheetId="18" r:id="rId17"/>
-    <sheet name="Solutions 4" sheetId="19" r:id="rId18"/>
+    <sheet name="Annuity Solution" sheetId="9" r:id="rId8"/>
+    <sheet name="Perpetuity" sheetId="10" r:id="rId9"/>
+    <sheet name="Perpetuity Challenge" sheetId="11" r:id="rId10"/>
+    <sheet name="Perpetuity Solution" sheetId="12" r:id="rId11"/>
+    <sheet name="NPV" sheetId="13" r:id="rId12"/>
+    <sheet name="IRR" sheetId="14" r:id="rId13"/>
+    <sheet name="Challenge Problems 3" sheetId="15" r:id="rId14"/>
+    <sheet name="Solutions 3" sheetId="16" r:id="rId15"/>
+    <sheet name="TVM Functions" sheetId="17" r:id="rId16"/>
+    <sheet name="PV with PMT &amp; FV" sheetId="18" r:id="rId17"/>
+    <sheet name="Challenge Problems 4" sheetId="19" r:id="rId18"/>
+    <sheet name="Solutions 4" sheetId="20" r:id="rId19"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -53,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="32">
   <si>
     <t>An asset pays $100 in 5 years. The annual discount rate is 10%. What is the price of the asset today?</t>
   </si>
@@ -85,16 +86,16 @@
     <t>You are 25 years old. Starting next year, you want to start making equal annual contributions for your retirement. You plan to retire at age 60 (and your last annual contribution will be when you turn 60). You want to have $1,000,000 saved when you retire at 60. With an annual discount rate of 6%, how much must you contribute each year to meet your retirement goal?</t>
   </si>
   <si>
+    <t>Number of contributions</t>
+  </si>
+  <si>
+    <t>Annual contributions</t>
+  </si>
+  <si>
     <t>You buy an asset that pays $100 per year in perpetuity. The first payment will be received next year. If the annual discount rate is 10%, what is the price of the asset today?</t>
   </si>
   <si>
     <t>You are 30 years old. You buy an asset that will begin paying your family annual payments in perpetuity when you turn 61. The first payment is $12,000 and will be made at age 61, and the payments will grow 2% per year. If the annual discount rate is 6%, what is the price of the asset today?</t>
-  </si>
-  <si>
-    <t>Number of contributions</t>
-  </si>
-  <si>
-    <t>Annual contributions</t>
   </si>
   <si>
     <t>PV_60</t>
@@ -150,9 +151,6 @@
   <si>
     <t>CF_0</t>
   </si>
-  <si>
-    <t>s</t>
-  </si>
 </sst>
 </file>
 
@@ -193,7 +191,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -203,12 +201,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -244,7 +236,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="8" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -255,8 +247,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="8" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -269,7 +260,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="8" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -292,6 +283,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFF2CEEF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -323,7 +319,7 @@
         <xdr:cNvPr id="2" name="Graphic 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7D2A33F-CF6C-4CE6-97CC-906B37828DF9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6BF6E154-32AE-4E5D-9F57-CB03031FA32D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -380,7 +376,7 @@
             <xdr14:cNvPr id="2" name="Ink 1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E290C951-FD34-4932-A378-900378FFA9E8}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DEF43FB6-FBEB-48E2-83C1-83367C90F6A2}"/>
                 </a:ext>
               </a:extLst>
             </xdr14:cNvPr>
@@ -445,7 +441,7 @@
             <xdr14:cNvPr id="3" name="Ink 2">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{89AB6EBF-74A0-48D5-9419-000BBD02D7D6}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{989B839B-5103-4098-B21D-A1BBF7FA3BE2}"/>
                 </a:ext>
               </a:extLst>
             </xdr14:cNvPr>
@@ -510,7 +506,7 @@
             <xdr14:cNvPr id="4" name="Ink 3">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{97AD19EC-020F-485A-B21F-4E9C11FED119}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5553178F-301D-4CCF-BA73-760407866DF9}"/>
                 </a:ext>
               </a:extLst>
             </xdr14:cNvPr>
@@ -575,7 +571,7 @@
             <xdr14:cNvPr id="5" name="Ink 4">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B804ECB-1954-4000-B015-E9F8352630DB}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{541C12A1-D90A-4548-878A-FBE2BFCED31F}"/>
                 </a:ext>
               </a:extLst>
             </xdr14:cNvPr>
@@ -640,7 +636,7 @@
             <xdr14:cNvPr id="6" name="Ink 5">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4DD48CD9-C73B-4C4A-B5E2-AF7E6E9A89BE}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7697BAE-C7BB-4755-9134-384B6797BE68}"/>
                 </a:ext>
               </a:extLst>
             </xdr14:cNvPr>
@@ -705,7 +701,7 @@
             <xdr14:cNvPr id="7" name="Ink 6">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A6810249-2E0D-47FB-A4C7-D7225C00F18D}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C68C3B8-7482-4087-8737-9530B0258ABC}"/>
                 </a:ext>
               </a:extLst>
             </xdr14:cNvPr>
@@ -770,7 +766,7 @@
             <xdr14:cNvPr id="8" name="Ink 7">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{05351CC8-4D82-45A6-B726-8F0E729E6515}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0306179E-AC0E-457A-BA9C-DBAF52CAF5FA}"/>
                 </a:ext>
               </a:extLst>
             </xdr14:cNvPr>
@@ -835,7 +831,7 @@
             <xdr14:cNvPr id="9" name="Ink 8">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{03789019-0E11-4984-99E8-DE7514772C26}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E37D880D-4DCF-4918-8811-79426BC988E5}"/>
                 </a:ext>
               </a:extLst>
             </xdr14:cNvPr>
@@ -900,7 +896,7 @@
             <xdr14:cNvPr id="10" name="Ink 9">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FAE5410B-3B90-4CD7-AD39-212A9F6921CE}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{04E905F1-2576-4115-AB1E-CCE26ABC5C79}"/>
                 </a:ext>
               </a:extLst>
             </xdr14:cNvPr>
@@ -965,7 +961,7 @@
             <xdr14:cNvPr id="11" name="Ink 10">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C9AB9016-6777-4F8A-858C-02536E175E43}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4073CC20-29C0-4FE1-993B-59DE02212444}"/>
                 </a:ext>
               </a:extLst>
             </xdr14:cNvPr>
@@ -1030,7 +1026,7 @@
             <xdr14:cNvPr id="12" name="Ink 11">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F024DCA2-F18D-4FEE-84CE-2180E73C4B7B}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC077B03-78EF-46F3-9EFD-18AB9D4E7C08}"/>
                 </a:ext>
               </a:extLst>
             </xdr14:cNvPr>
@@ -1095,7 +1091,7 @@
             <xdr14:cNvPr id="13" name="Ink 12">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F3FB9AE-467C-4EA2-9DDC-214FFA2EA046}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8EE93B0F-5CB3-44D5-9CFE-103019AAE9D0}"/>
                 </a:ext>
               </a:extLst>
             </xdr14:cNvPr>
@@ -1160,7 +1156,7 @@
             <xdr14:cNvPr id="14" name="Ink 13">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A80BF13-6CCA-456B-87E8-B19368090AA4}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FAD2A6BF-7526-4891-881B-74667C57A3F9}"/>
                 </a:ext>
               </a:extLst>
             </xdr14:cNvPr>
@@ -1225,7 +1221,7 @@
             <xdr14:cNvPr id="15" name="Ink 14">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{884F0BE2-45B2-44BE-A7E6-F15DE31B87ED}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{50D93344-79BA-4D7F-BCD7-03A96CA5F689}"/>
                 </a:ext>
               </a:extLst>
             </xdr14:cNvPr>
@@ -1293,7 +1289,7 @@
         <xdr:cNvPr id="2" name="Graphic 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BC8DC468-FB27-4CBE-B728-255F2F61B342}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E1C604EA-D11E-47F4-B0D5-2027754D595F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1348,7 +1344,7 @@
         <xdr:cNvPr id="2" name="Graphic 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4DECF419-3393-47B8-BE38-666A55198CBC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{945CEAB5-D7CD-46A1-964B-E4372DC7CF05}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1402,7 +1398,7 @@
         <xdr:cNvPr id="2" name="Graphic 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{042B9E2D-9A92-4C7F-A7CD-D851652F0F29}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BB21E88C-7854-492C-BF93-DF1E1207C3FD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1457,7 +1453,7 @@
         <xdr:cNvPr id="2" name="Group 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E1455DCE-C5AE-4CAF-9C71-ADFDE436263F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6BBBD015-8EF4-4706-A98E-3AE1B60CF2A4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1476,7 +1472,7 @@
           <xdr:cNvPr id="3" name="Group 2">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{550D7D91-30C8-A741-1C3E-30734394AFAB}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A9DD732-781F-8F41-EF27-8007622CD68A}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -1497,7 +1493,7 @@
                 <xdr14:cNvPr id="11" name="Ink 10">
                   <a:extLst>
                     <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{456B79C0-227D-738C-F700-C6B7C8120F53}"/>
+                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4CC59FB6-BD48-3E5F-02B7-3F6B3791F97E}"/>
                     </a:ext>
                   </a:extLst>
                 </xdr14:cNvPr>
@@ -1547,7 +1543,7 @@
                 <xdr14:cNvPr id="12" name="Ink 11">
                   <a:extLst>
                     <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D85E244-28E4-C516-DEF4-29A9A2422710}"/>
+                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{510F8556-13BB-A5F3-8720-AD9C1A22D5FC}"/>
                     </a:ext>
                   </a:extLst>
                 </xdr14:cNvPr>
@@ -1598,7 +1594,7 @@
               <xdr14:cNvPr id="4" name="Ink 3">
                 <a:extLst>
                   <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{81B92602-E298-7C97-26A6-F702FC3B1221}"/>
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0CE9688-EF2B-1FA9-EBE3-362E506DF4CF}"/>
                   </a:ext>
                 </a:extLst>
               </xdr14:cNvPr>
@@ -1648,7 +1644,7 @@
               <xdr14:cNvPr id="5" name="Ink 4">
                 <a:extLst>
                   <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CFED97B6-DFC6-198D-9B4E-D4B9F5B1E279}"/>
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5A6E4233-5613-788F-09F2-8461188944AD}"/>
                   </a:ext>
                 </a:extLst>
               </xdr14:cNvPr>
@@ -1696,7 +1692,7 @@
           <xdr:cNvPr id="6" name="Group 5">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A671C531-5647-DA95-2D20-8172C4A783DF}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED5885DA-34B0-DB29-222E-0D87ACBE4186}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -1717,7 +1713,7 @@
                 <xdr14:cNvPr id="9" name="Ink 8">
                   <a:extLst>
                     <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CDFF37D3-0DB0-5E71-6B3F-E3178CBF8A2F}"/>
+                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE72053E-897B-F2CD-20E3-43B734FBE336}"/>
                     </a:ext>
                   </a:extLst>
                 </xdr14:cNvPr>
@@ -1767,7 +1763,7 @@
                 <xdr14:cNvPr id="10" name="Ink 9">
                   <a:extLst>
                     <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED46A138-B2C3-A245-BDA6-D32962B66144}"/>
+                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CCED06FD-3A6B-A682-0C4D-636061901D44}"/>
                     </a:ext>
                   </a:extLst>
                 </xdr14:cNvPr>
@@ -1818,7 +1814,7 @@
               <xdr14:cNvPr id="7" name="Ink 6">
                 <a:extLst>
                   <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B462B539-6B57-25D4-F1B1-B5B4FBFECA86}"/>
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{05742DFD-A1A2-3FE9-2891-A975E63A04BC}"/>
                   </a:ext>
                 </a:extLst>
               </xdr14:cNvPr>
@@ -1868,7 +1864,7 @@
               <xdr14:cNvPr id="8" name="Ink 7">
                 <a:extLst>
                   <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F06A8BE1-3E50-CCE1-2D5E-F90D1572A3C8}"/>
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E4864486-4634-708E-F6F8-8B1C2569A2FB}"/>
                   </a:ext>
                 </a:extLst>
               </xdr14:cNvPr>
@@ -1934,7 +1930,7 @@
             <xdr14:cNvPr id="13" name="Ink 12">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A0303E4-055C-4068-9C43-07CB313FCFC5}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F121C01-05B8-4EC5-AA45-1B026661DFF7}"/>
                 </a:ext>
               </a:extLst>
             </xdr14:cNvPr>
@@ -1999,7 +1995,7 @@
             <xdr14:cNvPr id="14" name="Ink 13">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3CAA195F-06C3-4D2E-A40D-BAB9BCCC2F5D}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C826BA13-3EEC-4A13-836F-9324BEA3587B}"/>
                 </a:ext>
               </a:extLst>
             </xdr14:cNvPr>
@@ -2064,7 +2060,7 @@
             <xdr14:cNvPr id="15" name="Ink 14">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0ED512D5-038A-4B4E-8664-EC4BCD200097}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{321F303C-A0F3-4FBA-8091-3DAA5218BD38}"/>
                 </a:ext>
               </a:extLst>
             </xdr14:cNvPr>
@@ -2129,7 +2125,7 @@
             <xdr14:cNvPr id="16" name="Ink 15">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8894BBEB-5FBB-40E0-BDD1-5E68A994A921}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{990C0DA2-5DB2-4835-A32C-DB900A650705}"/>
                 </a:ext>
               </a:extLst>
             </xdr14:cNvPr>
@@ -2194,7 +2190,7 @@
             <xdr14:cNvPr id="17" name="Ink 16">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{60CEF946-675B-472D-AF39-F9DC4164106C}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9F44A39-1556-4CEE-BAA6-232A6B90447A}"/>
                 </a:ext>
               </a:extLst>
             </xdr14:cNvPr>
@@ -2259,7 +2255,7 @@
             <xdr14:cNvPr id="18" name="Ink 17">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5BCE2EE6-B602-483F-B0FA-4F0D4ACD3F7B}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C0097DB6-23BF-4C02-ADF2-95AB0CD000DC}"/>
                 </a:ext>
               </a:extLst>
             </xdr14:cNvPr>
@@ -2324,7 +2320,7 @@
             <xdr14:cNvPr id="19" name="Ink 18">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A74495ED-2544-4664-A481-E70423A9275B}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8595DA81-A80A-4154-A4B5-360A182DF062}"/>
                 </a:ext>
               </a:extLst>
             </xdr14:cNvPr>
@@ -2392,7 +2388,7 @@
         <xdr:cNvPr id="2" name="Graphic 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B2257E5-FD48-47BC-9009-EBFF704E7323}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F1D3377-6F12-451E-8BB1-C0E8C3E0D847}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2449,7 +2445,7 @@
             <xdr14:cNvPr id="2" name="Ink 1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA809C6C-B619-443F-A25A-EEDDF895BF15}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EA4CC3D5-4F45-4B2C-A92D-425C2073157F}"/>
                 </a:ext>
               </a:extLst>
             </xdr14:cNvPr>
@@ -2519,7 +2515,7 @@
             <xdr14:cNvPr id="2" name="Ink 1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3BF91382-D8FF-4C8C-8EC0-20EDE5AFF353}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BBF2F811-47C5-44B9-A8F1-1FAFBCD75B48}"/>
                 </a:ext>
               </a:extLst>
             </xdr14:cNvPr>
@@ -2587,7 +2583,7 @@
         <xdr:cNvPr id="2" name="Group 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1CD5A7E4-D0C6-4932-B0AA-1623D17DAA9A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE8C9B95-06E2-4D20-AA1D-E197F5C0DD4D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2606,7 +2602,7 @@
           <xdr:cNvPr id="3" name="Group 2">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DCB7B7A5-0526-08D2-780D-4CC797CC7195}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{72D0FB47-7C3B-6571-F786-F37A672B0FA9}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -2627,7 +2623,7 @@
                 <xdr14:cNvPr id="15" name="Ink 14">
                   <a:extLst>
                     <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E5ED10BF-D813-96CB-3AC7-4721538F2019}"/>
+                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{61850A7D-F1F2-9E76-BF9B-EA3052B8F669}"/>
                     </a:ext>
                   </a:extLst>
                 </xdr14:cNvPr>
@@ -2677,7 +2673,7 @@
                 <xdr14:cNvPr id="16" name="Ink 15">
                   <a:extLst>
                     <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2783D488-FB0A-2456-ABEE-886B8D046D71}"/>
+                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB30F0A5-87FB-4123-98ED-515F8B589B5A}"/>
                     </a:ext>
                   </a:extLst>
                 </xdr14:cNvPr>
@@ -2728,7 +2724,7 @@
               <xdr14:cNvPr id="4" name="Ink 3">
                 <a:extLst>
                   <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5245AB25-421E-5ABE-0450-597235051E02}"/>
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F1215D23-CEFB-E02A-5AC4-4BAB5365A1D9}"/>
                   </a:ext>
                 </a:extLst>
               </xdr14:cNvPr>
@@ -2778,7 +2774,7 @@
               <xdr14:cNvPr id="5" name="Ink 4">
                 <a:extLst>
                   <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B802F59-2B80-6CCE-2A94-659907957208}"/>
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC04F386-55FE-F101-0C21-8DC2E4001325}"/>
                   </a:ext>
                 </a:extLst>
               </xdr14:cNvPr>
@@ -2826,7 +2822,7 @@
           <xdr:cNvPr id="6" name="Group 5">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB067B6E-8288-D7E6-C5FD-46324DF2FBE8}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D60B9AB-EF63-4065-96AC-BF90482DB1E4}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -2847,7 +2843,7 @@
                 <xdr14:cNvPr id="13" name="Ink 12">
                   <a:extLst>
                     <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CFEE10A1-AB02-7CF0-065A-7CCA6DEE0A2E}"/>
+                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0BDEE7A0-7A98-E673-1224-EDC211598CF2}"/>
                     </a:ext>
                   </a:extLst>
                 </xdr14:cNvPr>
@@ -2897,7 +2893,7 @@
                 <xdr14:cNvPr id="14" name="Ink 13">
                   <a:extLst>
                     <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0679FC0-DD30-484E-651E-40CB9D796498}"/>
+                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8FD3E81C-5EBD-79A7-951D-A663DAD9336D}"/>
                     </a:ext>
                   </a:extLst>
                 </xdr14:cNvPr>
@@ -2948,7 +2944,7 @@
               <xdr14:cNvPr id="7" name="Ink 6">
                 <a:extLst>
                   <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0EC0400A-FD8B-825E-4E87-8C8015175CFD}"/>
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{06EE2BC4-0D05-E628-7D45-D567260B4163}"/>
                   </a:ext>
                 </a:extLst>
               </xdr14:cNvPr>
@@ -2998,7 +2994,7 @@
               <xdr14:cNvPr id="8" name="Ink 7">
                 <a:extLst>
                   <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{881EAC49-648E-CCE6-B64D-42C3A9D0531B}"/>
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A1BD3D75-A798-BB3E-EF88-3690DEC6083E}"/>
                   </a:ext>
                 </a:extLst>
               </xdr14:cNvPr>
@@ -3046,7 +3042,7 @@
           <xdr:cNvPr id="9" name="Group 8">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{03557F49-9AA7-3608-2838-B186CB4EE591}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78BED5DC-625F-7C1D-9DA0-9D51E701A093}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -3067,7 +3063,7 @@
                 <xdr14:cNvPr id="11" name="Ink 10">
                   <a:extLst>
                     <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D441BA9B-74C9-7903-E8C3-D48AD89BF687}"/>
+                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2A502F6-F1C4-8800-B765-357E85DC5DA4}"/>
                     </a:ext>
                   </a:extLst>
                 </xdr14:cNvPr>
@@ -3117,7 +3113,7 @@
                 <xdr14:cNvPr id="12" name="Ink 11">
                   <a:extLst>
                     <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{419636CD-6F19-1A4C-D712-10DDFC10D3E2}"/>
+                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{52CC0FA3-1069-976A-501B-DC935EDADF7D}"/>
                     </a:ext>
                   </a:extLst>
                 </xdr14:cNvPr>
@@ -3168,7 +3164,7 @@
               <xdr14:cNvPr id="10" name="Ink 9">
                 <a:extLst>
                   <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EFB407C9-DAAD-E28D-E0E4-6EAB05E334F9}"/>
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{89AC3B0C-51BD-C438-1380-748BF590EB26}"/>
                   </a:ext>
                 </a:extLst>
               </xdr14:cNvPr>
@@ -3229,7 +3225,7 @@
             <xdr14:cNvPr id="17" name="Ink 16">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E928ABB-7F3E-44EA-8350-301930D3BEA7}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{06ED398E-5DFF-4668-8447-08C2DFC99022}"/>
                 </a:ext>
               </a:extLst>
             </xdr14:cNvPr>
@@ -3289,7 +3285,7 @@
             <xdr14:cNvPr id="18" name="Ink 17">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46D3D3AB-8E52-45BB-93CD-0B6F9701ED44}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{469AD15E-D2D7-44EE-BE12-B7698B39505A}"/>
                 </a:ext>
               </a:extLst>
             </xdr14:cNvPr>
@@ -3349,7 +3345,7 @@
             <xdr14:cNvPr id="19" name="Ink 18">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27CE5CF0-2406-494E-8BCA-47B83BE0C745}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9960D337-9A4A-4C87-8BC6-1627A3113B6B}"/>
                 </a:ext>
               </a:extLst>
             </xdr14:cNvPr>
@@ -3409,7 +3405,7 @@
             <xdr14:cNvPr id="20" name="Ink 19">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{60D7F082-CEC9-4590-BCCD-9EE718E82715}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{95359AAC-173F-4516-8B49-A4FBFC219268}"/>
                 </a:ext>
               </a:extLst>
             </xdr14:cNvPr>
@@ -3469,7 +3465,7 @@
             <xdr14:cNvPr id="21" name="Ink 20">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF180B42-EF6E-4861-934D-3DC1B07620AC}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{063F641A-650F-4533-8487-27BDF82F719B}"/>
                 </a:ext>
               </a:extLst>
             </xdr14:cNvPr>
@@ -3533,14 +3529,14 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2023-12-12T19:21:10.264"/>
+      <inkml:timestamp xml:id="ts0" timeString="2024-01-09T19:28:26.488"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.035" units="cm"/>
       <inkml:brushProperty name="height" value="0.035" units="cm"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">18 11 6272,'0'-1'324,"0"1"0,0-1 1,-1 1-1,1-1 1,0 0-1,0 1 0,0-1 1,-1 0-1,1 1 0,-1 0 1,-4-4 8266,5 8-6585,1 7-966,5 20 1,0-9-456,22 199 1826,-26-198-2203,16 187 1269,-16 34 6,-20-91-681,14-119-522,-5 21-362,-15 116-161,15-118 213,1-31-3156,7-38-15160,1 6 16485</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">18 11 6272,'0'-1'324,"0"1"0,0-1 1,-1 1-1,1-1 1,0 0-1,0 1 0,0-1 1,-1 0-1,1 1 0,-1 0 1,-4-4 8266,5 8-6585,1 7-966,5 20 1,0-9-456,22 198 1826,-26-197-2203,16 188 1269,-16 33 6,-20-91-681,14-119-522,-5 22-362,-15 115-161,14-119 213,3-30-3156,6-37-15160,1 4 16485</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -3560,7 +3556,7 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2023-12-12T19:21:10.269"/>
+      <inkml:timestamp xml:id="ts0" timeString="2024-01-09T19:28:26.493"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.05" units="cm"/>
@@ -3568,9 +3564,9 @@
       <inkml:brushProperty name="color" value="#FF0000"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">34 1 6400,'-1'8'11563,"0"13"-7966,-1 36-2923,2-4 1561,-14 106-1,7-130-1798,5-20-691,0 1-1,0-1 0,-1 17 1,3-27-763,1-1 1,-1 0-1,1 1 1,-1-1 0,1 1-1,0-1 1,0 1 0,1-3-1,3-5-764,1-7 652</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1">314 62 7808,'3'3'8680,"-10"3"-7051,4-1-1403,-1 0 1,1 0-1,0 0 1,0 0-1,1 1 1,-1-1-1,-1 9 0,0 0 31,1-1-1,-2 17 1,4-18-185,0 0 0,1 0 1,0-1-1,1 1 0,0 0 0,3 12 0,-3-21-52,0 1-1,1 0 1,-1-1-1,0 0 0,1 1 1,0-1-1,0 0 1,0 0-1,0 0 0,4 3 1,-4-4-6,0 0 1,0-1-1,0 1 1,0-1-1,0 1 1,1-1-1,-1 0 1,0 0-1,1 0 1,-1-1-1,1 1 1,-1 0-1,1-1 1,-1 0-1,1 1 1,3-1-1,-2-1 12,0 1 0,-1-1-1,1 0 1,0 0-1,0 0 1,-1-1-1,1 1 1,-1-1 0,1 0-1,-1 0 1,0 0-1,1 0 1,-1 0 0,0-1-1,-1 0 1,1 0-1,0 1 1,-1-1 0,1-1-1,-1 1 1,2-4-1,3-5 205,0-1 0,-1 0 0,-1 0 0,6-19-1,-9 26-33,0 0-1,-1 0 0,0 0 0,-1 0 0,1 0 1,-1 0-1,0-1 0,-1 1 0,1 0 1,-1 0-1,-1 0 0,1 0 0,-1 0 1,0 0-1,0 1 0,-1-1 0,1 0 1,-1 1-1,0 0 0,-1 0 0,1 0 1,-8-8-1,-1-2-1867,31 32-14090,-5-6 14066</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2">743 117 9984,'0'11'4671,"-5"13"-3060,3-20-678,1 2-787,1 0 0,-1 0 0,1 0-1,0 0 1,0 0 0,1 0 0,-1 0-1,1 0 1,1 0 0,-1 0 0,1 0-1,0-1 1,5 11 0,-4-11-150,-1 0 0,1 0 0,0 0-1,1 0 1,-1-1 0,1 0 0,0 1 0,0-2 0,0 1 0,1 0 0,-1-1-1,1 1 1,0-1 0,9 4 0,-12-6 53,-1-1 0,1 1 0,-1-1 0,1 0 0,0 1 0,0-1 0,-1 0 0,1 0 0,0 0 0,-1 0 0,1 0 0,0-1 1,-1 1-1,1 0 0,0-1 0,-1 1 0,1-1 0,-1 0 0,3-1 0,-2 1 102,1-1 1,-1 0 0,0 0 0,0 1-1,0-2 1,-1 1 0,1 0-1,0 0 1,-1-1 0,1 1-1,0-3 1,0 0 180,0 0 0,0 0 1,0 0-1,-1 0 0,0 0 0,0 0 1,-1 0-1,1 0 0,-1-1 0,0 1 0,0 0 1,-2-7-1,1 7-100,-1 0 0,0 1 0,0-1 0,0 1 0,0 0 0,-1 0 0,0 0 0,0 0 0,0 0 0,-4-4 1,-4-2-26,0 1-1,-14-9 1,16 12-228,8 5-59,0 1 0,0-1 1,1 1-1,-1-1 0,0 1 0,1-1 1,-1 0-1,0 1 0,1-1 0,-1 0 1,1 1-1,-1-1 0,1 0 0,-1 0 1,1 1-1,-1-1 0,1 0 0,0 0 0,-1-2 1,1 2-52,1 0 1,-1 0-1,0 1 1,1-1-1,-1 0 1,1 0-1,-1 0 1,1 0-1,-1 0 1,1 0-1,0 1 1,-1-1-1,1 0 1,0 1-1,0-1 1,0 0-1,-1 1 1,2-1-1,16-11-765</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">34 1 6400,'-1'8'11563,"0"13"-7966,-2 36-2923,3-4 1561,-13 106-1,6-130-1798,5-20-691,0 1-1,0-1 0,-1 17 1,3-27-763,1-1 1,-1 0-1,1 1 1,-1-1 0,1 1-1,1-1 1,-2 1 0,2-3-1,3-5-764,1-7 652</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1">314 62 7808,'2'3'8680,"-8"3"-7051,2-1-1403,1 0 1,-1 0-1,2 0 1,-1 0-1,1 1 1,-1-1-1,-1 9 0,-1 0 31,3-1-1,-4 17 1,6-18-185,-1 0 0,1 0 1,0-1-1,1 1 0,-1 0 0,5 12 0,-4-21-52,0 1-1,0 0 1,0-1-1,0 0 0,2 1 1,-1-1-1,0 0 1,-1 0-1,2 0 0,2 3 1,-2-4-6,-1 0 1,0-1-1,-1 1 1,2-1-1,-1 1 1,1-1-1,-2 0 1,2 0-1,0 0 1,-2-1-1,3 1 1,-2 0-1,0-1 1,0 0-1,2 1 1,1-1-1,0-1 12,-2 1 0,1-1-1,-1 0 1,2 0-1,-2 0 1,1-1-1,0 1 1,-2-1 0,3 0-1,-3 0 1,2 0-1,0 0 1,-2 0 0,2-1-1,-2 0 1,0 0-1,2 1 1,-2-1 0,0-1-1,0 1 1,3-4-1,2-5 205,0-1 0,-2 0 0,1 0 0,4-19-1,-8 26-33,1 0-1,-2 0 0,0 0 0,-1 0 0,0 0 1,0 0-1,0-1 0,0 1 0,0 0 1,-1 0-1,-1 0 0,0 0 0,0 0 1,1 0-1,-1 1 0,-2-1 0,2 0 1,0 1-1,-2 0 0,1 0 0,0 0 1,-9-8-1,1-2-1867,29 32-14090,-3-6 14066</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2">742 117 9984,'0'11'4671,"-5"13"-3060,3-20-678,1 2-787,1 0 0,-1 0 0,1 0-1,0 0 1,0 0 0,1 0 0,-1 0-1,1 0 1,1 0 0,-1 0 0,2 0-1,-2-1 1,6 11 0,-4-11-150,-1 0 0,2 0 0,-2 0-1,2 0 1,-1-1 0,1 0 0,0 1 0,0-2 0,0 1 0,1 0 0,-1-1-1,1 1 1,0-1 0,9 4 0,-12-6 53,-1-1 0,1 1 0,-1-1 0,2 0 0,-2 1 0,1-1 0,-1 0 0,1 0 0,0 0 0,-1 0 0,1 0 0,0-1 1,-1 1-1,0 0 0,2-1 0,-2 1 0,1-1 0,-1 0 0,3-1 0,-2 1 102,1-1 1,-1 0 0,0 0 0,0 1-1,0-2 1,-1 1 0,1 0-1,0 0 1,-1-1 0,1 1-1,1-3 1,-2 0 180,1 0 0,0 0 1,0 0-1,-2 0 0,2 0 0,-1 0 1,-1 0-1,1 0 0,-1-1 0,0 1 0,0 0 1,-2-7-1,0 7-100,1 0 0,-1 1 0,0-1 0,0 1 0,0 0 0,-1 0 0,0 0 0,0 0 0,0 0 0,-4-4 1,-4-2-26,1 1-1,-15-9 1,16 12-228,7 5-59,1 1 0,0-1 1,1 1-1,-1-1 0,0 1 0,1-1 1,-1 0-1,0 1 0,1-1 0,0 0 1,0 1-1,-2-1 0,2 0 0,-1 0 1,1 1-1,-1-1 0,1 0 0,0 0 0,-1-2 1,1 2-52,1 0 1,-1 0-1,0 1 1,1-1-1,-1 0 1,1 0-1,-1 0 1,2 0-1,-2 0 1,0 0-1,1 1 1,-1-1-1,1 0 1,0 1-1,0-1 1,0 0-1,-1 1 1,3-1-1,14-11-765</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -3590,7 +3586,7 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2023-12-12T19:21:10.272"/>
+      <inkml:timestamp xml:id="ts0" timeString="2024-01-09T19:28:26.496"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.05" units="cm"/>
@@ -3598,9 +3594,9 @@
       <inkml:brushProperty name="color" value="#FF0000"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">57 0 10368,'-2'16'7349,"-1"0"-4335,-2 19-935,3-10-1558,0 1 0,-2-1 0,-1 0 0,-1 0 1,-2-1-1,-12 31 0,29-72-11305,1 0 9766</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1">304 91 8704,'-11'39'4601,"6"-25"-3923,1 1 0,0-1 1,1 1-1,1-1 0,0 1 1,0 29-1,3-41-655,-1-1 0,0 1-1,1-1 1,-1 0 0,1 1 0,0-1 0,-1 0 0,1 0 0,0 1 0,1-1 0,-1 0-1,0 0 1,0 0 0,1 0 0,0-1 0,1 3 0,-1-3 18,-1 0 1,1 0-1,-1 0 1,1-1-1,-1 1 1,1-1-1,0 1 1,-1-1-1,1 1 1,0-1 0,0 0-1,-1 0 1,1 0-1,0 0 1,-1 0-1,1 0 1,0 0-1,0-1 1,-1 1-1,1-1 1,0 1-1,2-2 1,8-3 373,-1 0 1,0-1 0,14-9 0,-20 12-177,-1-1 1,0 1-1,1-1 1,-1 0 0,-1 0-1,1 0 1,0 0-1,-1-1 1,0 1 0,3-6-1,-6 7-113,1 1-1,0 0 1,-1 0 0,1 0-1,-1 0 1,0 0-1,0-1 1,0 1 0,0 0-1,0 0 1,0 0-1,-1-1 1,1 1 0,-1 0-1,1 0 1,-1 0 0,0 0-1,0 0 1,0 0-1,0 0 1,0 0 0,0 0-1,-1 0 1,1 1-1,0-1 1,-1 0 0,0 1-1,1 0 1,-1-1-1,-3-1 1,0-1-183,0 1 0,1 1 0,-1-1 0,0 1 0,0 0 0,-1 0 0,1 0 1,0 1-1,-1-1 0,1 1 0,-9 0 0,14 1-142,-1 0 0,1 0-1,0 0 1,-1 0 0,1 0 0,0 0 0,0 0 0,-1 0-1,1 0 1,0 0 0,-1 0 0,1 0 0,0 0 0,-1 0-1,1 1 1,0-1 0,-1 0 0,1 0 0,0 0 0,0 0-1,-1 1 1,1-1 0,0 0 0,0 0 0,0 1 0,-1-1-1,1 0 55,0 1 0,1-1 0,-1 0 0,0 0-1,0 0 1,1 1 0,-1-1 0,0 0-1,0 0 1,0 0 0,1 0 0,-1 0-1,0 0 1,1 0 0,-1 0 0,0 0-1,0 0 1,1 1 0,-1-1 0,0 0-1,0 0 1,1-1 0,-1 1 0,0 0-1,1 0 1,-1 0 0,0 0 0,0 0-1,1 0 1,-1 0 0,0 0 0,1-1-1,11-3-909</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2">684 80 8576,'-6'80'6693,"6"-73"-6419,0 1-1,1-1 1,-1 0 0,1 0 0,0-1-1,1 1 1,0 0 0,0 0 0,0-1 0,1 1-1,0-1 1,0 0 0,1 1 0,7 8-1,-10-14-173,1 1-1,0-1 1,-1 0-1,1 1 1,0-1-1,0 0 1,0 0-1,0 0 1,0-1-1,0 1 1,0 0-1,0-1 1,0 1-1,1-1 1,-1 0-1,0 0 1,0 0-1,0 0 1,0 0-1,1 0 1,-1 0-1,0-1 1,0 1-1,4-2 1,-3 0 95,1 1 1,-1 0-1,0-1 0,1 1 1,-1-1-1,0 0 1,0 0-1,0-1 0,0 1 1,-1 0-1,1-1 1,0 0-1,-1 0 0,3-3 1,-4 4-54,0 0 1,-1 0-1,1 0 1,-1-1-1,1 1 1,-1 0-1,0 0 1,0 0-1,0 0 1,0-1-1,0 1 1,0 0-1,0 0 1,-1 0-1,1 0 1,-1 0-1,0 0 1,1 0-1,-3-4 1,-2-4 129,-1 0 0,-11-14 1,10 15-292,-14-17-566,2 3-2279,4-1-5703,14 11 5325</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">57 0 10368,'-1'16'7349,"-3"0"-4335,-1 19-935,3-10-1558,0 1 0,-1-1 0,-3 0 0,0 0 1,-2-1-1,-12 31 0,29-72-11305,1 0 9766</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1">304 91 8704,'-11'39'4601,"6"-25"-3923,1 1 0,0-1 1,1 1-1,1-1 0,0 1 1,0 29-1,3-41-655,-1-1 0,0 1-1,1-1 1,-1 0 0,1 1 0,0-1 0,-1 0 0,0 0 0,2 1 0,0-1 0,-1 0-1,0 0 1,0 0 0,1 0 0,0-1 0,1 3 0,0-3 18,-3 0 1,2 0-1,-1 0 1,1-1-1,-1 1 1,1-1-1,0 1 1,-1-1-1,1 1 1,1-1 0,-2 0-1,0 0 1,1 0-1,0 0 1,-1 0-1,1 0 1,0 0-1,0-1 1,-1 1-1,1-1 1,0 1-1,2-2 1,8-3 373,-1 0 1,0-1 0,14-9 0,-20 12-177,-1-1 1,-1 1-1,3-1 1,-2 0 0,-1 0-1,1 0 1,0 0-1,-1-1 1,0 1 0,3-6-1,-6 7-113,1 1-1,0 0 1,-1 0 0,1 0-1,-1 0 1,0 0-1,0-1 1,0 1 0,0 0-1,0 0 1,0 0-1,-1-1 1,1 1 0,-1 0-1,1 0 1,-1 0 0,1 0-1,-2 0 1,1 0-1,0 0 1,0 0 0,0 0-1,-1 0 1,1 1-1,0-1 1,-1 0 0,0 1-1,1 0 1,0-1-1,-5-1 1,1-1-183,-1 1 0,3 1 0,-2-1 0,0 1 0,0 0 0,-1 0 0,1 0 1,0 1-1,-1-1 0,1 1 0,-9 0 0,14 1-142,-1 0 0,1 0-1,0 0 1,-1 0 0,1 0 0,0 0 0,0 0 0,-2 0-1,2 0 1,0 0 0,0 0 0,0 0 0,0 0 0,-1 0-1,1 1 1,0-1 0,-1 0 0,1 0 0,0 0 0,0 0-1,-1 1 1,1-1 0,0 0 0,0 0 0,0 1 0,-1-1-1,1 0 55,0 1 0,1-1 0,-1 0 0,0 0-1,0 0 1,1 1 0,-1-1 0,0 0-1,0 0 1,0 0 0,1 0 0,-1 0-1,0 0 1,1 0 0,-1 0 0,0 0-1,0 0 1,0 1 0,0-1 0,0 0-1,0 0 1,2-1 0,-2 1 0,0 0-1,1 0 1,-1 0 0,0 0 0,0 0-1,1 0 1,-1 0 0,0 0 0,1-1-1,11-3-909</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2">684 80 8576,'-6'80'6693,"6"-73"-6419,0 1-1,1-1 1,-1 0 0,1 0 0,0-1-1,1 1 1,1 0 0,-2 0 0,1-1 0,1 1-1,0-1 1,0 0 0,1 1 0,7 8-1,-10-14-173,1 1-1,0-1 1,-1 0-1,1 1 1,0-1-1,0 0 1,0 0-1,0 0 1,0-1-1,0 1 1,0 0-1,0-1 1,0 1-1,1-1 1,-1 0-1,0 0 1,1 0-1,-2 0 1,1 0-1,1 0 1,-1 0-1,0-1 1,0 1-1,4-2 1,-3 0 95,1 1 1,-1 0-1,-1-1 0,3 1 1,-2-1-1,0 0 1,0 0-1,0-1 0,0 1 1,-1 0-1,1-1 1,0 0-1,-1 0 0,3-3 1,-4 4-54,0 0 1,-1 0-1,1 0 1,-1-1-1,1 1 1,-1 0-1,0 0 1,0 0-1,0 0 1,0-1-1,0 1 1,0 0-1,0 0 1,-1 0-1,1 0 1,-1 0-1,0 0 1,1 0-1,-3-4 1,-2-4 129,-1 0 0,-11-14 1,10 15-292,-14-17-566,2 3-2279,4-1-5703,14 11 5325</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -3620,7 +3616,7 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2023-12-12T19:21:10.275"/>
+      <inkml:timestamp xml:id="ts0" timeString="2024-01-09T19:28:26.499"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.05" units="cm"/>
@@ -3647,7 +3643,7 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2023-12-12T19:21:10.276"/>
+      <inkml:timestamp xml:id="ts0" timeString="2024-01-09T19:28:26.500"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.05" units="cm"/>
@@ -3655,12 +3651,12 @@
       <inkml:brushProperty name="color" value="#FF0000"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">112 1 8064,'0'3'1157,"-1"0"0,1 0 1,-1 0-1,0 0 0,-2 5 0,-3 14 156,-1 25-444,-3-1 0,-1 0 0,-26 68 1,22-84-632,10-23-75,1 1 0,1 0 0,-4 10 0,33-132 1395,13-46-1740,-36 150 177,1 0 0,-1 0-1,2 0 1,10-17 0,-14 25 22,0 0 0,0 0 1,1 0-1,-1 0 1,1 1-1,-1-1 1,1 1-1,0-1 0,-1 1 1,1 0-1,0 0 1,0-1-1,0 1 1,0 0-1,0 1 0,0-1 1,1 0-1,-1 1 1,0-1-1,0 1 1,0 0-1,1-1 0,-1 1 1,0 0-1,0 0 1,1 1-1,-1-1 0,0 0 1,3 2-1,6 2 23,-1 0-1,0 1 0,0 1 1,-1 0-1,0 0 1,0 1-1,0 0 0,-1 0 1,0 1-1,0 0 1,-1 1-1,9 12 0,-15-20-10,0 1 0,0-1 0,0 1 0,0-1 0,0 1 0,0-1 0,0 1 0,-1 0 1,1-1-1,-1 1 0,1 0 0,-1 0 0,0-1 0,0 1 0,0 0 0,0 0 0,0 1 0,0-1 28,-1-1 0,0 1 0,1-1 0,-1 1 0,0-1 0,0 0 0,0 1 0,0-1 0,0 0 0,0 0 1,0 0-1,0 0 0,0 0 0,0 0 0,-1 0 0,1 0 0,0 0 0,-1 0 0,-1 0 0,-3 2 101,0-1 1,0 0-1,0-1 0,-1 1 0,1-1 1,-11 1-1,-41-3 306,24 0-244,22 6-354</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1">557 145 7040,'-1'6'1051,"1"1"0,-1-1 1,0 0-1,-1 0 0,-2 7 1,-3 12 58,1 0 789,-13 35-1,44-116 836,-3 14-2693,41-58 0,-61 97-34,5-7 141,-1 1-1,2 1 1,11-12-1,-17 18-86,0 1 0,0-1 0,0 1 0,0 0 0,0-1 0,1 1 0,-1 0 0,0 0 0,5-1 0,-6 2-25,0 0 0,0 0 0,0 0 0,0 0-1,1 0 1,-1 0 0,0 0 0,0 1 0,0-1-1,0 0 1,1 1 0,-1-1 0,0 0 0,0 1-1,0 0 1,0-1 0,0 1 0,0 0 0,0-1-1,0 1 1,0 1 0,2 1-3,-1 0 1,0 0-1,0 0 0,0 0 0,0 1 1,0-1-1,-1 1 0,2 6 0,7 35 227,-6-25-216,-2-7-9,-1-7 42,0 1-1,1-1 0,0 0 0,0 0 0,0 0 1,4 7-1,-6-12-64,1 0 0,0 0-1,0 0 1,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0-1-1,0 1 1,0 0 0,0-1 0,0 1 0,1-1 0,-1 1 0,0-1-1,0 1 1,1-1 0,-1 0 0,0 0 0,0 0 0,1 0 0,-1 0-1,0 0 1,1 0 0,-1 0 0,0 0 0,1 0 0,-1-1 0,0 1-1,0-1 1,1 1 0,-1-1 0,0 1 0,0-1 0,2-1 0,6-3-8,1-2 1,-1 1-1,-1-1 1,1 0-1,-1-1 1,14-16-1,-14 14 1,0 1-1,1 0 1,0 1-1,1 0 1,13-9-1,-22 17-6,0-1 0,0 1 0,0-1 0,-1 1-1,2-1 1,-1 1 0,0 0 0,0 0 0,0-1 0,0 1-1,0 0 1,0 0 0,0 0 0,0 0 0,0 0 0,0 0-1,0 0 1,0 1 0,0-1 0,0 0 0,2 1 0,-1 0 10,-1 0 1,1 0-1,-1 1 1,1-1 0,-1 0-1,0 1 1,1-1 0,-1 0-1,0 1 1,0 0-1,1 2 1,2 3 60,-1 1 0,0-1 0,-1 1-1,3 13 1,5 55 216,-6-31-3311,2-22-1870,-3-12 3877</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2">1288 98 8576,'-4'12'4753,"4"-11"-4556,0-1 0,0 0 0,0 0 0,0 1-1,0-1 1,0 0 0,0 1 0,2 1 1773,-2-2-1774,1 0 1,-1 0 0,0 0 0,0 1 0,1-1 0,-1 0 0,0 0 0,3 1 521,0-1 1,0 0-1,0 1 1,0-1-1,0-1 1,4 1-1,-4-1-991,15-1 1491,29-8 0,-32 7-1771,0 0 0,0 0 0,20 0 0,-35 3 409,2 0-599,-1 0 0,0 0 1,0 0-1,0 0 0,1 0 0,-1-1 0,0 1 1,0 0-1,0-1 0,3 0 0,-4-1-323</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3">1394 186 11776,'-6'18'6856,"4"17"-3470,0-7-2514,-42 197 536,43-221-1947,-2 10-1140</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4">1288 120 8064,'1'1'888,"0"0"-1,0 1 1,0-1 0,0 0 0,0 0-1,0 0 1,0 0 0,0-1 0,0 1-1,1 0 1,-1 0 0,2 0 0,4 0-263,1 0 1,-1 0-1,1-1 1,-1 0-1,1-1 1,13-2-1,-3-1-515,27-9-1,-40 11-114,14-5-2184,-2-4-4171,-14 8 5272</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5">1416 112 10240,'2'10'3616,"0"1"1,0 21 0,-2-15-3210,0 0 1,-2 0-1,0 0 1,-1-1 0,-9 28-1,6-34-1464</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">112 1 8064,'0'3'1157,"-1"0"0,1 0 1,-1 0-1,0 0 0,-2 5 0,-3 14 156,0 25-444,-5-1 0,0 0 0,-26 68 1,22-84-632,10-23-75,1 1 0,2 0 0,-6 10 0,34-132 1395,13-46-1740,-36 150 177,1 0 0,-1 0-1,2 0 1,10-17 0,-14 25 22,0 0 0,0 0 1,1 0-1,-1 0 1,1 1-1,-1-1 1,2 1-1,-2-1 0,0 1 1,1 0-1,0 0 1,0-1-1,0 1 1,0 0-1,0 1 0,0-1 1,1 0-1,-1 1 1,0-1-1,0 1 1,1 0-1,-1-1 0,0 1 1,0 0-1,0 0 1,1 1-1,0-1 0,-2 0 1,4 2-1,6 2 23,0 0-1,-2 1 0,1 1 1,0 0-1,-2 0 1,1 1-1,1 0 0,-3 0 1,2 1-1,-2 0 1,0 1-1,9 12 0,-15-20-10,0 1 0,0-1 0,0 1 0,0-1 0,0 1 0,0-1 0,0 1 0,-1 0 1,1-1-1,-1 1 0,2 0 0,-2 0 0,0-1 0,0 1 0,0 0 0,0 0 0,0 1 0,0-1 28,-2-1 0,1 1 0,1-1 0,-1 1 0,0-1 0,0 0 0,0 1 0,0-1 0,0 0 0,0 0 1,0 0-1,0 0 0,0 0 0,1 0 0,-2 0 0,0 0 0,1 0 0,-1 0 0,-1 0 0,-2 2 101,-2-1 1,1 0-1,0-1 0,-1 1 0,1-1 1,-11 1-1,-41-3 306,24 0-244,22 6-354</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1">558 145 7040,'-2'6'1051,"2"1"0,-1-1 1,0 0-1,-1 0 0,-2 7 1,-3 12 58,1 0 789,-12 35-1,42-116 836,-2 14-2693,41-58 0,-60 97-34,3-7 141,1 1-1,0 1 1,12-12-1,-16 18-86,-1 1 0,0-1 0,-1 1 0,1 0 0,0-1 0,1 1 0,0 0 0,-1 0 0,4-1 0,-5 2-25,0 0 0,0 0 0,1 0 0,-1 0-1,1 0 1,-1 0 0,0 0 0,-1 1 0,1-1-1,0 0 1,1 1 0,-1-1 0,0 0 0,0 1-1,1 0 1,-1-1 0,0 1 0,0 0 0,0-1-1,0 1 1,0 1 0,1 1-3,0 0 1,0 0-1,1 0 0,-1 0 0,0 1 1,-1-1-1,0 1 0,2 6 0,7 35 227,-6-25-216,-2-7-9,0-7 42,-1 1-1,1-1 0,0 0 0,-1 0 0,1 0 1,5 7-1,-7-12-64,1 0 0,0 0-1,0 0 1,0 0 0,0 0 0,0 0 0,-1 0 0,1 0 0,0-1-1,0 1 1,0 0 0,0-1 0,1 1 0,0-1 0,-1 1 0,0-1-1,0 1 1,1-1 0,-2 0 0,1 0 0,0 0 0,1 0 0,-1 0-1,1 0 1,0 0 0,-1 0 0,0 0 0,1 0 0,-1-1 0,-1 1-1,1-1 1,1 1 0,-1-1 0,0 1 0,1-1 0,1-1 0,5-3-8,2-2 1,0 1-1,-3-1 1,3 0-1,-3-1 1,16-16-1,-15 14 1,-1 1-1,3 0 1,-2 1-1,2 0 1,14-9-1,-23 17-6,0-1 0,0 1 0,0-1 0,-1 1-1,1-1 1,0 1 0,0 0 0,0 0 0,1-1 0,-1 1-1,0 0 1,0 0 0,0 0 0,0 0 0,0 0 0,0 0-1,0 0 1,-1 1 0,1-1 0,0 0 0,3 1 0,-2 0 10,-1 0 1,1 0-1,-1 1 1,1-1 0,-1 0-1,-1 1 1,2-1 0,-1 0-1,1 1 1,-1 0-1,1 2 1,2 3 60,-2 1 0,1-1 0,0 1-1,2 13 1,5 55 216,-6-31-3311,1-22-1870,-1-12 3877</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2">1288 98 8576,'-3'12'4753,"3"-11"-4556,0-1 0,0 0 0,0 0 0,0 1-1,0-1 1,0 0 0,0 1 0,2 1 1773,-2-2-1774,0 0 1,0 0 0,0 0 0,0 1 0,1-1 0,-1 0 0,0 0 0,4 1 521,-1-1 1,0 0-1,0 1 1,0-1-1,0-1 1,4 1-1,-5-1-991,17-1 1491,28-8 0,-32 7-1771,0 0 0,0 0 0,20 0 0,-35 3 409,2 0-599,-1 0 0,0 0 1,0 0-1,0 0 0,1 0 0,-1-1 0,-1 1 1,2 0-1,-1-1 0,3 0 0,-4-1-323</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3">1395 186 11776,'-6'18'6856,"3"17"-3470,2-7-2514,-43 197 536,43-221-1947,-2 10-1140</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4">1288 120 8064,'2'1'888,"-1"0"-1,0 1 1,0-1 0,0 0 0,0 0-1,0 0 1,0 0 0,0-1 0,0 1-1,1 0 1,-2 0 0,4 0 0,3 0-263,1 0 1,-1 0-1,1-1 1,-1 0-1,1-1 1,13-2-1,-3-1-515,27-9-1,-40 11-114,13-5-2184,0-4-4171,-15 8 5272</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5">1417 112 10240,'2'10'3616,"0"1"1,0 21 0,-2-15-3210,0 0 1,-2 0-1,0 0 1,-2-1 0,-7 28-1,5-34-1464</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -3680,7 +3676,7 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2023-12-12T19:21:10.282"/>
+      <inkml:timestamp xml:id="ts0" timeString="2024-01-09T19:28:26.506"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.05" units="cm"/>
@@ -3688,15 +3684,15 @@
       <inkml:brushProperty name="color" value="#5B2D90"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">17 1135 10112,'3'-3'3872,"3"-2"-3040,10-1 576,-7 3-1,7 0-479,3 1-64,2-1-448,1 0-160,0 1-160,-4-2-96,1 1 96,-1 1-2752,-2-1-1215,-4 3 1951,-2 0 928</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1">4 941 11392,'-3'0'4224,"6"0"-3297,3 0 929,1 0 288,5 0-1120,7 0-288,3 0-480,3 0-128,2-3-64,8-2-3360,2-3-1503,0-6 2399,-6-3 1184</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2">527 90 3584,'-1'-1'216,"0"0"1,0-1-1,0 1 0,0 0 0,0-1 1,0 1-1,1 0 0,-1-1 1,1 1-1,-1-1 0,1 1 1,-1-4-1,-4-21 7984,3 18-1558,0 31-5273,-45 310-158,40-307-765,-1 1 0,-16 39 1,20-59-127,2-9 65,2-12-114,9-28-258,2 0 0,20-51 1,44-76-22,-72 163 6,5-11-54,1 0 0,1 0 0,0 1-1,15-18 1,-22 31 45,0 0 0,0 0 1,0 0-1,0 0 0,1 0 0,-1 1 0,1-1 0,-1 1 0,1 0 0,0 0 0,0 1 1,0-1-1,0 1 0,0-1 0,0 1 0,0 1 0,0-1 0,1 1 0,-1-1 0,0 1 0,0 0 1,1 1-1,-1-1 0,8 3 0,-10-3 26,-1 0 0,1 0 1,-1 1-1,1-1 0,-1 1 0,1 0 1,-1-1-1,0 1 0,1 0 0,-1 0 0,0 0 1,0 0-1,1 0 0,-1 0 0,0 0 1,0 0-1,0 0 0,0 0 0,0 1 1,-1-1-1,1 0 0,0 1 0,0-1 1,-1 1-1,1-1 0,-1 1 0,0-1 1,1 1-1,-1-1 0,0 1 0,0-1 0,0 1 1,0-1-1,0 1 0,0 0 0,0-1 1,-1 1-1,1-1 0,0 1 0,-1-1 1,1 1-1,-1-1 0,0 0 0,1 1 1,-1-1-1,0 0 0,0 1 0,-1 0 1,-2 3 183,-1 0 1,1-1 0,0 0-1,-1 0 1,0 0 0,0-1-1,-8 5 1,-41 16 385,32-16-1312,21-7 587,1-1-3,0 0 1,-1 0 0,1 0-1,0 0 1,0 0 0,-1 0-1,1 0 1,0 0 0,0 0-1,-1 0 1,1 1-1,0-1 1,0 0 0,0 0-1,-1 0 1,1 0 0,0 1-1,0-1 1,0 0 0,0 0-1,-1 0 1,1 1-1,0-1 1,0 0 0,0 0-1,0 0 1,0 1 0,0-1-1,0 0 1,0 0 0,0 1-1,0-1 1,0 0-1,0 0 1,0 1 0,0-1-1,0 0 1,0 0 0,0 1-1,0-1 1,0 0 0,0 0-1,0 1 1,0-1-1,0 0 1,1 1 0,4 6-744</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3">999 7 9472,'0'-7'6630,"0"20"-2399,0 2-3621,-5 307 1993,5-298-2435,2 75 933,-2-99-1064,0 1-1,0-1 0,0 1 1,0-1-1,0 1 0,0 0 0,1-1 1,-1 1-1,0-1 0,0 1 1,0-1-1,0 1 0,1-1 1,-1 1-1,0-1 0,1 1 1,-1-1-1,1 1 0,-1-1-11,0 0-1,1 0 1,-1 0 0,0 0-1,1 0 1,-1 0-1,0 0 1,0-1 0,1 1-1,-1 0 1,0 0-1,0 0 1,1 0-1,-1-1 1,0 1 0,0 0-1,0 0 1,1-1-1,-1 1 1,0 0 0,0 0-1,0-1 1,0 1-1,0-1 1,12-25 810,-11 21-745,16-41 249,39-96 1042,-41 109-2441,2 0-1,24-36 0,-32 57-1787,-5 12 944</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4">1431 400 10112,'-2'38'7843,"1"-21"-6786,1 24-1,1-36-1052,-1 1-1,1-1 1,0 1-1,1-1 1,-1 1 0,1-1-1,0 0 1,4 7 0,-5-11 25,-1 0 0,1 0 0,0 0 0,-1 0 0,1 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0-1 1,0 1-1,0 0 0,1-1 0,-1 1 0,0 0 0,0-1 0,0 0 0,1 1 0,-1-1 0,0 0 0,1 1 0,-1-1 0,0 0 0,0 0 0,1 0 1,-1 0-1,0-1 0,1 1 0,-1 0 0,0 0 0,1-1 0,-1 1 0,0-1 0,2 0 0,-1 0 149,1-1 0,-1 1 0,0 0-1,0-1 1,0 0 0,0 0 0,0 1 0,0-1-1,0-1 1,0 1 0,-1 0 0,1 0 0,-1 0-1,0-1 1,0 1 0,2-5 0,-2 3 118,0 0 1,-1 0-1,1 0 0,-1 0 1,0 0-1,0 0 0,-1 0 1,1 0-1,-1 0 0,0 0 1,0 0-1,-2-6 0,-3-3 90,0 0 1,-11-16-1,-2-4-2624,18 31 1175,-2-4-1293</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5">651 847 6400,'-1'0'191,"1"0"0,0 0 0,-1 0 0,1-1 1,0 1-1,-1 0 0,1 0 0,0 0 0,-1-1 0,1 1 1,0 0-1,0-1 0,-1 1 0,1 0 0,0 0 0,0-1 1,0 1-1,0-1 0,-1 1 0,1 0 0,0-1 0,0 1 1,0 0-1,0-1 0,0 1 0,0 0 0,0-1 0,0 1 1,0-1-1,0 1 0,0 0 0,0-1 0,0 1 0,0 0 1,0-1-1,0 1 0,1 0 0,-1-1 0,0 1 0,0 0 1,0-1-1,1 1 0,-1 0 0,0-1 0,0 1 0,1 0 1,-1 0-1,0-1 0,0 1 0,1 0 0,-1 0 0,0 0 1,1-1-1,-1 1 0,0 0 0,1 0 0,0 0 0,2-1 28,0 0 0,0 0-1,0 1 1,1 0-1,-1-1 1,0 1-1,0 0 1,0 1-1,1-1 1,-1 0-1,0 1 1,4 1-1,37 15 1059,-28-10-860,0 0 1,0 2 0,-1 0 0,23 19-1,-34-26-366,-1 1-1,1 1 0,-1-1 0,0 0 1,0 1-1,-1-1 0,1 1 1,-1 0-1,1 0 0,-1 0 1,-1 0-1,1 1 0,0-1 1,-1 0-1,0 1 0,0-1 0,0 1 1,-1-1-1,1 1 0,-1-1 1,0 1-1,-1-1 0,0 8 1,-2-4-9,1-1 0,-1 1 0,-1-1 0,1 1 0,-1-1 0,0 0 0,-1 0 0,0-1 0,0 1 0,0-1 0,-1 0 0,0-1 0,0 0 0,0 1 0,-10 4 0,-6 4 25,1-2-1,-2-1 1,-40 15-1,62-25-62,-1-1 8,0 1 0,-1 0 1,1 0-1,0 0 0,1 0 1,-1 0-1,0 0 0,0 0 0,0 1 1,-2 2-1,4-4-20,0 1-1,1-1 1,-1 1 0,0-1-1,0 0 1,1 1 0,-1-1 0,1 1-1,-1-1 1,0 0 0,1 1-1,-1-1 1,1 0 0,-1 1 0,1-1-1,-1 0 1,1 0 0,-1 1-1,1-1 1,0 0 0,12 6-37,2-1-31,0-1-1,1 0 0,-1-1 1,1-1-1,24 1 0,10-6-5921,-48 3 5502,0 0 1,-1 0 0,1 0-1,0-1 1,-1 1 0,1-1-1,-1 1 1,1-1 0,-1 0-1,1 0 1,-1 1-1,1-1 1,-1 0 0,1 0-1,-1-1 1,2-1 0,3-8-1137</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6">1127 859 9600,'-3'13'5159,"0"24"1,3-19-4503,1 0 0,0 0 0,2-1 1,7 32-1,-9-45-600,0-1 1,0-1-1,0 1 1,1 0-1,-1 0 1,1 0-1,-1-1 1,1 1-1,0-1 1,0 1-1,0-1 1,0 0-1,1 1 1,-1-1-1,1 0 1,-1-1-1,5 3 1,-3-2 92,0-1 1,0 1-1,0-1 1,0 0-1,0 0 1,0-1 0,0 1-1,0-1 1,0 0-1,0 0 1,1-1-1,3 0 1,-1 0-579,1-1 0,-1 0-1,0 0 1,1-1 0,-1 0 0,9-5 0,9-10-4766,-5-2-3442,-5-2 3906</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="7">1404 925 13440,'-1'90'9447,"-4"0"-6915,1-45-3832,-3-2 0,-11 47 0,17-85 422,0-2-97,0 0 0,1-1 0,-1 1 0,0 0 0,0 0 0,0 0 0,-1-1 0,-1 4 0,3-8-267</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="8">1736 1115 10496,'-2'-1'615,"-1"-1"1,0 0 0,1 0 0,-1 0 0,1 0-1,0 0 1,0 0 0,0 0 0,0-1-1,0 1 1,0-1 0,-2-4 0,-15-35 2877,17 36-3324,0 0 0,1 0 0,0 0 0,0 0 0,0 0 0,1 0 1,0 0-1,0 0 0,0-1 0,1 1 0,0 0 0,0 0 0,0 0 0,5-10 0,2-2 41,0 0 1,2 0-1,13-18 0,-18 29-174,0-2-14,1 1-1,0 0 0,0 0 1,0 1-1,1 0 0,1 0 1,-1 0-1,16-9 0,-22 15-16,0 1 0,-1-1 0,1 1 0,-1 0 0,1-1 0,0 1-1,-1 0 1,1-1 0,0 1 0,-1 0 0,1 0 0,0 0 0,0 0 0,-1 0 0,1 0 0,0 0-1,-1 0 1,1 0 0,0 0 0,-1 0 0,1 0 0,0 1 0,0-1 0,-1 0 0,1 0-1,-1 1 1,2-1 0,-2 1 4,1 0 0,0 0 0,-1 0 0,1 0 0,-1 0 0,1 0 0,-1 0 0,0 0 0,1 0 0,-1 0 0,0 1 0,0-1 0,0 0 0,1 0 0,-2 1 0,1 6 30,0 0 0,-1-1 0,-4 14 1,-5 12 38,-18 39 0,15-41-100,-13 45 0,17-41-98,2 0 0,-6 65 1,13-88 60,-1 0 0,2 1 0,0-1 0,0 0 0,1 0 0,1 0 0,0 0 0,0 0 0,1-1 0,1 1 0,11 20 0,-14-29 22,0 0 0,0 0 0,0 0 0,1 0 0,0 0 0,-1-1 1,1 1-1,0-1 0,0 0 0,0 0 0,1 0 0,-1 0 0,1 0 0,-1 0 0,4 0 0,-4-1 33,-1-1 0,1 0 0,0 1 0,-1-1 0,1 0 0,0 0 0,-1-1 0,1 1 0,0 0 0,-1-1 0,1 0 0,-1 0 0,1 0 0,-1 0 0,1 0 0,-1 0 0,0 0 0,1-1 0,-1 1 0,0-1 0,0 0 0,2-2 0,1-1 57,0-1 1,0 0-1,0 0 0,-1-1 0,0 1 0,0-1 0,-1 0 0,0 0 0,0 0 1,-1-1-1,0 1 0,0 0 0,0-1 0,-1 0 0,0 1 0,-1-1 0,0-8 1,-1 0 264,0 0 0,-1 0 1,-1 0-1,0 0 1,-2 0-1,1 1 1,-9-18-1,8 23-318,0 0 0,-1 1 0,0-1 0,-1 1 0,1 0 0,-14-12 0,20 21-121,0 0 0,0 0 1,-1 0-1,1 0 0,0 0 0,0 0 0,-1-1 0,1 1 1,0 0-1,0 0 0,-1 0 0,1 0 0,0 0 0,-1 0 1,1 0-1,0 0 0,0 0 0,-1 0 0,1 0 0,0 0 1,0 1-1,-1-1 0,1 0 0,0 0 0,0 0 0,-1 0 1,1 0-1,0 0 0,0 1 0,-1-1 0,1 0 0,0 0 1,0 0-1,0 1 0,0-1 0,-1 0 0,1 0 0,0 1 1,0-1-1,0 0 0,0 0 0,0 1 0,0-1 0,0 0 1,-1 0-1,1 1 0,0-1 0,0 0 0,0 1 0,0-1 1,0 1-1,0-1 122,-3 9-855</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">17 1134 10112,'3'-3'3872,"3"-2"-3040,10 0 576,-7 2-1,7 0-479,3 0-64,2 0-448,1 0-160,0 1-160,-4-2-96,1 1 96,-1 1-2752,-2-1-1215,-4 3 1951,-2 0 928</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1">4 940 11392,'-3'0'4224,"6"0"-3297,3 0 929,1 0 288,5 0-1120,7 0-288,3 0-480,3 0-128,2-3-64,8-2-3360,2-3-1503,0-5 2399,-6-5 1184</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2">528 90 3584,'-2'-1'216,"1"0"1,0-1-1,0 1 0,0 0 0,0-1 1,0 0-1,1 1 0,-1 0 1,1 0-1,-1-1 0,1 1 1,-1-4-1,-4-21 7984,3 18-1558,0 31-5273,-44 310-158,38-307-765,1 1 0,-18 38 1,22-57-127,0-11 65,3-11-114,9-28-258,2 1 0,20-52 1,45-76-22,-74 163 6,6-12-54,1 2 0,1-1 0,1 1-1,13-18 1,-20 31 45,-1 0 0,-1 0 1,1 0-1,0 0 0,2 0 0,-3 1 0,2-1 0,0 1 0,0 0 0,-1 0 0,1 1 1,1-1-1,-2 1 0,1-1 0,1 1 0,-1 1 0,-1-1 0,3 1 0,-2-1 0,-1 1 0,1 0 1,2 1-1,-3-1 0,9 3 0,-10-3 26,-1 0 0,1 0 1,-1 1-1,2-1 0,-2 1 0,1 0 1,-1-1-1,0 1 0,0 0 0,0 0 0,0 0 1,0 0-1,1 0 0,-1 0 0,1 0 1,-1 0-1,0-1 0,0 2 0,0 0 1,-1-1-1,1 0 0,-1 1 0,1-1 1,-1 1-1,1-1 0,-1 1 0,0-1 1,1 1-1,-1-1 0,0 1 0,0-1 0,0 1 1,0-1-1,0 1 0,0 0 0,0-1 1,-1 1-1,1-1 0,0 1 0,-1-1 1,1 1-1,-1-1 0,1 0 0,0 1 1,-1-1-1,0 0 0,0 1 0,-1 0 1,-3 3 183,1 0 1,0-1 0,-1 0-1,0 0 1,1 0 0,-2-1-1,-7 5 1,-41 15 385,33-14-1312,20-8 587,1-1-3,0 0 1,-1 0 0,1 0-1,0 0 1,0 0 0,-2 0-1,2 0 1,0 0 0,0 0-1,-1 0 1,1 1-1,0-1 1,0 0 0,0 0-1,-1 0 1,1 0 0,0 1-1,0-1 1,0 0 0,0 0-1,-1 0 1,1 1-1,0-1 1,0 0 0,0 0-1,0 0 1,0 1 0,0-1-1,0 0 1,0 0 0,0 1-1,0-1 1,0 0-1,0 0 1,0 1 0,0-1-1,0 0 1,0 0 0,0 1-1,0-1 1,0 0 0,0 0-1,0 1 1,0-1-1,0 0 1,1 1 0,5 6-744</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3">999 7 9472,'0'-7'6630,"0"20"-2399,0 2-3621,-4 306 1993,4-296-2435,2 74 933,-2-99-1064,0 1-1,0-1 0,0 1 1,0-1-1,0 1 0,0 0 0,1-1 1,-1 1-1,0-1 0,0 1 1,0-1-1,0 1 0,1-1 1,-1 1-1,0-1 0,0 1 1,0-1-1,1 1 0,-1-1-11,0 0-1,1 0 1,-1 0 0,0 0-1,1 0 1,-1 0-1,0 0 1,0-1 0,1 1-1,-1 0 1,0 0-1,0 0 1,1 0-1,-1-1 1,0 1 0,0 0-1,0 0 1,2-1-1,-2 1 1,0 0 0,0 0-1,0-1 1,0 1-1,0-1 1,11-26 810,-10 22-745,17-41 249,38-95 1042,-41 108-2441,1 0-1,25-36 0,-31 57-1787,-6 12 944</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4">1432 399 10112,'-2'39'7843,"0"-23"-6786,2 26-1,2-38-1052,-2 2-1,1-1 1,0 2-1,1-2 1,-1 1 0,1-1-1,0 0 1,4 6 0,-5-10 25,-1 0 0,1 0 0,0 0 0,-1 0 0,1 0 0,0 0 0,0 0 0,0 0 0,0 0 0,-1 0 0,1-1 1,0 1-1,1 0 0,0-1 0,-1 1 0,0 0 0,0-1 0,0 0 0,1 1 0,-1-1 0,0 0 0,0 1 0,0-1 0,1 0 0,-1 0 0,1 0 1,-1 0-1,0-1 0,1 1 0,-1 0 0,0 0 0,0-1 0,0 1 0,0-1 0,3 0 0,-2 0 149,1-1 0,-1 1 0,-1 0-1,2-1 1,-1 0 0,0 0 0,0 1 0,0 0-1,0-2 1,-1 1 0,0 0 0,2 0 0,-2 0-1,0-1 1,0 1 0,2-5 0,-2 3 118,0 0 1,-1-1-1,1 1 0,-1 0 1,0 0-1,0 0 0,-1 1 1,1-1-1,-1 0 0,0 0 1,0 0-1,-2-6 0,-4-4 90,2 2 1,-12-17-1,-2-4-2624,18 31 1175,-2-4-1293</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5">652 847 6400,'-1'0'191,"1"0"0,0 0 0,-2 0 0,2-1 1,0 1-1,-1 0 0,1 0 0,0 0 0,-1-1 0,1 1 1,0 0-1,0-1 0,-1 1 0,1 0 0,0 0 0,0-1 1,0 1-1,0-2 0,-1 2 0,1 0 0,0-1 0,0 1 1,0 0-1,0-1 0,0 1 0,0 0 0,0-1 0,0 1 1,0-1-1,0 1 0,0 0 0,0-1 0,0 1 0,0 0 1,0-1-1,0 1 0,1 0 0,-1-1 0,0 1 0,0 0 1,0-1-1,1 1 0,-1 0 0,0-1 0,0 1 0,1 0 1,-1 0-1,0-1 0,0 1 0,1 0 0,-1 0 0,0 0 1,2-1-1,-2 1 0,0 0 0,1 0 0,0 0 0,1-1 28,1 0 0,0 0-1,1 1 1,0 0-1,-2-1 1,1 1-1,1 0 1,-1 1-1,0-1 1,0 0-1,0 1 1,4 1-1,37 16 1059,-28-11-860,1 0 1,-1 1 0,-1 1 0,23 20-1,-34-27-366,-2 1-1,2 0 0,0 0 0,-1 0 1,-1 1-1,0-1 0,1 1 1,0 0-1,0 0 0,-1 0 1,-2 0-1,2 2 0,0-2 1,-1 0-1,0 1 0,1-2 0,-1 2 1,-1-1-1,1 1 0,-1-1 1,0 1-1,-1-1 0,0 9 1,-3-5-9,2-2 0,0 2 0,-2-1 0,0 1 0,0-1 0,1 1 0,-3-1 0,1-2 0,1 2 0,-2-1 0,1 0 0,-2-1 0,1 0 0,1 1 0,-12 5 0,-4 2 25,-1-1-1,0-1 1,-42 15-1,63-25-62,0-1 8,-1 1 0,-2 0 1,2 0-1,0 0 0,1 0 1,-1 0-1,1 0 0,-1 0 0,-1 1 1,-1 2-1,4-4-20,0 1-1,1-1 1,-1 1 0,0-1-1,0 0 1,1 1 0,-1-1 0,1 1-1,-1-1 1,0 0 0,1 1-1,-1-1 1,2 0 0,-2 1 0,1-1-1,-1 0 1,1 0 0,-1 1-1,1-1 1,0 0 0,12 6-37,1-1-31,1-1-1,1 1 0,-1-2 1,1-1-1,24 0 0,10-4-5921,-48 2 5502,0 0 1,-1 0 0,2 0-1,-1-1 1,-1 1 0,1-1-1,-1 1 1,0-1 0,0 0-1,1 0 1,-1 1-1,2-1 1,-2-1 0,1 1-1,-1-1 1,1-1 0,4-8-1137</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6">1127 859 9600,'-3'12'5159,"1"26"1,2-21-4503,1 1 0,-1 1 0,3-3 1,7 33-1,-9-45-600,0-1 1,0-1-1,0 1 1,2 0-1,-2 0 1,1 0-1,-1-1 1,1 1-1,-1-1 1,1 1-1,0 0 1,1-1-1,0 1 1,-1-1-1,0 0 1,0-1-1,6 2 1,-4-1 92,-1-1 1,2 1-1,-1-1 1,-1 0-1,2 0 1,-1-1 0,-1 1-1,1-1 1,1 0-1,-1 0 1,0-1-1,5 0 1,-3 0-579,3-1 0,-2 0-1,0 0 1,1 0 0,-2-1 0,10-5 0,9-11-4766,-4-1-3442,-6-2 3906</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="7">1405 924 13440,'-1'91'9447,"-5"-2"-6915,3-44-3832,-5-2 0,-9 47 0,16-85 422,0-2-97,0 0 0,1-1 0,-1 1 0,0 0 0,0 0 0,0 0 0,-2-1 0,0 4 0,3-8-267</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="8">1737 1115 10496,'-2'-2'615,"-1"0"1,-1 0 0,3 0 0,-2 0 0,1 0-1,0 0 1,0 0 0,-1 0 0,2-1-1,-1 1 1,0-1 0,-2-4 0,-15-35 2877,17 36-3324,0 0 0,1 0 0,0 1 0,0-1 0,0-1 0,1 1 1,0 0-1,0 0 0,0-1 0,1 1 0,0 1 0,0-1 0,0 0 0,4-11 0,4-1 41,-1 1 1,1-2-1,15-16 0,-20 28-174,2-3-14,0 2-1,0 0 0,0 1 1,0 0-1,1 0 0,1 0 1,-1-1-1,16-8 0,-22 15-16,0 1 0,-1-1 0,1 1 0,-1 0 0,1-1 0,0 1-1,-1 0 1,1-1 0,0 1 0,-1 0 0,0 0 0,2 0 0,-1 0 0,-1 0 0,1 0 0,0 0-1,-1 0 1,1 0 0,0 0 0,-1 0 0,1 0 0,0 1 0,0-1 0,-1 0 0,1 0-1,-1 1 1,2-1 0,-2 1 4,1 0 0,-1 0 0,0 0 0,2 0 0,-2 0 0,1 0 0,-1 0 0,0 0 0,1 0 0,-1 0 0,0 1 0,0-1 0,0 0 0,1 0 0,-2 1 0,1 7 30,0-1 0,-1-1 0,-4 13 1,-5 14 38,-19 37 0,17-39-100,-14 43 0,17-39-98,1-2 0,-5 66 1,13-88 60,-1 0 0,2 1 0,1-1 0,-1 0 0,1 1 0,1-2 0,0 1 0,-1 0 0,3-1 0,0 1 0,11 20 0,-15-29 22,2 0 0,-1 0 0,0 0 0,1 1 0,0-2 0,-2 0 1,3 1-1,-1-1 0,0 0 0,0 0 0,1 0 0,-1 0 0,1 0 0,-1 0 0,4 0 0,-4-1 33,-1-1 0,0 0 0,2 1 0,-2-1 0,1 0 0,0 0 0,-1-1 0,1 1 0,0 0 0,-1-1 0,1 0 0,-1 0 0,1 0 0,-1 0 0,1 0 0,-1 0 0,0 0 0,2-1 0,-3 1 0,1-1 0,0 0 0,2-2 0,1-1 57,0-1 1,0 0-1,0 0 0,-1-1 0,0 1 0,0-1 0,-1 0 0,0 0 0,0 0 1,-1-1-1,1 1 0,-2 0 0,1-1 0,-1 0 0,0 1 0,-1-1 0,0-8 1,-1 0 264,0 1 0,-1-2 1,-1 1-1,0 0 1,-2 0-1,1 1 1,-9-17-1,8 21-318,0 1 0,-1 1 0,0-1 0,0 2 0,-1-2 0,-13-11 0,20 21-121,0 0 0,0 0 1,-2 0-1,2 0 0,0 0 0,0 0 0,0-1 0,0 1 1,0 0-1,0 0 0,-1 0 0,1 0 0,0 0 0,-1 0 1,1 0-1,0 0 0,0 0 0,-1 0 0,1 0 0,0 0 1,0 1-1,-1-1 0,1 0 0,0 0 0,0 0 0,-1 0 1,1 0-1,0 0 0,0 1 0,-1-1 0,1 0 0,0 0 1,0 0-1,0 1 0,0-1 0,-1 0 0,1 0 0,0 1 1,0-1-1,0 0 0,0 0 0,0 1 0,0-1 0,0 0 1,-1 0-1,1 1 0,0-1 0,0 0 0,0 1 0,0-1 1,0 1-1,0-1 122,-3 9-855</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -3716,7 +3712,7 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2023-12-12T19:21:10.291"/>
+      <inkml:timestamp xml:id="ts0" timeString="2024-01-09T19:28:26.515"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.05" units="cm"/>
@@ -3724,17 +3720,17 @@
       <inkml:brushProperty name="color" value="#008C3A"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">488 62 8576,'4'2'13992,"-5"5"-14817,-8 55 2043,-3-1 0,-24 74 0,29-106-1142,5-21-279,0 0 0,0 1 0,0-1 0,-6 10 0,5-29-9514,6-2 8736</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1">468 84 7168,'18'-4'7646,"-2"0"-5709,21-1 993,45 0-1,-1 4-5858,-71 1 1887,-9 0 620,0 0 0,-1 0 0,1 0 0,0 0 0,0 0 0,-1 0 0,1 0 0,0 0 0,0 1 0,-1-1 0,1 0 0,0 0 0,0 1 0,0 0 0,3 4-879</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2">455 306 11904,'9'7'4480,"-2"-4"-3489,8 5 513,-9-8-64,6 4-608,7 1-64,-3-2-384,6-1-96,0-2-160,-1-2-1280,0-1-512,1-6 832,4 1 480</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">489 62 8576,'4'2'13992,"-5"5"-14817,-9 55 2043,-1-1 0,-26 74 0,30-106-1142,5-21-279,0 0 0,0 1 0,1-1 0,-8 10 0,6-29-9514,6-2 8736</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1">468 84 7168,'18'-4'7646,"-2"0"-5709,21-1 993,45 0-1,0 4-5858,-73 1 1887,-8 0 620,0 0 0,-1 0 0,1 0 0,0 0 0,0 0 0,-1 0 0,2 0 0,-1 0 0,0 1 0,-1-1 0,1 0 0,0 0 0,0 1 0,0 0 0,2 4-879</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2">456 306 11904,'8'7'4480,"0"-4"-3489,6 5 513,-7-8-64,4 4-608,9 1-64,-5-2-384,8-1-96,-2-2-160,0-2-1280,0-1-512,2-6 832,2 1 480</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3">486 283 7936,'0'41'9501,"-1"-30"-9002,0 1 0,0-1-1,-1 0 1,-1 0-1,0 0 1,-4 11-1,0-5-38,-42 117 2211,58-155-11412,-3 13 7696</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4">993 37 8960,'2'9'1359,"-1"0"0,0 1 0,0-1 0,-1 1 0,-1 15 0,-10 47 700,-5 56-119,15-109-1502,1 0-1,1 0 1,0 0-1,8 33 1,-9-51-384,1 1 1,-1-1-1,0 1 1,1-1 0,-1 0-1,1 1 1,-1-1 0,1 0-1,0 1 1,0-1-1,0 0 1,-1 0 0,1 0-1,0 0 1,0 0-1,1 0 1,-1 0 0,0 0-1,0 0 1,0 0-1,2 0 1,-1-1 7,-1 1-1,1-1 1,-1 0 0,1 0-1,-1 0 1,1 0 0,-1-1-1,1 1 1,-1 0-1,1-1 1,-1 1 0,0-1-1,1 1 1,-1-1 0,0 1-1,1-1 1,-1 0 0,0 0-1,0 0 1,3-2 0,5-5 94,0-1 0,0 0 0,-1-1 1,11-15-1,26-48 98,-24 36-169,90-125 338,-29 47-2612,-79 111 2011</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5">1447 368 8704,'-4'-8'12982,"11"6"-13101,0 2 274,0 0 0,-1 0 0,1 1 0,0 0 0,-1 0 0,1 1 0,-1 0 0,1 0 0,-1 0 0,0 1 0,0 0 0,0 0 0,0 0 0,0 1 0,6 5 0,-11-8-127,0 0-1,0 0 0,0 0 1,0 0-1,0 0 0,0 1 1,0-1-1,-1 0 0,1 1 1,0-1-1,-1 0 0,1 1 1,0-1-1,-1 1 0,0-1 1,1 1-1,-1-1 0,0 1 1,0-1-1,0 1 0,0-1 1,0 1-1,0-1 0,0 1 1,-1-1-1,1 1 1,-1-1-1,1 1 0,-1-1 1,0 3-1,-3 0-81,1 1 0,-1-1 1,0 0-1,-1 1 0,1-2 1,-8 6-1,-11 11-1138,22-19 1143,0 1 1,-1 0-1,1-1 0,1 1 0,-1 0 1,0-1-1,0 1 0,1 0 0,-1 0 0,1 0 1,-1 0-1,1 0 0,0 0 0,0 0 0,0 0 1,0-1-1,0 1 0,0 0 0,1 0 0,0 2 1,1 7-21,1-1 1,8 17-1,0 1 126,-10-24 82,0 0 1,0 0-1,0 0 0,-1 0 0,1 1 1,-1-1-1,0 0 0,0 0 1,0 0-1,-1 1 0,1-1 1,-3 5-1,2-6-47,0 0 0,-1-1 0,1 1 0,-1 0 0,0-1 0,0 0 0,0 1 0,0-1 0,0 0 0,-1 0 0,1 0 0,0 0 0,-1-1 0,0 1 0,1-1 0,-1 1 0,-4 0 0,-1 2-979,-1-2 0,-15 4 0,-18-1-7833,23-4 6026,3-1 1292</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6">1 1087 8064,'3'2'8309,"7"-1"-5406,13-1-2155,-20 0-229,78 7 1013,-62-4-1617,0-1 1,0-1-1,0 0 1,30-4 0,-47 2-506,1 0 0,0 1 1,-1-1-1,1 0 0,0-1 1,-1 1-1,0 0 0,1-1 1,-1 1-1,0-1 1,0 0-1,1 0 0,-1 0 1,-1 0-1,4-3 0,5-10-748</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="7">56 899 10624,'4'3'4032,"-1"0"-3136,9-1 799,-5-2 225,5 3-640,7 2-96,6 2-608,2-2-192,1 0-256,1 0-32,-1-1 32,-1-4-1344,1-4-608,1-1 928,-4 2 480</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="8">803 860 7296,'0'0'96,"0"0"0,0 0 1,0 0-1,-1 0 0,1 0 1,0 0-1,0 0 0,0 0 1,0 0-1,-1 0 0,1 0 1,0 0-1,0 0 0,0 0 0,-1 0 1,1 0-1,0 0 0,0 0 1,0 0-1,0 0 0,0 0 1,-1 0-1,1-1 0,0 1 1,0 0-1,0 0 0,0 0 1,0 0-1,-1 0 0,1 0 1,0-1-1,0 1 0,0 0 0,4-5 2708,10-3 77,-8 6-2659,0 0 0,0 1-1,0 0 1,0 0-1,0 0 1,0 1-1,0 0 1,0 0 0,0 1-1,0 0 1,0 0-1,7 2 1,-6-1-76,0 0 0,0 0 0,-1 1-1,0 0 1,1 1 0,-1-1 0,0 1 0,-1 0 0,1 0 0,6 8 0,-10-10-104,0 0 0,0 0 1,0 1-1,-1-1 0,1 1 1,-1-1-1,0 1 0,0 0 1,0 0-1,0-1 0,0 1 1,0 0-1,-1 0 0,0 0 1,1 0-1,-1 0 0,0 0 1,0 0-1,-1 0 0,1-1 1,-1 1-1,1 0 0,-1 0 1,-2 5-1,1-3-153,-1 1 1,0-1 0,0 0-1,0 1 1,-1-2-1,0 1 1,0 0 0,0-1-1,0 0 1,-1 1-1,-5 3 1,5-5-147,1 0-50,-1 0 0,1 0 0,0 1 0,-5 5 0,8-8 256,0 0 1,1 0-1,-1 0 0,0 0 0,1 0 0,-1 0 0,1 0 0,-1 0 0,1 1 0,-1-1 0,1 0 1,0 0-1,0 1 0,-1-1 0,1 0 0,0 0 0,0 1 0,0-1 0,0 0 0,1 1 0,-1-1 1,0 0-1,1 2 0,7 18-134,-2-8 445,-1 0 0,-1 0 0,0 0 0,2 15-1,-6-26-152,0 0 0,0 0 0,0-1-1,0 1 1,0 0 0,-1 0-1,1-1 1,0 1 0,-1 0 0,0 0-1,1-1 1,-1 1 0,0-1-1,0 1 1,0-1 0,0 1 0,0-1-1,-1 2 1,-1 0 132,1-1 0,-1 0 0,0 0 0,0 0 0,0 0 0,0 0 1,0-1-1,-6 3 0,1-1-194,0-1 0,-16 2 0,-11-1-4066,35-3 3527</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="9">1238 937 9728,'7'3'5945,"15"0"-3604,-13-3-1726,11 3-189,1 1 1,-1 1 0,-1 1-1,1 0 1,18 10 0,-35-15-384,-1 0 0,1 1 1,-1-1-1,1 1 0,-1 0 1,0 0-1,0 0 0,0 0 1,0 0-1,0 0 0,2 4 1,-3-5-37,-1 0 1,1 1 0,-1-1-1,0 0 1,1 0 0,-1 0-1,0 0 1,0 0 0,0 0-1,0 1 1,0-1 0,0 0-1,0 0 1,0 0 0,0 0-1,0 1 1,-1-1-1,1 0 1,0 0 0,-1 0-1,1 0 1,-1 0 0,1 0-1,-1 0 1,0 0 0,1 0-1,-1 0 1,0 0 0,0 0-1,-1 0 1,-5 6-200,0-2 1,-13 8-1,14-9-50,1-1 0,-1 1 0,1 0 0,0 0 0,0 0-1,0 1 1,-5 7 0,9-11 219,0 1-1,0-1 1,1 0-1,-1 1 1,1-1-1,0 1 1,-1-1 0,1 1-1,0-1 1,0 1-1,-1-1 1,1 0-1,0 1 1,1-1 0,-1 1-1,0-1 1,0 1-1,1-1 1,-1 1-1,1-1 1,0 3-1,3 3 126,0-1 0,0 1 0,6 7-1,-6-10 68,-1 1-1,0 0 1,5 9-1,-8-13-81,1 1 0,-1-1-1,1 1 1,-1-1-1,0 1 1,0-1-1,0 1 1,0-1-1,0 1 1,0-1 0,0 1-1,0-1 1,0 1-1,-1-1 1,1 1-1,-1-1 1,1 0 0,-2 3-1,0-2 52,1 1-1,-1-1 1,0 0-1,0 0 1,0 0 0,0 0-1,0 0 1,0 0-1,-4 2 1,-2 0 122,0 0 0,-1 0 0,1 0 0,-1-1 0,-10 2 1,11-3-242,-1-1 0,-15 1 1,7-1-3220</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="10">1822 935 10240,'1'0'269,"0"0"0,0 0 0,0 0 1,0 0-1,0 0 0,0 0 1,0 0-1,0 0 0,0 0 0,0 0 1,0 0-1,0 1 0,0-1 0,0 0 1,0 1-1,-1-1 0,1 1 0,0-1 1,0 1-1,0-1 0,0 1 0,-1 0 1,1-1-1,0 1 0,-1 0 0,1 0 1,0 0-1,-1-1 0,1 1 0,-1 0 1,0 0-1,1 0 0,-1 0 1,0 0-1,1 0 0,-1 0 0,0 0 1,0 0-1,0 0 0,0 1 0,4 17 233,-2 1 0,0-1 0,-2 1-1,0-1 1,-1 1 0,-1-1 0,-5 26-1,-2-7 110,-1-1-1,-27 62 1,36-96-413,0 1-416,-1 0 1,0-1-1,1 1 1,-2-1-1,1 1 1,-3 3-1,4-6-125,0 0-1,0-1 0,1 1 0,-1-1 0,0 1 1,0-1-1,1 1 0,-1-1 0,0 0 0,0 1 1,0-1-1,0 0 0,0 0 0,0 1 1,0-1-1,1 0 0,-1 0 0,0 0 0,0 0 1,0 0-1,0 0 0,0-1 0,0 1 0,0 0 1,0 0-1,0-1 0,1 1 0,-1 0 1,0-1-1,0 1 0,0-1 0,1 1 0,-2-2 1,-5-3-969</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4">993 37 8960,'2'9'1359,"-1"0"0,0 1 0,0-1 0,-1 1 0,-1 15 0,-9 47 700,-6 56-119,15-109-1502,1 0-1,1 0 1,0 0-1,7 33 1,-8-51-384,1 1 1,-1-1-1,0 1 1,1-1 0,-1 0-1,1 1 1,-1-1 0,2 0-1,-1 1 1,0-1-1,0 0 1,-1 0 0,1 0-1,0 0 1,0 0-1,1 0 1,-2 0 0,1 0-1,0 0 1,0 0-1,2 0 1,0-1 7,-2 1-1,1-1 1,-1 0 0,1 0-1,-1 0 1,1 0 0,-2-1-1,2 1 1,-1 0-1,1-1 1,-1 1 0,0-1-1,2 1 1,-2-1 0,0 1-1,1-1 1,-1 0 0,0 0-1,0 0 1,2-2 0,7-5 94,-2-1 0,2 0 0,-3-1 1,12-15-1,27-48 98,-25 36-169,89-125 338,-27 47-2612,-80 111 2011</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5">1448 368 8704,'-5'-8'12982,"13"6"-13101,-1 2 274,0 0 0,-1 0 0,0 1 0,2 0 0,-2 0 0,1 1 0,-1 0 0,1 0 0,-1 0 0,0 1 0,0 0 0,0 0 0,0 0 0,0 1 0,6 5 0,-11-8-127,0 0-1,0 0 0,0 0 1,0 0-1,0 0 0,-1 1 1,1-1-1,-1 0 0,1 1 1,1-1-1,-2 0 0,1 1 1,0-1-1,-1 1 0,0-1 1,1 1-1,-1-1 0,0 1 1,0-1-1,0 1 0,0-1 1,0 1-1,0-1 0,0 1 1,-1-1-1,1 1 1,-1-1-1,1 1 0,-1-1 1,-1 3-1,-1 0-81,0 1 0,-1-1 1,0 0-1,-2 1 0,3-2 1,-10 6-1,-9 11-1138,21-19 1143,0 1 1,-1 0-1,1-1 0,1 1 0,-1 0 1,0-1-1,0 1 0,1 0 0,-1 0 0,1 0 1,-1 0-1,1 0 0,0 0 0,0 0 0,0 0 1,0-1-1,0 1 0,0 0 0,1 0 0,0 2 1,1 7-21,1-1 1,8 17-1,0 1 126,-10-24 82,-1 0 1,1 0-1,0 0 0,-1 0 0,2 1 1,-2-1-1,0 0 0,0 0 1,0 0-1,-2 1 0,2-1 1,-2 5-1,1-6-47,0 0 0,-1-1 0,1 1 0,-1 0 0,0-1 0,0 0 0,0 1 0,-1-1 0,1 0 0,0 0 0,0 0 0,0 0 0,-1-1 0,0 1 0,0-1 0,0 1 0,-3 0 0,-3 2-979,1-2 0,-16 4 0,-18-1-7833,23-4 6026,2-1 1292</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6">1 1087 8064,'3'2'8309,"7"-1"-5406,13-1-2155,-20 0-229,78 7 1013,-62-4-1617,0-1 1,0-1-1,0 0 1,30-4 0,-47 2-506,1 0 0,0 1 1,-1-1-1,2 0 0,-2-1 1,0 1-1,0 0 0,1-1 1,-1 1-1,0-1 1,1 0-1,-1 0 0,0 0 1,-1 0-1,4-3 0,5-10-748</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="7">56 899 10624,'4'3'4032,"0"0"-3136,7-1 799,-4-2 225,5 3-640,7 2-96,6 2-608,2-2-192,1 0-256,2 0-32,-3-1 32,1-4-1344,-1-4-608,2-1 928,-4 2 480</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="8">803 860 7296,'0'0'96,"0"0"0,0 0 1,0 0-1,-1 0 0,1 0 1,0 0-1,0 0 0,0 0 1,0 0-1,-1 0 0,1 0 1,0 0-1,0 0 0,0 0 0,-1 0 1,1 0-1,0 0 0,0 0 1,0 0-1,0 0 0,0 0 1,-1 0-1,1-1 0,0 1 1,0 0-1,0 0 0,0 0 1,0 0-1,-1 0 0,1 0 1,0-1-1,0 1 0,0 0 0,4-5 2708,10-3 77,-8 6-2659,1 0 0,-2 1-1,1 0 1,1 0-1,-2 0 1,1 1-1,1 0 1,-2 0 0,1 1-1,1 0 1,-2 0-1,9 2 1,-8-1-76,2 0 0,-2 0 0,0 1-1,1 0 1,-1 1 0,0-1 0,1 1 0,-3 0 0,2 0 0,6 8 0,-10-10-104,0 0 0,0 0 1,1 1-1,-2-1 0,1 1 1,-1-1-1,0 1 0,0 0 1,0 0-1,0-1 0,-1 1 1,1 0-1,-1 0 0,0 0 1,1 0-1,-1 0 0,0 0 1,0 0-1,-1 0 0,1-1 1,-1 1-1,1 0 0,0 0 1,-3 5-1,1-3-153,-1 1 1,-1-1 0,1 0-1,0 1 1,0-2-1,-1 1 1,-1 0 0,1-1-1,1 0 1,-2 1-1,-6 3 1,7-5-147,0 0-50,-2 0 0,2 0 0,1 1 0,-7 5 0,9-8 256,0 0 1,1 0-1,-1 0 0,0 0 0,1 0 0,-1 0 0,1 0 0,0 0 0,0 1 0,-1-1 0,1 0 1,0 0-1,0 1 0,-1-1 0,1 0 0,0 0 0,0 1 0,0-1 0,0 0 0,1 1 0,-1-1 1,0 0-1,1 2 0,6 18-134,0-8 445,-3 0 0,0 0 0,1 0 0,1 15-1,-6-26-152,0 0 0,0 0 0,0-1-1,0 1 1,0 0 0,-1 0-1,1-1 1,0 1 0,-1 0 0,0 0-1,1-1 1,-1 1 0,0-1-1,0 1 1,-1-1 0,1 1 0,0-1-1,-1 2 1,-1 0 132,2-1 0,-2 0 0,0 0 0,-1 0 0,1 0 0,0 0 1,1-1-1,-8 3 0,3-1-194,-1-1 0,-17 2 0,-10-1-4066,35-3 3527</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="9">1239 937 9728,'6'3'5945,"17"0"-3604,-14-3-1726,11 3-189,0 1 1,0 1 0,0 1-1,0 0 1,18 10 0,-35-15-384,-1 0 0,0 1 1,0-1-1,2 1 0,-2 0 1,0 0-1,0 0 0,0 0 1,0 0-1,0 0 0,1 4 1,-1-5-37,-2 0 1,1 1 0,-1-1-1,0 0 1,1 0 0,-1 0-1,0 0 1,0 0 0,0 0-1,0 1 1,0-1 0,0 0-1,0 0 1,0 0 0,0 0-1,0 1 1,-1-1-1,1 0 1,0 0 0,-1 0-1,1 0 1,-2 0 0,2 0-1,-1 0 1,0 0 0,1 0-1,-1 0 1,1 0 0,-1 0-1,-1 0 1,-5 6-200,-1-2 1,-11 8-1,13-9-50,1-1 0,-1 1 0,1 0 0,0 0 0,-1 0-1,2 1 1,-6 7 0,8-11 219,1 1-1,0-1 1,1 0-1,-1 1 1,1-1-1,0 1 1,-1-1 0,1 1-1,0-1 1,0 1-1,0-1 1,0 0-1,0 1 1,0-1 0,0 1-1,0-1 1,0 1-1,1-1 1,-1 1-1,1-1 1,0 3-1,4 3 126,-1-1 0,0 1 0,6 7-1,-6-10 68,-1 1-1,0 0 1,5 9-1,-8-13-81,1 1 0,-1-1-1,1 1 1,-1-1-1,0 1 1,0-1-1,0 1 1,0-1-1,0 1 1,0-1 0,0 1-1,0-1 1,0 1-1,-1-1 1,1 1-1,-1-1 1,1 0 0,-2 3-1,-1-2 52,2 1-1,-1-1 1,1 0-1,-1 0 1,0 0 0,0 0-1,0 0 1,0 0-1,-5 2 1,0 0 122,-2 0 0,1 0 0,-1 0 0,1-1 0,-11 2 1,10-3-242,1-1 0,-17 1 1,9-1-3220</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="10">1823 935 10240,'1'0'269,"0"0"0,0 0 0,0 0 1,0 0-1,0 0 0,0 0 1,0 0-1,0 0 0,1 0 0,-2 0 1,1 0-1,0 1 0,0-1 0,0 0 1,0 1-1,-1-1 0,1 1 0,0-1 1,0 1-1,0-1 0,0 1 0,-1 0 1,1-1-1,0 1 0,-1 0 0,1 0 1,0 0-1,-1-1 0,1 1 0,-1 0 1,0 0-1,1 0 0,-1 0 1,0 0-1,2 0 0,-2 0 0,0 0 1,0 0-1,0 0 0,0 1 0,3 17 233,-1 1 0,0-1 0,-2 1-1,0-1 1,-1 1 0,-1-1 0,-5 26-1,-2-7 110,-1-1-1,-27 62 1,36-96-413,0 1-416,-1 0 1,0-1-1,1 1 1,-2-1-1,1 1 1,-3 3-1,4-6-125,0 0-1,0-1 0,1 1 0,-1-1 0,0 1 1,0-1-1,1 1 0,-1-1 0,0 0 0,0 1 1,0-1-1,0 0 0,0 0 0,-1 1 1,1-1-1,1 0 0,0 0 0,-1 0 0,0 0 1,0 0-1,0 0 0,0-1 0,0 1 0,0 0 1,0 0-1,0-1 0,1 1 0,-1 0 1,0-1-1,0 1 0,0-1 0,1 1 0,-2-2 1,-5-3-969</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -3754,7 +3750,7 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2023-12-12T19:21:11.050"/>
+      <inkml:timestamp xml:id="ts0" timeString="2024-01-09T19:28:27.706"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.035" units="cm"/>
@@ -3785,90 +3781,90 @@
           <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2023-12-12T19:21:11.451"/>
+      <inkml:timestamp xml:id="ts0" timeString="2024-01-09T19:28:28.339"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.05" units="cm"/>
       <inkml:brushProperty name="height" value="0.05" units="cm"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1828 3503 11231 0 0,'-1'0'131'0'0,"1"0"-1"0"0,-1 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,-1 0-1 0 0,1 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,1 1 1 0 0,0-1-1 0 0,-1 1 1 0 0,1-1-1 0 0,0 1 1 0 0,-1 0 0 0 0,0 17 2797 0 0,1-14-3093 0 0,14 170 3208 0 0,1 58-1073 0 0,-42 210 485 0 0,25-417-2301 0 0,-5 24 630 0 0,-19 72 0 0 0,9-47-25 0 0,14-54-594 0 0,21-48-2302 0 0,-10 17-302 0 0,-2-2-6030 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1">1884 4112 7367 0 0,'5'1'8379'0'0,"17"1"-5534"0"0,-14-1-2390 0 0,1 0-1 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,12-3 1 0 0,-5 1-107 0 0,43-3 698 0 0,0 2 0 0 0,93 7 0 0 0,-67 3-670 0 0,0-4 0 0 0,128-11-1 0 0,500-41 1029 0 0,-568 43-1272 0 0,376-9 251 0 0,-431 15-363 0 0,382 6 125 0 0,913 17-17 0 0,-422-23-24 0 0,-44 0-8 0 0,188-7-85 0 0,-1050 7 31 0 0,229 0-31 0 0,-160 0-11 0 0,209 3 0 0 0,-96-4 0 0 0,-99 1 0 0 0,195 0 53 0 0,-196 1-42 0 0,203 3-11 0 0,-202-2 0 0 0,43 1 11 0 0,-102-1 31 0 0,225 6-31 0 0,-212-5 0 0 0,-33-1 31 0 0,145 7-31 0 0,-6-2 1 0 0,-119-4 36 0 0,124 6-24 0 0,39 2 24 0 0,1 1-25 0 0,0 0 19 0 0,-4 0-20 0 0,11 2 20 0 0,-24-1-31 0 0,-96-7 0 0 0,-65-3 31 0 0,152 4-31 0 0,27-5 0 0 0,-67 0 42 0 0,59 2 11 0 0,20 0 5 0 0,-13-1 6 0 0,-108-2-43 0 0,-69 1 32 0 0,136 1-37 0 0,-26-1 26 0 0,200-1 24 0 0,-140-2 3 0 0,-172 0-26 0 0,290-3 39 0 0,143-3 99 0 0,-438 7-117 0 0,140-1-1 0 0,39 0 17 0 0,-7 3 2 0 0,-6-1-10 0 0,-8 1-3 0 0,-9 0 0 0 0,-4 1-13 0 0,78 0 6 0 0,-210-3-50 0 0,-29 0 19 0 0,75 1-18 0 0,-63 0 30 0 0,153 3 12 0 0,-78-2-36 0 0,100 5 103 0 0,-166-2 20 0 0,96 20-1 0 0,-150-23-106 0 0,-1 0 0 0 0,0 1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0-1 0 0,-1 1 1 0 0,18 11 0 0 0,-28-16-42 0 0,1 0 1 0 0,-1 1-1 0 0,0-1 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 1 0 0 0,-1-1 1 0 0,0 0-1 0 0,1 1 0 0 0,-1-1 1 0 0,0 0-1 0 0,1 1 0 0 0,-1-1 1 0 0,0 0-1 0 0,0 1 0 0 0,1-1 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,-1 0 1 0 0,1-1-7 0 0,-1 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,-40 2-604 0 0,38-2 419 0 0,-89-3-2399 0 0,46-1 831 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2">1566 5069 4607 0 0,'-4'-1'1267'0'0,"0"0"0"0"0,-1 0 0 0 0,0 0 0 0 0,1 0 1 0 0,-1 1-1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-8 2 0 0 0,7 0-674 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 1 0 0,-8 6-1 0 0,6-3-454 0 0,1-1 0 0 0,-1 1 0 0 0,2 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0 1 0 0 0,0 0 0 0 0,-4 12 0 0 0,3-2-90 0 0,1 0 1 0 0,0 1-1 0 0,2-1 1 0 0,-1 30-1 0 0,3-9 32 0 0,6 46 0 0 0,-3-62 116 0 0,0-1-1 0 0,2 1 1 0 0,13 38 0 0 0,-15-52-134 0 0,0-1 0 0 0,1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1-1-1 0 0,0 1 1 0 0,1-1 0 0 0,14 9 0 0 0,-18-13-149 0 0,0 0 0 0 0,0-1-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,1 0-1 0 0,-1-1 1 0 0,0 1-1 0 0,1 0 1 0 0,-1-1 0 0 0,0 0-1 0 0,1 0 1 0 0,3 0-1 0 0,-1-1 13 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1-1 1 0 0,6-2-1 0 0,3-4 55 0 0,-1 0 1 0 0,0 0-1 0 0,0-1 1 0 0,19-20-1 0 0,-16 12 75 0 0,-1-1-1 0 0,-1 0 1 0 0,0 0-1 0 0,-1-2 1 0 0,-2 0-1 0 0,0 0 1 0 0,-1-1-1 0 0,-1 0 1 0 0,-1 0-1 0 0,-1-1 1 0 0,-1 0-1 0 0,-1-1 1 0 0,-1 1 0 0 0,-1-1-1 0 0,-1 0 1 0 0,-2-37-1 0 0,0 55 25 0 0,-1 0 1 0 0,1 0-1 0 0,-1 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,-1 1 0 0 0,0-1 1 0 0,0 1-1 0 0,-1 0 0 0 0,-3-7 1 0 0,3 8 45 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,-1 1 0 0 0,-7-3 0 0 0,-1 1 89 0 0,1 1 0 0 0,-1 0 1 0 0,0 1-1 0 0,0 0 0 0 0,0 1 0 0 0,0 0 0 0 0,-20 2 1 0 0,-7 3-189 0 0,-44 11 1 0 0,78-13-121 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3">145 2161 8319 0 0,'-6'-3'4344'0'0,"4"10"-1024"0"0,-3 69 566 0 0,-13 38-3248 0 0,8-57-370 0 0,-1 20-124 0 0,6-33 84 0 0,-3 0 0 0 0,-1-1 0 0 0,-16 48 0 0 0,12-66 231 0 0,12-23-410 0 0,1-1 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 1 0 0,-1 0-1 0 0,1-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,-1-1 1 0 0,-1 1-1 0 0,3-1-19 0 0,-1-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1-1 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,-1-19 408 0 0,3-13-246 0 0,1 0-1 0 0,2 0 0 0 0,11-39 1 0 0,-8 40-117 0 0,9-38-67 0 0,52-133-1 0 0,-62 188-25 0 0,16-28 0 0 0,-20 37 14 0 0,1 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,1 1-1 0 0,0-1 1 0 0,9-6-1 0 0,-12 10 3 0 0,-1 0-1 0 0,1 0 0 0 0,-1 1 1 0 0,1-1-1 0 0,-1 1 1 0 0,1-1-1 0 0,-1 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,3 1 0 0 0,-1 0-9 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,3 4 0 0 0,2 1-16 0 0,0 0 0 0 0,-1 1 0 0 0,0 0 0 0 0,9 11 0 0 0,-14-15 38 0 0,0-1-1 0 0,0 1 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 1-1 0 0,-1-1 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 6-1 0 0,-1-6 2 0 0,1 0-1 0 0,-1 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-4 2-1 0 0,-16 11 254 0 0,-1-2 0 0 0,0 0 0 0 0,-1-2 0 0 0,0 0 0 0 0,-1-2 0 0 0,-39 10 0 0 0,54-20-981 0 0,9-1-544 0 0,7-1-924 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4">479 2193 15863 0 0,'1'84'4910'0'0,"2"45"-3949"0"0,1 19-1075 0 0,-4-136 133 0 0,1 44 170 0 0,11 75 0 0 0,-13-131-144 0 0,1 1 1 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1-1 0 0,0-1 1 0 0,1 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1-1 0 0,1 1 1 0 0,0 0 0 0 0,-1-1 8 0 0,1-1-1 0 0,-1 1 1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,1-1 0 0 0,-1 1-1 0 0,0 0 1 0 0,1 0 0 0 0,-1-1-1 0 0,0 1 1 0 0,0 0 0 0 0,1-1 0 0 0,-1 1-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1-1 0 0,1 0 1 0 0,-1-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0-1 0 0 0,10-29 1366 0 0,13-63-121 0 0,50-165-249 0 0,-68 242-1089 0 0,1 1 0 0 0,1-1 1 0 0,0 1-1 0 0,1 0 0 0 0,1 1 0 0 0,0 0 0 0 0,1 0 1 0 0,11-12-1 0 0,-19 25-407 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,3 0-1 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5">774 2668 12295 0 0,'0'8'210'0'0,"0"-1"0"0"0,1 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,1 0 0 0 0,-1-1-1 0 0,1 1 1 0 0,0-1 0 0 0,1 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0-1-1 0 0,6 7 1 0 0,-7-9-146 0 0,-1 0 0 0 0,1-1-1 0 0,1 1 1 0 0,-1-1 0 0 0,0 0 0 0 0,0 1 0 0 0,1-2 0 0 0,-1 1-1 0 0,1 0 1 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 0 0 0 0,4 0-1 0 0,-5-1 44 0 0,0 1-1 0 0,0 0 1 0 0,0-1-1 0 0,0 0 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,0-1-1 0 0,0 1 0 0 0,-1 0 1 0 0,1-1-1 0 0,-1 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,0-1-1 0 0,0 1 0 0 0,-1-1 1 0 0,0 0-1 0 0,2-4 1 0 0,-2 6-4 0 0,-1 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1-1 1 0 0,0 1-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0-1 1 0 0,0 1 92 0 0,-1-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 1 0 0,0 1-1 0 0,0 0 1 0 0,-2-1-1 0 0,-6-1 619 0 0,1 0-1 0 0,-1 1 0 0 0,-17-3 0 0 0,18 4-442 0 0,-3-1-55 0 0,7 2-266 0 0,1 0 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1-1-1 0 0,0 1 1 0 0,0-1 0 0 0,-6-4 0 0 0,10 6-86 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,1 0 1 0 0,-1-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,1 0-1 0 0,-1-1 1 0 0,0 1 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,1 0 1 0 0,9-6-2581 0 0,-2 2 841 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1828 3503 11231 0 0,'-1'0'131'0'0,"1"0"-1"0"0,0 0 1 0 0,0 0 0 0 0,-2 0-1 0 0,2 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,-1 0-1 0 0,1 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,1 1 1 0 0,0-1-1 0 0,-1 1 1 0 0,1-1-1 0 0,0 1 1 0 0,-1 0 0 0 0,0 17 2797 0 0,1-14-3093 0 0,14 170 3208 0 0,1 58-1073 0 0,-42 210 485 0 0,25-417-2301 0 0,-5 24 630 0 0,-19 72 0 0 0,9-47-25 0 0,14-54-594 0 0,21-48-2302 0 0,-10 17-302 0 0,-2-2-6030 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1">1884 4112 7367 0 0,'5'1'8379'0'0,"17"1"-5534"0"0,-14-1-2390 0 0,1 0-1 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,12-3 1 0 0,-5 1-107 0 0,43-3 698 0 0,0 2 0 0 0,93 7 0 0 0,-67 3-670 0 0,-1-4 0 0 0,131-11-1 0 0,497-41 1029 0 0,-567 43-1272 0 0,376-9 251 0 0,-431 15-363 0 0,383 6 125 0 0,911 17-17 0 0,-421-23-24 0 0,-44 0-8 0 0,188-7-85 0 0,-1050 7 31 0 0,229 0-31 0 0,-159 0-11 0 0,207 3 0 0 0,-95-4 0 0 0,-99 1 0 0 0,195 0 53 0 0,-196 1-42 0 0,203 3-11 0 0,-202-2 0 0 0,43 1 11 0 0,-102-1 31 0 0,225 6-31 0 0,-212-5 0 0 0,-33-1 31 0 0,145 7-31 0 0,-6-2 1 0 0,-119-4 36 0 0,124 6-24 0 0,39 2 24 0 0,1 1-25 0 0,0 0 19 0 0,-4 0-20 0 0,11 2 20 0 0,-24-1-31 0 0,-96-7 0 0 0,-65-3 31 0 0,152 4-31 0 0,27-5 0 0 0,-67 0 42 0 0,59 2 11 0 0,20 0 5 0 0,-14-1 6 0 0,-106-2-43 0 0,-70 1 32 0 0,137 1-37 0 0,-27-1 26 0 0,199-1 24 0 0,-139-2 3 0 0,-172 0-26 0 0,290-3 39 0 0,143-3 99 0 0,-438 7-117 0 0,139-1-1 0 0,41 0 17 0 0,-8 3 2 0 0,-6-1-10 0 0,-8 1-3 0 0,-9 0 0 0 0,-3 1-13 0 0,76 0 6 0 0,-209-3-50 0 0,-29 0 19 0 0,75 1-18 0 0,-63 0 30 0 0,153 3 12 0 0,-78-2-36 0 0,100 5 103 0 0,-166-2 20 0 0,96 20-1 0 0,-150-23-106 0 0,-1 0 0 0 0,0 1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0-1 0 0,-1 1 1 0 0,18 11 0 0 0,-28-16-42 0 0,1 0 1 0 0,-1 1-1 0 0,0-1 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 1 0 0 0,-1-1 1 0 0,0 0-1 0 0,1 1 0 0 0,-1-1 1 0 0,0 0-1 0 0,1 1 0 0 0,-1-1 1 0 0,0 0-1 0 0,0 1 0 0 0,1-1 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,-1 0 1 0 0,1-1-7 0 0,-1 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,-40 2-604 0 0,38-2 419 0 0,-89-3-2399 0 0,46-1 831 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2">1566 5069 4607 0 0,'-4'-1'1267'0'0,"0"0"0"0"0,-1 0 0 0 0,0 0 0 0 0,1 0 1 0 0,-1 1-1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-8 2 0 0 0,7 0-674 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 1 1 0 0,-8 6-1 0 0,7-3-454 0 0,-1-1 0 0 0,0 1 0 0 0,3 1 0 0 0,-3-1 0 0 0,2 1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0 1 0 0 0,0 0 0 0 0,-4 12 0 0 0,3-2-90 0 0,1 0 1 0 0,0 1-1 0 0,2-1 1 0 0,-1 30-1 0 0,3-9 32 0 0,5 46 0 0 0,-1-62 116 0 0,-1-1-1 0 0,2 1 1 0 0,13 38 0 0 0,-15-52-134 0 0,0-1 0 0 0,1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1-1-1 0 0,0 1 1 0 0,1-1 0 0 0,14 9 0 0 0,-18-13-149 0 0,0 0 0 0 0,0-1-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,1 0-1 0 0,-1-1 1 0 0,0 1-1 0 0,1 0 1 0 0,-1-1 0 0 0,0 0-1 0 0,1 0 1 0 0,3 0-1 0 0,-1-1 13 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1-1 1 0 0,6-2-1 0 0,3-4 55 0 0,-1 0 1 0 0,0 0-1 0 0,0-1 1 0 0,19-20-1 0 0,-16 12 75 0 0,-1-1-1 0 0,0 0 1 0 0,-2 0-1 0 0,0-2 1 0 0,-2 0-1 0 0,0 0 1 0 0,-1-1-1 0 0,-1 0 1 0 0,-1 0-1 0 0,-1-1 1 0 0,0 0-1 0 0,-3-1 1 0 0,0 1 0 0 0,-1-1-1 0 0,-1 0 1 0 0,-2-37-1 0 0,0 55 25 0 0,-1 0 1 0 0,1 0-1 0 0,-1 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,-1 1 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,-5-7 1 0 0,4 8 45 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,-1 1 0 0 0,-7-3 0 0 0,-1 1 89 0 0,1 1 0 0 0,-1 0 1 0 0,0 1-1 0 0,0 0 0 0 0,0 1 0 0 0,0 0 0 0 0,-20 2 1 0 0,-7 3-189 0 0,-44 11 1 0 0,78-13-121 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3">145 2161 8319 0 0,'-6'-3'4344'0'0,"4"10"-1024"0"0,-3 69 566 0 0,-13 38-3248 0 0,8-57-370 0 0,-1 20-124 0 0,6-33 84 0 0,-3 0 0 0 0,-1-1 0 0 0,-17 48 0 0 0,14-66 231 0 0,11-23-410 0 0,1-1 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-2 0-1 0 0,2 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 1 0 0,-1 0-1 0 0,1-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,-1-1 1 0 0,-1 1-1 0 0,3-1-19 0 0,-2-1 0 0 0,2 1 1 0 0,0 0-1 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1-1 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,-1-19 408 0 0,3-13-246 0 0,1 0-1 0 0,2 0 0 0 0,11-39 1 0 0,-8 40-117 0 0,9-38-67 0 0,52-133-1 0 0,-62 188-25 0 0,16-28 0 0 0,-20 37 14 0 0,1 1-1 0 0,0-1 1 0 0,0 1-1 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,9-6-1 0 0,-12 10 3 0 0,-1 0-1 0 0,1 0 0 0 0,-1 1 1 0 0,1-1-1 0 0,-1 1 1 0 0,1-1-1 0 0,-2 1 1 0 0,3-1-1 0 0,-2 1 0 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,3 1 0 0 0,-1 0-9 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,3 4 0 0 0,2 1-16 0 0,0 0 0 0 0,-1 1 0 0 0,0 0 0 0 0,9 11 0 0 0,-14-15 38 0 0,0-1-1 0 0,0 1 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,2 0 1 0 0,-1 1-1 0 0,-1-1 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 6-1 0 0,-1-6 2 0 0,1 0-1 0 0,-1 0 1 0 0,-1-1-1 0 0,2 1 1 0 0,-1 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,2 0-1 0 0,-1 0 1 0 0,-4 2-1 0 0,-16 11 254 0 0,-1-2 0 0 0,0 0 0 0 0,-1-2 0 0 0,0 0 0 0 0,-1-2 0 0 0,-39 10 0 0 0,54-20-981 0 0,9-1-544 0 0,7-1-924 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4">479 2193 15863 0 0,'1'84'4910'0'0,"2"45"-3949"0"0,1 19-1075 0 0,-4-136 133 0 0,1 44 170 0 0,11 75 0 0 0,-13-131-144 0 0,1 1 1 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1-1 0 0,0-1 1 0 0,1 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1-1 0 0,1 1 1 0 0,0 0 0 0 0,-1-1 8 0 0,1-1-1 0 0,-1 1 1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,2-1 0 0 0,-2 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,1-1 0 0 0,-1 1-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1-1 0 0,1 0 1 0 0,-1-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0-1 0 0 0,10-29 1366 0 0,14-63-121 0 0,48-165-249 0 0,-67 242-1089 0 0,1 1 0 0 0,1-1 1 0 0,0 1-1 0 0,1 0 0 0 0,1 1 0 0 0,0 0 0 0 0,1 0 1 0 0,11-12-1 0 0,-19 25-407 0 0,-1 0 0 0 0,2 0-1 0 0,-3 0 1 0 0,2 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,4 0-1 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5">774 2668 12295 0 0,'0'8'210'0'0,"0"-1"0"0"0,1 0-1 0 0,-1 0 1 0 0,3 0 0 0 0,-2 0-1 0 0,1 0 1 0 0,1 0 0 0 0,-1-1-1 0 0,1 1 1 0 0,0-1 0 0 0,1 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0-1-1 0 0,6 7 1 0 0,-7-9-146 0 0,-1 0 0 0 0,1-1-1 0 0,1 1 1 0 0,-1-1 0 0 0,0 0 0 0 0,0 1 0 0 0,1-2 0 0 0,-1 1-1 0 0,1 0 1 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,0 0-1 0 0,2-1 1 0 0,-1 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 0 0 0 0,4 0-1 0 0,-5-1 44 0 0,0 1-1 0 0,0 0 1 0 0,0-1-1 0 0,0 0 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,0-1-1 0 0,0 1 0 0 0,-1 0 1 0 0,1-1-1 0 0,-1 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,-1 0 1 0 0,3 0-1 0 0,-2 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,0-1-1 0 0,0 1 0 0 0,-1-1 1 0 0,0 0-1 0 0,2-4 1 0 0,-2 6-4 0 0,-1 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1-1 1 0 0,0 1-1 0 0,-1 0 0 0 0,1 0 1 0 0,-2 0-1 0 0,2-1 1 0 0,-1 1 92 0 0,-1-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 1 0 0,0 1-1 0 0,0 0 1 0 0,-2-1-1 0 0,-6-1 619 0 0,1 0-1 0 0,-1 1 0 0 0,-17-3 0 0 0,18 4-442 0 0,-3-1-55 0 0,7 2-266 0 0,0 0 0 0 0,2-1 0 0 0,-2 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1-1-1 0 0,0 1 1 0 0,0-1 0 0 0,-6-4 0 0 0,10 6-86 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,1 0 1 0 0,-1-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,1 0-1 0 0,-1-1 1 0 0,0 1 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,1 0 1 0 0,9-6-2581 0 0,-2 2 841 0 0</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6">1233 2563 11975 0 0,'7'-2'7974'0'0,"17"-5"-6701"0"0,-12 3-567 0 0,60-24-1936 0 0,-61 24 299 0 0</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="7">1196 2316 17103 0 0,'3'-1'715'0'0,"-1"0"-1"0"0,1 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,-1 1 0 0 0,5-1 1 0 0,29 2 685 0 0,-13 1-994 0 0,51-7-438 0 0,-42 1-6340 0 0,-8 0-1159 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="8">1899 2175 8751 0 0,'-54'43'5070'0'0,"-20"24"-1765"0"0,72-65-3254 0 0,1-1 1 0 0,-1 0 0 0 0,1 1-1 0 0,0-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0-1 1 0 0,1 1-1 0 0,0 0 1 0 0,-1 3 0 0 0,1-4-29 0 0,1 0 0 0 0,-1 1 1 0 0,0-1-1 0 0,1 0 1 0 0,0 1-1 0 0,-1-1 1 0 0,1 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,1 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,1 0-1 0 0,-1-1 1 0 0,0 1-1 0 0,0-1 0 0 0,1 1 1 0 0,1 0-1 0 0,17 6 138 0 0,37 8 0 0 0,-34-10 163 0 0,37 14 1 0 0,-54-16-287 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,-1 1 0 0 0,1-1 1 0 0,-1 1-1 0 0,0 0 0 0 0,0 1 1 0 0,-1-1-1 0 0,8 10 0 0 0,-8-9 79 0 0,-1 1-1 0 0,0-1 0 0 0,-1 1 1 0 0,0 0-1 0 0,1 0 1 0 0,-2 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,0 1-1 0 0,0-1 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 1 1 0 0,-1-1-1 0 0,-2 8 0 0 0,0-3 188 0 0,0-1-1 0 0,0 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,0-1 1 0 0,-1 0-1 0 0,0 0 1 0 0,0-1-1 0 0,-10 9 1 0 0,9-10-136 0 0,0-1-1 0 0,-1 0 1 0 0,0 0 0 0 0,0-1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0-1 0 0 0,-1 1-1 0 0,1-1 1 0 0,-14-1 0 0 0,23 0-195 0 0,-1 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,-1 1 0 0 0,1-1-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0 0 0 0,-1-3 0 0 0,1 1-364 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,2-5 0 0 0,3-8-1650 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="9">1843 2098 9215 0 0,'-1'2'812'0'0,"-1"-1"0"0"0,1 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 4-1 0 0,-4 21 2346 0 0,7 25-1142 0 0,14 78 156 0 0,1 5-1574 0 0,-22 219 214 0 0,7-340-606 0 0,-1-14-221 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,2-1-172 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1-2 0 0 0,6-10-1341 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="10">2122 2216 5983 0 0,'8'-1'1211'0'0,"1"-1"-1"0"0,-1 2 0 0 0,1-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1 0 0 0 0,1 0 1 0 0,8 3-1 0 0,0 1-391 0 0,-1 0 0 0 0,-1 1 0 0 0,27 14 0 0 0,-33-15-638 0 0,0 1 1 0 0,0-1-1 0 0,-1 1 1 0 0,0 1 0 0 0,-1-1-1 0 0,1 1 1 0 0,-1 1 0 0 0,0-1-1 0 0,9 15 1 0 0,-12-16-126 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,-2 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,-1 0 0 0 0,1-1 0 0 0,-2 9 0 0 0,-1 1-55 0 0,-1 1-1 0 0,0-1 0 0 0,-1 0 1 0 0,-1 0-1 0 0,-1 0 1 0 0,-13 23-1 0 0,13-28-5 0 0,0-1 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,-1-1-1 0 0,-1-1 0 0 0,1 1 1 0 0,-1-2-1 0 0,-16 10 0 0 0,8-8-22 0 0,13-6 10 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 1 0 0 0,-5 3-1 0 0,10-7 16 0 0,0 1-1 0 0,0-1 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,1 0 0 0 0,8 8-80 0 0,13 4 139 0 0,-10-7 66 0 0,1-1 0 0 0,0-1-1 0 0,-1 0 1 0 0,1 0 0 0 0,1-1-1 0 0,-1-1 1 0 0,0 0-1 0 0,0-1 1 0 0,0 0 0 0 0,20-4-1 0 0,-22 3-479 0 0,-1-2 0 0 0,1 1 0 0 0,-1-2 0 0 0,15-6 0 0 0,-10 2-1975 0 0,-2-2-5367 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="11">2547 2266 4607 0 0,'6'2'1354'0'0,"16"-3"8937"0"0,-15 0-8938 0 0,69-6 3257 0 0,-46 3-4015 0 0,-1 2 1 0 0,1 1-1 0 0,57 4 0 0 0,-81-2-527 0 0,5 1 112 0 0,1 0 1 0 0,18 6-1 0 0,-28-8-145 0 0,0 1 0 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0-1 0 0,-1 1 1 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1-1 0 0 0,2 4 0 0 0,-2-2 19 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0 0 0 0,0-1 0 0 0,-3 5-1 0 0,-23 35 344 0 0,19-31-277 0 0,-21 37 268 0 0,-34 70-1 0 0,9-13-30 0 0,46-94-295 0 0,1 0 0 0 0,-1 0 0 0 0,-1-1-1 0 0,-16 14 1 0 0,14-13 17 0 0,20-18-1932 0 0,3-3-5860 0 0,-2 1-553 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="12">3145 2194 15919 0 0,'1'-1'152'0'0,"1"0"-1"0"0,-1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,1 1 1 0 0,-1-1-1 0 0,1 1 1 0 0,-1-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 1 0 0,-1 0-1 0 0,1 0 1 0 0,2 0 0 0 0,4 1 539 0 0,-1 1 0 0 0,0-1-1 0 0,10 4 1 0 0,-3-1-435 0 0,2 0 192 0 0,0 1 0 0 0,-1 0 0 0 0,0 1-1 0 0,28 15 1 0 0,-38-18-398 0 0,0 0 0 0 0,0 0-1 0 0,-1 1 1 0 0,1-1 0 0 0,-1 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,-1 1 1 0 0,1-1 0 0 0,-1 1-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 1-1 0 0,2 8 1 0 0,-3-9-29 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-5 7 0 0 0,-5 8 9 0 0,-16 23 0 0 0,21-34-38 0 0,-5 8 129 0 0,-1 0 1 0 0,-1 0-1 0 0,0-1 0 0 0,-1-1 0 0 0,-1 0 0 0 0,-1-1 1 0 0,0-1-1 0 0,0 0 0 0 0,-1-2 0 0 0,-28 16 0 0 0,44-27-172 0 0,0 0-1 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 1 0 0 0,2 0 64 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,2 0 0 0 0,2 2-11 0 0,0-1-1 0 0,0 1 0 0 0,0-1 0 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,1-1-1 0 0,-1 0 0 0 0,1 0 0 0 0,9-2 0 0 0,0 0-775 0 0,0-1 0 0 0,-1 0 0 0 0,27-11 0 0 0,-26 7-1328 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="8">1899 2175 8751 0 0,'-54'43'5070'0'0,"-20"24"-1765"0"0,72-65-3254 0 0,1-1 1 0 0,-1 0 0 0 0,1 1-1 0 0,0-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,1 0 1 0 0,-2 0-1 0 0,2-1 1 0 0,0 1-1 0 0,0 0 1 0 0,-1 3 0 0 0,1-4-29 0 0,1 0 0 0 0,-1 1 1 0 0,0-1-1 0 0,0 0 1 0 0,2 1-1 0 0,-2-1 1 0 0,1 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,1 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,1 0-1 0 0,-1-1 1 0 0,0 1-1 0 0,0-1 0 0 0,1 1 1 0 0,1 0-1 0 0,17 6 138 0 0,37 8 0 0 0,-34-10 163 0 0,37 14 1 0 0,-54-16-287 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,-1 1 0 0 0,1-1 1 0 0,-1 1-1 0 0,0 0 0 0 0,0 1 1 0 0,-1-1-1 0 0,8 10 0 0 0,-8-9 79 0 0,-1 1-1 0 0,0-1 0 0 0,-1 1 1 0 0,0 0-1 0 0,1 0 1 0 0,-2 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,0 1-1 0 0,0-1 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 1 1 0 0,0-1-1 0 0,-4 8 0 0 0,1-3 188 0 0,0-1-1 0 0,0 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,0-1 1 0 0,-1 0-1 0 0,0 0 1 0 0,0-1-1 0 0,-10 9 1 0 0,9-10-136 0 0,0-1-1 0 0,-1 0 1 0 0,0 0 0 0 0,0-1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0-1 0 0 0,-1 1-1 0 0,1-1 1 0 0,-14-1 0 0 0,23 0-195 0 0,-1 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,-1 1 0 0 0,1-1-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-2 0-1 0 0,3 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0 0 0 0,-1-3 0 0 0,1 1-364 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,2-5 0 0 0,3-8-1650 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="9">1843 2098 9215 0 0,'-1'2'812'0'0,"-1"-1"0"0"0,1 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 4-1 0 0,-3 21 2346 0 0,5 25-1142 0 0,15 78 156 0 0,1 5-1574 0 0,-22 219 214 0 0,7-340-606 0 0,-1-14-221 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,2-1-172 0 0,-2 1 0 0 0,2-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1-2 0 0 0,6-10-1341 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="10">2122 2216 5983 0 0,'8'-1'1211'0'0,"1"-1"-1"0"0,-2 2 0 0 0,3-1 0 0 0,-1 1 0 0 0,-1 0 0 0 0,2 1 0 0 0,-3 0 0 0 0,2 0 1 0 0,8 3-1 0 0,0 1-391 0 0,-1 0 0 0 0,-1 1 0 0 0,27 14 0 0 0,-33-15-638 0 0,0 1 1 0 0,0-1-1 0 0,-1 1 1 0 0,0 1 0 0 0,-1-1-1 0 0,1 1 1 0 0,-1 1 0 0 0,1-1-1 0 0,7 15 1 0 0,-11-16-126 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,-2 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,-1 0 0 0 0,1-1 0 0 0,-2 9 0 0 0,-1 1-55 0 0,-1 1-1 0 0,0-1 0 0 0,-1 0 1 0 0,-1 0-1 0 0,-1 0 1 0 0,-13 23-1 0 0,14-28-5 0 0,-2-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,-1-1-1 0 0,-1-1 0 0 0,1 1 1 0 0,-1-2-1 0 0,-16 10 0 0 0,8-8-22 0 0,13-6 10 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 1 0 0 0,-5 3-1 0 0,10-7 16 0 0,0 1-1 0 0,0-1 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,1 0 0 0 0,8 8-80 0 0,13 4 139 0 0,-10-7 66 0 0,1-1 0 0 0,0-1-1 0 0,-1 0 1 0 0,1 0 0 0 0,1-1-1 0 0,-1-1 1 0 0,0 0-1 0 0,0-1 1 0 0,0 0 0 0 0,20-4-1 0 0,-22 3-479 0 0,-1-2 0 0 0,1 1 0 0 0,-1-2 0 0 0,15-6 0 0 0,-10 2-1975 0 0,-2-2-5367 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="11">2547 2266 4607 0 0,'6'2'1354'0'0,"16"-3"8937"0"0,-15 0-8938 0 0,69-6 3257 0 0,-46 3-4015 0 0,-1 2 1 0 0,1 1-1 0 0,57 4 0 0 0,-81-2-527 0 0,5 1 112 0 0,1 0 1 0 0,18 6-1 0 0,-29-8-145 0 0,2 1 0 0 0,-1 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-3 0 0 0 0,2 0-1 0 0,-1 1 1 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1-1 0 0 0,2 4 0 0 0,-2-2 19 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0 0 0 0,0-1 0 0 0,-3 5-1 0 0,-23 35 344 0 0,19-31-277 0 0,-21 37 268 0 0,-34 70-1 0 0,9-13-30 0 0,46-94-295 0 0,1 0 0 0 0,-1 0 0 0 0,-1-1-1 0 0,-16 14 1 0 0,14-13 17 0 0,20-18-1932 0 0,3-3-5860 0 0,-2 1-553 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="12">3145 2194 15919 0 0,'1'-1'152'0'0,"1"0"-1"0"0,-1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,1 1 1 0 0,-1-1-1 0 0,1 1 1 0 0,-1-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 1 0 0,-1 0-1 0 0,1 0 1 0 0,2 0 0 0 0,4 1 539 0 0,-1 1 0 0 0,0-1-1 0 0,10 4 1 0 0,-3-1-435 0 0,2 0 192 0 0,0 1 0 0 0,-1 0 0 0 0,0 1-1 0 0,28 15 1 0 0,-38-18-398 0 0,0 0 0 0 0,0 0-1 0 0,-1 1 1 0 0,1-1 0 0 0,-1 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,-1 1 1 0 0,1-1 0 0 0,-1 1-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 1-1 0 0,2 8 1 0 0,-3-9-29 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-5 7 0 0 0,-5 8 9 0 0,-16 23 0 0 0,21-34-38 0 0,-5 8 129 0 0,-2 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,-1-1 0 0 0,-1 0 0 0 0,-2-1 1 0 0,2-1-1 0 0,-1 0 0 0 0,-1-2 0 0 0,-28 16 0 0 0,44-27-172 0 0,0 0-1 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,2 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 1 0 0 0,2 0 64 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,2 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,2 0 0 0 0,1 2-11 0 0,2-1-1 0 0,-1 1 0 0 0,0-1 0 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,2-1-1 0 0,-3 0 0 0 0,2 0 0 0 0,9-2 0 0 0,0 0-775 0 0,0-1 0 0 0,-1 0 0 0 0,27-11 0 0 0,-26 7-1328 0 0</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="13">3609 2639 10135 0 0,'-4'8'-27'0'0,"-7"13"2868"0"0,0-4 8068 0 0,23-33-9022 0 0,-1-1-5725 0 0,-7 11 324 0 0,4-8-4392 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="14">3913 2166 1839 0 0,'2'6'12430'0'0,"6"0"-7349"0"0,14 3-4660 0 0,-16-6 723 0 0,28 12-277 0 0,-16-7-571 0 0,0 0 0 0 0,0 1 0 0 0,23 17 0 0 0,-34-21-240 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,5 9 1 0 0,-8-12-31 0 0,0 0 0 0 0,-1 0 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 1 0 0,-1-1-1 0 0,-2 5 0 0 0,1-3-13 0 0,0 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,-8 5 0 0 0,15-10-78 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,1 1-1 0 0,-1-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,-1 1-1 0 0,1 0 1 0 0,0-1-1 0 0,2 4 1 0 0,1 0 92 0 0,0 1 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,0 0 0 0 0,0 11 0 0 0,-1-14 103 0 0,0 1-1 0 0,-1 0 1 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,-6 3 0 0 0,4-2 20 0 0,-1-1-1 0 0,0-1 1 0 0,1 1-1 0 0,-2-1 1 0 0,1 0 0 0 0,0-1-1 0 0,-1 0 1 0 0,1 0-1 0 0,-16 1 1 0 0,23-3-164 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1-319 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 1 0 0 0,1-1-1 0 0,0-1 1 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="15">4460 2197 16527 0 0,'5'-3'512'0'0,"-4"2"-405"0"0,1 0 0 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 1 0 0 0,3 0 0 0 0,11 3 455 0 0,1 1 1 0 0,-1 0-1 0 0,0 1 0 0 0,0 0 0 0 0,18 11 0 0 0,-25-12-480 0 0,-1 1-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-2 1-1 0 0,1 1 1 0 0,-1-1-1 0 0,0 1 1 0 0,10 17-1 0 0,-14-21-81 0 0,-1 0 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-2 0 0 0 0,1-1 1 0 0,0 1-1 0 0,-1 0 0 0 0,0 9 0 0 0,-1-6-8 0 0,0 0 0 0 0,-1-1-1 0 0,0 1 1 0 0,0 0 0 0 0,-1-1-1 0 0,-5 13 1 0 0,0-6-7 0 0,0 0 0 0 0,-1-1 1 0 0,0 0-1 0 0,-1-1 0 0 0,-1 1 0 0 0,-18 16 0 0 0,17-20 62 0 0,0 1 0 0 0,-1-2 0 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,0-1 0 0 0,-28 8 0 0 0,42-14-18 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,1 1 0 0 0,9 7 556 0 0,15 4-185 0 0,-4-6-573 0 0,1 0 0 0 0,0-2 0 0 0,0 0-1 0 0,0-2 1 0 0,0 0 0 0 0,0-1 0 0 0,0-2 0 0 0,42-5-1 0 0,-38 2-747 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="16">10027 3709 7367 0 0,'0'-5'10710'0'0,"1"19"-9886"0"0,1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,1-2 0 0 0,5 15 1 0 0,1 3-128 0 0,1 10-130 0 0,-3 0-1 0 0,0 0 0 0 0,-3 1 1 0 0,-2 0-1 0 0,-2 56 1 0 0,-3-31 225 0 0,-18 111 1 0 0,16-164-605 0 0,0 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,-9 16 0 0 0,8-17-278 0 0,-3 6-1502 0 0,6-3-8306 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="17">9583 5076 9847 0 0,'2'0'8751'0'0,"24"-33"-5081"0"0,-5 12-2802 0 0,0-1 0 0 0,-2-1 0 0 0,0-1-1 0 0,26-45 1 0 0,11-30-144 0 0,-47 85-620 0 0,0 0-1 0 0,0 1 1 0 0,18-19 0 0 0,-27 32-93 0 0,0 0 0 0 0,0 0 0 0 0,1-1 1 0 0,-1 1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,5 12 258 0 0,-1 22-158 0 0,-3-28-94 0 0,7 102 140 0 0,-7 139-1 0 0,-4-104-129 0 0,-9 169 21 0 0,11-310-39 0 0,1-1-1 0 0,0 1 1 0 0,-1-1 0 0 0,1 1-1 0 0,-1-1 1 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 1-1 0 0,-3 3 1 0 0,4-5-3 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,0-1 1 0 0,-1 1-1 0 0,1-1 0 0 0,0 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,-1 0 1 0 0,-1 0-1 0 0,-24-1 249 0 0,0 0 0 0 0,-1-2 0 0 0,-40-10 0 0 0,53 10-154 0 0,0 1-1 0 0,0 0 1 0 0,-26 0 0 0 0,58 4-73 0 0,0 0 0 0 0,22 7 0 0 0,-10-3-19 0 0,265 44 245 0 0,-256-44-236 0 0,21 1 331 0 0,-59-7-346 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,-6-10-874 0 0,2 4-2451 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="18">8519 1923 3223 0 0,'-2'-7'295'0'0,"1"-9"8029"0"0,2 22-3804 0 0,1 13-3094 0 0,0-8-897 0 0,0 25-37 0 0,-2 0 1 0 0,-1 0 0 0 0,-2 0 0 0 0,-1-1-1 0 0,-2 1 1 0 0,-15 51 0 0 0,2-32 352 0 0,-47 98 0 0 0,61-143-677 0 0,4-8-107 0 0,0 0 0 0 0,1 0-1 0 0,-1-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,-1 0-1 0 0,1 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,-3 2 1 0 0,5-3-25 0 0,-1 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-2-1 0 0 0,1 0 10 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-2-3 0 0 0,-2-7 3 0 0,1-1-1 0 0,-1 0 1 0 0,2 0 0 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,1-1 0 0 0,1 1 0 0 0,3-12-1 0 0,6-18 174 0 0,2 1 0 0 0,19-43-1 0 0,-13 37-166 0 0,-5 9-87 0 0,31-55 0 0 0,-39 82 26 0 0,0 1-1 0 0,1-1 1 0 0,1 1-1 0 0,0 1 1 0 0,0-1 0 0 0,1 2-1 0 0,0-1 1 0 0,0 1-1 0 0,16-10 1 0 0,-20 15 6 0 0,1 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 2 0 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,0 0 0 0 0,7 1 0 0 0,-5 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,-1 2 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,6 7 0 0 0,-11-10 10 0 0,-1 1 0 0 0,1-1 1 0 0,-1 1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 5 1 0 0,-1-3 26 0 0,0-1-1 0 0,0 0 1 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-5 9 0 0 0,0-3 34 0 0,0-1 1 0 0,-1 1 0 0 0,-1-1 0 0 0,1 0-1 0 0,-1-1 1 0 0,-1 0 0 0 0,0 0 0 0 0,-13 9-1 0 0,6-6 76 0 0,-1-2 0 0 0,0 0 0 0 0,-1-1 0 0 0,0-1 0 0 0,0-1-1 0 0,-1 0 1 0 0,-36 7 0 0 0,33-12-240 0 0,17-5-580 0 0,12-4-1390 0 0,0 2 989 0 0,-1 1 1 0 0,1 0 0 0 0,12-4-1 0 0,0 0-827 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="19">8852 1953 2303 0 0,'2'15'9706'0'0,"0"-5"-2857"0"0,-1-3-8264 0 0,2 121 5623 0 0,-4-86-3920 0 0,-2 0 1 0 0,-14 66 0 0 0,11-92-91 0 0,5-13-64 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 4-1 0 0,3-16 241 0 0,0 1 0 0 0,0 0 0 0 0,1 0 0 0 0,0 0 0 0 0,6-14 0 0 0,3-5-218 0 0,3-8-98 0 0,27-48 1 0 0,5-7-67 0 0,7-36 7 0 0,-39 99 0 0 0,-14 26 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,2-1 0 0 0,-3 2 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,8 19 0 0 0,-7-15 0 0 0,5 18 52 0 0,-2 1-1 0 0,0-1 1 0 0,-2 1-1 0 0,0 32 1 0 0,-2-30 75 0 0,2 1 0 0 0,1-1 0 0 0,7 33-1 0 0,-10-57-125 0 0,0-1 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,1 1 1 0 0,0-1-1 0 0,-1 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,2-2 0 0 0,18-22 10 0 0,-13 15 1 0 0,1-1 1 0 0,11-10-1 0 0,-17 19-10 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,1 1-1 0 0,4-1 0 0 0,-6 1-1 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 2 0 0 0,2 6 0 0 0,0 0 0 0 0,3 13 0 0 0,-3-12 0 0 0,1 9 75 0 0,3 31-1 0 0,1 6 33 0 0,-7-52-581 0 0,0 0 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,3 7 0 0 0,-4-9 230 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="20">9422 2037 12551 0 0,'10'1'1084'0'0,"0"0"0"0"0,1 1 0 0 0,-1 1 0 0 0,0 0 0 0 0,-1 0-1 0 0,12 6 1 0 0,14 4 281 0 0,-24-10-1085 0 0,0-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1-1 0 0 0,22-2 0 0 0,-15-1-211 0 0,0-1 0 0 0,0 0 0 0 0,0-1-1 0 0,20-9 1 0 0,-30 11-1107 0 0,0 1 1 0 0,14-3-1 0 0,-16 4-641 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="21">9569 2119 15463 0 0,'0'15'1417'0'0,"0"0"-1"0"0,0 0 0 0 0,3 17 0 0 0,0-8-618 0 0,-1-3-385 0 0,-1 1 1 0 0,-1-1-1 0 0,-1 1 1 0 0,-1-1 0 0 0,-5 24-1 0 0,3-29-324 0 0,2-11-439 0 0,0 0 0 0 0,1 1 1 0 0,0-1-1 0 0,0 7 0 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="22">9848 2375 8751 0 0,'-13'27'1524'0'0,"6"-6"3812"0"0,-6 27-1 0 0,5-16-4839 0 0,-47 194 2338 0 0,53-210-2646 0 0,3-10-415 0 0,-1-6 188 0 0,0 0-1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,4-4-1464 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="23">10124 2340 7831 0 0,'5'2'1814'0'0,"-1"0"-1"0"0,0-1 0 0 0,1 0 0 0 0,5 2 0 0 0,38 1 258 0 0,-37-3-1218 0 0,5 0-585 0 0,0-1 0 0 0,0 0 0 0 0,0-1 0 0 0,30-7 0 0 0,0-6-6107 0 0,-26 5-740 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="24">10158 2154 12895 0 0,'-1'0'159'0'0,"1"0"-1"0"0,-1 0 1 0 0,1 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,1-1-1 0 0,0 1 1 0 0,-1-1 0 0 0,1 1-1 0 0,0-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,-1-1-1 0 0,1 1 1 0 0,0 1-1 0 0,1-2 256 0 0,-1 1-1 0 0,1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,2 1-1 0 0,7 3-216 0 0,1 0-1 0 0,-1-1 0 0 0,1-1 0 0 0,0 1 0 0 0,0-2 1 0 0,0 0-1 0 0,17 0 0 0 0,-1-2-1935 0 0,52-8-1 0 0,-48 3-5904 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="25">11029 2002 8751 0 0,'-12'8'1640'0'0,"1"-1"0"0"0,-1 0-1 0 0,0-1 1 0 0,0 0 0 0 0,-1-1-1 0 0,0 0 1 0 0,-14 3 0 0 0,-11 4-1414 0 0,27-9-23 0 0,-13 6 315 0 0,23-9-499 0 0,-1 1 0 0 0,1 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 2-1 0 0,3-1-33 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0-1 0 0,1-1 1 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,2 1 0 0 0,0 1-23 0 0,13 18 49 0 0,-1 1-1 0 0,-1 1 1 0 0,16 36 0 0 0,-29-58 79 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,-1-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,-4 2 1 0 0,-3 1 59 0 0,1 0 0 0 0,-1-1 1 0 0,-1 0-1 0 0,1-1 1 0 0,0 0-1 0 0,-1 0 0 0 0,1-1 1 0 0,-1-1-1 0 0,0 1 0 0 0,0-1 1 0 0,1-1-1 0 0,-1 0 0 0 0,0 0 1 0 0,0-1-1 0 0,0 0 0 0 0,-10-3 1 0 0,10-1-2536 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="26">10937 1842 9671 0 0,'-1'0'87'0'0,"0"0"1"0"0,1 0-1 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 1 0 0,0-1-1 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,-3 15 5814 0 0,3-12-4844 0 0,-5 47 2118 0 0,1 92 0 0 0,6-97-3046 0 0,-3 1 0 0 0,-12 79 0 0 0,-11-30 159 0 0,-4 20 192 0 0,28-105-1252 0 0,9-18-2784 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="14">3913 2166 1839 0 0,'2'6'12430'0'0,"6"0"-7349"0"0,15 3-4660 0 0,-18-6 723 0 0,29 12-277 0 0,-16-7-571 0 0,0 0 0 0 0,0 1 0 0 0,23 17 0 0 0,-34-21-240 0 0,-1 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-2 1 0 0 0,0 0 0 0 0,0 0 0 0 0,5 9 1 0 0,-8-12-31 0 0,0 0 0 0 0,-1 0 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,2 0 1 0 0,-2 1-1 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 1 0 0 0,-2-1 0 0 0,2 1 1 0 0,0-1-1 0 0,-3 5 0 0 0,1-3-13 0 0,0 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,-8 5 0 0 0,15-10-78 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,1 1-1 0 0,-1-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,-1 1-1 0 0,1 0 1 0 0,0-1-1 0 0,2 4 1 0 0,1 0 92 0 0,0 1 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,-2 0 0 0 0,1-1 1 0 0,-1 1-1 0 0,0 0 0 0 0,0 11 0 0 0,-1-14 103 0 0,0 1-1 0 0,-1 0 1 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-6 3 0 0 0,4-2 20 0 0,-1-1-1 0 0,0-1 1 0 0,1 1-1 0 0,-2-1 1 0 0,1 0 0 0 0,0-1-1 0 0,-1 0 1 0 0,1 0-1 0 0,-16 1 1 0 0,23-3-164 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1-319 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 1 0 0 0,1-1-1 0 0,0-1 1 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="15">4460 2197 16527 0 0,'5'-3'512'0'0,"-4"2"-405"0"0,1 0 0 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 1 0 0 0,3 0 0 0 0,11 3 455 0 0,1 1 1 0 0,-1 0-1 0 0,0 1 0 0 0,1 0 0 0 0,16 11 0 0 0,-24-12-480 0 0,-1 1-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-2 1-1 0 0,1 1 1 0 0,-1-1-1 0 0,0 1 1 0 0,10 17-1 0 0,-14-21-81 0 0,-1 0 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-2 0 0 0 0,1-1 1 0 0,0 1-1 0 0,-1 0 0 0 0,0 9 0 0 0,-1-6-8 0 0,0 0 0 0 0,-1-1-1 0 0,0 1 1 0 0,0 0 0 0 0,-1-1-1 0 0,-5 13 1 0 0,0-6-7 0 0,0 0 0 0 0,-1-1 1 0 0,0 0-1 0 0,-1-1 0 0 0,-1 1 0 0 0,-18 16 0 0 0,17-20 62 0 0,0 1 0 0 0,-1-2 0 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,0-1 0 0 0,-28 8 0 0 0,42-14-18 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,1 1 0 0 0,9 7 556 0 0,15 4-185 0 0,-4-6-573 0 0,1 0 0 0 0,0-2 0 0 0,0 0-1 0 0,0-2 1 0 0,0 0 0 0 0,0-1 0 0 0,0-2 0 0 0,42-5-1 0 0,-38 2-747 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="16">10027 3709 7367 0 0,'0'-5'10710'0'0,"1"19"-9886"0"0,1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,1-2 0 0 0,5 15 1 0 0,1 3-128 0 0,2 10-130 0 0,-5 0-1 0 0,1 0 0 0 0,-3 1 1 0 0,-2 0-1 0 0,-2 56 1 0 0,-3-31 225 0 0,-18 111 1 0 0,16-164-605 0 0,0 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,-9 16 0 0 0,8-17-278 0 0,-2 6-1502 0 0,4-3-8306 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="17">9583 5076 9847 0 0,'2'0'8751'0'0,"24"-33"-5081"0"0,-5 12-2802 0 0,0-1 0 0 0,-2-1 0 0 0,0-1-1 0 0,26-45 1 0 0,11-30-144 0 0,-47 85-620 0 0,0 0-1 0 0,0 1 1 0 0,18-19 0 0 0,-27 32-93 0 0,0 0 0 0 0,0 0 0 0 0,1-1 1 0 0,-1 1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,4 12 258 0 0,1 22-158 0 0,-4-28-94 0 0,7 102 140 0 0,-7 139-1 0 0,-4-104-129 0 0,-9 169 21 0 0,11-310-39 0 0,1-1-1 0 0,0 1 1 0 0,-1-1 0 0 0,1 1-1 0 0,-1-1 1 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 1-1 0 0,-3 3 1 0 0,4-5-3 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,0-1 1 0 0,-1 1-1 0 0,1-1 0 0 0,0 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,0 0 1 0 0,-3 0-1 0 0,-23-1 249 0 0,0 0 0 0 0,-1-2 0 0 0,-40-10 0 0 0,53 10-154 0 0,0 1-1 0 0,0 0 1 0 0,-26 0 0 0 0,58 4-73 0 0,0 0 0 0 0,22 7 0 0 0,-10-3-19 0 0,265 44 245 0 0,-256-44-236 0 0,21 1 331 0 0,-59-7-346 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,-6-10-874 0 0,2 4-2451 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="18">8519 1923 3223 0 0,'-2'-7'295'0'0,"1"-9"8029"0"0,2 22-3804 0 0,1 13-3094 0 0,1-8-897 0 0,-2 25-37 0 0,-1 0 1 0 0,-1 0 0 0 0,-2 0 0 0 0,-1-1-1 0 0,-2 1 1 0 0,-15 51 0 0 0,2-32 352 0 0,-47 98 0 0 0,61-143-677 0 0,3-8-107 0 0,2 0 0 0 0,0 0-1 0 0,-1-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,-1 0-1 0 0,1 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,-1 0 0 0 0,-1 0-1 0 0,-1 2 1 0 0,4-3-25 0 0,-1 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,-1 0 10 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-2-3 0 0 0,-2-7 3 0 0,1-1-1 0 0,-1 0 1 0 0,2 0 0 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,1-1 0 0 0,1 1 0 0 0,3-12-1 0 0,6-18 174 0 0,2 1 0 0 0,19-43-1 0 0,-12 37-166 0 0,-7 9-87 0 0,32-55 0 0 0,-39 82 26 0 0,0 1-1 0 0,1-1 1 0 0,1 1-1 0 0,0 1 1 0 0,0-1 0 0 0,1 2-1 0 0,0-1 1 0 0,0 1-1 0 0,16-10 1 0 0,-20 15 6 0 0,1 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 2 0 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1 0 0 0 0,7 1 0 0 0,-5 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,-1 2 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,6 7 0 0 0,-11-10 10 0 0,-1 1 0 0 0,1-1 1 0 0,-1 1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,-1 1-1 0 0,2-1 0 0 0,-3 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 5 1 0 0,-1-3 26 0 0,0-1-1 0 0,0 0 1 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-5 9 0 0 0,0-3 34 0 0,0-1 1 0 0,-1 1 0 0 0,-2-1 0 0 0,3 0-1 0 0,-2-1 1 0 0,-1 0 0 0 0,0 0 0 0 0,-13 9-1 0 0,5-6 76 0 0,1-2 0 0 0,-1 0 0 0 0,-1-1 0 0 0,0-1 0 0 0,0-1-1 0 0,-2 0 1 0 0,-34 7 0 0 0,32-12-240 0 0,17-5-580 0 0,12-4-1390 0 0,0 2 989 0 0,-1 1 1 0 0,1 0 0 0 0,13-4-1 0 0,-2 0-827 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="19">8852 1953 2303 0 0,'2'15'9706'0'0,"0"-5"-2857"0"0,-1-3-8264 0 0,1 121 5623 0 0,-2-86-3920 0 0,-3 0 1 0 0,-14 66 0 0 0,11-92-91 0 0,5-13-64 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 4-1 0 0,3-16 241 0 0,0 1 0 0 0,0 0 0 0 0,1 0 0 0 0,0 0 0 0 0,6-14 0 0 0,3-5-218 0 0,3-8-98 0 0,27-48 1 0 0,5-7-67 0 0,7-36 7 0 0,-39 99 0 0 0,-14 26 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,-1 1 0 0 0,2-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,2-1 0 0 0,-2 2 0 0 0,-2 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,8 19 0 0 0,-7-15 0 0 0,5 18 52 0 0,-2 1-1 0 0,0-1 1 0 0,-2 1-1 0 0,0 32 1 0 0,-2-30 75 0 0,2 1 0 0 0,1-1 0 0 0,6 33-1 0 0,-9-57-125 0 0,0-1 0 0 0,0 0-1 0 0,2 0 1 0 0,-2 0-1 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,1 1 1 0 0,0-1-1 0 0,-1 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 1 0 0 0,3-1 0 0 0,-2 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,2-2 0 0 0,18-22 10 0 0,-13 15 1 0 0,1-1 1 0 0,11-10-1 0 0,-17 19-10 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,2 0 0 0 0,-2 0 1 0 0,1 1-1 0 0,4-1 0 0 0,-6 1-1 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-2 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 2 0 0 0,2 6 0 0 0,0 0 0 0 0,2 13 0 0 0,-1-12 0 0 0,0 9 75 0 0,3 31-1 0 0,1 6 33 0 0,-7-52-581 0 0,0 0 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,3 7 0 0 0,-5-9 230 0 0,2 0 0 0 0,-2 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,2 1 0 0 0,-3-1 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="20">9422 2037 12551 0 0,'10'1'1084'0'0,"0"0"0"0"0,1 1 0 0 0,-1 1 0 0 0,0 0 0 0 0,-1 0-1 0 0,12 6 1 0 0,14 4 281 0 0,-24-10-1085 0 0,0-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1-1 0 0 0,22-2 0 0 0,-15-1-211 0 0,0-1 0 0 0,0 0 0 0 0,0-1-1 0 0,20-9 1 0 0,-31 11-1107 0 0,2 1 1 0 0,13-3-1 0 0,-16 4-641 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="21">9569 2119 15463 0 0,'0'15'1417'0'0,"0"0"-1"0"0,0 0 0 0 0,2 17 0 0 0,2-8-618 0 0,-2-3-385 0 0,-1 1 1 0 0,-1-1-1 0 0,-1 1 1 0 0,-1-1 0 0 0,-5 24-1 0 0,3-29-324 0 0,2-11-439 0 0,0 0 0 0 0,1 1 1 0 0,0-1-1 0 0,0 7 0 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="22">9848 2375 8751 0 0,'-13'27'1524'0'0,"6"-6"3812"0"0,-6 27-1 0 0,5-16-4839 0 0,-47 194 2338 0 0,52-210-2646 0 0,5-10-415 0 0,-2-6 188 0 0,0 0-1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,4-4-1464 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="23">10123 2340 7831 0 0,'6'2'1814'0'0,"-2"0"-1"0"0,0-1 0 0 0,0 0 0 0 0,7 2 0 0 0,37 1 258 0 0,-37-3-1218 0 0,5 0-585 0 0,0-1 0 0 0,0 0 0 0 0,0-1 0 0 0,30-7 0 0 0,0-6-6107 0 0,-26 5-740 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="24">10158 2154 12895 0 0,'-1'0'159'0'0,"1"0"-1"0"0,-1 0 1 0 0,1 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,1-1-1 0 0,0 1 1 0 0,-1-1 0 0 0,1 1-1 0 0,0-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,-1-1-1 0 0,1 1 1 0 0,0 1-1 0 0,1-2 256 0 0,-1 1-1 0 0,1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,1-1 1 0 0,-2 1-1 0 0,1-1 1 0 0,2 1-1 0 0,7 3-216 0 0,1 0-1 0 0,0-1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-2 1 0 0,0 0-1 0 0,17 0 0 0 0,-1-2-1935 0 0,53-8-1 0 0,-50 3-5904 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="25">11029 2002 8751 0 0,'-12'8'1640'0'0,"1"-1"0"0"0,-1 0-1 0 0,0-1 1 0 0,0 0 0 0 0,-1-1-1 0 0,0 0 1 0 0,-14 3 0 0 0,-11 4-1414 0 0,27-9-23 0 0,-13 6 315 0 0,23-9-499 0 0,-1 1 0 0 0,1 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,1 0-1 0 0,-2-1 1 0 0,1 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 2-1 0 0,3-1-33 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0-1 0 0,1-1 1 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,2 1 0 0 0,0 1-23 0 0,13 18 49 0 0,-1 1-1 0 0,-1 1 1 0 0,16 36 0 0 0,-29-58 79 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,-1-1 1 0 0,2 1-1 0 0,-2-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,-2 1-1 0 0,2 0 1 0 0,-1-1-1 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-2 0 1 0 0,1-1-1 0 0,0 1 0 0 0,-4 2 1 0 0,-3 1 59 0 0,1 0 0 0 0,-1-1 1 0 0,-1 0-1 0 0,1-1 1 0 0,0 0-1 0 0,-1 0 0 0 0,1-1 1 0 0,-1-1-1 0 0,0 1 0 0 0,0-1 1 0 0,0-1-1 0 0,1 0 0 0 0,-1 0 1 0 0,0-1-1 0 0,0 0 0 0 0,-10-3 1 0 0,10-1-2536 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="26">10937 1842 9671 0 0,'-1'0'87'0'0,"0"0"1"0"0,1 0-1 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 1 0 0,0-1-1 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 1 1 0 0,0-1-1 0 0,0 0 0 0 0,-2 1 0 0 0,2-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,-3 15 5814 0 0,3-12-4844 0 0,-5 47 2118 0 0,1 92 0 0 0,7-97-3046 0 0,-5 1 0 0 0,-11 79 0 0 0,-11-30 159 0 0,-4 20 192 0 0,29-105-1252 0 0,7-18-2784 0 0</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="27">11436 2042 2303 0 0,'-4'2'6550'0'0,"4"-1"-6411"0"0,-7 10 7159 0 0,1 4-2190 0 0,1-3-4989 0 0,4-11-230 0 0,-35 102 3426 0 0,2-1-2288 0 0,-9 14-582 0 0,39-101-620 0 0,1 0-1 0 0,0 0 0 0 0,0 1 0 0 0,2-1 1 0 0,0 31-1 0 0,2-38-972 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="28">11560 2084 7831 0 0,'-9'41'3049'0'0,"-4"54"-1"0"0,11-67-2316 0 0,2 0 0 0 0,5 52-1 0 0,-4-72-667 0 0,0 0 0 0 0,1 0 0 0 0,0-1-1 0 0,4 10 1 0 0,-5-14-51 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,3 1-1 0 0,-3-1 24 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,-1 1 1 0 0,1 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,0 0-1 0 0,-1 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,-1 0-1 0 0,0-1 1 0 0,0 1-1 0 0,2-3 0 0 0,4-6 335 0 0,-1 1 0 0 0,8-17 0 0 0,-13 25-324 0 0,4-9 362 0 0,0 1 1 0 0,-1-1 0 0 0,0-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,2-20 0 0 0,-3 25-136 0 0,-1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-2-1 0 0 0,1 0-1 0 0,-1 1 1 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-6-6 0 0 0,-21-18 917 0 0,23 23-984 0 0,-1-1-1 0 0,-8-10 0 0 0,16 17-247 0 0,-1-1 0 0 0,1 1 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0 0 0 0,0-1-1 0 0,-1 1 1 0 0,1-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1 0 0 0,0 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1-1 0 0,1 0 1 0 0,-1-1 0 0 0,0 1 0 0 0,0 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,0 0 0 0 0,1 0-1 0 0,-1-1 1 0 0,0 1 0 0 0,1 0 0 0 0,-1 0-1 0 0,0-1 1 0 0,1 1 0 0 0,-1 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1-1-1 0 0,20-6-3716 0 0,-11 4 1855 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="29">11869 2202 8287 0 0,'2'10'957'0'0,"0"0"-1"0"0,1-1 0 0 0,1 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 0 1 0 0,1 0-1 0 0,1-1 0 0 0,-1 0 1 0 0,10 10-1 0 0,-12-14-817 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,5 0 0 0 0,-7 0-47 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,0-1 0 0 0,2-3 0 0 0,-3 4 50 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-2-3 0 0 0,-6-7 427 0 0,-1 1 0 0 0,-23-19-1 0 0,21 19-150 0 0,0 0 0 0 0,-12-16 0 0 0,22 25-835 0 0,-6-9-3323 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="28">11560 2084 7831 0 0,'-9'41'3049'0'0,"-4"54"-1"0"0,11-67-2316 0 0,2 0 0 0 0,5 52-1 0 0,-4-72-667 0 0,0 0 0 0 0,1 0 0 0 0,0-1-1 0 0,4 10 1 0 0,-5-14-51 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,2 0 1 0 0,-3 0-1 0 0,2-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,3 1-1 0 0,-3-1 24 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,-1 1 1 0 0,1 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,0 0-1 0 0,-1 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1-1 1 0 0,-2 1-1 0 0,3 0 1 0 0,-2 0-1 0 0,0-1 1 0 0,0 1-1 0 0,2-3 0 0 0,4-6 335 0 0,-1 1 0 0 0,9-17 0 0 0,-15 25-324 0 0,5-9 362 0 0,0 1 1 0 0,-1-1 0 0 0,0-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,2-20 0 0 0,-3 25-136 0 0,-1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-2-1 0 0 0,1 0-1 0 0,-1 1 1 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-6-6 0 0 0,-21-18 917 0 0,23 23-984 0 0,-1-1-1 0 0,-8-10 0 0 0,16 17-247 0 0,-1-1 0 0 0,1 1 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0 0 0 0,0-1-1 0 0,-1 1 1 0 0,1-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1 0 0 0,0 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1-1 0 0,1 0 1 0 0,-1-1 0 0 0,0 1 0 0 0,0 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,0 0 0 0 0,1 0-1 0 0,-1-1 1 0 0,0 1 0 0 0,1 0 0 0 0,-1 0-1 0 0,0-1 1 0 0,1 1 0 0 0,-1 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1-1-1 0 0,20-6-3716 0 0,-11 4 1855 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="29">11868 2202 8287 0 0,'3'10'957'0'0,"-1"0"-1"0"0,1-1 0 0 0,1 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 0 1 0 0,1 0-1 0 0,1-1 0 0 0,-1 0 1 0 0,10 10-1 0 0,-12-14-817 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,1 0 0 0 0,-2 0 0 0 0,1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,5 0 0 0 0,-7 0-47 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-2-1 1 0 0,1 1-1 0 0,0-1 0 0 0,2-3 0 0 0,-3 4 50 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-2-3 0 0 0,-6-7 427 0 0,-1 1 0 0 0,-23-19-1 0 0,21 19-150 0 0,0 0 0 0 0,-12-16 0 0 0,22 25-835 0 0,-6-9-3323 0 0</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="30">17462 3805 14455 0 0,'2'-5'1460'0'0,"1"9"28"0"0,2 8 716 0 0,-1 6-1303 0 0,-1 1-1 0 0,0-1 1 0 0,-2 0-1 0 0,0 26 1 0 0,-10 75 494 0 0,5-75-918 0 0,-27 294 1656 0 0,30-307-1810 0 0,3 36-1 0 0,0-9-327 0 0,-2-58-217 0 0,1 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,-1-1 1 0 0,1 1 0 0 0,0 0-1 0 0,-1 0 1 0 0,1-1-1 0 0,-1 1 1 0 0,2-1 0 0 0,2-1-1752 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="31">16917 5270 7367 0 0,'0'-1'389'0'0,"1"0"0"0"0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,0 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,1 0 0 0 0,21-7 2454 0 0,-11 6-2595 0 0,-1 0-1 0 0,1 1 1 0 0,-1 0 0 0 0,1 0 0 0 0,0 2-1 0 0,-1-1 1 0 0,1 1 0 0 0,-1 1 0 0 0,1 0-1 0 0,-1 1 1 0 0,0 0 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0-1 0 0,0 2 1 0 0,11 6 0 0 0,-5-1 110 0 0,0 1 0 0 0,-1 0 0 0 0,0 1-1 0 0,-1 1 1 0 0,0 0 0 0 0,-1 1 0 0 0,-1 0 0 0 0,17 26 0 0 0,-24-31-386 0 0,1 1-1 0 0,-1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 1-1 0 0,-1 0 1 0 0,2 12-1 0 0,-5-18 28 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-2 0 0 0 0,1 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,0-1 0 0 0,-1 1-1 0 0,0-1 1 0 0,-4 6 0 0 0,5-7 20 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-2 1 0 0,-1 1-1 0 0,1 0 0 0 0,-6 0 0 0 0,-21 12 30 0 0,28-12-44 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0-1 1 0 0,0 0-1 0 0,-1 1 1 0 0,1-1-1 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 1 0 0,-1-1-1 0 0,0 0 1 0 0,-6 0-1 0 0,3-1-5 0 0,-18-3-1 0 0,24 4 3 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,2 0 5 0 0,-1-1 0 0 0,1 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1-1 0 0,-1 0 1 0 0,1 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,0-1-1 0 0,1 1 1 0 0,8 14 138 0 0,-6-11-118 0 0,7 8 6 0 0,1 1 0 0 0,1-2 1 0 0,0 1-1 0 0,0-2 0 0 0,1 1 0 0 0,1-2 0 0 0,-1 0 1 0 0,1 0-1 0 0,1-2 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 1 0 0,22 5-1 0 0,-26-9-32 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,-1 0-1 0 0,1-1 1 0 0,13-2 0 0 0,-3-1-447 0 0,0-2-1 0 0,32-12 0 0 0,-15 3-355 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="32">17866 2105 10135 0 0,'3'1'560'0'0,"0"-1"-1"0"0,0 1 1 0 0,0-1-1 0 0,1 1 0 0 0,-1-1 1 0 0,0 0-1 0 0,0-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,0-1 1 0 0,0 0-1 0 0,4-1 0 0 0,6 0 1407 0 0,13-1-748 0 0,-9 2-304 0 0,31-7-1 0 0,-44 7-1020 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,4-5 1 0 0,0-2-808 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="33">17923 1881 10135 0 0,'-32'8'1096'0'0,"32"-8"-1057"0"0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,6 5 4402 0 0,9 0 2219 0 0,-1-2-6452 0 0,1-2 0 0 0,-1 1 0 0 0,0-2 0 0 0,15-1 0 0 0,58-8-1172 0 0,-69 7 295 0 0,15-3-1101 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="34">15865 1646 12239 0 0,'-7'96'6219'0'0,"2"-9"-4844"0"0,-10 122 208 0 0,9-150-1023 0 0,-23 88 1 0 0,28-144-533 0 0,-1 7 147 0 0,-1 1 1 0 0,-1 0-1 0 0,1-1 0 0 0,-2 1 0 0 0,1-1 0 0 0,-9 13 0 0 0,12-23-152 0 0,1 1 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 1 0 0,-1 0-1 0 0,1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0-1 5 0 0,1 1 0 0 0,-1 0 1 0 0,1-1-1 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,-1-1 1 0 0,1 1-1 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 1 0 0,0 1-1 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 1 0 0,0 0-1 0 0,-3-28 429 0 0,5 3-407 0 0,1 0 1 0 0,1 0 0 0 0,1 0-1 0 0,10-28 1 0 0,4-20 1 0 0,-12 39-53 0 0,3-14-11 0 0,1 1 1 0 0,20-50-1 0 0,-25 85 10 0 0,-1-1-1 0 0,2 1 1 0 0,0 0 0 0 0,0 1-1 0 0,1 0 1 0 0,1 0 0 0 0,0 0-1 0 0,0 1 1 0 0,1 1 0 0 0,1 0-1 0 0,20-16 1 0 0,-28 24 2 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,7 2 0 0 0,-3-1 0 0 0,-1 1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,-1 1 0 0 0,1 0 0 0 0,6 6 0 0 0,-11-10 9 0 0,-1 0 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 1 0 0,1 0-1 0 0,-1 1 0 0 0,0-1 1 0 0,-1 1-1 0 0,1-1 0 0 0,0 1 1 0 0,0 0-1 0 0,-1-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,1-1 0 0 0,-1 1 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 2 1 0 0,-1-2 23 0 0,1 0-1 0 0,-1 1 1 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 0 0 0 0,-2 3 0 0 0,-2 1 64 0 0,0-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,0-1 1 0 0,-1 0-1 0 0,-7 4 0 0 0,1-2 27 0 0,1-1-1 0 0,-1-1 1 0 0,-1 0-1 0 0,1 0 1 0 0,0-1-1 0 0,-1-1 0 0 0,1-1 1 0 0,-1 0-1 0 0,0-1 1 0 0,1 0-1 0 0,-1-1 1 0 0,0-1-1 0 0,-17-4 0 0 0,36 4-2392 0 0,5 1 1256 0 0,6 1-799 0 0,3 0-335 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="35">16345 1664 13183 0 0,'0'0'152'0'0,"0"-1"0"0"0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 5 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1 21 409 0 0,0 0 1 0 0,-2 0 0 0 0,0 0 0 0 0,-2 0 0 0 0,-5 22-1 0 0,0 4-317 0 0,-4 32-71 0 0,-4 0 0 0 0,-31 88 0 0 0,29-127 180 0 0,20-88 502 0 0,38-130-674 0 0,-22 109-179 0 0,-14 52-7 0 0,35-123 0 0 0,-31 116 0 0 0,1 0 0 0 0,1 0 0 0 0,23-37 0 0 0,-31 56 0 0 0,1 0 0 0 0,0 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,7-5 0 0 0,-9 8 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1 1 0 0 0,4 8 10 0 0,0 0 1 0 0,0 1-1 0 0,-1-1 0 0 0,-1 1 0 0 0,1 0 1 0 0,-2 1-1 0 0,3 21 0 0 0,-3 2 35 0 0,-3 44-1 0 0,-1-50-3 0 0,2 0-1 0 0,5 48 0 0 0,-5-76-37 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 1 0 0,0 0-1 0 0,0 0 0 0 0,-1-1-3 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,1-1 0 0 0,-1 1 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0-1 0 0 0,0 1 1 0 0,1 0-1 0 0,-1 0 0 0 0,0-1 1 0 0,0 1-1 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 0 0 0,4-6-4 0 0,-1 1 0 0 0,0-1 0 0 0,3-7-1 0 0,-5 13 5 0 0,8-22-6 0 0,6-12-10 0 0,21-36 1 0 0,-30 60 13 0 0,0 0 0 0 0,1 1 1 0 0,0 0-1 0 0,0 0 0 0 0,1 1 0 0 0,0 0 1 0 0,1 1-1 0 0,10-8 0 0 0,-18 14 1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 1 0 0 0,2 6-4 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1-1 0 0,-1 0 1 0 0,0 9 0 0 0,1 88 35 0 0,-2-65-14 0 0,1 1-1 0 0,9 53 0 0 0,-9-90-495 0 0,4 19 1078 0 0,0-12-3090 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="36">16838 1761 11975 0 0,'66'2'9639'0'0,"46"-2"-6143"0"0,-24-11-1911 0 0,-55 6-1271 0 0,47-2 0 0 0,-77 7-403 0 0,0 1-1 0 0,-1-1 1 0 0,1 0-1 0 0,0 0 1 0 0,-1 1-1 0 0,1 0 1 0 0,0-1-1 0 0,2 2 1 0 0,-4-1-118 0 0,0-1 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 1 1 0 0,0-1-1 0 0,0 1 0 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 1 0 0,-1 0-1 0 0,1 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0 2 1 0 0,-1 2-1581 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="31">16917 5270 7367 0 0,'0'-1'389'0'0,"1"0"0"0"0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,0 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0-1 0 0,2 1 1 0 0,-1-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,1 0 0 0 0,21-7 2454 0 0,-11 6-2595 0 0,-1 0-1 0 0,1 1 1 0 0,-1 0 0 0 0,1 0 0 0 0,0 2-1 0 0,-1-1 1 0 0,1 1 0 0 0,-1 1 0 0 0,1 0-1 0 0,-1 1 1 0 0,0 0 0 0 0,-1 1 0 0 0,2 0 0 0 0,-1 0-1 0 0,0 2 1 0 0,11 6 0 0 0,-5-1 110 0 0,-1 1 0 0 0,1 0 0 0 0,-1 1-1 0 0,-1 1 1 0 0,0 0 0 0 0,-1 1 0 0 0,-2 0 0 0 0,19 26 0 0 0,-26-31-386 0 0,3 1-1 0 0,-2 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 1-1 0 0,-1 0 1 0 0,2 12-1 0 0,-5-18 28 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-2 0 0 0 0,1 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,-1 0 0 0 0,2 0-1 0 0,-3 0 1 0 0,1 0 0 0 0,0-1 0 0 0,-1 1-1 0 0,0-1 1 0 0,-4 6 0 0 0,5-7 20 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-2 1 0 0,-1 1-1 0 0,1 0 0 0 0,-6 0 0 0 0,-21 12 30 0 0,28-12-44 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0-1 1 0 0,0 0-1 0 0,-1 1 1 0 0,1-1-1 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 1 0 0,-1-1-1 0 0,0 0 1 0 0,-6 0-1 0 0,3-1-5 0 0,-18-3-1 0 0,24 4 3 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-3 0 0 0 0,2 0 0 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,2 0 5 0 0,-2-1 0 0 0,2 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1-1 0 0,2 1 1 0 0,7 14 138 0 0,-6-11-118 0 0,7 8 6 0 0,1 1 0 0 0,1-2 1 0 0,0 1-1 0 0,0-2 0 0 0,1 1 0 0 0,1-2 0 0 0,-1 0 1 0 0,2 0-1 0 0,-1-2 0 0 0,1 0 0 0 0,0 0 0 0 0,0-1 1 0 0,22 5-1 0 0,-26-9-32 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,-2 0-1 0 0,3-1 1 0 0,13-2 0 0 0,-5-1-447 0 0,1-2-1 0 0,32-12 0 0 0,-15 3-355 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="32">17866 2105 10135 0 0,'3'1'560'0'0,"0"-1"-1"0"0,0 1 1 0 0,0-1-1 0 0,1 1 0 0 0,-1-1 1 0 0,0 0-1 0 0,0-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,0-1 1 0 0,0 0-1 0 0,4-1 0 0 0,6 0 1407 0 0,13-1-748 0 0,-9 2-304 0 0,31-7-1 0 0,-44 7-1020 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,5-5 1 0 0,-2-2-808 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="33">17924 1881 10135 0 0,'-33'8'1096'0'0,"33"-8"-1057"0"0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,6 5 4402 0 0,9 0 2219 0 0,0-2-6452 0 0,-1-2 0 0 0,0 1 0 0 0,0-2 0 0 0,15-1 0 0 0,58-8-1172 0 0,-69 7 295 0 0,15-3-1101 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="34">15865 1646 12239 0 0,'-7'96'6219'0'0,"2"-9"-4844"0"0,-10 122 208 0 0,9-150-1023 0 0,-23 88 1 0 0,28-144-533 0 0,-1 7 147 0 0,-1 1 1 0 0,-1 0-1 0 0,1-1 0 0 0,-2 1 0 0 0,1-1 0 0 0,-8 13 0 0 0,10-23-152 0 0,2 1 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 1 0 0,-1 0-1 0 0,1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0-1 5 0 0,1 1 0 0 0,-1 0 1 0 0,1-1-1 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,-1-1 1 0 0,1 1-1 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 1 0 0,0 1-1 0 0,0-1 0 0 0,-2 1 0 0 0,2-1 0 0 0,0 0 1 0 0,0 0-1 0 0,-2-28 429 0 0,4 3-407 0 0,1 0 1 0 0,1 0 0 0 0,1 0-1 0 0,10-28 1 0 0,4-20 1 0 0,-12 39-53 0 0,3-14-11 0 0,1 1 1 0 0,20-50-1 0 0,-25 85 10 0 0,-1-1-1 0 0,2 1 1 0 0,0 0 0 0 0,0 1-1 0 0,1 0 1 0 0,1 0 0 0 0,0 0-1 0 0,0 1 1 0 0,1 1 0 0 0,1 0-1 0 0,20-16 1 0 0,-28 24 2 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,2 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,7 2 0 0 0,-3-1 0 0 0,-1 1 0 0 0,0 1 0 0 0,1-1 0 0 0,-2 1 0 0 0,2 0 0 0 0,-2 1 0 0 0,1 0 0 0 0,6 6 0 0 0,-11-10 9 0 0,-2 0 1 0 0,2 0-1 0 0,-1 1 0 0 0,0-1 1 0 0,1 0-1 0 0,-1 1 0 0 0,0-1 1 0 0,-1 1-1 0 0,1-1 0 0 0,0 1 1 0 0,0 0-1 0 0,-1-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,1-1 0 0 0,-1 1 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 2 1 0 0,-1-2 23 0 0,1 0-1 0 0,-1 1 1 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 0 0 0 0,-2 3 0 0 0,-2 1 64 0 0,0-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,0-1 1 0 0,-1 0-1 0 0,-7 4 0 0 0,1-2 27 0 0,1-1-1 0 0,-1-1 1 0 0,-1 0-1 0 0,1 0 1 0 0,0-1-1 0 0,-1-1 0 0 0,1-1 1 0 0,-1 0-1 0 0,0-1 1 0 0,1 0-1 0 0,-1-1 1 0 0,0-1-1 0 0,-17-4 0 0 0,36 4-2392 0 0,5 1 1256 0 0,6 1-799 0 0,3 0-335 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="35">16345 1664 13183 0 0,'0'0'152'0'0,"0"-1"0"0"0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 5 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,2 1 0 0 0,-2-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1 21 409 0 0,0 0 1 0 0,-2 0 0 0 0,0 0 0 0 0,-2 0 0 0 0,-5 22-1 0 0,0 4-317 0 0,-4 32-71 0 0,-4 0 0 0 0,-31 88 0 0 0,29-127 180 0 0,20-88 502 0 0,38-130-674 0 0,-22 109-179 0 0,-14 52-7 0 0,35-123 0 0 0,-31 116 0 0 0,1 0 0 0 0,1 0 0 0 0,24-37 0 0 0,-33 56 0 0 0,2 0 0 0 0,0 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,7-5 0 0 0,-9 8 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1 0 0 0 0,-2 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,0-1 0 0 0,2 1 0 0 0,-2 0 0 0 0,1 1 0 0 0,4 8 10 0 0,0 0 1 0 0,0 1-1 0 0,-1-1 0 0 0,-1 1 0 0 0,1 0 1 0 0,-2 1-1 0 0,4 21 0 0 0,-5 2 35 0 0,-2 44-1 0 0,-1-50-3 0 0,2 0-1 0 0,5 48 0 0 0,-5-76-37 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 1 0 0,0 0-1 0 0,0 0 0 0 0,-1-1-3 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,1-1 0 0 0,-1 1 1 0 0,0 0-1 0 0,2 0 1 0 0,-2 0-1 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 0 0 0,4-6-4 0 0,-1 1 0 0 0,0-1 0 0 0,4-7-1 0 0,-7 13 5 0 0,9-22-6 0 0,6-12-10 0 0,21-36 1 0 0,-30 60 13 0 0,0 0 0 0 0,1 1 1 0 0,0 0-1 0 0,0 0 0 0 0,1 1 0 0 0,0 0 1 0 0,1 1-1 0 0,10-8 0 0 0,-18 14 1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 1 0 0 0,2-1 0 0 0,-1 0 1 0 0,0 1-1 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 1 0 0,0 0-1 0 0,1 0 0 0 0,0 0 0 0 0,-2 0 0 0 0,1 0 1 0 0,1 0-1 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1 0 1 0 0,-2 0-1 0 0,1-1 0 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 1 0 0 0,2 6-4 0 0,-1-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,2 1-1 0 0,-2 0 1 0 0,0 9 0 0 0,1 88 35 0 0,-2-65-14 0 0,1 1-1 0 0,9 53 0 0 0,-10-90-495 0 0,6 19 1078 0 0,-1-12-3090 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="36">16838 1761 11975 0 0,'66'2'9639'0'0,"46"-2"-6143"0"0,-25-11-1911 0 0,-53 6-1271 0 0,46-2 0 0 0,-77 7-403 0 0,0 1-1 0 0,-1-1 1 0 0,1 0-1 0 0,0 0 1 0 0,-1 1-1 0 0,1 0 1 0 0,0-1-1 0 0,2 2 1 0 0,-4-1-118 0 0,1-1 1 0 0,-2 1-1 0 0,0-1 0 0 0,1 1 1 0 0,0-1-1 0 0,0 1 0 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 1 0 0,-1 0-1 0 0,1 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0 2 1 0 0,-1 2-1581 0 0</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="37">17116 1793 5527 0 0,'-3'8'819'0'0,"-3"3"5560"0"0,0 2 121 0 0,3-4-6834 0 0,-8 32 2536 0 0,3 0-1 0 0,-6 71 1 0 0,4-24-976 0 0,6-62-952 0 0,-9 51 113 0 0,13-77-422 0 0,0-1 0 0 0,0 1-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,8-7-2066 0 0,-8 6 1736 0 0,6-5-1396 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="38">17244 2104 6911 0 0,'8'8'2143'0'0,"1"1"-1"0"0,0-1 0 0 0,0-1 1 0 0,18 11-1 0 0,-17-12-1217 0 0,-1 0 1 0 0,0 1 0 0 0,0 0-1 0 0,-1 1 1 0 0,11 12-1 0 0,-18-19-893 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,-2 1 0 0 0,-3 3 19 0 0,0 0 0 0 0,-1-1 0 0 0,1 0 1 0 0,-10 5-1 0 0,11-6 35 0 0,-40 18 178 0 0,29-14-182 0 0,0 0 1 0 0,-15 10 0 0 0,31-16-53 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0-1 0 0,0 1 1 0 0,-1-1 0 0 0,1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 1 0 0 0,0 1 26 0 0,0-1 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,4 2 0 0 0,1 1 68 0 0,1 1-1 0 0,13 5 1 0 0,-14-7-104 0 0,0-1 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 0 0 0 0,9-2 0 0 0,-5 1-895 0 0,-1-1-1 0 0,1 0 0 0 0,13-6 0 0 0,-7 1-7760 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="39">27434 5435 14743 0 0,'0'0'59'0'0,"0"0"0"0"0,0 0 0 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,6 7 2998 0 0,-4-5-2811 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,0 0-1 0 0,4 2 1 0 0,24 3 231 0 0,53 21 0 0 0,-70-21-386 0 0,0 0 0 0 0,0 0 0 0 0,-1 2 0 0 0,0-1 0 0 0,-1 1 0 0 0,15 13-1 0 0,-24-19-42 0 0,0 0-1 0 0,0 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,0 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,0 1 0 0 0,-1-1 1 0 0,0 0-1 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,-1-1 1 0 0,1 1-1 0 0,-1-1 0 0 0,1 0 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,-4 2 1 0 0,0 0 38 0 0,-1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,1 0 0 0 0,-2 0 0 0 0,1-1 0 0 0,-13 1 0 0 0,24-1-42 0 0,1 0 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,6 5 1 0 0,-2-1 257 0 0,-1-1-488 0 0,0 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 1-1 0 0,-1-1 1 0 0,0 1 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-2 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1-1 0 0,-1 0 1 0 0,0 1 0 0 0,0 10 0 0 0,-1-8 302 0 0,0 0 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 0 1 0 0,-1 0-1 0 0,-1 0 0 0 0,0-1 1 0 0,0 1-1 0 0,-1-1 0 0 0,-1 1 1 0 0,0-1-1 0 0,0 0 0 0 0,-1-1 1 0 0,0 1-1 0 0,-8 8 0 0 0,10-14 26 0 0,-1 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0-1 1 0 0,-1 1 0 0 0,1-1-1 0 0,-1 0 1 0 0,-11 4 0 0 0,-5 0 281 0 0,-24 4-1 0 0,43-10-388 0 0,-5 0-3 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,-11-1 1 0 0,-2 1-1441 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="40">25872 5547 1839 0 0,'1'7'9616'0'0,"-2"7"-3355"0"0,1-6-4918 0 0,-2 16-469 0 0,-1-1 1 0 0,0 1-1 0 0,-12 37 0 0 0,3-12-435 0 0,-25 134 716 0 0,36-179-1165 0 0,-3 13 476 0 0,4-16-144 0 0,3-10-91 0 0,-1 4-227 0 0,12-46 98 0 0,2 1-1 0 0,28-59 1 0 0,-37 94-83 0 0,1 1 0 0 0,0 0 0 0 0,1 1 0 0 0,1 0 0 0 0,0 0-1 0 0,0 1 1 0 0,1 0 0 0 0,1 1 0 0 0,0 0 0 0 0,1 1 0 0 0,23-15 0 0 0,-33 23-19 0 0,-1 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1-1 0 0,-1 1 1 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,5 3-1 0 0,-3-1 3 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,1 7 1 0 0,2 7 103 0 0,-1 0 1 0 0,-1 0 0 0 0,2 37-1 0 0,-3 61 442 0 0,-3-82-430 0 0,-1-1-57 0 0,2 40 67 0 0,-1-73-252 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,0-2 36 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,1 0 0 0 0,6-4-1896 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="41">26389 5754 17503 0 0,'7'1'890'0'0,"-1"0"-1"0"0,1-1 1 0 0,0 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,0-1-1 0 0,9-2 1 0 0,4 1-1262 0 0,11 0-326 0 0,32-4 1355 0 0,-23-2-7655 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="42">26431 5570 10135 0 0,'-11'13'10902'0'0,"29"-9"-7487"0"0,0 1-2792 0 0,1 0 1 0 0,29 2 0 0 0,-15-6-1495 0 0,54-5 1 0 0,-58 1-1097 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="43">24569 2044 10135 0 0,'-7'24'3990'0'0,"-5"40"0"0"0,3-13-2447 0 0,8-48-1488 0 0,-36 149 1588 0 0,29-123-1266 0 0,-2 0 0 0 0,-2 0-1 0 0,-16 29 1 0 0,28-57-316 0 0,-1 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,-1 0 0 0 0,2-1-25 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,1 0 0 0 0,0-1 0 0 0,-1 1-1 0 0,1 0 1 0 0,-1 0 0 0 0,1-1 0 0 0,-2-1 6 0 0,2 1-1 0 0,-1 0 1 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,1 1 0 0 0,-1-1 0 0 0,0 1-1 0 0,1-3 1 0 0,-2-6-4 0 0,0 1 0 0 0,1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0 1-1 0 0,1-1 1 0 0,0 0 0 0 0,5-14 0 0 0,6-11 135 0 0,22-46 1 0 0,-34 78-174 0 0,77-145-32 0 0,-68 131 28 0 0,2 1-1 0 0,0-1 0 0 0,1 2 1 0 0,0 0-1 0 0,1 0 1 0 0,19-14-1 0 0,-30 27 5 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,0-1 0 0 0,5 3-1 0 0,-4-1 2 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,3 6 0 0 0,-3-2 25 0 0,1-1 0 0 0,-1 1 1 0 0,0-1-1 0 0,-1 1 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,0-1 1 0 0,-1 11-1 0 0,1-13 10 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,-4 4 0 0 0,-4 0 201 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1-1 0 0,0-1 1 0 0,-1 0 0 0 0,0-1 0 0 0,-18 5-1 0 0,7-3-18 0 0,0-2-1 0 0,0-1 0 0 0,-32 2 0 0 0,52-5-248 0 0,2-1-3 0 0,0 0-1 0 0,0 0 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,-3-2 1 0 0,19-2-1521 0 0,55-6-4231 0 0,-45 6 3712 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="44">25095 2053 5983 0 0,'-9'6'14446'0'0,"10"-1"-12601"0"0,-2 2-3782 0 0,-3 25 3251 0 0,-17 62-1 0 0,14-66-1069 0 0,-2-1-1 0 0,0 0 0 0 0,-2 0 0 0 0,-1-1 0 0 0,-30 45 0 0 0,41-69-198 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1-1 0 0,-1 1 1 0 0,1-1 0 0 0,-1 1-1 0 0,-1 0 1 0 0,3-2-34 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 0-1 0 0,0-12 258 0 0,1 0-228 0 0,1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,1 0-1 0 0,0 0 1 0 0,6-16 0 0 0,35-66 307 0 0,-15 36-261 0 0,11-21-105 0 0,-33 66 13 0 0,1 1-1 0 0,0 0 0 0 0,1 0 0 0 0,11-11 0 0 0,-20 22 7 0 0,1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 1 0 0,0 1-1 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,3 0 0 0 0,-2 1 7 0 0,0 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,-1 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,0-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 3 1 0 0,6 13 27 0 0,-2 0 1 0 0,0 0-1 0 0,-1 1 0 0 0,-1-1 0 0 0,1 27 0 0 0,-5 94 120 0 0,1-129-137 0 0,-1-2-10 0 0,2 26 70 0 0,1-32-5 0 0,3-6-31 0 0,1-7-5 0 0,13-28 2 0 0,26-40 0 0 0,-32 60-24 0 0,0 1-1 0 0,1 0 1 0 0,31-30 0 0 0,-41 44-14 0 0,0 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,2 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,1 0 0 0 0,4-2 0 0 0,-8 3 0 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 2 0 0 0,3 10 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,-1 1 0 0 0,1 23 0 0 0,0-4 11 0 0,0-11 10 0 0,0 3 55 0 0,5 24 1 0 0,-6-42-66 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,8 9-1 0 0,-11-15-54 0 0,0 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,0-1 0 0 0,1 0 0 0 0,-1 1-1 0 0,0-1 1 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0-1 0 0,1 1 1 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,0-1 1 0 0,11-9-2148 0 0,-12 9 2152 0 0,7-7-1810 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="45">25714 2087 15407 0 0,'0'1'200'0'0,"-1"0"0"0"0,1-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1-1 0 0,1 1 1 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1-1 0 0,1 0 1 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-1-1-1 0 0,1 1 1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,10 2 154 0 0,-1 1 0 0 0,0 0 0 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,-1 2 0 0 0,12 6 0 0 0,-11-7-294 0 0,-6-4 26 0 0,-4-3 301 0 0,-2 2-376 0 0,1-1 0 0 0,0 1 0 0 0,-1-1 1 0 0,1 1-1 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 1 0 0,1 1-1 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,5-3-99 0 0,0 2 0 0 0,-1-1 0 0 0,13-1 0 0 0,-9 1-8 0 0,6-1-104 0 0,1 1-1 0 0,0 0 1 0 0,23 1 0 0 0,-20 1-656 0 0,30-4 1 0 0,-41 3-360 0 0,0-1-1 0 0,0 0 1 0 0,13-6 0 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="38">17244 2104 6911 0 0,'8'8'2143'0'0,"1"1"-1"0"0,0-1 0 0 0,0-1 1 0 0,18 11-1 0 0,-17-12-1217 0 0,-1 0 1 0 0,0 1 0 0 0,0 0-1 0 0,-1 1 1 0 0,11 12-1 0 0,-17-19-893 0 0,-2 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-2 0 0 0 0,1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,-2 1 0 0 0,-3 3 19 0 0,0 0 0 0 0,-1-1 0 0 0,1 0 1 0 0,-10 5-1 0 0,10-6 35 0 0,-38 18 178 0 0,28-14-182 0 0,0 0 1 0 0,-15 10 0 0 0,31-16-53 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0-1 0 0,0 1 1 0 0,-1-1 0 0 0,1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 1 0 0 0,0 1 26 0 0,0-1 0 0 0,0 0 1 0 0,0 1-1 0 0,-1-1 0 0 0,2 0 0 0 0,-1 1 1 0 0,0-1-1 0 0,4 2 0 0 0,1 1 68 0 0,1 1-1 0 0,13 5 1 0 0,-14-7-104 0 0,1-1 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 0 0 0 0,9-2 0 0 0,-5 1-895 0 0,-1-1-1 0 0,1 0 0 0 0,13-6 0 0 0,-7 1-7760 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="39">27434 5435 14743 0 0,'0'0'59'0'0,"0"0"0"0"0,0 0 0 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-2 0 0 0 0,2 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,6 7 2998 0 0,-4-5-2811 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,1-1 1 0 0,0 0 0 0 0,-2 0-1 0 0,5 2 1 0 0,24 3 231 0 0,53 21 0 0 0,-70-21-386 0 0,0 0 0 0 0,0 0 0 0 0,-1 2 0 0 0,0-1 0 0 0,-1 1 0 0 0,15 13-1 0 0,-24-19-42 0 0,0 0-1 0 0,0 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,-1 0 1 0 0,3 1-1 0 0,-2-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,0 1 0 0 0,-1-1 1 0 0,0 0-1 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,-1-1 1 0 0,1 1-1 0 0,-1-1 0 0 0,1 0 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 1 0 0,1-1-1 0 0,-2 0 0 0 0,-3 2 1 0 0,0 0 38 0 0,-1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,1 0 0 0 0,-2 0 0 0 0,1-1 0 0 0,-13 1 0 0 0,24-1-42 0 0,1 0 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,6 5 1 0 0,-2-1 257 0 0,-1-1-488 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-2 1 0 0 0,1 1-1 0 0,-1-1 1 0 0,0 1 0 0 0,0 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,-1 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,-2-1-1 0 0,0 0 1 0 0,0 1 0 0 0,0 10 0 0 0,-1-8 302 0 0,0 0 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,-3 0 0 0 0,1-1 1 0 0,0 1-1 0 0,-1-1 0 0 0,-1 1 1 0 0,0-1-1 0 0,0 0 0 0 0,-1-1 1 0 0,0 1-1 0 0,-8 8 0 0 0,10-14 26 0 0,-1 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0-1 1 0 0,-1 1 0 0 0,2-1-1 0 0,-3 0 1 0 0,-10 4 0 0 0,-5 0 281 0 0,-24 4-1 0 0,43-10-388 0 0,-5 0-3 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,-11-1 1 0 0,-2 1-1441 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="40">25872 5547 1839 0 0,'1'7'9616'0'0,"-2"7"-3355"0"0,1-6-4918 0 0,-2 16-469 0 0,-1-1 1 0 0,0 1-1 0 0,-12 37 0 0 0,3-12-435 0 0,-25 134 716 0 0,36-179-1165 0 0,-3 13 476 0 0,4-16-144 0 0,3-10-91 0 0,-1 4-227 0 0,12-46 98 0 0,2 1-1 0 0,28-59 1 0 0,-37 94-83 0 0,1 1 0 0 0,0 0 0 0 0,1 1 0 0 0,1 0 0 0 0,0 0-1 0 0,-1 1 1 0 0,3 0 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 1 0 0 0,24-15 0 0 0,-33 23-19 0 0,-2 1 0 0 0,3 0 0 0 0,-2 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0 0 0 0,-2 1 0 0 0,3-1 0 0 0,-1 1 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,1 0 0 0 0,-3 0 0 0 0,2 1 0 0 0,0-1-1 0 0,-1 1 1 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,5 3-1 0 0,-3-1 3 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,1 7 1 0 0,2 7 103 0 0,-1 0 1 0 0,-1 0 0 0 0,2 37-1 0 0,-3 61 442 0 0,-3-82-430 0 0,-1-1-57 0 0,2 40 67 0 0,-1-73-252 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,0-2 36 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,2 1 0 0 0,-2-1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,1 0 0 0 0,6-4-1896 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="41">26389 5754 17503 0 0,'7'1'890'0'0,"-1"0"-1"0"0,1-1 1 0 0,0 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,0-1-1 0 0,10-2 1 0 0,2 1-1262 0 0,12 0-326 0 0,32-4 1355 0 0,-23-2-7655 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="42">26431 5570 10135 0 0,'-11'13'10902'0'0,"29"-9"-7487"0"0,0 1-2792 0 0,1 0 1 0 0,30 2 0 0 0,-17-6-1495 0 0,55-5 1 0 0,-58 1-1097 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="43">24569 2044 10135 0 0,'-7'24'3990'0'0,"-5"40"0"0"0,3-13-2447 0 0,8-48-1488 0 0,-36 149 1588 0 0,29-123-1266 0 0,-2 0 0 0 0,-2 0-1 0 0,-16 29 1 0 0,28-57-316 0 0,-1 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,1 1-1 0 0,-2-1 1 0 0,1 0 0 0 0,0 1-1 0 0,0-1 1 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,-1 0 0 0 0,2-1-25 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-2 0 0 0 0,2 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,1 0 0 0 0,0-1 0 0 0,-1 1-1 0 0,1 0 1 0 0,-1 0 0 0 0,1-1 0 0 0,-2-1 6 0 0,2 1-1 0 0,-1 0 1 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,1 1 0 0 0,-1-1 0 0 0,0 1-1 0 0,1-3 1 0 0,-1-6-4 0 0,-2 1 0 0 0,2-1 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0 1-1 0 0,1-1 1 0 0,0 0 0 0 0,5-14 0 0 0,6-11 135 0 0,22-46 1 0 0,-34 78-174 0 0,77-145-32 0 0,-68 131 28 0 0,2 1-1 0 0,0-1 0 0 0,1 2 1 0 0,0 0-1 0 0,1 0 1 0 0,19-14-1 0 0,-30 27 5 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,0-1 0 0 0,5 3-1 0 0,-4-1 2 0 0,0 1 0 0 0,1-1 0 0 0,-2 1 0 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,3 6 0 0 0,-3-2 25 0 0,1-1 0 0 0,-1 1 1 0 0,0-1-1 0 0,-1 1 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,0-1 1 0 0,-1 11-1 0 0,1-13 10 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,-4 4 0 0 0,-4 0 201 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1-1 0 0,0-1 1 0 0,-1 0 0 0 0,0-1 0 0 0,-18 5-1 0 0,8-3-18 0 0,-2-2-1 0 0,1-1 0 0 0,-32 2 0 0 0,52-5-248 0 0,2-1-3 0 0,0 0-1 0 0,0 0 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,0-1 1 0 0,1 1-1 0 0,-2 0 0 0 0,-2-2 1 0 0,19-2-1521 0 0,55-6-4231 0 0,-45 6 3712 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="44">25095 2053 5983 0 0,'-9'6'14446'0'0,"10"-1"-12601"0"0,-2 2-3782 0 0,-3 25 3251 0 0,-17 62-1 0 0,14-66-1069 0 0,-1-1-1 0 0,-2 0 0 0 0,-1 0 0 0 0,-1-1 0 0 0,-30 45 0 0 0,41-69-198 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1-1 0 0,-1 1 1 0 0,1-1 0 0 0,-1 1-1 0 0,-1 0 1 0 0,3-2-34 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,-2 0-1 0 0,2 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 0-1 0 0,0-12 258 0 0,1 0-228 0 0,1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,1 0-1 0 0,0 0 1 0 0,6-16 0 0 0,35-66 307 0 0,-14 36-261 0 0,9-21-105 0 0,-32 66 13 0 0,1 1-1 0 0,0 0 0 0 0,0 0 0 0 0,13-11 0 0 0,-21 22 7 0 0,1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,1 1 0 0 0,0-1 1 0 0,-2 1-1 0 0,1 0 0 0 0,1-1 0 0 0,-1 1 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,3 0 0 0 0,-2 1 7 0 0,0 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,-1 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,0-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,-1 3 1 0 0,8 13 27 0 0,-3 0 1 0 0,0 0-1 0 0,-1 1 0 0 0,-1-1 0 0 0,1 27 0 0 0,-5 94 120 0 0,1-129-137 0 0,-1-2-10 0 0,2 26 70 0 0,1-32-5 0 0,3-6-31 0 0,1-7-5 0 0,13-28 2 0 0,26-40 0 0 0,-32 60-24 0 0,0 1-1 0 0,1 0 1 0 0,31-30 0 0 0,-41 44-14 0 0,0 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,2 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,1 0 0 0 0,5-2 0 0 0,-10 3 0 0 0,2 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,1 1 0 0 0,-2-1 0 0 0,0 0 0 0 0,1 2 0 0 0,3 10 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,-1 1 0 0 0,1 23 0 0 0,0-4 11 0 0,0-11 10 0 0,0 3 55 0 0,5 24 1 0 0,-6-42-66 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,1 0-1 0 0,1 0 1 0 0,-2 0-1 0 0,1 0 1 0 0,8 9-1 0 0,-11-15-54 0 0,0 1 0 0 0,2-1-1 0 0,-2 1 1 0 0,0-1 0 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0-1 0 0,1 1 1 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,0-1 1 0 0,11-9-2148 0 0,-12 9 2152 0 0,7-7-1810 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="45">25714 2087 15407 0 0,'0'1'200'0'0,"-1"0"0"0"0,1-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1-1 0 0,1 1 1 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1-1 0 0,1 0 1 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-1-1-1 0 0,2 1 1 0 0,-2-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,10 2 154 0 0,-2 1 0 0 0,2 0 0 0 0,0 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,-1 2 0 0 0,12 6 0 0 0,-11-7-294 0 0,-6-4 26 0 0,-4-3 301 0 0,-2 2-376 0 0,1-1 0 0 0,0 1 0 0 0,-1-1 1 0 0,1 1-1 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 1 0 0,1 1-1 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,5-3-99 0 0,0 2 0 0 0,-1-1 0 0 0,13-1 0 0 0,-9 1-8 0 0,6-1-104 0 0,1 1-1 0 0,0 0 1 0 0,23 1 0 0 0,-20 1-656 0 0,30-4 1 0 0,-41 3-360 0 0,0-1-1 0 0,0 0 1 0 0,13-6 0 0 0</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="46">25852 2097 12783 0 0,'2'68'7539'0'0,"0"35"-4481"0"0,-6-61-2297 0 0,-2-1 0 0 0,-20 79 0 0 0,24-111-1963 0 0,2-9 1124 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="47">26161 2439 8751 0 0,'15'7'4211'0'0,"24"13"1019"0"0,-25-12-4001 0 0,26 18 1 0 0,-38-24-1154 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 1 0 0 0,0-1-1 0 0,-1 1 1 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 0 0 0 0,1 3-1 0 0,-2-2 2 0 0,1-1-1 0 0,-1 1 0 0 0,1-1 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,-2 3-1 0 0,1-2-24 0 0,-1 1-1 0 0,1-1 0 0 0,-1 0 1 0 0,1-1-1 0 0,-1 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,0 0 1 0 0,-1-1-1 0 0,1 0 1 0 0,-1 1-1 0 0,0-2 1 0 0,1 1-1 0 0,-1-1 0 0 0,-7 1 1 0 0,17-1-99 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1-1 0 0,-1 0 1 0 0,7 3-1 0 0,29 21-185 0 0,-35-23 228 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,1 6 0 0 0,-2-7 38 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1-1-1 0 0,1 1 1 0 0,-1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1 0 0 0,0 1-1 0 0,-1 0 1 0 0,1-1 0 0 0,-1 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1-1 0 0 0,-4 4-1 0 0,1-2 167 0 0,-1 1 0 0 0,1-2 0 0 0,-1 1-1 0 0,-13 3 1 0 0,18-5-145 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0-1 0 0 0,-2-1 0 0 0,3 3-98 0 0,1 0-1 0 0,0-1 0 0 0,0 1 1 0 0,-1 0-1 0 0,1 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 0 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,1 0 0 0 0,-1-1 1 0 0,0 1-1 0 0,1 0 0 0 0,4-6-2445 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="48">26560 2390 4607 0 0,'24'11'1564'0'0,"16"3"9688"0"0,-28-11-9041 0 0,19 7-219 0 0,48 7 0 0 0,-66-15-2219 0 0,1 0 0 0 0,-1-2 0 0 0,0 1 0 0 0,0-2 0 0 0,0 0 0 0 0,22-4-1 0 0,-28 4-1553 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="49">26609 2240 8287 0 0,'-3'7'11379'0'0,"7"-6"-10649"0"0,-2-1-1267 0 0,22 5 1941 0 0,1-1 0 0 0,49 0 0 0 0,-32-5-3325 0 0,-1-1-3363 0 0,-15-1-1967 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="50">27504 2052 8287 0 0,'-10'1'1926'0'0,"-1"-1"-1"0"0,0 2 0 0 0,1 0 0 0 0,-16 4 1 0 0,-40 18 1345 0 0,63-23-3251 0 0,-1 1 43 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0-1 0 0,-4 7 1 0 0,5-8-36 0 0,1 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,1-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,1-1 0 0 0,-1 1 1 0 0,1-1-1 0 0,0 1 0 0 0,0 0 1 0 0,2 3-1 0 0,3 5-20 0 0,0-1 0 0 0,1 0 0 0 0,1-1-1 0 0,-1 0 1 0 0,2 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,20 14-1 0 0,-16-12 7 0 0,1 1 0 0 0,-2 1 0 0 0,16 17-1 0 0,-27-28 12 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 1 0 0,0 1-1 0 0,-1 1 0 0 0,0-1 106 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,1-1-1 0 0,-1 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,-3 2 0 0 0,-7 3 67 0 0,0-1-1 0 0,-1 0 1 0 0,0-1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,-1-1 0 0 0,1 0 1 0 0,-1-1-1 0 0,1 0 1 0 0,-1-1-1 0 0,1-1 1 0 0,-22-5-1 0 0,32 6-201 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-4-3 0 0 0,-1-5-2183 0 0,7 8 1658 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,1-1 0 0 0,0-1-1 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="47">26161 2439 8751 0 0,'15'7'4211'0'0,"24"13"1019"0"0,-25-12-4001 0 0,26 18 1 0 0,-38-24-1154 0 0,2 0 0 0 0,-3 0-1 0 0,1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 1 0 0 0,0-1-1 0 0,-1 1 1 0 0,0-1 0 0 0,-1 1-1 0 0,2 0 1 0 0,-1-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 0 0 0 0,1 3-1 0 0,-2-2 2 0 0,1-1-1 0 0,-1 1 0 0 0,1-1 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,-2 3-1 0 0,1-2-24 0 0,-1 1-1 0 0,1-1 0 0 0,-1 0 1 0 0,1-1-1 0 0,-1 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,0 0 1 0 0,-1-1-1 0 0,1 0 1 0 0,-1 1-1 0 0,0-2 1 0 0,1 1-1 0 0,-1-1 0 0 0,-7 1 1 0 0,17-1-99 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,2 1-1 0 0,-2 0 1 0 0,7 3-1 0 0,29 21-185 0 0,-35-23 228 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,1 6 0 0 0,-2-7 38 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1-1-1 0 0,1 1 1 0 0,-1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1-1 0 0 0,2 1-1 0 0,-2 0 1 0 0,1-1 0 0 0,-1 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,1 0-1 0 0,-2 0 1 0 0,0-1 0 0 0,-4 4-1 0 0,2-2 167 0 0,-3 1 0 0 0,2-2 0 0 0,-1 1-1 0 0,-13 3 1 0 0,18-5-145 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,1-1 0 0 0,-2 0 0 0 0,1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0-1 0 0 0,-2-1 0 0 0,3 3-98 0 0,1 0-1 0 0,0-1 0 0 0,0 1 1 0 0,-1 0-1 0 0,1 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 0 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,1 0 0 0 0,-1-1 1 0 0,0 1-1 0 0,1 0 0 0 0,4-6-2445 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="48">26560 2390 4607 0 0,'24'11'1564'0'0,"16"3"9688"0"0,-28-11-9041 0 0,19 7-219 0 0,48 7 0 0 0,-66-15-2219 0 0,0 0 0 0 0,1-2 0 0 0,-1 1 0 0 0,0-2 0 0 0,0 0 0 0 0,22-4-1 0 0,-28 4-1553 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="49">26609 2240 8287 0 0,'-3'7'11379'0'0,"7"-6"-10649"0"0,-1-1-1267 0 0,20 5 1941 0 0,2-1 0 0 0,49 0 0 0 0,-32-5-3325 0 0,-1-1-3363 0 0,-16-1-1967 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="50">27504 2052 8287 0 0,'-10'1'1926'0'0,"-1"-1"-1"0"0,0 2 0 0 0,1 0 0 0 0,-16 4 1 0 0,-40 18 1345 0 0,63-23-3251 0 0,-1 1 43 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0-1 0 0,-4 7 1 0 0,5-8-36 0 0,1 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 1 0 0,-2 0-1 0 0,2-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0-1 0 0 0,2 1 1 0 0,-2 0-1 0 0,1-1 0 0 0,-1 1 1 0 0,1-1-1 0 0,0 1 0 0 0,0 0 1 0 0,2 3-1 0 0,3 5-20 0 0,0-1 0 0 0,1 0 0 0 0,2-1-1 0 0,-3 0 1 0 0,3 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,20 14-1 0 0,-16-12 7 0 0,1 1 0 0 0,-2 1 0 0 0,16 17-1 0 0,-27-28 12 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 1 0 0,0 1-1 0 0,-1 1 0 0 0,0-1 106 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,1-1-1 0 0,-1 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,-3 2 0 0 0,-7 3 67 0 0,0-1-1 0 0,-1 0 1 0 0,0-1-1 0 0,0-1 1 0 0,1 0-1 0 0,-2 0 1 0 0,1-1-1 0 0,-1-1 0 0 0,0 0 1 0 0,1-1-1 0 0,0 0 1 0 0,-1-1-1 0 0,2-1 1 0 0,-25-5-1 0 0,35 6-201 0 0,0 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-4-3 0 0 0,-1-5-2183 0 0,7 8 1658 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,1-1 0 0 0,0-1-1 0 0</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="51">27490 1896 3679 0 0,'0'-21'16970'0'0,"-4"28"-15996"0"0,-5 24-108 0 0,1 0-1 0 0,2 1 1 0 0,-4 56-1 0 0,0 2 993 0 0,-4-11-2253 0 0,-30 96 1 0 0,43-171 399 0 0,-3 6 39 0 0,1 1-1 0 0,1 0 0 0 0,-1 0 0 0 0,0 15 0 0 0,3-26-59 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1 0 0 0,9-5-1620 0 0,-9 6 1513 0 0,12-13-3944 0 0</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="52">27862 1969 9671 0 0,'-4'36'9382'0'0,"-6"2"-6173"0"0,-17 34-3013 0 0,21-57 637 0 0,-17 43-278 0 0,2-5-149 0 0,-28 51 0 0 0,29-62-1049 0 0,20-39-1376 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="53">28052 2112 7831 0 0,'-1'20'1196'0'0,"-1"0"-1"0"0,-5 23 0 0 0,-3 29 3647 0 0,9-65-4534 0 0,1 1-1 0 0,0 0 1 0 0,1 0-1 0 0,0-1 1 0 0,0 1-1 0 0,1 0 1 0 0,2 8-1 0 0,-3-14-292 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 0 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,-1-1 0 0 0,4 2 0 0 0,-4-2-5 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 0 0 0 0,-1 1 1 0 0,1-1-1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0-1 0 0 0,7-7 311 0 0,-2 0 1 0 0,1 0-1 0 0,-2 0 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 1 0 0,-1-1-1 0 0,0 1 0 0 0,-1-1 0 0 0,4-20 0 0 0,-7 27-152 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,-5-4-1 0 0,-2-3 396 0 0,-2 1 0 0 0,0 0 0 0 0,-18-12-1 0 0,8 6-207 0 0,17 12-722 0 0,6 4-997 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="54">28262 2124 10999 0 0,'8'14'1238'0'0,"-1"-1"0"0"0,10 26-1 0 0,-10-22 217 0 0,11 22 0 0 0,-15-34-1360 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1-1-1 0 0,0 1 1 0 0,0-1 0 0 0,1 0 0 0 0,5 4-1 0 0,-7-6-13 0 0,1 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 0 0 0 0,1 1-1 0 0,4-3 1 0 0,-6 2 86 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 1 0 0 0,2-4-1 0 0,-2 3 39 0 0,-1 1-1 0 0,1 0 0 0 0,0-1 0 0 0,-1 1 1 0 0,1 0-1 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 1 0 0 0,-3-3 1 0 0,-4-3 371 0 0,-1 1 1 0 0,-20-10 0 0 0,22 11-381 0 0,7 5-184 0 0,-33-17 102 0 0,0-2 1 0 0,2 0-1 0 0,-38-32 0 0 0,63 44-345 0 0,6 3-1852 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="55">24742 80 9215 0 0,'0'10'5650'0'0,"3"5"-2590"0"0,-1 3-1927 0 0,1 30-166 0 0,-3-1 0 0 0,-1 0 0 0 0,-3 1 0 0 0,-2-1 0 0 0,-2-1 0 0 0,-17 60 0 0 0,-19 54 482 0 0,40-147-1387 0 0,4-12-60 0 0,-1-1 1 0 0,1 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 1-1 0 0,-1-1 1 0 0,1 0-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 1-1 0 0,0-1 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1-3-242 0 0,0 1-1 0 0,0 0 1 0 0,0-1-1 0 0,1 1 1 0 0,-1 0 0 0 0,2-5-1 0 0,-1 4-61 0 0,9-31-2384 0 0,-4 13 589 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="53">28052 2112 7831 0 0,'-1'20'1196'0'0,"-1"0"-1"0"0,-5 23 0 0 0,-3 29 3647 0 0,9-65-4534 0 0,1 1-1 0 0,0 0 1 0 0,1 0-1 0 0,0-1 1 0 0,0 1-1 0 0,1 0 1 0 0,2 8-1 0 0,-3-14-292 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 0 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,-1-1 0 0 0,4 2 0 0 0,-4-2-5 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 1 0 0,-1 0-1 0 0,2 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 0 0 0 0,-1 1 1 0 0,1-1-1 0 0,1 0 0 0 0,-2 1 0 0 0,1-1 1 0 0,0 0-1 0 0,0-1 0 0 0,7-7 311 0 0,-1 0 1 0 0,-1 0-1 0 0,-1 0 0 0 0,2-1 0 0 0,-3 0 0 0 0,1 0 1 0 0,-1-1-1 0 0,-1 1 0 0 0,1-1 0 0 0,3-20 0 0 0,-7 27-152 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,-5-4-1 0 0,-2-3 396 0 0,-2 1 0 0 0,0 0 0 0 0,-18-12-1 0 0,8 6-207 0 0,17 12-722 0 0,6 4-997 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="54">28262 2124 10999 0 0,'8'14'1238'0'0,"-1"-1"0"0"0,10 26-1 0 0,-10-22 217 0 0,11 22 0 0 0,-16-34-1360 0 0,2 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,2-1 0 0 0,0 0 0 0 0,5 4-1 0 0,-7-6-13 0 0,1 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 0 0 0 0,1 1-1 0 0,4-3 1 0 0,-6 2 86 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,0 0 0 0 0,1-1 0 0 0,0 0 0 0 0,-2 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1-1 0 0 0,2 1 0 0 0,-3-1 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 1 0 0 0,2-4-1 0 0,-2 3 39 0 0,-1 1-1 0 0,1 0 0 0 0,0-1 0 0 0,-1 1 1 0 0,1 0-1 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 1 0 0,1 0-1 0 0,-2-1 0 0 0,1 1 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 1 0 0 0,-3-3 1 0 0,-4-3 371 0 0,-1 1 1 0 0,-20-10 0 0 0,22 11-381 0 0,7 5-184 0 0,-33-17 102 0 0,0-2 1 0 0,2 0-1 0 0,-38-32 0 0 0,63 44-345 0 0,6 3-1852 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="55">24742 80 9215 0 0,'0'10'5650'0'0,"3"5"-2590"0"0,-1 3-1927 0 0,1 30-166 0 0,-3-1 0 0 0,-1 0 0 0 0,-3 1 0 0 0,-2-1 0 0 0,-2-1 0 0 0,-17 60 0 0 0,-19 54 482 0 0,40-147-1387 0 0,4-12-60 0 0,-1-1 1 0 0,1 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 1-1 0 0,-1-1 1 0 0,1 0-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 1-1 0 0,0-1 1 0 0,-2 0-1 0 0,2 0 1 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1-3-242 0 0,0 1-1 0 0,0 0 1 0 0,0-1-1 0 0,1 1 1 0 0,-1 0 0 0 0,2-5-1 0 0,-1 4-61 0 0,9-31-2384 0 0,-4 13 589 0 0</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="56">24706 77 7367 0 0,'21'-10'10040'0'0,"7"1"-5417"0"0,-14 6-4100 0 0,0-1 0 0 0,1 2 0 0 0,-1 0 0 0 0,27 0-1 0 0,-17 2-431 0 0,-1 2-1 0 0,1 0 0 0 0,-1 2 0 0 0,37 10 0 0 0,-58-13-318 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,3 3 0 0 0,2 3-908 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="57">24743 256 1839 0 0,'2'10'167'0'0,"4"11"1468"0"0,3-8 8311 0 0,-2-7-8763 0 0,-1 0-1 0 0,1 0 1 0 0,0-1 0 0 0,1 0-1 0 0,10 5 1 0 0,-10-6-809 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,10 2 1 0 0,-7-3-583 0 0,0 0 1 0 0,0-1-1 0 0,0 0 0 0 0,0 0 1 0 0,0-1-1 0 0,0-1 1 0 0,-1 0-1 0 0,1 0 0 0 0,17-8 1 0 0,-9 3-7280 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="58">25220 131 5063 0 0,'3'25'10457'0'0,"2"0"-6275"0"0,2 14-2266 0 0,-3 40-1077 0 0,-6 83 0 0 0,-1 28-765 0 0,4-185-19 0 0,-1-1 16 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 1 0 0,0 0-1 0 0,2 6 0 0 0,-3-10-54 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,7-8 417 0 0,3-11 93 0 0,80-147 1881 0 0,-2 4-1344 0 0,-77 139-950 0 0,11-23 182 0 0,48-77-1 0 0,-70 122-353 0 0,0 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,1 1 0 0 0,-1 0-350 0 0,1 0 1 0 0,-1 0-1 0 0,1 1 1 0 0,-1-1-1 0 0,1 1 1 0 0,-1-1-1 0 0,0 1 1 0 0,1-1-1 0 0,-1 1 1 0 0,1 2-1 0 0,3 6-1745 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="59">25679 526 5983 0 0,'7'-3'10333'0'0,"0"3"-4314"0"0,9 10-2869 0 0,-13-8-3536 0 0,0 1 0 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,2 5 0 0 0,-1 1 1859 0 0,-2-3-1445 0 0,-1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,-1 0-1 0 0,-3 10 1 0 0,-1-2 37 0 0,0-1-1 0 0,-1 0 1 0 0,0-1 0 0 0,-11 14-1 0 0,17-25-67 0 0,1-1-1 0 0,0 1 0 0 0,0-1 1 0 0,-1 0-1 0 0,1 1 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,-1 1 1 0 0,1-1-1 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,1-1 0 0 0,-1 1 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,1 1 1 0 0,-1-1-1 0 0,0 0 1 0 0,0 1-1 0 0,1-1 0 0 0,-1 1 1 0 0,0-1-1 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,1 0 1 0 0,0 1-1 0 0,29 10-268 0 0,-9-3 153 0 0,-19-7 119 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,-1-1-1 0 0,1 1 1 0 0,-1-1 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 2 0 0 0,0-1 11 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,-1 3 0 0 0,-2 2 120 0 0,0-1 0 0 0,0 1-1 0 0,-1-1 1 0 0,0 0 0 0 0,0-1 0 0 0,0 0-1 0 0,-9 6 1 0 0,10-8-6 0 0,0-1-1 0 0,-1 1 1 0 0,1-1 0 0 0,0-1 0 0 0,-1 1-1 0 0,0-1 1 0 0,-10 2 0 0 0,-5-2-5304 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="60">26216 515 17503 0 0,'8'2'595'0'0,"-1"0"-1"0"0,1 0 1 0 0,0-1-1 0 0,-1 0 0 0 0,1-1 1 0 0,0 0-1 0 0,12-1 1 0 0,-3 1-216 0 0,2 0 249 0 0,36-5 1 0 0,-45 3-1790 0 0,0-1-1 0 0,18-6 1 0 0,-18 4-6275 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="57">24742 256 1839 0 0,'3'10'167'0'0,"3"11"1468"0"0,3-8 8311 0 0,-2-7-8763 0 0,-1 0-1 0 0,1 0 1 0 0,0-1 0 0 0,1 0-1 0 0,10 5 1 0 0,-10-6-809 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,10 2 1 0 0,-7-3-583 0 0,0 0 1 0 0,0-1-1 0 0,0 0 0 0 0,0 0 1 0 0,0-1-1 0 0,0-1 1 0 0,-1 0-1 0 0,1 0 0 0 0,17-8 1 0 0,-9 3-7280 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="58">25220 131 5063 0 0,'3'25'10457'0'0,"2"0"-6275"0"0,2 14-2266 0 0,-3 40-1077 0 0,-6 83 0 0 0,-1 28-765 0 0,4-185-19 0 0,-1-1 16 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 1 0 0,0 0-1 0 0,2 6 0 0 0,-3-10-54 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,2 0 0 0 0,-2 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,7-8 417 0 0,3-11 93 0 0,80-147 1881 0 0,-2 4-1344 0 0,-77 139-950 0 0,10-23 182 0 0,50-77-1 0 0,-71 122-353 0 0,0 1 1 0 0,2-1-1 0 0,-2 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 1 0 0,-1 1-1 0 0,0-1 0 0 0,3 1 0 0 0,-2 0-350 0 0,1 0 1 0 0,-1 0-1 0 0,1 1 1 0 0,-1-1-1 0 0,1 1 1 0 0,-1-1-1 0 0,0 1 1 0 0,1-1-1 0 0,-1 1 1 0 0,0 2-1 0 0,5 6-1745 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="59">25679 526 5983 0 0,'8'-3'10333'0'0,"-2"3"-4314"0"0,10 10-2869 0 0,-13-8-3536 0 0,0 1 0 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,2 5 0 0 0,-1 1 1859 0 0,-2-3-1445 0 0,-1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,-1 0-1 0 0,-3 10 1 0 0,0-2 37 0 0,-2-1-1 0 0,0 0 1 0 0,0-1 0 0 0,-11 14-1 0 0,17-25-67 0 0,1-1-1 0 0,0 1 0 0 0,0-1 1 0 0,-1 0-1 0 0,1 1 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,-1 1 1 0 0,1-1-1 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,1-1 0 0 0,-1 1 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,1 1 1 0 0,-1-1-1 0 0,0 0 1 0 0,0 1-1 0 0,1-1 0 0 0,-1 1 1 0 0,0-1-1 0 0,1 0 1 0 0,-1 1-1 0 0,2-1 1 0 0,-2 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,1 0 1 0 0,0 1-1 0 0,29 10-268 0 0,-10-3 153 0 0,-17-7 119 0 0,-2 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,-1-1-1 0 0,1 1 1 0 0,-1-1 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 2 0 0 0,0-1 11 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,-1 3 0 0 0,-2 2 120 0 0,0-1 0 0 0,0 1-1 0 0,-1-1 1 0 0,0 0 0 0 0,0-1 0 0 0,0 0-1 0 0,-9 6 1 0 0,10-8-6 0 0,0-1-1 0 0,-1 1 1 0 0,1-1 0 0 0,0-1 0 0 0,-1 1-1 0 0,0-1 1 0 0,-10 2 0 0 0,-5-2-5304 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="60">26216 515 17503 0 0,'8'2'595'0'0,"-1"0"-1"0"0,1 0 1 0 0,0-1-1 0 0,-1 0 0 0 0,1-1 1 0 0,0 0-1 0 0,12-1 1 0 0,-3 1-216 0 0,2 0 249 0 0,35-5 1 0 0,-43 3-1790 0 0,-1-1-1 0 0,18-6 1 0 0,-18 4-6275 0 0</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="61">26308 319 11975 0 0,'1'-1'559'0'0,"-1"1"-466"0"0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-2 1768 0 0,1 2-1768 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,11-7 3637 0 0,3 4-2537 0 0,22-4 0 0 0,1 0-1550 0 0,-17 2-226 0 0,0 1-37 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="62">27253 53 11975 0 0,'-15'3'1351'0'0,"0"1"0"0"0,1 0-1 0 0,-1 1 1 0 0,-15 8 0 0 0,0-1-637 0 0,11-5-194 0 0,-1 0 1 0 0,1 2-1 0 0,1 0 0 0 0,-20 14 0 0 0,37-23-509 0 0,0 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,0-1-1 0 0,1 1 1 0 0,-1-1 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,1 0-1 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 1 0 0,-1 0 0 0 0,1-1-1 0 0,0 1 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,1 1 0 0 0,-1 0-1 0 0,0 0 1 0 0,1-1-1 0 0,-1 1 1 0 0,0 0-1 0 0,1 0 1 0 0,-1-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,1-1-1 0 0,-1 1 1 0 0,2 0 0 0 0,3 3-47 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,11 5 0 0 0,-9-4 35 0 0,65 29-131 0 0,-48-23 156 0 0,0 1 1 0 0,-1 1-1 0 0,0 1 0 0 0,30 22 0 0 0,-50-32 1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 1-1 0 0,-1-1 1 0 0,1 1 0 0 0,-1 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,0 0 0 0 0,0 0 0 0 0,-1 1-1 0 0,2 5 1 0 0,-2-7 31 0 0,-1 1 0 0 0,0-1-1 0 0,1 0 1 0 0,-1 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,0 1-1 0 0,-1-1 1 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,0-1 1 0 0,-3 6-1 0 0,-2-1 222 0 0,0 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 0 0 0 0,-1-1 0 0 0,1 0 0 0 0,-15 4 0 0 0,8-3-6 0 0,0-1 1 0 0,-1-1-1 0 0,1-1 0 0 0,-1 0 0 0 0,0-1 1 0 0,-21-2-1 0 0,32 1-331 0 0,0-1 0 0 0,1 1-1 0 0,-1-1 1 0 0,0 0 0 0 0,1 0-1 0 0,-1-1 1 0 0,1 0 0 0 0,0 0 0 0 0,-8-3-1 0 0,13 4-152 0 0,0 1-1 0 0,-1-1 0 0 0,1 1 1 0 0,0-1-1 0 0,-1 1 0 0 0,1-1 1 0 0,0 0-1 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,1 0 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 1 0 0,0-1-1 0 0,2 0 0 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="63">27184 0 10591 0 0,'0'1'235'0'0,"-1"-1"-1"0"0,0 1 0 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,1 1 0 0 0,-1-1 1 0 0,0 1-1 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 1 0 0,-5 34 5146 0 0,4-28-5515 0 0,-3 28 1101 0 0,-53 391 2839 0 0,53-397-3682 0 0,-2 54 0 0 0,6-83-201 0 0,0-1 0 0 0,0 0 0 0 0,0 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,1-1-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1-1 0 0,1 0 1 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="64">27646 125 9215 0 0,'1'0'220'0'0,"-1"0"0"0"0,0-1 0 0 0,0 1 0 0 0,1 0-1 0 0,-1-1 1 0 0,0 1 0 0 0,1 0 0 0 0,-1-1-1 0 0,1 1 1 0 0,-1 0 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,17 0 3617 0 0,-17 0-3915 0 0,13 1 527 0 0,0 0 0 0 0,-1 1 0 0 0,0 0 0 0 0,1 1 0 0 0,-1 1 0 0 0,0 0 0 0 0,0 1 0 0 0,-1 0 0 0 0,0 1 0 0 0,0 1 0 0 0,0 0 0 0 0,12 9 0 0 0,-23-15-419 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 1 0 0,0 0-1 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,0 3 0 0 0,0-1 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,-1 0 1 0 0,1-1 0 0 0,-3 4-1 0 0,-3 4-89 0 0,-1 0 1 0 0,0-1-1 0 0,-1-1 0 0 0,-18 15 0 0 0,-45 29-1537 0 0,72-52 1560 0 0,-1 0-1 0 0,1 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,0 1 0 0 0,0-1 1 0 0,-1 0-1 0 0,1 1 1 0 0,0-1-1 0 0,-1 1 0 0 0,1-1 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,-1-1 1 0 0,1 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0-1 1 0 0,1 0-1 0 0,-1 1 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,1-1 0 0 0,-1 1 1 0 0,0-1-1 0 0,0 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 0 1 0 0,1 1-1 0 0,0 0 1 0 0,20 14-580 0 0,-11-9 435 0 0,-1 0 152 0 0,-1 1 1 0 0,1 1 0 0 0,-1 0-1 0 0,0 0 1 0 0,-1 1 0 0 0,8 10 0 0 0,-14-17 85 0 0,1 1 0 0 0,0 0 0 0 0,-1 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,0 1-1 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,1-1-1 0 0,-3 3 0 0 0,-1 1 244 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,-11 6 1 0 0,12-9-123 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,-10 0 0 0 0,14 0-180 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0-1 1 0 0,0 1-1 0 0,1 0 0 0 0,-1 0 1 0 0,0-1-1 0 0,1 1 1 0 0,-1 0-1 0 0,0-1 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 1 1 0 0,1-1-1 0 0,-1 1 1 0 0,1-1-1 0 0,-2 0 0 0 0,2 0-112 0 0,0 1 1 0 0,1 0-1 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 1 0 0,0-1-1 0 0,0 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,1-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,1-1 0 0 0,0 1 0 0 0,6-1-1629 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="65">28119 153 15343 0 0,'2'5'471'0'0,"0"-1"0"0"0,-1 1 0 0 0,0 0-1 0 0,1-1 1 0 0,-2 1 0 0 0,1 0 0 0 0,-1 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,-1 0 0 0 0,0 7 0 0 0,-3 25 993 0 0,-1 1 1 0 0,-14 50 0 0 0,-16 70-672 0 0,31-140-724 0 0,-2 22-1 0 0,4-21-21 0 0,4-7-987 0 0,-2-12 853 0 0,0 1-1 0 0,0-1 0 0 0,0 0 0 0 0,0 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 1 0 0 0,0-1 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0-1 0 0 0,3 0-1596 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="66">28624 188 6911 0 0,'-6'3'1378'0'0,"-10"-3"8035"0"0,7 0-5723 0 0,3 0-3853 0 0,-4 2 502 0 0,1 1 0 0 0,-1-1 0 0 0,1 2 1 0 0,0-1-1 0 0,0 2 0 0 0,0-1 0 0 0,1 1 1 0 0,0 0-1 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,-10 11 0 0 0,17-15-334 0 0,0 0 1 0 0,-1 0-1 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 1 0 0,0 0-1 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,0 4 1 0 0,1-2-14 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1-1 0 0,4 5 1 0 0,1 1-46 0 0,1 0 0 0 0,1 0 0 0 0,0-1 0 0 0,18 14-1 0 0,-13-12 37 0 0,0 0 0 0 0,-1 1 0 0 0,-1 0 0 0 0,17 22 0 0 0,-26-30 23 0 0,0 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,1 1 1 0 0,-2-1 0 0 0,1 0-1 0 0,0 1 1 0 0,-1-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1-1-1 0 0,0 1 1 0 0,-1 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,-3 5 1 0 0,2-4 78 0 0,-1-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,-1-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,0-1 0 0 0,1 0 0 0 0,-2 1-1 0 0,1-2 1 0 0,0 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,0-1-1 0 0,0 0 1 0 0,-1 0 0 0 0,-10 1-1 0 0,13-2-151 0 0,-1 0 0 0 0,1 0 0 0 0,0-1-1 0 0,0 1 1 0 0,-1-1 0 0 0,1-1 0 0 0,0 1-1 0 0,-1 0 1 0 0,1-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,-3-4 1 0 0,7 6-93 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0-2-1128 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="62">27254 53 11975 0 0,'-16'3'1351'0'0,"1"1"0"0"0,1 0-1 0 0,-1 1 1 0 0,-14 8 0 0 0,-2-1-637 0 0,12-5-194 0 0,-1 0 1 0 0,1 2-1 0 0,0 0 0 0 0,-18 14 0 0 0,36-23-509 0 0,0 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,0-1-1 0 0,1 1 1 0 0,-1-1 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,1 0-1 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 1 0 0,-1 0 0 0 0,1-1-1 0 0,0 1 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,1 1 0 0 0,-1 0-1 0 0,0 0 1 0 0,1-1-1 0 0,-1 1 1 0 0,0 0-1 0 0,1 0 1 0 0,-1-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,1-1-1 0 0,-1 1 1 0 0,2 0 0 0 0,3 3-47 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,11 5 0 0 0,-9-4 35 0 0,65 29-131 0 0,-48-23 156 0 0,0 1 1 0 0,-1 1-1 0 0,0 1 0 0 0,30 22 0 0 0,-50-32 1 0 0,0 0 0 0 0,2 0 0 0 0,-3 0 0 0 0,1 1-1 0 0,-1-1 1 0 0,1 1 0 0 0,-1 0 0 0 0,1-1-1 0 0,-2 1 1 0 0,2 0 0 0 0,-1 0 0 0 0,-1 1-1 0 0,2 5 1 0 0,-2-7 31 0 0,-1 1 0 0 0,0-1-1 0 0,1 0 1 0 0,-1 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,0 1-1 0 0,-1-1 1 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0-1 0 0,0 0 1 0 0,-2 0 0 0 0,2 0-1 0 0,-1-1 1 0 0,-3 6-1 0 0,-2-1 222 0 0,0 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 0 0 0 0,-1-1 0 0 0,1 0 0 0 0,-15 4 0 0 0,8-3-6 0 0,0-1 1 0 0,-1-1-1 0 0,1-1 0 0 0,-1 0 0 0 0,0-1 1 0 0,-21-2-1 0 0,31 1-331 0 0,2-1 0 0 0,0 1-1 0 0,-1-1 1 0 0,0 0 0 0 0,1 0-1 0 0,-1-1 1 0 0,1 0 0 0 0,0 0 0 0 0,-8-3-1 0 0,13 4-152 0 0,0 1-1 0 0,-1-1 0 0 0,1 1 1 0 0,0-1-1 0 0,-1 1 0 0 0,1-1 1 0 0,0 0-1 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,1 0 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 1 0 0,0-1-1 0 0,3 0 0 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="63">27184 0 10591 0 0,'0'1'235'0'0,"-1"-1"-1"0"0,1 1 0 0 0,-2-1 0 0 0,1 1 1 0 0,0-1-1 0 0,1 1 0 0 0,-1-1 1 0 0,0 1-1 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 1 0 0,-5 34 5146 0 0,4-28-5515 0 0,-3 28 1101 0 0,-53 391 2839 0 0,53-397-3682 0 0,-2 54 0 0 0,6-83-201 0 0,0-1 0 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,1-1-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1-1 0 0,1 0 1 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="64">27646 125 9215 0 0,'1'0'220'0'0,"-1"0"0"0"0,0-1 0 0 0,0 1 0 0 0,1 0-1 0 0,-1-1 1 0 0,0 1 0 0 0,1 0 0 0 0,-1-1-1 0 0,1 1 1 0 0,-1 0 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,17 0 3617 0 0,-17 0-3915 0 0,13 1 527 0 0,0 0 0 0 0,-1 1 0 0 0,0 0 0 0 0,1 1 0 0 0,-1 1 0 0 0,-1 0 0 0 0,2 1 0 0 0,-2 0 0 0 0,0 1 0 0 0,0 1 0 0 0,0 0 0 0 0,12 9 0 0 0,-23-15-419 0 0,1 0 0 0 0,-2 0 0 0 0,2 0 1 0 0,0 0-1 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 1 0 0,0 0-1 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,0 3 0 0 0,0-1 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,-1 0 1 0 0,1-1 0 0 0,-3 4-1 0 0,-3 4-89 0 0,-1 0 1 0 0,0-1-1 0 0,-1-1 0 0 0,-18 15 0 0 0,-45 29-1537 0 0,72-52 1560 0 0,-1 0-1 0 0,1 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,0 1 0 0 0,0-1 1 0 0,-1 0-1 0 0,1 1 1 0 0,0-1-1 0 0,-1 1 0 0 0,1-1 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,-1-1 1 0 0,1 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0-1 1 0 0,1 0-1 0 0,-1 1 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,1-1 0 0 0,-1 1 1 0 0,0-1-1 0 0,0 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 0 1 0 0,1 1-1 0 0,0 0 1 0 0,20 14-580 0 0,-11-9 435 0 0,-2 0 152 0 0,1 1 1 0 0,0 1 0 0 0,-1 0-1 0 0,0 0 1 0 0,-1 1 0 0 0,8 10 0 0 0,-14-17 85 0 0,1 1 0 0 0,0 0 0 0 0,-1 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,0 1-1 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,1-1-1 0 0,-2 3 0 0 0,-3 1 244 0 0,1 0 1 0 0,0 0-1 0 0,0-1 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,-11 6 1 0 0,12-9-123 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,-10 0 0 0 0,13 0-180 0 0,2 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0-1 1 0 0,0 1-1 0 0,1 0 0 0 0,-1 0 1 0 0,0-1-1 0 0,1 1 1 0 0,-1 0-1 0 0,0-1 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 1 1 0 0,1-1-1 0 0,-1 1 1 0 0,1-1-1 0 0,-2 0 0 0 0,2 0-112 0 0,0 1 1 0 0,1 0-1 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 1 0 0,0-1-1 0 0,0 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,1-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,1-1 0 0 0,0 1 0 0 0,6-1-1629 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="65">28119 153 15343 0 0,'2'5'471'0'0,"0"-1"0"0"0,-1 1 0 0 0,0 0-1 0 0,1-1 1 0 0,-2 1 0 0 0,1 0 0 0 0,-1 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,-1 0 0 0 0,0 7 0 0 0,-3 25 993 0 0,-1 1 1 0 0,-14 50 0 0 0,-16 70-672 0 0,31-140-724 0 0,-2 22-1 0 0,4-21-21 0 0,4-7-987 0 0,-2-12 853 0 0,0 1-1 0 0,0-1 0 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,2 1 0 0 0,-2-1 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 1 0 0 0,0-1 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0-1 0 0 0,3 0-1596 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="66">28624 188 6911 0 0,'-6'3'1378'0'0,"-10"-3"8035"0"0,7 0-5723 0 0,3 0-3853 0 0,-4 2 502 0 0,1 1 0 0 0,-1-1 0 0 0,1 2 1 0 0,0-1-1 0 0,0 2 0 0 0,0-1 0 0 0,1 1 1 0 0,0 0-1 0 0,0 1 0 0 0,0 0 1 0 0,1 0-1 0 0,-11 11 0 0 0,16-15-334 0 0,1 0 1 0 0,-1 0-1 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 1 0 0,0 0-1 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,0 4 1 0 0,1-2-14 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1-1 0 0,4 5 1 0 0,1 1-46 0 0,1 0 0 0 0,1 0 0 0 0,0-1 0 0 0,18 14-1 0 0,-13-12 37 0 0,0 0 0 0 0,-1 1 0 0 0,-1 0 0 0 0,17 22 0 0 0,-26-30 23 0 0,0 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,1 1 1 0 0,-2-1 0 0 0,1 0-1 0 0,0 1 1 0 0,-1-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1-1-1 0 0,0 1 1 0 0,-1 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,-3 5 1 0 0,2-4 78 0 0,-1-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,-1-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,-2 0 1 0 0,2-1 0 0 0,0 0 0 0 0,-2 1-1 0 0,1-2 1 0 0,0 1 0 0 0,-1-1-1 0 0,2 0 1 0 0,-3 0 0 0 0,1 0 0 0 0,1-1-1 0 0,-2 0 1 0 0,0 0 0 0 0,-10 1-1 0 0,13-2-151 0 0,-1 0 0 0 0,1 0 0 0 0,0-1-1 0 0,0 1 1 0 0,-1-1 0 0 0,1-1 0 0 0,0 1-1 0 0,-1 0 1 0 0,1-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,1-1 0 0 0,-2 1-1 0 0,1-1 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,-3-4 1 0 0,7 6-93 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0-2-1128 0 0</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="67">28879 680 5983 0 0,'7'16'13120'0'0,"-5"-15"-12328"0"0,3 1-504 0 0,-1-1-104 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="68">29238 209 7367 0 0,'3'0'575'0'0,"1"1"0"0"0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,1 1 0 0 0,-1-1-1 0 0,6 5 1 0 0,8 3 2087 0 0,7 2-1628 0 0,0 0 1 0 0,-1 2 0 0 0,-1 1-1 0 0,23 18 1 0 0,-35-23-790 0 0,0-1 0 0 0,0 1 0 0 0,-1 1-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 1 0 0 0,-1 0 0 0 0,9 17 0 0 0,-15-25-208 0 0,0 0-1 0 0,0-1 1 0 0,-1 1 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,-1 1 0 0 0,1 0 0 0 0,-2 5-1 0 0,0-3-3 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 1 0 0,0-1 0 0 0,-6 6-1 0 0,-3 2 247 0 0,0-1 0 0 0,-1-1 0 0 0,0 0 0 0 0,-18 10 0 0 0,-34 16 2316 0 0,-3-7-5312 0 0,46-24 2444 0 0,18-4 267 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-6 4-1 0 0,10-5 6 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,6 5 0 0 0,9 2 0 0 0,-2-3 231 0 0,0-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,0-1-1 0 0,-1 0 1 0 0,1-1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1-1 0 0 0,18-4 0 0 0,-7 0-1984 0 0,-7 3-2319 0 0,-7 1-1014 0 0,0 0-1934 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="69">30146 240 6911 0 0,'0'0'528'0'0,"-13"0"7323"0"0,-26 3-3489 0 0,-72 10 393 0 0,97-11-4323 0 0,-1 1 0 0 0,1 1 0 0 0,0 0 0 0 0,-20 8 0 0 0,33-11-425 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 1 1 0 0,1-1-1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 2 0 0 0,3 5-40 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,7 8 1 0 0,-5-7 18 0 0,2 3-27 0 0,1-1 0 0 0,1 0 0 0 0,17 14-1 0 0,-14-13 25 0 0,21 23-1 0 0,-31-30 19 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,0 1 0 0 0,0-1-1 0 0,2 9 1 0 0,-3-12 22 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-2 2 0 0 0,1-2 50 0 0,0 0 0 0 0,0 0 0 0 0,-1-1-1 0 0,1 1 1 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1-1 0 0,0 1 1 0 0,0-1 0 0 0,1 0 0 0 0,-4 1-1 0 0,-74-1 1235 0 0,32-1-705 0 0,40 1-83 0 0,-9 0-594 0 0,6 0-4589 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="70">20626 4307 7343 0 0,'-9'-9'8159'0'0,"9"9"-8044"0"0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,8 6 1568 0 0,18 7-1120 0 0,-19-10 166 0 0,-1-1-492 0 0,0 0 0 0 0,0 0 0 0 0,0-1-1 0 0,0 0 1 0 0,1 0 0 0 0,-1-1-1 0 0,1 1 1 0 0,9-1 0 0 0,3 0 412 0 0,31-4 1 0 0,-12 0-122 0 0,52-4 137 0 0,-40 7-518 0 0,0-2 0 0 0,0-2 1 0 0,-1-3-1 0 0,52-13 0 0 0,-73 13-91 0 0,1 2 0 0 0,0 1 0 0 0,0 2 0 0 0,46 0 0 0 0,116 21 200 0 0,13 0-139 0 0,24 3 22 0 0,-26-1 63 0 0,2-17 15 0 0,-93-3-113 0 0,-19 2 6 0 0,0-5 0 0 0,97-15 0 0 0,-126 9-3 0 0,90-1 0 0 0,64 16-62 0 0,188-4 147 0 0,12-24-64 0 0,-271 23-101 0 0,32-1 10 0 0,-46-11-17 0 0,96-2 24 0 0,128 18 20 0 0,-186 3 255 0 0,-86-3-329 0 0,158 2-109 0 0,-125-5 137 0 0,156 13 101 0 0,-219-11-110 0 0,9 2-9 0 0,-37-3 0 0 0,36 1 0 0 0,79-7 19 0 0,145 4 222 0 0,-150-4-101 0 0,-94 0-62 0 0,-20 2-19 0 0,0-1 1 0 0,30-6-1 0 0,-50 7-49 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,3 0 0 0 0,10 0 190 0 0,-7-26-5848 0 0,-5 20 3712 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="71">27037 3909 2759 0 0,'1'6'14249'0'0,"5"20"-10206"0"0,-5 7-2610 0 0,-1 0-1 0 0,-6 44 1 0 0,-16 66-299 0 0,3-26-530 0 0,7-36 212 0 0,-3-1-1 0 0,-28 82 1 0 0,35-137-481 0 0,-2-1 1 0 0,-1 0 0 0 0,-16 27-1 0 0,26-48-488 0 0,4-6-376 0 0,7-9-2165 0 0,-8 10 1718 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="72">18780 1717 13791 0 0,'-13'3'787'0'0,"0"0"0"0"0,1 1 0 0 0,0 0 0 0 0,0 1 0 0 0,-15 9 0 0 0,-54 35 2384 0 0,62-37-2774 0 0,1 1 0 0 0,0 0 0 0 0,1 2 0 0 0,-29 30-1 0 0,45-44-395 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 3 0 0 0,1-1-23 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,6 3-1 0 0,53 35-223 0 0,-7-5 141 0 0,-32-20 67 0 0,-2 2 0 0 0,0 0 1 0 0,22 25-1 0 0,-41-41 71 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,-1 3 0 0 0,0-2 75 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,-1 1 1 0 0,1-1-1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,0-1 0 0 0,1 1 0 0 0,-5 3 0 0 0,-1 0 169 0 0,-1 0 1 0 0,0-1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1-1 0 0 0,-12 3 0 0 0,-12-1 250 0 0,-1-2 1 0 0,0-2 0 0 0,-64-6-1 0 0,88 5-561 0 0,-3-1-943 0 0,12 2 868 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 1 0 0,1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 0 0 0,1 0 1 0 0,-1 0-1 0 0,0-1 0 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 1 0 0,0 0-1 0 0,0-1 0 0 0,1 1 0 0 0,1-5-1969 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="68">29238 209 7367 0 0,'3'0'575'0'0,"1"1"0"0"0,-2 0-1 0 0,3 0 1 0 0,-2 0-1 0 0,0 0 1 0 0,1 1 0 0 0,-1-1-1 0 0,6 5 1 0 0,8 3 2087 0 0,7 2-1628 0 0,0 0 1 0 0,-1 2 0 0 0,-1 1-1 0 0,23 18 1 0 0,-35-23-790 0 0,0-1 0 0 0,0 1 0 0 0,-1 1-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 1 0 0 0,-1 0 0 0 0,9 17 0 0 0,-15-25-208 0 0,0 0-1 0 0,0-1 1 0 0,-1 1 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,-1 1 0 0 0,1 0 0 0 0,-2 5-1 0 0,0-3-3 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 1 0 0,0-1 0 0 0,-6 6-1 0 0,-2 2 247 0 0,-2-1 0 0 0,0-1 0 0 0,0 0 0 0 0,-18 10 0 0 0,-34 16 2316 0 0,-3-7-5312 0 0,46-24 2444 0 0,18-4 267 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-6 4-1 0 0,10-5 6 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,6 5 0 0 0,9 2 0 0 0,-2-3 231 0 0,0-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,0-1-1 0 0,-1 0 1 0 0,1-1 0 0 0,0-1 0 0 0,0 0 0 0 0,0-1 0 0 0,16-4 0 0 0,-6 0-1984 0 0,-7 3-2319 0 0,-7 1-1014 0 0,0 0-1934 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="69">30146 240 6911 0 0,'0'0'528'0'0,"-13"0"7323"0"0,-26 3-3489 0 0,-72 10 393 0 0,97-11-4323 0 0,-1 1 0 0 0,1 1 0 0 0,0 0 0 0 0,-20 8 0 0 0,33-11-425 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 1 1 0 0,1-1-1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 2 0 0 0,3 5-40 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,6 8 1 0 0,-3-7 18 0 0,1 3-27 0 0,1-1 0 0 0,1 0 0 0 0,17 14-1 0 0,-14-13 25 0 0,21 23-1 0 0,-31-30 19 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,0 1 0 0 0,0-1-1 0 0,2 9 1 0 0,-3-12 22 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,-2-1 0 0 0,1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-2 2 0 0 0,1-2 50 0 0,0 0 0 0 0,0 0 0 0 0,-1-1-1 0 0,2 1 1 0 0,-2-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1-1 0 0,0 1 1 0 0,0-1 0 0 0,1 0 0 0 0,-4 1-1 0 0,-74-1 1235 0 0,32-1-705 0 0,40 1-83 0 0,-9 0-594 0 0,6 0-4589 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="70">20626 4307 7343 0 0,'-9'-9'8159'0'0,"9"9"-8044"0"0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,8 6 1568 0 0,18 7-1120 0 0,-19-10 166 0 0,0-1-492 0 0,-2 0 0 0 0,1 0 0 0 0,-1-1-1 0 0,2 0 1 0 0,0 0 0 0 0,-1-1-1 0 0,1 1 1 0 0,9-1 0 0 0,3 0 412 0 0,31-4 1 0 0,-12 0-122 0 0,52-4 137 0 0,-40 7-518 0 0,0-2 0 0 0,0-2 1 0 0,-1-3-1 0 0,52-13 0 0 0,-73 13-91 0 0,1 2 0 0 0,0 1 0 0 0,0 2 0 0 0,46 0 0 0 0,116 21 200 0 0,13 0-139 0 0,24 3 22 0 0,-26-1 63 0 0,2-17 15 0 0,-93-3-113 0 0,-19 2 6 0 0,0-5 0 0 0,97-15 0 0 0,-126 9-3 0 0,90-1 0 0 0,64 16-62 0 0,189-4 147 0 0,10-24-64 0 0,-270 23-101 0 0,32-1 10 0 0,-47-11-17 0 0,98-2 24 0 0,127 18 20 0 0,-186 3 255 0 0,-86-3-329 0 0,158 2-109 0 0,-125-5 137 0 0,156 13 101 0 0,-219-11-110 0 0,9 2-9 0 0,-37-3 0 0 0,36 1 0 0 0,80-7 19 0 0,143 4 222 0 0,-149-4-101 0 0,-94 0-62 0 0,-20 2-19 0 0,0-1 1 0 0,30-6-1 0 0,-50 7-49 0 0,1-1 0 0 0,-1 1 0 0 0,2 0 0 0 0,-3 0 0 0 0,2 0 0 0 0,0 1 0 0 0,3 0 0 0 0,10 0 190 0 0,-7-26-5848 0 0,-5 20 3712 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="71">27037 3909 2759 0 0,'1'6'14249'0'0,"5"20"-10206"0"0,-5 7-2610 0 0,-1 0-1 0 0,-6 44 1 0 0,-16 66-299 0 0,3-26-530 0 0,8-36 212 0 0,-5-1-1 0 0,-27 82 1 0 0,35-137-481 0 0,-2-1 1 0 0,-1 0 0 0 0,-16 27-1 0 0,26-48-488 0 0,4-6-376 0 0,7-9-2165 0 0,-8 10 1718 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="72">18780 1717 13791 0 0,'-13'3'787'0'0,"0"0"0"0"0,2 1 0 0 0,-2 0 0 0 0,1 1 0 0 0,-15 9 0 0 0,-54 35 2384 0 0,62-37-2774 0 0,1 1 0 0 0,0 0 0 0 0,1 2 0 0 0,-29 30-1 0 0,45-44-395 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 3 0 0 0,1-1-23 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,6 3-1 0 0,53 35-223 0 0,-7-5 141 0 0,-32-20 67 0 0,-2 2 0 0 0,0 0 1 0 0,22 25-1 0 0,-41-41 71 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,-1 3 0 0 0,0-2 75 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,-1 1 1 0 0,1-1-1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0-1 0 0 0,1 1 0 0 0,-5 3 0 0 0,-1 0 169 0 0,-1 0 1 0 0,0-1-1 0 0,0 0 0 0 0,-1 0 0 0 0,2 0 0 0 0,-2-1 0 0 0,1-1 0 0 0,-12 3 0 0 0,-12-1 250 0 0,-1-2 1 0 0,1-2 0 0 0,-66-6-1 0 0,89 5-561 0 0,-3-1-943 0 0,12 2 868 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 1 0 0,1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 0 0 0,1 0 1 0 0,-1 0-1 0 0,0-1 0 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 1 0 0,0 0-1 0 0,0-1 0 0 0,1 1 0 0 0,1-5-1969 0 0</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="73">18629 1589 13679 0 0,'1'10'1614'0'0,"0"0"0"0"0,1 1 0 0 0,5 16 1 0 0,2 11 46 0 0,-2 31-114 0 0,-2 1 0 0 0,-9 129 0 0 0,3-171-1372 0 0,-1 19 342 0 0,-2 0 0 0 0,-2 0 0 0 0,-13 48 1 0 0,17-86-598 0 0,6-17-1533 0 0,3-4-624 0 0,-2 2 548 0 0</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="74">19061 1732 8287 0 0,'5'10'10240'0'0,"-1"3"-6069"0"0,-2 17-3956 0 0,-1-17 1022 0 0,0 13-893 0 0,0 1 1 0 0,-2-1-1 0 0,-1 0 1 0 0,-1 0-1 0 0,-11 42 1 0 0,-48 122 1994 0 0,61-188-2284 0 0,-6 19-271 0 0,7-21 202 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,9-11-1435 0 0,17-31-2723 0 0,-12 22 2431 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="75">19381 1735 7367 0 0,'-10'22'3532'0'0,"-23"56"4006"0"0,5 2-5030 0 0,23-62-2342 0 0,1 0-1 0 0,0 1 0 0 0,1-1 1 0 0,1 1-1 0 0,1 0 1 0 0,2 36-1 0 0,-1-49-152 0 0,1 0 0 0 0,1 0-1 0 0,-1 1 1 0 0,1-2 0 0 0,0 1-1 0 0,4 8 1 0 0,-4-11 3 0 0,-1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,1 0 0 0 0,5 2 0 0 0,-7-2 10 0 0,1-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 0 0 0,0-1 1 0 0,-1 0-1 0 0,1 1 0 0 0,0-1 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1-1 1 0 0,-1 1-1 0 0,2-2 0 0 0,4-5 154 0 0,-1 1 0 0 0,9-13 0 0 0,-15 20-178 0 0,13-20 281 0 0,-2 1-1 0 0,0-2 1 0 0,-1 1-1 0 0,8-24 0 0 0,-14 33-105 0 0,-1 1-1 0 0,0 0 0 0 0,-1-1 0 0 0,0 0 1 0 0,-1 0-1 0 0,0 1 0 0 0,-1-1 0 0 0,0 0 1 0 0,0 0-1 0 0,-4-18 0 0 0,3 25-58 0 0,0 1 1 0 0,0-1-1 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 1 0 0,-5-2-1 0 0,3 2 29 0 0,0 1 0 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 1 0 0,-8 1-1 0 0,13 0-145 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,1-1-1 0 0,-1 0 1 0 0,0 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,3 0-142 0 0,-1 0-1 0 0,0-1 1 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,1-1 0 0 0,-1 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 1 1 0 0,0-1 0 0 0,13 7-1936 0 0,-4-3-720 0 0,2 0-5572 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="76">19746 1718 14399 0 0,'-2'7'442'0'0,"-14"35"2573"0"0,-19 76 0 0 0,33-104-2899 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,1 1 1 0 0,0-1-1 0 0,1 1 0 0 0,0 0 0 0 0,1-1 0 0 0,1 0 0 0 0,5 17 0 0 0,-4-18-111 0 0,0-1-1 0 0,2 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,1-1 0 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,15 15 0 0 0,-19-20 1 0 0,1-1 0 0 0,-1 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,0-1-1 0 0,1 0 1 0 0,-1 0 0 0 0,0-1 0 0 0,7-2-1 0 0,-7 2 108 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,0-1 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1-1-1 0 0,0 0 0 0 0,-1 1 1 0 0,2-12-1 0 0,-1 6 229 0 0,-1 1 1 0 0,-1-1-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,-1 0 1 0 0,0 1-1 0 0,0-1 0 0 0,-1 0 1 0 0,-8-19-1 0 0,3 13-45 0 0,-1 0 0 0 0,-1 0 1 0 0,-1 1-1 0 0,0 0 0 0 0,-1 0 0 0 0,-1 2 0 0 0,0-1 1 0 0,-1 2-1 0 0,-26-20 0 0 0,3-2-1939 0 0,33 32 728 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="75">19381 1735 7367 0 0,'-10'22'3532'0'0,"-23"56"4006"0"0,5 2-5030 0 0,23-62-2342 0 0,1 0-1 0 0,0 1 0 0 0,2-1 1 0 0,-1 1-1 0 0,2 0 1 0 0,2 36-1 0 0,-1-49-152 0 0,1 0 0 0 0,1 0-1 0 0,-1 1 1 0 0,1-2 0 0 0,0 1-1 0 0,4 8 1 0 0,-4-11 3 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,5 2 0 0 0,-7-2 10 0 0,1-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 0 0 0,1-1 1 0 0,-3 0-1 0 0,2 1 0 0 0,0-1 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1-1 1 0 0,-1 1-1 0 0,3-2 0 0 0,2-5 154 0 0,0 1 0 0 0,9-13 0 0 0,-15 20-178 0 0,13-20 281 0 0,-2 1-1 0 0,0-2 1 0 0,-1 1-1 0 0,8-24 0 0 0,-14 33-105 0 0,-1 1-1 0 0,0 0 0 0 0,-1-1 0 0 0,0 0 1 0 0,-1 0-1 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,-3-18 0 0 0,2 25-58 0 0,0 1 1 0 0,0-1-1 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 1 1 0 0,0-1-1 0 0,1 1 0 0 0,-3 0 1 0 0,2 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 1 0 0,-5-2-1 0 0,3 2 29 0 0,0 1 0 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 1 0 0,-8 1-1 0 0,13 0-145 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,1 1 0 0 0,0-1-1 0 0,-2 0 1 0 0,1 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,3 0-142 0 0,-1 0-1 0 0,0-1 1 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,1-1 0 0 0,-1 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,2-1 0 0 0,-2 0 0 0 0,0 0-1 0 0,1 1 1 0 0,0-1 0 0 0,13 7-1936 0 0,-4-3-720 0 0,2 0-5572 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="76">19746 1718 14399 0 0,'-2'7'442'0'0,"-14"35"2573"0"0,-19 76 0 0 0,33-104-2899 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,2 1 1 0 0,0-1-1 0 0,2 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,1 0 0 0 0,5 17 0 0 0,-4-18-111 0 0,0-1-1 0 0,2 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,1-1 0 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,15 15 0 0 0,-19-20 1 0 0,1-1 0 0 0,-1 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,0-1-1 0 0,1 0 1 0 0,-1 0 0 0 0,0-1 0 0 0,7-2-1 0 0,-7 2 108 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,0-1 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1-1-1 0 0,0 0 0 0 0,-1 1 1 0 0,2-12-1 0 0,-1 6 229 0 0,-1 1 1 0 0,-1-1-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,-1 0 1 0 0,0 1-1 0 0,0-1 0 0 0,-1 0 1 0 0,-9-19-1 0 0,5 13-45 0 0,-2 0 0 0 0,-1 0 1 0 0,-1 1-1 0 0,0 0 0 0 0,-1 0 0 0 0,-1 2 0 0 0,0-1 1 0 0,-1 2-1 0 0,-26-20 0 0 0,2-2-1939 0 0,35 32 728 0 0</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -3888,7 +3884,7 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2023-12-12T19:21:11.585"/>
+      <inkml:timestamp xml:id="ts0" timeString="2024-01-09T19:28:28.499"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.035" units="cm"/>
@@ -3915,7 +3911,7 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2023-12-12T19:21:11.586"/>
+      <inkml:timestamp xml:id="ts0" timeString="2024-01-09T19:28:28.500"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.035" units="cm"/>
@@ -3942,14 +3938,14 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2023-12-12T19:21:10.265"/>
+      <inkml:timestamp xml:id="ts0" timeString="2024-01-09T19:28:26.489"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.035" units="cm"/>
       <inkml:brushProperty name="height" value="0.035" units="cm"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">149 5 5248,'0'-4'12507,"0"7"-9495,-2 46 77,-2-13-2524,-13 43 0,2-19-55,-4 80 0,14 63 890,5-190-1303,-15 165 1034,-23 63 527,30-187-1343,-2 16-24,0-25-3339,5-31-307,5-13 2699</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">148 5 5248,'0'-4'12507,"0"7"-9495,-1 46 77,-3-12-2524,-13 41 0,2-18-55,-4 80 0,14 63 890,5-190-1303,-15 165 1034,-23 63 527,30-188-1343,-2 18-24,0-26-3339,5-30-307,5-14 2699</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -3969,7 +3965,7 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2023-12-12T19:21:11.576"/>
+      <inkml:timestamp xml:id="ts0" timeString="2024-01-09T19:28:28.490"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.035" units="cm"/>
@@ -3996,7 +3992,7 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2023-12-12T19:21:11.577"/>
+      <inkml:timestamp xml:id="ts0" timeString="2024-01-09T19:28:28.491"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.035" units="cm"/>
@@ -4023,7 +4019,7 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2023-12-12T19:21:11.583"/>
+      <inkml:timestamp xml:id="ts0" timeString="2024-01-09T19:28:28.497"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.035" units="cm"/>
@@ -4050,7 +4046,7 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2023-12-12T19:21:11.584"/>
+      <inkml:timestamp xml:id="ts0" timeString="2024-01-09T19:28:28.498"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.035" units="cm"/>
@@ -4077,7 +4073,7 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2023-12-12T19:21:11.578"/>
+      <inkml:timestamp xml:id="ts0" timeString="2024-01-09T19:28:28.492"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.035" units="cm"/>
@@ -4104,7 +4100,7 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2023-12-12T19:21:11.579"/>
+      <inkml:timestamp xml:id="ts0" timeString="2024-01-09T19:28:28.493"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.035" units="cm"/>
@@ -4131,7 +4127,7 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2023-12-12T19:21:11.581"/>
+      <inkml:timestamp xml:id="ts0" timeString="2024-01-09T19:28:28.495"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.035" units="cm"/>
@@ -4158,7 +4154,7 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2023-12-12T19:21:11.582"/>
+      <inkml:timestamp xml:id="ts0" timeString="2024-01-09T19:28:28.496"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.035" units="cm"/>
@@ -4185,7 +4181,7 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2023-12-12T19:21:11.580"/>
+      <inkml:timestamp xml:id="ts0" timeString="2024-01-09T19:28:28.494"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.035" units="cm"/>
@@ -4212,7 +4208,7 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2023-12-12T19:21:11.587"/>
+      <inkml:timestamp xml:id="ts0" timeString="2024-01-09T19:28:28.501"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.035" units="cm"/>
@@ -4239,14 +4235,14 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2023-12-12T19:21:10.258"/>
+      <inkml:timestamp xml:id="ts0" timeString="2024-01-09T19:28:26.482"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.035" units="cm"/>
       <inkml:brushProperty name="height" value="0.035" units="cm"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">9 160 7296,'-9'1'14408,"15"-1"-13126,25 3 96,-6-2-1039,191-3 888,-97 0-1024,-34 1-214,182-5 657,83-3-98,152-2-238,-398 12-238,881-9 133,-555 0-204,453-15 105,-443 2-90,9-3-128,1257-25 106,-1234 47 92,1245 16-172,-948 7 194,0 19-34,-329-9-96,338 23 243,-204-15-100,-91-15 121,-371-19-170,202 8 94,-194-9-156,118 2 93,-92-3 2,102 0 22,-162-2-40,67 0-14,50 0 275,126 1-492,-202-3 245,192 0-362,-150-3 69,-38 1 78,-40 2 873,-46-1-243,13 0-450,106-2 168,-64 2-132,-80 1-36,21-2 0,-21 2-49,22-1-1,47 0 480,-89 2-1104,-8-2-3397,-24-1-1440,-4-4 4351</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">8 160 7296,'-8'1'14408,"14"-1"-13126,25 3 96,-6-2-1039,191-3 888,-97 0-1024,-34 1-214,182-5 657,83-3-98,152-3-238,-398 13-238,881-9 133,-554 1-204,450-16 105,-439 2-90,5-3-128,1260-25 106,-1235 47 92,1245 16-172,-949 8 194,3 17-34,-332-8-96,339 23 243,-205-15-100,-89-15 121,-372-19-170,201 8 94,-193-9-156,120 2 93,-95-3 2,103 0 22,-162-2-40,67 1-14,50-1 275,127 1-492,-204-3 245,193 0-362,-150-4 69,-39 2 78,-38 2 873,-47-1-243,12 0-450,108-2 168,-64 2-132,-81 1-36,20-2 0,-20 2-49,23-1-1,46 0 480,-89 2-1104,-9-2-3397,-23-1-1440,-4-4 4351</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -4266,7 +4262,7 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2023-12-12T19:21:11.588"/>
+      <inkml:timestamp xml:id="ts0" timeString="2024-01-09T19:28:28.502"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.035" units="cm"/>
@@ -4297,7 +4293,7 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2023-12-12T19:21:11.593"/>
+      <inkml:timestamp xml:id="ts0" timeString="2024-01-09T19:28:28.507"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.035" units="cm"/>
@@ -4328,7 +4324,7 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2023-12-12T19:21:11.598"/>
+      <inkml:timestamp xml:id="ts0" timeString="2024-01-09T19:28:28.512"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.035" units="cm"/>
@@ -4359,7 +4355,7 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2023-12-12T19:21:11.603"/>
+      <inkml:timestamp xml:id="ts0" timeString="2024-01-09T19:28:28.517"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.035" units="cm"/>
@@ -4390,14 +4386,14 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2023-12-12T19:21:11.766"/>
+      <inkml:timestamp xml:id="ts0" timeString="2024-01-09T19:28:28.710"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.035" units="cm"/>
       <inkml:brushProperty name="height" value="0.035" units="cm"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">18 11 6272,'0'-1'324,"0"1"0,0-1 1,-1 1-1,1-1 1,0 0-1,0 1 0,0-1 1,-1 0-1,1 1 0,-1 0 1,-4-4 8266,5 8-6585,1 7-966,5 21 1,0-11-456,22 200 1826,-26-198-2203,16 187 1269,-16 34 6,-20-91-681,14-120-522,-5 23-362,-15 115-161,14-118 213,3-32-3156,6-36-15160,1 5 16485</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">17 11 6272,'0'-1'324,"0"1"0,0-1 1,0 1-1,0-1 1,0 0-1,0 1 0,0-1 1,-3 0-1,3 1 0,0 0 1,-5-4 8266,5 8-6585,2 7-966,4 21 1,0-11-456,19 200 1826,-22-197-2203,14 186 1269,-14 34 6,-20-91-681,11-121-522,-2 25-362,-15 114-161,15-118 213,-1-32-3156,9-36-15160,0 5 16485</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -4417,14 +4413,14 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2023-12-12T19:21:11.767"/>
+      <inkml:timestamp xml:id="ts0" timeString="2024-01-09T19:28:28.711"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.035" units="cm"/>
       <inkml:brushProperty name="height" value="0.035" units="cm"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">75 50 12160,'-3'0'771,"0"0"-1,0 0 1,-1 1 0,3 0 0,-2 0 0,0 0 0,1-1 0,-1 1 0,0 0 0,0 0 0,-2 3 0,2-2-472,0 0 1,1 0-1,0 0 1,-1 0-1,1 0 1,0 1-1,-2 3 1,0 1-330,1 1 0,0-1 0,0 1 1,-1 15-1,4-9 56,-1 2 1,2-1-1,1 2 1,8 26-1,-2-22 154,2 2 0,21 34 0,-28-53-179,0 1 1,0-1-1,1 0 0,0 0 1,0 0-1,0 0 0,6 3 1,-8-6 7,1 0 1,-1 1 0,0-1-1,0 0 1,1 0-1,0 0 1,-2 0 0,2-1-1,0 1 1,0-1 0,0 1-1,0-1 1,-1 1 0,1-1-1,0 0 1,-1 1 0,2-1-1,-2 0 1,1-1 0,5 0-1,3 0 23,-1-1-1,-1-1 0,2 1 1,-2-1-1,1 0 1,-1-1-1,0 1 0,0-1 1,-1-1-1,0 1 1,0-1-1,-1 0 0,12-10 1,-7 7 85,-2-2 0,-1 1 0,-1-1 0,0 0 0,0 0 0,-2-2 0,9-18 0,-12 24 79,-1-1 1,-1 1-1,0-1 0,0 1 0,-1-2 1,-1 1-1,-1-8 0,1 10-66,-1 0 0,0 0 0,-1 1 0,0-1 0,0 0 0,0 1 0,-1-1 0,0 0 0,-9-7-1,4 4 67,0 2-1,-2-1 0,0 1 0,0 0 0,-1 0 0,-18-7 0,-81-21 722,82 25-1488,20 6 563,1-2-4605,7 5 4400,1-1-1,0 1 0,-1 0 0,1 0 0,0-1 0,0 1 0,0 0 0,0 0 1,0 0-1,0 0 0,0-1 0,0 1 0,0 0 0,0-1 0,0 1 0,0 0 0,0 0 1,0-1-1,0 1 0,0 0 0,0-1 0,0 1 0,0 0 0,0 0 0,1 0 1,-1 0-1,0-1 0,1 1 0,-1 0 0,0 0 0,0-1 0,0 1 0,1 0 1,-1 0-1,1 0 0,-1 0 0,0-1 0,0 1 0,1 0 0,-1 0 0,1 0 1,-1 0-1,0 0 0,4-1-1439</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">75 50 12160,'-2'0'771,"-2"0"-1,1 0 1,-1 1 0,3 0 0,-2 0 0,0 0 0,1-1 0,-1 1 0,1 0 0,-2 0 0,0 3 0,0-2-472,1 0 1,0 0-1,2 0 1,-2 0-1,1 0 1,0 1-1,-2 3 1,1 1-330,-1 1 0,1-1 0,0 1 1,-1 14-1,4-7 56,-1 1 1,2-1-1,1 1 1,8 27-1,-2-21 154,1 0 0,23 35 0,-29-52-179,-1 0 1,2-2-1,0 1 0,0 0 1,0 0-1,0 0 0,5 3 1,-6-6 7,0 0 1,-1 1 0,0-1-1,0 0 1,1 0-1,0 0 1,-2 0 0,2-1-1,0 1 1,0-1 0,0 1-1,-1-1 1,1 1 0,0-1-1,1 0 1,-3 1 0,3-1-1,-1 0 1,-1-1 0,6 0-1,3 0 23,-1-1-1,0-1 0,0 1 1,-1-1-1,1 0 1,-1-1-1,0 1 0,0-1 1,-1-1-1,0 1 1,0 0-1,-1-1 0,12-11 1,-7 8 85,-2-2 0,-1 1 0,-1-1 0,0 0 0,0 1 0,-2-3 0,9-19 0,-13 25 79,1-1 1,-2 1-1,-1-1 0,2 1 0,-2-1 1,-2 0-1,1-8 0,0 10-66,-1 0 0,0 0 0,-1 1 0,0-2 0,0 1 0,0 1 0,-1-1 0,0 0 0,-9-6-1,3 3 67,3 2-1,-5-1 0,1 1 0,1 0 0,-4 0 0,-15-7 0,-82-21 722,82 25-1488,20 6 563,1-2-4605,7 5 4400,1-1-1,0 1 0,-1 0 0,1 0 0,0-1 0,0 1 0,0 0 0,0 0 1,0 0-1,0 0 0,0-1 0,0 1 0,0 0 0,0-1 0,0 1 0,0 0 0,0 0 1,0-1-1,0 1 0,0 0 0,0-1 0,0 1 0,0 0 0,0 0 0,1 0 1,-1 0-1,0-1 0,1 1 0,-1 0 0,0 0 0,0-1 0,0 1 0,1 0 1,-1 0-1,0 0 0,0 0 0,0-1 0,0 1 0,2 0 0,-2 0 0,1 0 1,-1 0-1,0 0 0,4-1-1439</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -4444,7 +4440,7 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2023-12-12T19:21:11.768"/>
+      <inkml:timestamp xml:id="ts0" timeString="2024-01-09T19:28:28.712"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.035" units="cm"/>
@@ -4471,7 +4467,7 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2023-12-12T19:21:11.769"/>
+      <inkml:timestamp xml:id="ts0" timeString="2024-01-09T19:28:28.713"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.035" units="cm"/>
@@ -4498,7 +4494,7 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2023-12-12T19:21:11.770"/>
+      <inkml:timestamp xml:id="ts0" timeString="2024-01-09T19:28:28.714"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.035" units="cm"/>
@@ -4529,14 +4525,14 @@
           <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2023-12-12T19:21:11.771"/>
+      <inkml:timestamp xml:id="ts0" timeString="2024-01-09T19:28:28.715"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.05" units="cm"/>
       <inkml:brushProperty name="height" value="0.05" units="cm"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 144 6911 0 0,'30'-1'7099'0'0,"27"-3"-5605"0"0,-40 3-583 0 0,-1-2-437 0 0,-1 0-1 0 0,1 0 0 0 0,20-9 0 0 0,-15 5-94 0 0,16-5 359 0 0,-16 4-347 0 0,1 2-1 0 0,0 0 1 0 0,28-4-1 0 0,-15 5-69 0 0,53-15 0 0 0,19-3 201 0 0,-38 16-218 0 0,1 3 0 0 0,69 5 0 0 0,12-6-92 0 0,16 2 61 0 0,24 11 143 0 0,-86-13-240 0 0,-17 0 50 0 0,19 10 90 0 0,113 19-1 0 0,-99-8-46 0 0,42 16-85 0 0,-108-19-91 0 0,69 7 0 0 0,125-11 208 0 0,-113-6-91 0 0,50 3-62 0 0,-134-6-137 0 0,146-1 95 0 0,128-13 33 0 0,-291 13-136 0 0,74-3 60 0 0,123 12-1 0 0,-18 6 7 0 0,-53-5-10 0 0,86-9 95 0 0,-169-4-105 0 0,-26 3-31 0 0,357-17 145 0 0,-216 10-842 0 0,55-5 1598 0 0,104 8-855 0 0,-255 10-38 0 0,29 1 12 0 0,31-9 60 0 0,58 0 60 0 0,-159 2-131 0 0,64-9-1 0 0,-59 4-4 0 0,-2 0 33 0 0,75-5-57 0 0,-70 10 16 0 0,153-8 36 0 0,-163 6-61 0 0,151-6 86 0 0,-117 12-60 0 0,241 1 98 0 0,-104-2-82 0 0,6 0 2 0 0,-165-4-27 0 0,219-2 52 0 0,-271 4-58 0 0,378 8 64 0 0,-335-6-64 0 0,76 14 0 0 0,-70-7 0 0 0,189 12 64 0 0,3-30 11 0 0,-158 9 95 0 0,-74 1-36 0 0,-13-1 7 0 0,0 0 0 0 0,15-1 1 0 0,24-2 68 0 0,4-1 9 0 0,-47 3-211 0 0,1 1 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 1 0 0 0,1 0 0 0 0,6 2 0 0 0,-7-2-7 0 0,-4 0-171 0 0,1-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0-1 0 0,4-2 1 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 143 6911 0 0,'30'-1'7099'0'0,"27"-3"-5605"0"0,-40 4-583 0 0,-1-4-437 0 0,-1 1-1 0 0,1 0 0 0 0,20-9 0 0 0,-15 6-94 0 0,16-6 359 0 0,-16 3-347 0 0,1 4-1 0 0,0-2 1 0 0,28-2-1 0 0,-15 3-69 0 0,53-13 0 0 0,19-5 201 0 0,-38 18-218 0 0,1 2 0 0 0,69 5 0 0 0,12-6-92 0 0,17 2 61 0 0,22 11 143 0 0,-85-13-240 0 0,-17 0 50 0 0,19 10 90 0 0,113 19-1 0 0,-99-8-46 0 0,42 15-85 0 0,-108-18-91 0 0,70 8 0 0 0,123-13 208 0 0,-112-5-91 0 0,50 3-62 0 0,-134-6-137 0 0,147-1 95 0 0,127-13 33 0 0,-292 14-136 0 0,75-5 60 0 0,123 13-1 0 0,-18 6 7 0 0,-52-5-10 0 0,84-9 95 0 0,-168-4-105 0 0,-26 3-31 0 0,357-17 145 0 0,-216 10-842 0 0,56-4 1598 0 0,103 6-855 0 0,-256 12-38 0 0,31-1 12 0 0,30-7 60 0 0,57-1 60 0 0,-157 1-131 0 0,63-7-1 0 0,-60 2-4 0 0,0 2 33 0 0,74-7-57 0 0,-71 11 16 0 0,154-7 36 0 0,-163 4-61 0 0,151-4 86 0 0,-116 11-60 0 0,240 1 98 0 0,-104-3-82 0 0,6 1 2 0 0,-165-4-27 0 0,219-1 52 0 0,-271 3-58 0 0,378 8 64 0 0,-336-6-64 0 0,78 14 0 0 0,-71-8 0 0 0,189 13 64 0 0,3-30 11 0 0,-158 9 95 0 0,-74 1-36 0 0,-13-1 7 0 0,0 0 0 0 0,15-1 1 0 0,24-2 68 0 0,4 0 9 0 0,-47 2-211 0 0,1 1 0 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 1 0 0 0,1 0 0 0 0,6 1 0 0 0,-7-1-7 0 0,-4 0-171 0 0,2-1 0 0 0,-3 0 0 0 0,2 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,2 1 0 0 0,-3 0-1 0 0,5-2 1 0 0</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -4556,14 +4552,14 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2023-12-12T19:21:10.259"/>
+      <inkml:timestamp xml:id="ts0" timeString="2024-01-09T19:28:26.483"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.035" units="cm"/>
       <inkml:brushProperty name="height" value="0.035" units="cm"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">75 50 12160,'-3'0'771,"0"0"-1,0 0 1,0 1 0,1 0 0,-1 0 0,0 0 0,1-1 0,-1 1 0,0 0 0,1 0 0,-4 3 0,3-2-472,0 0 1,1 0-1,0 0 1,-1 0-1,1 0 1,0 1-1,-2 3 1,0 1-330,1 1 0,0-1 0,0 1 1,-1 14-1,4-7 56,-1 1 1,2 0-1,1 0 1,8 27-1,-2-21 154,2 0 0,21 35 0,-28-53-179,0 1 1,0-1-1,1 0 0,0 0 1,0 0-1,0 0 0,6 3 1,-8-6 7,1 0 1,-1 1 0,0-1-1,0 0 1,1 0-1,0 0 1,-1 0 0,0-1-1,1 1 1,0-1 0,0 1-1,0-1 1,-1 1 0,1-1-1,0 0 1,-1 1 0,2-1-1,-2 0 1,1-1 0,5 0-1,3 0 23,-1-1-1,0-1 0,0 1 1,-1-1-1,1 0 1,-1-1-1,0 1 0,0-1 1,-1-1-1,0 1 1,0-1-1,0 0 0,11-10 1,-8 7 85,-1-2 0,-1 1 0,-1-1 0,0 0 0,0 0 0,-2-1 0,9-20 0,-12 25 79,-1-1 1,-1 1-1,0-1 0,0 1 0,-1-1 1,-1 0-1,-1-9 0,1 11-66,-1 0 0,0 0 0,-1 0 0,1 0 0,-2 0 0,1 1 0,-1-1 0,0 0 0,-9-6-1,4 3 67,0 2-1,-2-1 0,0 1 0,0 0 0,-1 0 0,-18-7 0,-80-21 722,80 25-1488,21 6 563,1-2-4605,7 5 4400,1-1-1,0 1 0,-1 0 0,1 0 0,0-1 0,0 1 0,0 0 0,0 0 1,0 0-1,0 0 0,0-1 0,0 1 0,0 0 0,0-1 0,0 1 0,0 0 0,0 0 1,0-1-1,0 1 0,0 0 0,0-1 0,0 1 0,0 0 0,0 0 0,1 0 1,-1 0-1,0-1 0,1 1 0,-1 0 0,0 0 0,0-1 0,0 1 0,1 0 1,-1 0-1,1 0 0,-1 0 0,0-1 0,0 1 0,1 0 0,-1 0 0,1 0 1,-1 0-1,0 0 0,4-1-1439</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">75 50 12160,'-3'0'771,"0"0"-1,0 0 1,0 1 0,0 0 0,1 0 0,-1 0 0,1-1 0,-1 1 0,0 0 0,1 0 0,-4 3 0,3-2-472,0 0 1,1 0-1,0 0 1,-2 0-1,3 0 1,-1 1-1,-2 3 1,0 2-330,1-1 0,0 0 0,0 1 1,-1 13-1,4-5 56,-1 0 1,2 0-1,1 0 1,8 27-1,-2-20 154,2-1 0,21 34 0,-28-52-179,0 1 1,0-1-1,1 0 0,-1 0 1,2 0-1,-1-1 0,6 5 1,-8-7 7,1 0 1,-1 1 0,0-1-1,0 0 1,1 0-1,0 0 1,-1 0 0,0-1-1,1 1 1,0-1 0,0 1-1,-1-1 1,1 1 0,0-1-1,0 0 1,-1 1 0,2-1-1,-2 0 1,1-1 0,5 0-1,3 0 23,-1-1-1,0-1 0,-1 1 1,1-1-1,-1 0 1,1-2-1,-2 3 0,2-2 1,-3-1-1,2 1 1,-2-1-1,2 0 0,10-10 1,-8 7 85,-1-3 0,-1 2 0,-1-1 0,0 2 0,0-2 0,-3-1 0,10-21 0,-12 26 79,-1-1 1,0 1-1,-1 0 0,0-1 0,-1 0 1,-1 0-1,-2-9 0,2 11-66,-1 0 0,0 0 0,0 0 0,0-1 0,-2 1 0,0 1 0,0-1 0,1 0 0,-11-5-1,6 2 67,-2 2-1,0 0 0,-1-1 0,-1 1 0,1 0 0,-19-7 0,-80-21 722,80 25-1488,20 6 563,3-2-4605,6 5 4400,1-1-1,0 1 0,-1 0 0,1 0 0,0-1 0,0 1 0,0 0 0,0 0 1,0 0-1,0 0 0,0-1 0,0 1 0,0 0 0,0-1 0,0 1 0,0 0 0,0 0 1,0-1-1,0 1 0,0 0 0,0-1 0,0 1 0,0 0 0,0 0 0,1 0 1,-1 0-1,0-1 0,1 1 0,-1 0 0,0 0 0,0-1 0,0 1 0,1 0 1,-1 0-1,1 0 0,-1 0 0,0-1 0,0 1 0,1 0 0,-1 0 0,1 0 1,-1 0-1,0 0 0,3-1-1439</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -4587,7 +4583,7 @@
           <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2023-12-12T19:21:11.772"/>
+      <inkml:timestamp xml:id="ts0" timeString="2024-01-09T19:28:28.716"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.05" units="cm"/>
@@ -4618,27 +4614,27 @@
           <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2023-12-12T19:21:11.773"/>
+      <inkml:timestamp xml:id="ts0" timeString="2024-01-09T19:28:28.717"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.05" units="cm"/>
       <inkml:brushProperty name="height" value="0.05" units="cm"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">152 1310 13183 0 0,'-9'8'497'0'0,"1"-1"-1"0"0,0 1 1 0 0,0 0-1 0 0,1 1 1 0 0,0 0-1 0 0,-11 17 1 0 0,-26 63 2180 0 0,43-87-2676 0 0,-7 16 244 0 0,1 1 0 0 0,0 1 1 0 0,2-1-1 0 0,0 1 1 0 0,-3 24-1 0 0,7-34-182 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,0 0 0 0 0,0 1 0 0 0,1-1 0 0 0,5 8 0 0 0,-7-13-58 0 0,1 0 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,2 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,0-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0-1 0 0,-1-1 1 0 0,0 0 0 0 0,5-1 0 0 0,1-1 9 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,7-9 0 0 0,1-3 61 0 0,-1-1 1 0 0,0 0-1 0 0,-2-1 0 0 0,13-25 0 0 0,-21 36 78 0 0,-1 0 1 0 0,1 0-1 0 0,-2-1 0 0 0,0 0 1 0 0,0 1-1 0 0,-1-1 0 0 0,0 0 1 0 0,0-1-1 0 0,-2 1 0 0 0,1 0 1 0 0,-3-17-1 0 0,1 23 21 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 1 0 0,0 0-1 0 0,1 1 0 0 0,-1-1 0 0 0,-1 1 0 0 0,1-1 1 0 0,0 1-1 0 0,-1 1 0 0 0,0-1 0 0 0,-5-2 0 0 0,0 1-9 0 0,-1 0 0 0 0,0 0 0 0 0,1 1-1 0 0,-1 1 1 0 0,-1-1 0 0 0,1 2 0 0 0,0 0 0 0 0,0 0-1 0 0,-13 1 1 0 0,21 0-168 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-6-2 0 0 0,8 2-16 0 0,-1-1 0 0 0,1 1 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 1 0 0,1 0-1 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 1 0 0,0-1-74 0 0,0 0 1 0 0,0 0 0 0 0,1 1-1 0 0,-1-1 1 0 0,0 0 0 0 0,1 1 0 0 0,-1-1-1 0 0,0 0 1 0 0,1 1 0 0 0,-1-1-1 0 0,1 1 1 0 0,-1-1 0 0 0,1 1-1 0 0,-1-1 1 0 0,2 0 0 0 0,8-8-1532 0 0,4 0-73 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1">3313 1594 9215 0 0,'-8'14'396'0'0,"2"-1"0"0"0,-6 16 0 0 0,-12 60 7044 0 0,13-49-6565 0 0,5-15-934 0 0,-8 50 1 0 0,14-68-4433 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2">6497 1329 11519 0 0,'19'0'968'0'0,"0"1"0"0"0,0 2-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 2-1 0 0,26 10 1 0 0,-32-10-881 0 0,-1 1 1 0 0,1 0 0 0 0,-1 1-1 0 0,0 0 1 0 0,-1 1-1 0 0,1 0 1 0 0,-2 1-1 0 0,1 0 1 0 0,14 17 0 0 0,-23-23-60 0 0,0 0 1 0 0,0-1 0 0 0,0 1 0 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,-1 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1-1 0 0,-1-1 1 0 0,1 1 0 0 0,0-1 0 0 0,-1 1-1 0 0,0-1 1 0 0,0 7 0 0 0,-1-5 21 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1-1 0 0,-1 1 1 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,-3 3 0 0 0,-5 3 116 0 0,-1 0 1 0 0,1-1-1 0 0,-1-1 0 0 0,-24 11 0 0 0,-8 5 315 0 0,43-22-445 0 0,-1 0-1 0 0,0 0 1 0 0,1 0 0 0 0,0 1-1 0 0,-1-1 1 0 0,1 0-1 0 0,0 1 1 0 0,-1-1 0 0 0,1 0-1 0 0,0 1 1 0 0,0 0 0 0 0,0-1-1 0 0,1 1 1 0 0,-1 0-1 0 0,0-1 1 0 0,0 1 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0-1-1 0 0,0 1 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 1 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1-1 0 0 0,1 1-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,3 3-1 0 0,2 0-29 0 0,0 1 0 0 0,0-2 0 0 0,0 1 1 0 0,0 0-1 0 0,1-1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 1 0 0,1 0-1 0 0,-1 0 0 0 0,0-1 0 0 0,0 0 0 0 0,15-1 0 0 0,13-4-1636 0 0,4-1-6140 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">152 1310 13183 0 0,'-10'8'497'0'0,"3"-1"-1"0"0,-1 1 1 0 0,0 0-1 0 0,1 1 1 0 0,0 0-1 0 0,-11 17 1 0 0,-26 63 2180 0 0,44-87-2676 0 0,-9 16 244 0 0,2 1 0 0 0,0 1 1 0 0,2-1-1 0 0,0 1 1 0 0,-3 24-1 0 0,7-34-182 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,0 0 0 0 0,0 1 0 0 0,1-1 0 0 0,5 8 0 0 0,-7-13-58 0 0,1 0 0 0 0,-1-1 0 0 0,1 0 0 0 0,1 0 0 0 0,-3 0 0 0 0,3 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,0-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,2 1 0 0 0,-1-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1-1 0 0 0,0 0 0 0 0,-2 0 0 0 0,1 0 0 0 0,0 0 0 0 0,2 0-1 0 0,-3-1 1 0 0,1 0 0 0 0,4-1 0 0 0,3-1 9 0 0,-2-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,7-9 0 0 0,1-3 61 0 0,-1-1 1 0 0,0 0-1 0 0,-2-1 0 0 0,13-25 0 0 0,-22 36 78 0 0,1 0 1 0 0,0 0-1 0 0,-2-1 0 0 0,0 0 1 0 0,0 1-1 0 0,-1-1 0 0 0,0 0 1 0 0,0-1-1 0 0,-2 1 0 0 0,1 0 1 0 0,-3-17-1 0 0,1 23 21 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 1 0 0 0,-1 0 0 0 0,2-1 0 0 0,-2 1 1 0 0,0 0-1 0 0,1 1 0 0 0,-1-1 0 0 0,-1 1 0 0 0,1-1 1 0 0,0 1-1 0 0,-1 1 0 0 0,0-1 0 0 0,-5-2 0 0 0,0 1-9 0 0,-1 0 0 0 0,0 0 0 0 0,1 1-1 0 0,-1 1 1 0 0,-1-1 0 0 0,1 2 0 0 0,0 0 0 0 0,0 0-1 0 0,-13 1 1 0 0,21 0-168 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-6-2 0 0 0,8 2-16 0 0,-1-1 0 0 0,1 1 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-2 0 1 0 0,2 0-1 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 1 0 0,0-1-74 0 0,0 0 1 0 0,0 0 0 0 0,2 1-1 0 0,-2-1 1 0 0,0 0 0 0 0,1 1 0 0 0,-1-1-1 0 0,0 0 1 0 0,1 1 0 0 0,-1-1-1 0 0,1 1 1 0 0,-1-1 0 0 0,1 1-1 0 0,-1-1 1 0 0,2 0 0 0 0,7-8-1532 0 0,6 0-73 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1">3313 1594 9215 0 0,'-9'14'396'0'0,"4"-1"0"0"0,-7 16 0 0 0,-12 60 7044 0 0,13-49-6565 0 0,5-15-934 0 0,-8 50 1 0 0,14-68-4433 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2">6497 1329 11519 0 0,'19'0'968'0'0,"-1"1"0"0"0,1 2-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 2-1 0 0,26 10 1 0 0,-31-10-881 0 0,-2 1 1 0 0,0 0 0 0 0,0 1-1 0 0,1 0 1 0 0,-3 1-1 0 0,2 0 1 0 0,-1 1-1 0 0,-1 0 1 0 0,16 17 0 0 0,-25-23-60 0 0,1 0 1 0 0,0-1 0 0 0,0 1 0 0 0,1 1 0 0 0,-1-1-1 0 0,0 0 1 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1-1 0 0,-1-1 1 0 0,1 1 0 0 0,0-1 0 0 0,-1 1-1 0 0,0-1 1 0 0,0 7 0 0 0,-1-5 21 0 0,0-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,1-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,-4 3 0 0 0,-3 3 116 0 0,-2 0 1 0 0,0-1-1 0 0,1-1 0 0 0,-26 11 0 0 0,-6 5 315 0 0,42-22-445 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,1 1-1 0 0,-1-1 1 0 0,1 0-1 0 0,0 1 1 0 0,-1-1 0 0 0,2 0-1 0 0,-1 1 1 0 0,0 0 0 0 0,0-1-1 0 0,1 1 1 0 0,-1 0-1 0 0,0-1 1 0 0,0 1 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0-1-1 0 0,0 1 1 0 0,-2 0-1 0 0,2 0 1 0 0,0 0 0 0 0,0 0-1 0 0,2 0 1 0 0,-2-1-1 0 0,0 1 1 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1-1 0 0 0,1 1-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,-1-1-1 0 0,1 1 1 0 0,0-1 0 0 0,3 3-1 0 0,3 0-29 0 0,-2 1 0 0 0,1-2 0 0 0,1 1 1 0 0,-2 0-1 0 0,3-1 0 0 0,-2-1 0 0 0,0 1 0 0 0,2-1 0 0 0,-2 0 0 0 0,2 0 0 0 0,-2-1 1 0 0,2 0-1 0 0,0 0 0 0 0,-2-1 0 0 0,2 0 0 0 0,13-1 0 0 0,14-4-1636 0 0,4-1-6140 0 0</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3">476 0 5983 0 0,'-5'2'9588'0'0,"6"9"-7470"0"0,1 13-916 0 0,-2 1 0 0 0,0-1 1 0 0,-7 40-1 0 0,-20 72-293 0 0,10-61-320 0 0,-70 328 763 0 0,67-323-1190 0 0,-5 25 31 0 0,25-104-246 0 0,6-5-3814 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4">355 497 8751 0 0,'-1'1'338'0'0,"1"0"-1"0"0,-1 0 1 0 0,0 1-1 0 0,0-1 0 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,1-1 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,0 1-1 0 0,0-1 1 0 0,0 4-1 0 0,0-5-153 0 0,1 0-1 0 0,-1 1 1 0 0,0-1 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,0 1-1 0 0,0-1 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 1 1 0 0,1-1 0 0 0,-1 0-1 0 0,0 0 1 0 0,1 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,1 0-1 0 0,0 0 1 0 0,15 0 839 0 0,39-14 961 0 0,-42 10-1798 0 0,0 0 0 0 0,1 1 0 0 0,-1 1-1 0 0,15-2 1 0 0,533 4 996 0 0,-523 1-1145 0 0,-7-1 1 0 0,99 0 169 0 0,270 13 302 0 0,-318-7-361 0 0,576 23 882 0 0,-266-16-766 0 0,448 1 100 0 0,-279-21-247 0 0,589 8 11 0 0,-1051 2-128 0 0,23 2 0 0 0,169 5 0 0 0,144 2 0 0 0,357 4 0 0 0,-594-14 0 0 0,140-2 0 0 0,391-10 141 0 0,-142 19 331 0 0,-305 11 48 0 0,-112-6-78 0 0,-157-13-407 0 0,39 1 107 0 0,-47-2-137 0 0,0 0 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,5-3 0 0 0,-9 3-127 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0-1 0 0,-1 1 1 0 0,1-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0-1 0 0,1 0 1 0 0,-1-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0-2 0 0 0,-5-9-8533 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5">3406 139 8751 0 0,'-1'4'820'0'0,"1"-1"0"0"0,-1 1 0 0 0,1-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,3 6 0 0 0,0 12 346 0 0,0 67 1328 0 0,-11 96 1 0 0,-22 87-1016 0 0,29-266-1440 0 0,-1 8-213 0 0,1 1 1 0 0,0-1 0 0 0,1 1-1 0 0,1 0 1 0 0,0-1 0 0 0,5 22-1 0 0,-4-29-1499 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6">6996 131 11519 0 0,'-1'2'383'0'0,"0"1"0"0"0,0-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,1-1 0 0 0,-1 1 0 0 0,1-1-1 0 0,0 1 1 0 0,0 5 0 0 0,0 1 437 0 0,-33 217 4930 0 0,19-147-4392 0 0,-8 155-1 0 0,22-231-1317 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,1 6 0 0 0,-2-9-141 0 0,0 1 0 0 0,0-1 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 1 0 0 0,1-1 1 0 0,-1 1-1 0 0,1-1 0 0 0,-1 1 1 0 0,0-1-1 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="7">9343 598 8695 0 0,'-1'1'269'0'0,"0"0"0"0"0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 1-1 0 0,0-1 1 0 0,1 0-1 0 0,-1 1 1 0 0,0-1 0 0 0,1 0-1 0 0,-1 1 1 0 0,1-1-1 0 0,0 0 1 0 0,-1 1 0 0 0,1-1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,0 0 0 0 0,2 3-1 0 0,-1-1-13 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,1 0 0 0 0,3 3 0 0 0,2-1-61 0 0,1-1-1 0 0,-1 1 1 0 0,0-1-1 0 0,1 0 1 0 0,-1-1-1 0 0,1 0 1 0 0,15 2-1 0 0,66-2 364 0 0,-69-2-442 0 0,286 21 1520 0 0,-303-21-1594 0 0,94 4 1192 0 0,-68-5-1578 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="8">9944 175 6911 0 0,'2'2'315'0'0,"0"-1"0"0"0,-1 0-1 0 0,1 1 1 0 0,0-1 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 3 0 0 0,11 33 3484 0 0,-9-23-3491 0 0,6 22 579 0 0,-2 0 0 0 0,-2 1 0 0 0,-1-1 0 0 0,-2 64 0 0 0,-24 150 1277 0 0,-18-50-595 0 0,23-135-754 0 0,-9 95-1 0 0,23-137-694 0 0,1-10-42 0 0,1-1 0 0 0,1 1 0 0 0,1 23 0 0 0,-1-37-140 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,1 0 1 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 1 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 1 0 0 0,1-1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0-1 0 0,0-1 1 0 0,1 1 0 0 0,4-3-1658 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="9">9617 1785 9215 0 0,'0'3'1719'0'0,"6"0"457"0"0,12 4 1249 0 0,-12-4-3278 0 0,10 4 604 0 0,0 1 0 0 0,0 0 0 0 0,25 20 0 0 0,-32-21-593 0 0,0 1 0 0 0,0 0-1 0 0,-1 0 1 0 0,0 1 0 0 0,-1 0-1 0 0,12 18 1 0 0,-17-23-119 0 0,0-1 0 0 0,-1 1 1 0 0,1 0-1 0 0,-1-1 0 0 0,0 1 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 1 0 0,-1 0-1 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 1 0 0,0 0-1 0 0,-3 4 0 0 0,-1 0 87 0 0,0 1-1 0 0,-1-1 1 0 0,1 0-1 0 0,-1 0 1 0 0,-1-1-1 0 0,1 0 1 0 0,-1 0-1 0 0,-17 8 0 0 0,-14 9 166 0 0,39-23-297 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,10 13-251 0 0,-10-13 224 0 0,0 1 26 0 0,0-1-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,-1 1-1 0 0,1 0 1 0 0,-1-1-1 0 0,1 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,-1 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,-1 2-1 0 0,0-2 40 0 0,0 1 1 0 0,0-1-1 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,-2 1 0 0 0,-5 2 189 0 0,0-1-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1-2-1 0 0,-10 3 0 0 0,9-3-5 0 0,0 0-1 0 0,0-1 1 0 0,-13-1-1 0 0,21 0-339 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,1 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,-4-3 0 0 0,1-4-1035 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="10">9913 747 7367 0 0,'19'7'6884'0'0,"5"-1"-4785"0"0,35 3 0 0 0,72-1-707 0 0,-65-5-818 0 0,173 2 898 0 0,41 3-312 0 0,-122 3-727 0 0,76 6-34 0 0,416 12 1273 0 0,-173-39-505 0 0,-212 6-478 0 0,-239 6-483 0 0,-2 0-837 0 0,-8-3-2567 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="11">12647 352 4607 0 0,'-2'3'1087'0'0,"0"0"0"0"0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 5 0 0 0,-9 29 3507 0 0,8-26-4452 0 0,-33 150 3998 0 0,20-85-2926 0 0,-35 103-1 0 0,25-114-679 0 0,-11 34 316 0 0,36-96-823 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 3 1 0 0,0-6-211 0 0,0 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1-1 0 0,0 1 1 0 0,1-1 0 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="12">12197 1505 14399 0 0,'-1'1'199'0'0,"1"0"-1"0"0,-1 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,0 1-1 0 0,1-1 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 3 1 0 0,-2 29 2330 0 0,2-22-2558 0 0,0-3 170 0 0,0 0 1 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1-1 0 0,1 0 1 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,9 5 0 0 0,-11-8-91 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 0-1 0 0,0-1 1 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 0-1 0 0,-1-1 1 0 0,0 1 0 0 0,7-3 0 0 0,-3 1-56 0 0,-1-1 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,0-2 0 0 0,0 1 0 0 0,0-1 0 0 0,12-11 0 0 0,-2 0-2086 0 0,19-21 1 0 0,-19 16-5376 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="13">12560 1591 13127 0 0,'-28'59'4429'0'0,"-40"120"0"0"0,48-120-3848 0 0,-46 161 1793 0 0,53-151-3448 0 0,13-67-64 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4">355 497 8751 0 0,'-1'1'338'0'0,"1"0"-1"0"0,-1 0 1 0 0,0 1-1 0 0,0-1 0 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,1-1 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,0 1-1 0 0,0-1 1 0 0,0 4-1 0 0,0-5-153 0 0,1 0-1 0 0,-1 1 1 0 0,0-1 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,0 1-1 0 0,0-1 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 1 1 0 0,1-1 0 0 0,-1 0-1 0 0,0 0 1 0 0,1 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,1 0-1 0 0,0 0 1 0 0,15 0 839 0 0,39-14 961 0 0,-42 10-1798 0 0,0 0 0 0 0,1 1 0 0 0,-2 1-1 0 0,17-2 1 0 0,531 4 996 0 0,-521 1-1145 0 0,-8-1 1 0 0,99 0 169 0 0,270 13 302 0 0,-318-7-361 0 0,576 23 882 0 0,-266-16-766 0 0,448 1 100 0 0,-280-21-247 0 0,591 8 11 0 0,-1052 2-128 0 0,23 2 0 0 0,168 5 0 0 0,146 2 0 0 0,355 4 0 0 0,-592-14 0 0 0,139-2 0 0 0,390-10 141 0 0,-141 19 331 0 0,-304 11 48 0 0,-114-6-78 0 0,-155-13-407 0 0,38 1 107 0 0,-48-2-137 0 0,1 0 0 0 0,2-1 0 0 0,-3 0 0 0 0,1 0 0 0 0,2 0 0 0 0,-3 0 0 0 0,6-3 0 0 0,-8 3-127 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0-1 0 0,-1 1 1 0 0,1-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0-1 0 0,1 0 1 0 0,-1-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0-2 0 0 0,-4-9-8533 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5">3405 139 8751 0 0,'0'4'820'0'0,"0"-1"0"0"0,-1 1 0 0 0,1-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,2 6 0 0 0,2 12 346 0 0,-1 67 1328 0 0,-12 96 1 0 0,-21 87-1016 0 0,29-266-1440 0 0,-1 8-213 0 0,2 1 1 0 0,-1-1 0 0 0,1 1-1 0 0,1 0 1 0 0,-1-1 0 0 0,7 22-1 0 0,-5-29-1499 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6">6995 131 11519 0 0,'-1'2'383'0'0,"0"1"0"0"0,0-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,1-1 0 0 0,-1 1 0 0 0,1-1-1 0 0,0 1 1 0 0,0 5 0 0 0,0 1 437 0 0,-33 217 4930 0 0,19-147-4392 0 0,-8 155-1 0 0,22-231-1317 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,1 6 0 0 0,-2-9-141 0 0,0 1 0 0 0,0-1 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 1 0 0 0,1-1 1 0 0,-1 1-1 0 0,1-1 0 0 0,-1 1 1 0 0,0-1-1 0 0,2 1 0 0 0,-2-1 0 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="7">9343 598 8695 0 0,'-1'1'269'0'0,"0"0"0"0"0,-1 0-1 0 0,0 0 1 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 1-1 0 0,0-1 1 0 0,1 0-1 0 0,-1 1 1 0 0,0-1 0 0 0,1 0-1 0 0,-1 1 1 0 0,1-1-1 0 0,0 0 1 0 0,-1 1 0 0 0,1-1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,0 0 0 0 0,2 3-1 0 0,-1-1-13 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,2 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,1 0 0 0 0,3 3 0 0 0,2-1-61 0 0,1-1-1 0 0,-1 1 1 0 0,0-1-1 0 0,1 0 1 0 0,-1-1-1 0 0,1 0 1 0 0,15 2-1 0 0,66-2 364 0 0,-69-2-442 0 0,287 21 1520 0 0,-305-21-1594 0 0,96 4 1192 0 0,-70-5-1578 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="8">9943 175 6911 0 0,'3'2'315'0'0,"-1"-1"0"0"0,-2 0-1 0 0,2 1 1 0 0,0-1 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1-1 0 0 0,-1 1-1 0 0,0 0 1 0 0,0 3 0 0 0,10 33 3484 0 0,-7-23-3491 0 0,4 22 579 0 0,0 0 0 0 0,-4 1 0 0 0,0-1 0 0 0,-2 64 0 0 0,-24 150 1277 0 0,-17-50-595 0 0,22-135-754 0 0,-10 95-1 0 0,24-137-694 0 0,2-10-42 0 0,0-1 0 0 0,1 1 0 0 0,1 23 0 0 0,-1-37-140 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,1 0 1 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 1 0 0 0,1-1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1-1 0 0 0,0 1 0 0 0,2 0 0 0 0,-2 0 0 0 0,0 0-1 0 0,0-1 1 0 0,1 1 0 0 0,3-3-1658 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="9">9616 1785 9215 0 0,'0'3'1719'0'0,"6"0"457"0"0,12 4 1249 0 0,-12-4-3278 0 0,10 4 604 0 0,1 1 0 0 0,-1 0 0 0 0,24 20 0 0 0,-30-21-593 0 0,-2 1 0 0 0,2 0-1 0 0,-3 0 1 0 0,2 1 0 0 0,-3 0-1 0 0,13 18 1 0 0,-17-23-119 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,-1-1 0 0 0,-1 1 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0-1 0 0 0,0 1 1 0 0,-2 0-1 0 0,2-1 0 0 0,-1 1 0 0 0,0-1 1 0 0,0 0-1 0 0,-2 4 0 0 0,-3 0 87 0 0,1 1-1 0 0,0-1 1 0 0,-1 0-1 0 0,0 0 1 0 0,-1-1-1 0 0,1 0 1 0 0,-1 0-1 0 0,-17 8 0 0 0,-13 9 166 0 0,38-23-297 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,11 13-251 0 0,-10-13 224 0 0,1 1 26 0 0,-1-1-1 0 0,0 0 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 1 1 0 0,0-1-1 0 0,0 0 1 0 0,-1 1-1 0 0,1 0 1 0 0,-1-1-1 0 0,1 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,-1 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,-1 2-1 0 0,0-2 40 0 0,0 1 1 0 0,0-1-1 0 0,-1 0 0 0 0,2 0 1 0 0,-1 0-1 0 0,-1 0 0 0 0,-1 0 1 0 0,2 0-1 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,-1 1 0 0 0,-7 2 189 0 0,2-1-1 0 0,-2 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1-2-1 0 0,-10 3 0 0 0,10-3-5 0 0,-2 0-1 0 0,1-1 1 0 0,-13-1-1 0 0,22 0-339 0 0,-2 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,1 1-1 0 0,-1-1 1 0 0,-1 0 0 0 0,1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1-1 0 0,0-1 1 0 0,1 0 0 0 0,-3-3 0 0 0,-1-4-1035 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="10">9913 747 7367 0 0,'18'7'6884'0'0,"6"-1"-4785"0"0,36 3 0 0 0,70-1-707 0 0,-64-5-818 0 0,174 2 898 0 0,39 3-312 0 0,-120 3-727 0 0,74 6-34 0 0,417 12 1273 0 0,-173-39-505 0 0,-212 6-478 0 0,-239 6-483 0 0,-2 0-837 0 0,-8-3-2567 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="11">12646 352 4607 0 0,'-2'3'1087'0'0,"0"0"0"0"0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 5 0 0 0,-9 29 3507 0 0,8-26-4452 0 0,-33 150 3998 0 0,20-85-2926 0 0,-35 103-1 0 0,25-114-679 0 0,-11 34 316 0 0,36-96-823 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 3 1 0 0,0-6-211 0 0,0 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-2 0-1 0 0,1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1-1 0 0,0 1 1 0 0,1-1 0 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="12">12196 1505 14399 0 0,'-1'1'199'0'0,"1"0"-1"0"0,-1 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,0 1-1 0 0,1-1 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 3 1 0 0,-2 29 2330 0 0,2-22-2558 0 0,0-3 170 0 0,0 0 1 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1-1 0 0,2 0 1 0 0,-3 0 0 0 0,2-1 0 0 0,1 1 0 0 0,7 5 0 0 0,-10-8-91 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 0-1 0 0,-1-1 1 0 0,0 1 0 0 0,7-3 0 0 0,-2 1-56 0 0,-3-1 0 0 0,3 0 0 0 0,-3-1 0 0 0,1 1 0 0 0,0-2 0 0 0,0 1 0 0 0,0-1 0 0 0,12-11 0 0 0,-2 0-2086 0 0,19-21 1 0 0,-19 16-5376 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="13">12559 1591 13127 0 0,'-28'59'4429'0'0,"-40"120"0"0"0,48-120-3848 0 0,-46 161 1793 0 0,53-151-3448 0 0,13-67-64 0 0</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -4662,38 +4658,38 @@
           <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2023-12-12T19:21:11.787"/>
+      <inkml:timestamp xml:id="ts0" timeString="2024-01-09T19:28:28.731"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.05" units="cm"/>
       <inkml:brushProperty name="height" value="0.05" units="cm"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">7197 313 8287 0 0,'24'-1'7534'0'0,"42"1"-3671"0"0,-59 0-3682 0 0,1 1 1 0 0,-1 0-1 0 0,0 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,14 7 1 0 0,-20-8-167 0 0,-1 1 1 0 0,1-1-1 0 0,0 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,0 1-1 0 0,-1-1 1 0 0,1 0-1 0 0,-1 1 1 0 0,1 0-1 0 0,-1-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,0 1-1 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 1 0 0,0 0-1 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0-1 1 0 0,0 3-1 0 0,0-2 14 0 0,0 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,1 0-1 0 0,-1-1 1 0 0,0 1 0 0 0,0-1 0 0 0,-2 3 0 0 0,-3 3 68 0 0,0-1 0 0 0,0 1 0 0 0,-11 7 0 0 0,4-5-22 0 0,0-1 1 0 0,-17 8-1 0 0,18-11-29 0 0,1 1 1 0 0,0 1-1 0 0,0 0 0 0 0,-10 8 0 0 0,21-14-51 0 0,-1 0-1 0 0,0 0 1 0 0,0-1-1 0 0,1 1 1 0 0,-1 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,1-1 1 0 0,1 2-1 0 0,3 4-53 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,9 5 0 0 0,-4-2 25 0 0,-6-4 17 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 1 0 0 0,0-1-1 0 0,5 9 1 0 0,-8-12 47 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0-1 0 0,0-1 1 0 0,0 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,-1 0-1 0 0,0-1 1 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,-2 1 0 0 0,-11 11 392 0 0,-1-1 0 0 0,0 0 0 0 0,0-2 0 0 0,-1 0 0 0 0,-1 0 0 0 0,-25 11 0 0 0,34-18-358 0 0,2-1-56 0 0,-1 1 1 0 0,0-1 0 0 0,0-1-1 0 0,0 1 1 0 0,-10 1-1 0 0,17-4-37 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,7-4-3313 0 0,-6 3 3021 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1">7579 486 8287 0 0,'-16'57'7148'0'0,"13"-43"-6017"0"0,0 1 1 0 0,0 17 0 0 0,2-25-1057 0 0,1-1 0 0 0,0 1 1 0 0,0-1-1 0 0,1 0 1 0 0,0 1-1 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,0-1 1 0 0,1 1-1 0 0,6 7 1 0 0,-9-12-66 0 0,0 1 1 0 0,0-1 0 0 0,1 0-1 0 0,-1 1 1 0 0,0-1 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,-1-1 1 0 0,1 1 0 0 0,0 0-1 0 0,-1-1 1 0 0,1 1 0 0 0,0-1 0 0 0,0 0-1 0 0,-1 1 1 0 0,1-1 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,0-1-1 0 0,0 1 1 0 0,-1 0 0 0 0,1-1-1 0 0,0 1 1 0 0,0-1 0 0 0,2-1 0 0 0,-1 0 71 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,0 1 0 0 0,-1-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,2-6 0 0 0,-2 3 124 0 0,0-1 1 0 0,0 1-1 0 0,-1-1 1 0 0,1 0-1 0 0,-1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,-1 1 1 0 0,0-1 0 0 0,0 0-1 0 0,0 1 1 0 0,-5-10-1 0 0,2 7 9 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,-1 1-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 1 0 0 0,0 0-1 0 0,-1 0 1 0 0,0 1 0 0 0,-11-6-1 0 0,9 6-134 0 0,7 4-91 0 0,0 0-1 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,1-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,-1-1 1 0 0,-1-2-1 0 0,4 4-53 0 0,0 1 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,1-1 0 0 0,-1 1 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 1 0 0,1 0-1 0 0,-1-1 0 0 0,0 1 1 0 0,0 0-1 0 0,1 0 0 0 0,-1-1 1 0 0,0 1-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1-1 0 0 0,11-3-1195 0 0,17 4-1965 0 0,-11 1 1453 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2">7866 614 6911 0 0,'0'7'2139'0'0,"0"0"-1"0"0,1 1 0 0 0,3 12 1 0 0,-3-16-1664 0 0,1 1 0 0 0,-1-1-1 0 0,1 1 1 0 0,0-1 0 0 0,0 0 0 0 0,5 6 0 0 0,-6-7-417 0 0,1-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,1-1-1 0 0,-1 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 0 0 0,3 0 1 0 0,1-1 45 0 0,-1 1 0 0 0,0-1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 1 0 0,0-1-1 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,7-7 1 0 0,-8 9 17 0 0,-1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,-4-5 0 0 0,2 3 137 0 0,-1 1-1 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,0 0 1 0 0,-6-3-1 0 0,-6-2 293 0 0,-32-11 0 0 0,13 6-620 0 0,36 13 48 0 0,0 0 1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,11-2-2612 0 0,2 4 754 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3">10450 445 6447 0 0,'-46'-1'9314'0'0,"46"-4"-6256"0"0,5-3-1116 0 0,-1 7-1814 0 0,0-1 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 1 1 0 0,0 1-1 0 0,1-1 0 0 0,-1 0 1 0 0,0 1-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 1 1 0 0,1-1-1 0 0,5 2 0 0 0,-5-1-104 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,7 7 0 0 0,-11-8-8 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,-2 1 0 0 0,-1 4 56 0 0,0-1 1 0 0,0 1-1 0 0,-1-1 0 0 0,0-1 0 0 0,-10 11 0 0 0,9-11-45 0 0,-1-1-1 0 0,1 1 1 0 0,-1-1 0 0 0,0 0-1 0 0,-10 3 1 0 0,17-6-35 0 0,-1-1 1 0 0,1 0-1 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 1 1 0 0,1 0-1 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,1 1 0 0 0,-1 0 0 0 0,15 27-448 0 0,-9-18 357 0 0,-4-7 96 0 0,-1-1 0 0 0,0 2 1 0 0,0-1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-2 6 0 0 0,0-4 79 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0 0 0 0,-5 4 0 0 0,1-1 136 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0-1 0 0,0-1 1 0 0,0 0 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,-12 2 0 0 0,14-5-134 0 0,0 1 0 0 0,-1-2 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 0 0 0 0,0 0-1 0 0,-8-3 1 0 0,15 4-113 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,1 0-392 0 0,-1 0 0 0 0,1 0-1 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,2-2 1 0 0,6-8-7504 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4">10768 644 13415 0 0,'-3'6'356'0'0,"1"0"-102"0"0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,1 0-1 0 0,-1 1 0 0 0,1 8 1 0 0,1-6 366 0 0,-1-3-366 0 0,1 1 0 0 0,0-1-1 0 0,1 0 1 0 0,-1 1 0 0 0,5 9 0 0 0,-6-15-232 0 0,1 0 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1-1 1 0 0,0 0-1 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,3 1 0 0 0,0-2 69 0 0,1 1-1 0 0,0-1 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1-1 1 0 0,-1 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,1-5 0 0 0,-2 3 124 0 0,1-1-1 0 0,-1 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 1 0 0,-1-1-1 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 1 0 0,-1 0-1 0 0,1 1 0 0 0,-1-1 0 0 0,-2-7 0 0 0,1 9-11 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0-1 0 0,1 1 1 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-8-4-1 0 0,0 1-175 0 0,0 0-1 0 0,1 1 1 0 0,-2 0 0 0 0,-18-4-1 0 0,36 12-4580 0 0,2-1 2642 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5">11054 752 7367 0 0,'0'2'349'0'0,"0"0"0"0"0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,0-1 0 0 0,1 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,0 0 0 0 0,-1 1-1 0 0,1-1 1 0 0,0 0 0 0 0,0 0 0 0 0,2 1-1 0 0,1 0-237 0 0,0 0-1 0 0,1 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,1 0-1 0 0,0-1 0 0 0,0 1 1 0 0,10-2-1 0 0,-8 1-27 0 0,0-2 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,12-7 0 0 0,-16 7 26 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0-4 0 0 0,-1 5 76 0 0,-1-1 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1-1 0 0,-3-3 1 0 0,-21-25 1413 0 0,16 21-1065 0 0,-1 1 1 0 0,-1-1 0 0 0,-21-12-1 0 0,20 14-468 0 0,0 0 0 0 0,1-2-1 0 0,-14-11 1 0 0,25 19-92 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1-1 0 0 0,-1 1 0 0 0,14-4-2634 0 0,-3 3 878 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6">10756 555 5063 0 0,'-2'3'988'0'0,"1"0"-1"0"0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 4 0 0 0,-4 12 408 0 0,-5 1-144 0 0,8-15-981 0 0,-1 1 0 0 0,1 0 0 0 0,0 0-1 0 0,1 0 1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 9 0 0 0,3-15-295 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 1 0 0,0 0-1 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 1 0 0,0 0-1 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,2-1 0 0 0,6-2-6415 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="7">13221 580 16183 0 0,'-8'3'462'0'0,"5"-3"-36"0"0,0 1 0 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 1 0 0,-7-1 691 0 0,29 3 381 0 0,-11-3-1474 0 0,-1 1 0 0 0,0 0 0 0 0,1 0 1 0 0,-1 1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 1 0 0,6 7-1 0 0,-10-10 6 0 0,1 1 1 0 0,-1 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1-1-1 0 0,1 1 1 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,-1 1-1 0 0,0-1 39 0 0,0 1 0 0 0,0-1 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,-4 4 0 0 0,-1-1 62 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 1 0 0,1-1-1 0 0,-1-1 0 0 0,0 0 0 0 0,-15 6 0 0 0,11-6-45 0 0,8-3-62 0 0,0 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0 0 0 0 0,1 0-1 0 0,-6 3 1 0 0,8-5-30 0 0,0 1 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,2 6-56 0 0,0 0-1 0 0,1-1 0 0 0,6 10 0 0 0,-5-9 36 0 0,0 0 0 0 0,5 14 0 0 0,-9-20 32 0 0,-1 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 0 0 0,0 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,0 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 1 0 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 1 0 0,1 0-1 0 0,-3 2 0 0 0,-2 3 153 0 0,0-1 0 0 0,-1 0 0 0 0,-13 7-1 0 0,10-8-24 0 0,-1 0-1 0 0,0 0 0 0 0,0-1 0 0 0,0 0 1 0 0,-1-1-1 0 0,1 0 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1-1 1 0 0,0 0-1 0 0,-13-2 0 0 0,18-1-1877 0 0,5 0-64 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="8">13568 758 6447 0 0,'-24'25'2602'0'0,"14"-15"1189"0"0,-15 19 1 0 0,23-27-3451 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,1 0 1 0 0,-1 6 0 0 0,1-8-338 0 0,0 1-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,1 0-1 0 0,-1-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,0-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,1 0-1 0 0,1 2 1 0 0,-1-2 8 0 0,1 1 1 0 0,0-1-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,-1-1-1 0 0,1 1 1 0 0,6-1-1 0 0,-6 0 7 0 0,1-1 1 0 0,0 1-1 0 0,0-1 0 0 0,-1 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 1 0 0,3-3-1 0 0,-5 3-7 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,1-3 0 0 0,-1 0 222 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 1 0 0,1 0-1 0 0,-1 1 1 0 0,0-1-1 0 0,-1 1 1 0 0,-4-7-1 0 0,2 4 22 0 0,-1 0 0 0 0,0 0-1 0 0,0 1 1 0 0,-1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1-1 0 0,-14-8 1 0 0,20 13-290 0 0,0 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,1 1 0 0 0,-1-1-1 0 0,0 1 1 0 0,0-1 0 0 0,1 0-1 0 0,-1 1 1 0 0,1-1 0 0 0,-1 0-1 0 0,0-1 1 0 0,1 1-180 0 0,0 1 0 0 0,1 0 0 0 0,-1-1-1 0 0,1 1 1 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1 0-1 0 0,-1-1 1 0 0,1 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,-1-1 1 0 0,1 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,9 0-7927 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="9">13849 899 15231 0 0,'-1'1'137'0'0,"0"1"0"0"0,1-1 0 0 0,-1 0 0 0 0,0 1 0 0 0,1-1 0 0 0,0 1 0 0 0,-1-1-1 0 0,1 1 1 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 2-1 0 0,1-1-36 0 0,0 1 0 0 0,0-1-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,1-1-1 0 0,-1 1 1 0 0,1 0-1 0 0,3 2 1 0 0,-1-1-97 0 0,-1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,0 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,4-2 0 0 0,-4 2 123 0 0,-1 0-1 0 0,1 0 1 0 0,-1-1-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0-1 0 0,-1-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0-1 1 0 0,-1 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0-5 1 0 0,-1 5 87 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,-2-1 0 0 0,-8-5 276 0 0,0 1 0 0 0,-1 0 0 0 0,-18-6 0 0 0,18 9-319 0 0,-20-9 300 0 0,32 13-577 0 0,0-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-3 0 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="10">6889 41 4143 0 0,'1'-2'9323'0'0,"0"17"-8248"0"0,0 1 0 0 0,-2 0 1 0 0,-3 27-1 0 0,0-15-444 0 0,-2 26 603 0 0,-23 83 1 0 0,-26 51 182 0 0,45-156-1225 0 0,-92 256 508 0 0,95-266-661 0 0,-7 11 1 0 0,14-33-63 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 1 0 0 0,4-7-1016 0 0,2-5 116 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="11">6831 94 7367 0 0,'0'0'79'0'0,"0"0"0"0"0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,1-1 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,1 1 0 0 0,10 2 2265 0 0,21-4 126 0 0,-26 0-2192 0 0,124 0 2953 0 0,21 0-1380 0 0,72 0 223 0 0,-104 2-1166 0 0,40 1-40 0 0,195-5-72 0 0,-146-11-366 0 0,-104 6-112 0 0,209-14 489 0 0,-49 6-560 0 0,-114 9-140 0 0,236-2 96 0 0,-62 16-107 0 0,2-1 0 0 0,-181-1-60 0 0,-33-1 3 0 0,90 10 138 0 0,-124-7-76 0 0,77 8 57 0 0,-45-3-85 0 0,152-2-1 0 0,-89-15-34 0 0,100-5 52 0 0,215-18 27 0 0,-247 0-57 0 0,-130 13-21 0 0,129-2 1 0 0,-211 17-40 0 0,341 8 0 0 0,-98 3 25 0 0,90 8 14 0 0,-22 0 9 0 0,-176-12-32 0 0,-72 0 0 0 0,97 0 32 0 0,-138-6 43 0 0,55 7-1 0 0,-103-8-67 0 0,0 1 0 0 0,-1-1 0 0 0,1 1-1 0 0,0 0 1 0 0,-1-1 0 0 0,1 1 0 0 0,0 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,-1 1 0 0 0,0-1 0 0 0,3 3-1 0 0,-4-2 29 0 0,0 1-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 5-1 0 0,0 4-37 0 0,2 28 21 0 0,-2 0 0 0 0,-6 56 0 0 0,-21 78 0 0 0,13-90-42 0 0,-20 101 8 0 0,8-81 26 0 0,-54 146 0 0 0,37-128-14 0 0,34-93-20 0 0,-24 62 38 0 0,28-80-16 0 0,0-1-1 0 0,-1 0 1 0 0,0 0 0 0 0,-1 0-1 0 0,0-1 1 0 0,-10 11-1 0 0,15-18-6 0 0,-1 1-1 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,-6 1 1 0 0,7-2 4 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,-3-2 0 0 0,-10-3 21 0 0,-1-1-1 0 0,0 2 1 0 0,0 0-1 0 0,-1 1 1 0 0,-30-3-1 0 0,34 5-12 0 0,-113-9 24 0 0,36 6-11 0 0,-169-5 70 0 0,153 9-76 0 0,-194-1 43 0 0,-362 44 1 0 0,292-20-21 0 0,272-19-45 0 0,-183-1 44 0 0,1-1-32 0 0,96-4-14 0 0,138 1 7 0 0,-389-29 89 0 0,248 15-79 0 0,-313-29 45 0 0,228 15-64 0 0,-100-6 0 0 0,20 17 0 0 0,88 7 0 0 0,-60-4 0 0 0,183 1 0 0 0,32 3 0 0 0,-265-27 0 0 0,309 31 0 0 0,-89-16 0 0 0,-140-21 0 0 0,273 42 0 0 0,0-2 0 0 0,-34-11 0 0 0,34 9 0 0 0,-1 1 0 0 0,-31-5 0 0 0,-16 6 0 0 0,-24-4 0 0 0,7-10 0 0 0,64 15 0 0 0,11 3 0 0 0,0-1 0 0 0,0-1 0 0 0,0 1 0 0 0,1-2 0 0 0,-1 1 0 0 0,-10-7 0 0 0,3 1 5 0 0,8 2 5 0 0,-1 1 0 0 0,0 0 0 0 0,0 1-1 0 0,-1 1 1 0 0,-17-6 0 0 0,-40-5 186 0 0,53 12-171 0 0,0 1 1 0 0,-22 0-1 0 0,26-2-25 0 0,11 4 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,15-10-4340 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="12">3567 415 6447 0 0,'-2'0'483'0'0,"0"0"0"0"0,0-1-1 0 0,0 1 1 0 0,-1 0-1 0 0,1-1 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,1 0-1 0 0,-3-2 1 0 0,1 0-32 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-3-6 0 0 0,3 4-108 0 0,0-1 0 0 0,0 1 0 0 0,0 0-1 0 0,1-1 1 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 0 0 0 0,1 1-1 0 0,0-1 1 0 0,1-8 0 0 0,2 3 42 0 0,-1 0 0 0 0,2 1 0 0 0,-1 0 0 0 0,1-1-1 0 0,1 1 1 0 0,8-13 0 0 0,-11 19-312 0 0,0 1 0 0 0,1-1 1 0 0,-1 1-1 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 1 0 0 0,1 0 0 0 0,4-1 0 0 0,-7 2-54 0 0,0 0-1 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 1 0 0,1 2-1 0 0,1 2 19 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,-1 1-1 0 0,0 0 1 0 0,1 9-1 0 0,-2-6-3 0 0,0 1 1 0 0,-1 0-1 0 0,-1-1 1 0 0,1 1-1 0 0,-2 0 0 0 0,1-1 1 0 0,-2 1-1 0 0,1-1 1 0 0,-5 11-1 0 0,-7 13 17 0 0,-24 43-1 0 0,-1 3-47 0 0,29-56 28 0 0,-9 35 0 0 0,16-48-30 0 0,1-1-1 0 0,0 1 0 0 0,1 0 0 0 0,0 0 1 0 0,1 0-1 0 0,1 12 0 0 0,-1-21-3 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,0-1 1 0 0,1 0 0 0 0,-1 1-1 0 0,1-1 1 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,3 1-1 0 0,-2-2-5 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0-1 0 0,5-3 1 0 0,-2 0 6 0 0,0 1-1 0 0,0-1 0 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,4-12 0 0 0,-4 9 50 0 0,-1 0-1 0 0,0 0 0 0 0,0 1 1 0 0,-1-1-1 0 0,0 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 1 0 0,-4-14-1 0 0,2 13 94 0 0,-1 0 0 0 0,0 1 0 0 0,0 0-1 0 0,-1 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,-1 2 0 0 0,0-1 0 0 0,0 1-1 0 0,-1 0 1 0 0,-9-4 0 0 0,18 10-147 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,10 0-1281 0 0,13 2-1002 0 0,-8 0 471 0 0,-1 1-277 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="13">4086 233 12439 0 0,'-1'0'322'0'0,"1"1"-1"0"0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 1 0 0,0-1-1 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,-1-1 0 0 0,1 3 0 0 0,-4 22 2357 0 0,3-16-2469 0 0,-52 210 2144 0 0,11-58-2181 0 0,35-136-116 0 0,5-18-63 0 0,0 0 0 0 0,0-1 1 0 0,1 1-1 0 0,-1 11 1 0 0,2-18-26 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,5-7-5938 0 0,2-4-1027 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="14">4334 331 8751 0 0,'-17'25'1738'0'0,"11"-11"1448"0"0,1-2-1618 0 0,-17 44 2408 0 0,-22 78-2706 0 0,43-128-1240 0 0,-5 16 92 0 0,1 1 1 0 0,-1 25-1 0 0,5-41-109 0 0,1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,5 6 0 0 0,-6-11-13 0 0,1 1-1 0 0,0-1 1 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1-1 0 0,1 1 1 0 0,-1 0 0 0 0,0-1-1 0 0,1 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0-1-1 0 0,-1 1 1 0 0,1-1 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,4-1 1 0 0,-3 1 8 0 0,1-1 0 0 0,-1 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,4-6 0 0 0,-2 3 46 0 0,-1 0 1 0 0,0 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,1-10 0 0 0,-3 13 83 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,0 1-1 0 0,-3-6 1 0 0,1 3 81 0 0,-1 1 0 0 0,0 0 0 0 0,0-1-1 0 0,0 2 1 0 0,-1-1 0 0 0,1 0 0 0 0,-1 1 0 0 0,0 0 0 0 0,-1 1-1 0 0,1-1 1 0 0,0 1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,-9-1 0 0 0,10 0-465 0 0,8 0-531 0 0,10-1-2589 0 0,-11 4 2580 0 0,11-3-7543 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="15">4875 401 10999 0 0,'-9'4'-67'0'0,"0"0"4848"0"0,19-3-1128 0 0,4-2-2698 0 0,29 1 1 0 0,-9 2 609 0 0,393 20-236 0 0,95 2 323 0 0,-377-26-1237 0 0,151 4 985 0 0,-276 0-1169 0 0,-15-1-141 0 0,0 0-1 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,0-1 1 0 0,0 1-1 0 0,8-2 0 0 0,-11 1-72 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,-1 0 1 0 0,1-1-1 0 0,-1 1 1 0 0,0-1-1 0 0,0 0 0 0 0,1-1 1 0 0,-1 1-366 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,3-2 0 0 0,0 1-1485 0 0,1-1-78 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="16">4840 349 5063 0 0,'4'5'6618'0'0,"-3"-5"-6429"0"0,10-2 2720 0 0,15-7-1552 0 0,-21 7-526 0 0,167-81 5036 0 0,-6 3-4345 0 0,-106 59-1980 0 0,-33 13-2738 0 0,-17 5 1373 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="17">4857 412 11519 0 0,'4'17'6330'0'0,"13"13"-3980"0"0,-3-6-1470 0 0,26 91 1136 0 0,-2-3-1100 0 0,-34-105-775 0 0,-1 1-1 0 0,1 0 0 0 0,1-1 1 0 0,6 9-1 0 0,-9-14-325 0 0,0 0 0 0 0,0 1 0 0 0,0-1 1 0 0,1 0-1 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,5 2 0 0 0,-5-4-319 0 0,-1 1 0 0 0,1 0 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,9-2-7018 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="18">6358 462 7743 0 0,'-2'1'473'0'0,"0"1"-1"0"0,0-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,0-1 1 0 0,1 1-1 0 0,-2 2 1 0 0,2-4-357 0 0,1 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1-54 0 0,1-1 0 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,1 0 0 0 0,107 5 3318 0 0,-73-3-2672 0 0,-13-1-329 0 0,9 2 201 0 0,1-3 0 0 0,52-4 0 0 0,-61 0-323 0 0,-13 2-70 0 0,0 0 0 0 0,-1 1 0 0 0,1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,0 1 0 0 0,16 2 0 0 0,-27-3-159 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 1 0 0 0,0-1 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 1-1 0 0,0-1 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 1 0 0,0-1 5 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 0-1 0 0,1 1 1 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,-2-4-1912 0 0,3 0 782 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="19">1528 384 2759 0 0,'0'8'7334'0'0,"0"-7"-7111"0"0,10 7 2755 0 0,14 4-697 0 0,-8-9-1494 0 0,1-1 1 0 0,-1-1-1 0 0,1 0 0 0 0,32-3 0 0 0,77-8 888 0 0,287 18 938 0 0,-151 6-1589 0 0,84 7 224 0 0,-262-10-841 0 0,23 1 726 0 0,-31-12-667 0 0,-32-1 291 0 0,-44 1-775 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,1-1-1 0 0,-1 1 0 0 0,0 0 0 0 0,0 0 1 0 0,1-1-1 0 0,-1 1 0 0 0,0 0 0 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,0-1 1 0 0,1-2-1121 0 0,1-2-815 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">7197 313 8287 0 0,'24'-1'7534'0'0,"42"1"-3671"0"0,-59 0-3682 0 0,1 1 1 0 0,-1 0-1 0 0,0 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,14 7 1 0 0,-20-8-167 0 0,-1 1 1 0 0,1-1-1 0 0,0 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,0 1-1 0 0,-1-1 1 0 0,0 0-1 0 0,0 1 1 0 0,2 0-1 0 0,-2-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,0 1-1 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 1 0 0,0 0-1 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0-1 1 0 0,0 3-1 0 0,0-2 14 0 0,0 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,1 0-1 0 0,-1-1 1 0 0,-1 1 0 0 0,2-1 0 0 0,-3 3 0 0 0,-3 3 68 0 0,1-1 0 0 0,-2 1 0 0 0,-10 7 0 0 0,4-5-22 0 0,0-1 1 0 0,-17 8-1 0 0,18-11-29 0 0,1 1 1 0 0,0 1-1 0 0,0 0 0 0 0,-10 8 0 0 0,21-14-51 0 0,-1 0-1 0 0,0 0 1 0 0,0-1-1 0 0,1 1 1 0 0,-1 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,-2 0 1 0 0,2 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,2 0 0 0 0,-2 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,1-1 1 0 0,1 2-1 0 0,3 4-53 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,9 5 0 0 0,-4-2 25 0 0,-6-4 17 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 1 0 0 0,0-1-1 0 0,5 9 1 0 0,-9-12 47 0 0,0 1 0 0 0,2-1 0 0 0,-1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0-1 0 0,0-1 1 0 0,0 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,-1 0-1 0 0,0-1 1 0 0,1 1 0 0 0,-2-1 0 0 0,2 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 1 0 0 0,-2 1 0 0 0,-11 11 392 0 0,-1-1 0 0 0,0 0 0 0 0,0-2 0 0 0,-1 0 0 0 0,-1 0 0 0 0,-25 11 0 0 0,34-18-358 0 0,3-1-56 0 0,-3 1 1 0 0,1-1 0 0 0,0-1-1 0 0,0 1 1 0 0,-10 1-1 0 0,17-4-37 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,-2 0-1 0 0,2 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,7-4-3313 0 0,-6 3 3021 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1">7579 486 8287 0 0,'-16'57'7148'0'0,"13"-43"-6017"0"0,0 1 1 0 0,0 17 0 0 0,2-25-1057 0 0,1-1 0 0 0,0 1 1 0 0,0-1-1 0 0,1 0 1 0 0,0 1-1 0 0,0-1 1 0 0,2 1-1 0 0,-3-1 1 0 0,2 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,0-1 1 0 0,1 1-1 0 0,7 7 1 0 0,-11-12-66 0 0,1 1 1 0 0,0-1 0 0 0,1 0-1 0 0,-1 1 1 0 0,0-1 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,-2-1 1 0 0,3 1 0 0 0,-1 0-1 0 0,-1-1 1 0 0,1 1 0 0 0,0-1 0 0 0,0 0-1 0 0,-1 1 1 0 0,1-1 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,0-1-1 0 0,0 1 1 0 0,-1 0 0 0 0,1-1-1 0 0,0 1 1 0 0,0-1 0 0 0,2-1 0 0 0,-1 0 71 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,0 1 0 0 0,-1-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,2-6 0 0 0,-2 3 124 0 0,0-1 1 0 0,0 1-1 0 0,-1-1 1 0 0,1 0-1 0 0,-1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,-1 1 1 0 0,0-1 0 0 0,0 0-1 0 0,0 1 1 0 0,-5-10-1 0 0,2 7 9 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,-1 1-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 1 0 0 0,0 0-1 0 0,-1 0 1 0 0,0 1 0 0 0,-11-6-1 0 0,9 6-134 0 0,7 4-91 0 0,0 0-1 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,1-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,-1-1 1 0 0,-1-2-1 0 0,4 4-53 0 0,0 1 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 1 0 0,2 0-1 0 0,-2-1 0 0 0,0 1 1 0 0,0 0-1 0 0,1 0 0 0 0,-1-1 1 0 0,0 1-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1-1 0 0 0,11-3-1195 0 0,17 4-1965 0 0,-11 1 1453 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2">7866 614 6911 0 0,'0'7'2139'0'0,"0"0"-1"0"0,2 1 0 0 0,1 12 1 0 0,-2-16-1664 0 0,1 1 0 0 0,-1-1-1 0 0,1 1 1 0 0,0-1 0 0 0,0 0 0 0 0,5 6 0 0 0,-6-7-417 0 0,1-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,1-1-1 0 0,-1 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 0 1 0 0,1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 0 0 0,3 0 1 0 0,1-1 45 0 0,-1 1 0 0 0,0-1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 1 0 0,0-1-1 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,7-7 1 0 0,-8 9 17 0 0,-1 1 0 0 0,-1-1 0 0 0,2 0 0 0 0,-2 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,-4-5 0 0 0,2 3 137 0 0,-1 1-1 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,0 0 1 0 0,-6-3-1 0 0,-6-2 293 0 0,-32-11 0 0 0,13 6-620 0 0,36 13 48 0 0,0 0 1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,2 0 0 0 0,-2 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,-2 0 0 0 0,2 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,11-2-2612 0 0,2 4 754 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3">10450 445 6447 0 0,'-46'-1'9314'0'0,"46"-4"-6256"0"0,5-3-1116 0 0,-1 7-1814 0 0,0-1 0 0 0,1 1 1 0 0,-1-1-1 0 0,1 1 1 0 0,-2 1-1 0 0,2-1 0 0 0,-1 0 1 0 0,0 1-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 1 1 0 0,1-1-1 0 0,5 2 0 0 0,-5-1-104 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,9 7 0 0 0,-12-8-8 0 0,0-1 0 0 0,1 1 0 0 0,-2-1 0 0 0,1 1 0 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,-2 1 0 0 0,-1 4 56 0 0,0-1 1 0 0,0 1-1 0 0,-1-1 0 0 0,0-1 0 0 0,-10 11 0 0 0,9-11-45 0 0,-1-1-1 0 0,1 1 1 0 0,-1-1 0 0 0,0 0-1 0 0,-10 3 1 0 0,17-6-35 0 0,-1-1 1 0 0,1 0-1 0 0,-1 1 0 0 0,1-1 0 0 0,-2 1 0 0 0,2-1 0 0 0,0 0 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 1 1 0 0,1 0-1 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,1 1 0 0 0,-1 0 0 0 0,15 27-448 0 0,-9-18 357 0 0,-4-7 96 0 0,-1-1 0 0 0,0 2 1 0 0,0-1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-2 6 0 0 0,0-4 79 0 0,0-1 0 0 0,0 1 0 0 0,-2 0 0 0 0,3-1 0 0 0,-2 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0 0 0 0,-5 4 0 0 0,1-1 136 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0-1 0 0,0-1 1 0 0,0 0 0 0 0,-2-1 0 0 0,3 0 0 0 0,-2 0 0 0 0,0 0 0 0 0,-11 2 0 0 0,12-5-134 0 0,1 1 0 0 0,-1-2 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 0 0 0 0,0 0-1 0 0,-8-3 1 0 0,15 4-113 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 0 0 0,-2 1 0 0 0,2 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,1 0-392 0 0,-1 0 0 0 0,1 0-1 0 0,-1-1 1 0 0,0 1-1 0 0,2 0 1 0 0,-2 0-1 0 0,1 0 1 0 0,0 0-1 0 0,2-2 1 0 0,7-8-7504 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4">10768 644 13415 0 0,'-3'6'356'0'0,"1"0"-102"0"0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,1 0-1 0 0,-1 1 0 0 0,1 8 1 0 0,1-6 366 0 0,-1-3-366 0 0,1 1 0 0 0,1-1-1 0 0,-1 0 1 0 0,0 1 0 0 0,5 9 0 0 0,-6-15-232 0 0,1 0 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,2 0-1 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1-1 1 0 0,0 0-1 0 0,2 1 0 0 0,-3-1 0 0 0,2 0 0 0 0,-1 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,3 1 0 0 0,0-2 69 0 0,1 1-1 0 0,0-1 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1-1 1 0 0,-1 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,1-5 0 0 0,-2 3 124 0 0,1-1-1 0 0,-1 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,2 1 1 0 0,-3-1-1 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 1 0 0,-1 0-1 0 0,1 1 0 0 0,0-1 0 0 0,-4-7 0 0 0,2 9-11 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-2 1-1 0 0,2 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,-1 1 1 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,-6-4-1 0 0,-1 1-175 0 0,0 0-1 0 0,1 1 1 0 0,-2 0 0 0 0,-18-4-1 0 0,36 12-4580 0 0,2-1 2642 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5">11054 752 7367 0 0,'0'2'349'0'0,"0"0"0"0"0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,0-1 0 0 0,1 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,0 0 0 0 0,-1 1-1 0 0,1-1 1 0 0,0 0 0 0 0,0 0 0 0 0,2 1-1 0 0,1 0-237 0 0,-1 0-1 0 0,3 0 0 0 0,-2-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,1 0-1 0 0,0-1 0 0 0,0 1 1 0 0,10-2-1 0 0,-8 1-27 0 0,0-2 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,10-7 0 0 0,-15 7 26 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0-4 0 0 0,-1 5 76 0 0,-1-1 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1-1 0 0,-3-3 1 0 0,-21-25 1413 0 0,16 21-1065 0 0,-1 1 1 0 0,-1-1 0 0 0,-21-12-1 0 0,20 14-468 0 0,0 0 0 0 0,0-2-1 0 0,-12-11 1 0 0,24 19-92 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1-1 0 0 0,-1 1 0 0 0,14-4-2634 0 0,-4 3 878 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6">10756 555 5063 0 0,'-1'3'988'0'0,"-1"0"-1"0"0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 4 0 0 0,-4 12 408 0 0,-5 1-144 0 0,8-15-981 0 0,-1 1 0 0 0,1 0 0 0 0,0 0-1 0 0,1 0 1 0 0,1 0 0 0 0,-2 1 0 0 0,1-1 0 0 0,-1 9 0 0 0,3-15-295 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 1 0 0,0 0-1 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 1 0 0,0 0-1 0 0,1 1 0 0 0,-1-1 0 0 0,2 0 0 0 0,-2 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,2-1 0 0 0,6-2-6415 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="7">13221 580 16183 0 0,'-8'3'462'0'0,"5"-3"-36"0"0,0 1 0 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 1 0 0,-7-1 691 0 0,29 3 381 0 0,-11-3-1474 0 0,-1 1 0 0 0,0 0 0 0 0,1 0 1 0 0,-1 1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 1 0 0 0,2 1 1 0 0,-2-1-1 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 1 0 0,6 7-1 0 0,-10-10 6 0 0,1 1 1 0 0,-1 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,-1 0-1 0 0,2 0 1 0 0,-2-1-1 0 0,1 1 1 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,-1 1-1 0 0,0-1 39 0 0,0 1 0 0 0,-1-1 0 0 0,2 0-1 0 0,-2 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,-4 4 0 0 0,-1-1 62 0 0,0 0 0 0 0,0-1 0 0 0,0 1 1 0 0,-1-1-1 0 0,-1-1 0 0 0,2 0 0 0 0,-15 6 0 0 0,9-6-45 0 0,9-3-62 0 0,0 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0 0 0 0 0,1 0-1 0 0,-6 3 1 0 0,7-5-30 0 0,2 1 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,2 6-56 0 0,-1 0-1 0 0,3-1 0 0 0,5 10 0 0 0,-5-9 36 0 0,0 0 0 0 0,5 14 0 0 0,-9-20 32 0 0,-1 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 0 0 0,0 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,0 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,-1-1 0 0 0,2 1 1 0 0,0-1-1 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 1 0 0,1 0-1 0 0,-3 2 0 0 0,-2 3 153 0 0,0-1 0 0 0,-1 0 0 0 0,-13 7-1 0 0,10-8-24 0 0,-1 0-1 0 0,0 0 0 0 0,0-1 0 0 0,0 0 1 0 0,-1-1-1 0 0,1 0 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1-1 1 0 0,0 0-1 0 0,-13-2 0 0 0,18-1-1877 0 0,5 0-64 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="8">13568 758 6447 0 0,'-24'25'2602'0'0,"14"-15"1189"0"0,-15 19 1 0 0,23-27-3451 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,1 0 1 0 0,-1 6 0 0 0,1-8-338 0 0,0 1-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,1 0-1 0 0,-1-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,0-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 1 0 0 0,1-1 1 0 0,-2 0-1 0 0,1 0 1 0 0,1 0-1 0 0,1 2 1 0 0,-1-2 8 0 0,1 1 1 0 0,0-1-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,-1-1-1 0 0,1 1 1 0 0,6-1-1 0 0,-6 0 7 0 0,1-1 1 0 0,0 1-1 0 0,0-1 0 0 0,-1 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 1 0 0,3-3-1 0 0,-5 3-7 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,1-3 0 0 0,-1 0 222 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,-2 0 1 0 0,3 1-1 0 0,-2-1 1 0 0,1 0-1 0 0,-1 1 1 0 0,0-1-1 0 0,-1 1 1 0 0,-4-7-1 0 0,2 4 22 0 0,-1 0 0 0 0,0 0-1 0 0,0 1 1 0 0,-1 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,2 1-1 0 0,-15-8 1 0 0,20 13-290 0 0,0 0-1 0 0,1-1 1 0 0,-2 1 0 0 0,2-1-1 0 0,-1 1 1 0 0,0-1 0 0 0,1 1 0 0 0,-1-1-1 0 0,0 1 1 0 0,0-1 0 0 0,1 0-1 0 0,-1 1 1 0 0,1-1 0 0 0,-1 0-1 0 0,0-1 1 0 0,1 1-180 0 0,0 1 0 0 0,1 0 0 0 0,-1-1-1 0 0,1 1 1 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1 0-1 0 0,-1-1 1 0 0,1 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,-1-1 1 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,2 0-1 0 0,-1 0 1 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,9 0-7927 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="9">13849 899 15231 0 0,'-1'1'137'0'0,"0"1"0"0"0,1-1 0 0 0,-1 0 0 0 0,0 1 0 0 0,1-1 0 0 0,0 1 0 0 0,-1-1-1 0 0,1 1 1 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 2-1 0 0,1-1-36 0 0,0 1 0 0 0,0-1-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,1-1-1 0 0,-1 1 1 0 0,1 0-1 0 0,3 2 1 0 0,-1-1-97 0 0,-1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,0 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,4-2 0 0 0,-4 2 123 0 0,-1 0-1 0 0,0 0 1 0 0,1-1-1 0 0,-1 0 1 0 0,0 1-1 0 0,0-1 1 0 0,1 0-1 0 0,-2-1 1 0 0,1 1 0 0 0,0 0-1 0 0,-1-1 1 0 0,1 1-1 0 0,-2-1 1 0 0,2 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0-1 1 0 0,-1 1-1 0 0,0-1 1 0 0,-1 1-1 0 0,2-1 1 0 0,-1 1-1 0 0,0-5 1 0 0,-1 5 87 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,-1 0-1 0 0,2 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-4-1 0 0 0,-7-5 276 0 0,1 1 0 0 0,-3 0 0 0 0,-18-6 0 0 0,20 9-319 0 0,-21-9 300 0 0,32 13-577 0 0,0-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-3 0 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="10">6889 41 4143 0 0,'1'-2'9323'0'0,"0"17"-8248"0"0,0 1 0 0 0,-2 0 1 0 0,-3 27-1 0 0,0-15-444 0 0,-2 26 603 0 0,-22 83 1 0 0,-28 51 182 0 0,46-156-1225 0 0,-92 256 508 0 0,95-266-661 0 0,-7 11 1 0 0,14-33-63 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 1 0 0 0,4-7-1016 0 0,2-5 116 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="11">6831 94 7367 0 0,'0'0'79'0'0,"0"0"0"0"0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,1-1 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,1 1 0 0 0,10 2 2265 0 0,21-4 126 0 0,-26 0-2192 0 0,124 0 2953 0 0,21 0-1380 0 0,72 0 223 0 0,-104 2-1166 0 0,40 1-40 0 0,195-5-72 0 0,-146-11-366 0 0,-104 6-112 0 0,209-14 489 0 0,-49 6-560 0 0,-113 9-140 0 0,235-2 96 0 0,-62 16-107 0 0,1-1 0 0 0,-180-1-60 0 0,-33-1 3 0 0,90 10 138 0 0,-124-7-76 0 0,77 8 57 0 0,-45-3-85 0 0,151-2-1 0 0,-87-15-34 0 0,99-5 52 0 0,215-18 27 0 0,-247 0-57 0 0,-130 13-21 0 0,129-2 1 0 0,-211 17-40 0 0,341 8 0 0 0,-98 3 25 0 0,90 8 14 0 0,-22 0 9 0 0,-176-12-32 0 0,-72 0 0 0 0,97 0 32 0 0,-138-6 43 0 0,55 7-1 0 0,-102-8-67 0 0,-2 1 0 0 0,0-1 0 0 0,1 1-1 0 0,0 0 1 0 0,-1-1 0 0 0,0 1 0 0 0,2 1 0 0 0,-2-1-1 0 0,1 0 1 0 0,-1 1 0 0 0,0-1 0 0 0,3 3-1 0 0,-4-2 29 0 0,0 1-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 5-1 0 0,0 4-37 0 0,2 28 21 0 0,-2 0 0 0 0,-6 56 0 0 0,-21 78 0 0 0,13-90-42 0 0,-20 101 8 0 0,8-81 26 0 0,-54 146 0 0 0,37-128-14 0 0,34-93-20 0 0,-24 62 38 0 0,28-80-16 0 0,0-1-1 0 0,-1 0 1 0 0,0 0 0 0 0,-1 0-1 0 0,0-1 1 0 0,-10 11-1 0 0,15-18-6 0 0,-1 1-1 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-2 0 0 0 0,-4 1 1 0 0,6-2 4 0 0,0-1 0 0 0,0 1 0 0 0,2-1 0 0 0,-3 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-2-1 0 0 0,2 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,-3-2 0 0 0,-10-3 21 0 0,-1-1-1 0 0,0 2 1 0 0,-1 0-1 0 0,1 1 1 0 0,-31-3-1 0 0,34 5-12 0 0,-113-9 24 0 0,36 6-11 0 0,-169-5 70 0 0,153 9-76 0 0,-193-1 43 0 0,-364 44 1 0 0,293-20-21 0 0,272-19-45 0 0,-183-1 44 0 0,1-1-32 0 0,96-4-14 0 0,138 1 7 0 0,-389-29 89 0 0,248 15-79 0 0,-313-29 45 0 0,228 15-64 0 0,-100-6 0 0 0,20 17 0 0 0,88 7 0 0 0,-60-4 0 0 0,183 1 0 0 0,32 3 0 0 0,-265-27 0 0 0,309 31 0 0 0,-89-16 0 0 0,-140-21 0 0 0,273 42 0 0 0,0-2 0 0 0,-34-11 0 0 0,35 9 0 0 0,-3 1 0 0 0,-30-5 0 0 0,-16 6 0 0 0,-24-4 0 0 0,7-10 0 0 0,64 15 0 0 0,11 3 0 0 0,0-1 0 0 0,0-1 0 0 0,0 1 0 0 0,1-2 0 0 0,-1 1 0 0 0,-10-7 0 0 0,3 1 5 0 0,8 2 5 0 0,-1 1 0 0 0,0 0 0 0 0,0 1-1 0 0,-1 1 1 0 0,-17-6 0 0 0,-41-5 186 0 0,56 12-171 0 0,-3 1 1 0 0,-21 0-1 0 0,26-2-25 0 0,11 4 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-2 0 0 0 0,0 0 0 0 0,15-10-4340 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="12">3567 415 6447 0 0,'-2'0'483'0'0,"0"0"0"0"0,0-1-1 0 0,0 1 1 0 0,-1 0-1 0 0,1-1 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,1 0-1 0 0,-2 0 1 0 0,1 0 0 0 0,1 0-1 0 0,-3-2 1 0 0,1 0-32 0 0,-1 0 0 0 0,3 0-1 0 0,-2 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-3-6 0 0 0,3 4-108 0 0,0-1 0 0 0,0 1 0 0 0,0 0-1 0 0,1-1 1 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 0 0 0 0,1 1-1 0 0,0-1 1 0 0,1-8 0 0 0,2 3 42 0 0,-1 0 0 0 0,2 1 0 0 0,-1 0 0 0 0,1-1-1 0 0,1 1 1 0 0,8-13 0 0 0,-11 19-312 0 0,0 1 0 0 0,1-1 1 0 0,-1 1-1 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 1 0 0 0,1 0 0 0 0,5-1 0 0 0,-9 2-54 0 0,1 0-1 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 1 0 0 0,1 0 0 0 0,-2-1 0 0 0,1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 1 0 0,1 2-1 0 0,1 2 19 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,-1 1-1 0 0,0 0 1 0 0,1 9-1 0 0,-2-6-3 0 0,0 1 1 0 0,-1 0-1 0 0,-1-1 1 0 0,1 1-1 0 0,-2 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,-5 11-1 0 0,-7 13 17 0 0,-24 43-1 0 0,-1 3-47 0 0,29-56 28 0 0,-9 35 0 0 0,16-48-30 0 0,1-1-1 0 0,-1 1 0 0 0,3 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,1 12 0 0 0,-1-21-3 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,2 0 0 0 0,-2 0-1 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,0-1 1 0 0,2 0 0 0 0,-3 1-1 0 0,2-1 1 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,3 1-1 0 0,-2-2-5 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0-1 0 0,5-3 1 0 0,-2 0 6 0 0,0 1-1 0 0,0-1 0 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,2 0 1 0 0,-2 0-1 0 0,0 0 0 0 0,0 0 0 0 0,4-12 0 0 0,-4 9 50 0 0,-1 0-1 0 0,0 0 0 0 0,0 1 1 0 0,-1-1-1 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,-4-14-1 0 0,2 13 94 0 0,-1 0 0 0 0,0 1 0 0 0,0 0-1 0 0,-1 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,-1 2 0 0 0,0-1 0 0 0,0 1-1 0 0,-1 0 1 0 0,-9-4 0 0 0,18 10-147 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-2 0 0 0 0,2 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,10 0-1281 0 0,13 2-1002 0 0,-8 0 471 0 0,-1 1-277 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="13">4086 233 12439 0 0,'-2'0'322'0'0,"2"1"-1"0"0,0-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 1 0 0,0-1-1 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,-1-1 0 0 0,1 3 0 0 0,-4 22 2357 0 0,3-16-2469 0 0,-52 210 2144 0 0,11-58-2181 0 0,35-136-116 0 0,5-18-63 0 0,0 0 0 0 0,0-1 1 0 0,2 1-1 0 0,-3 11 1 0 0,3-18-26 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,2 0-1 0 0,-2 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,5-7-5938 0 0,2-4-1027 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="14">4334 331 8751 0 0,'-17'25'1738'0'0,"11"-11"1448"0"0,1-2-1618 0 0,-17 44 2408 0 0,-22 78-2706 0 0,44-128-1240 0 0,-7 16 92 0 0,2 1 1 0 0,-1 25-1 0 0,5-41-109 0 0,1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,3 1 0 0 0,-2-1 0 0 0,1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,5 6 0 0 0,-6-11-13 0 0,1 1-1 0 0,0-1 1 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1-1 0 0,1 1 1 0 0,-1 0 0 0 0,0-1-1 0 0,1 1 1 0 0,-1-1-1 0 0,0 0 1 0 0,1 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0-1-1 0 0,0 1 1 0 0,-1-1 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,4-1 1 0 0,-3 1 8 0 0,1-1 0 0 0,-1 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,-1 0 0 0 0,6-6 0 0 0,-3 3 46 0 0,-1 0 1 0 0,0 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,1-10 0 0 0,-3 13 83 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 1-1 0 0,-5-6 1 0 0,2 3 81 0 0,-1 1 0 0 0,0 0 0 0 0,0-1-1 0 0,0 2 1 0 0,-1-1 0 0 0,1 0 0 0 0,0 1 0 0 0,-2 0 0 0 0,0 1-1 0 0,1-1 1 0 0,0 1 0 0 0,-1 1 0 0 0,0-1 0 0 0,-1 1-1 0 0,2 0 1 0 0,-10-1 0 0 0,10 0-465 0 0,8 0-531 0 0,10-1-2589 0 0,-11 4 2580 0 0,11-3-7543 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="15">4875 401 10999 0 0,'-9'4'-67'0'0,"-1"0"4848"0"0,21-3-1128 0 0,3-2-2698 0 0,29 1 1 0 0,-9 2 609 0 0,393 20-236 0 0,95 2 323 0 0,-377-26-1237 0 0,151 4 985 0 0,-276 0-1169 0 0,-15-1-141 0 0,0 0-1 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,0-1 1 0 0,0 1-1 0 0,8-2 0 0 0,-11 1-72 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,-1 0 1 0 0,2-1-1 0 0,-3 1 1 0 0,1-1-1 0 0,0 0 0 0 0,1-1 1 0 0,-1 1-366 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,2-1 0 0 0,2-2 0 0 0,0 1-1485 0 0,1-1-78 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="16">4840 349 5063 0 0,'4'5'6618'0'0,"-3"-5"-6429"0"0,10-2 2720 0 0,15-7-1552 0 0,-20 7-526 0 0,165-81 5036 0 0,-5 3-4345 0 0,-106 59-1980 0 0,-33 13-2738 0 0,-17 5 1373 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="17">4856 412 11519 0 0,'5'17'6330'0'0,"12"13"-3980"0"0,-3-6-1470 0 0,26 91 1136 0 0,-2-3-1100 0 0,-34-105-775 0 0,-1 1-1 0 0,1 0 0 0 0,1-1 1 0 0,6 9-1 0 0,-9-14-325 0 0,0 0 0 0 0,0 1 0 0 0,0-1 1 0 0,1 0-1 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,5 2 0 0 0,-5-4-319 0 0,-1 1 0 0 0,1 0 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,11-2-7018 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="18">6358 462 7743 0 0,'-2'1'473'0'0,"1"1"-1"0"0,-2-1 1 0 0,2 1-1 0 0,-1 0 0 0 0,0-1 1 0 0,1 1-1 0 0,-2 2 1 0 0,2-4-357 0 0,1 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1-54 0 0,1-1 0 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,1 0 0 0 0,108 5 3318 0 0,-75-3-2672 0 0,-12-1-329 0 0,9 2 201 0 0,0-3 0 0 0,54-4 0 0 0,-62 0-323 0 0,-13 2-70 0 0,0 0 0 0 0,-1 1 0 0 0,1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,0 1 0 0 0,16 2 0 0 0,-27-3-159 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,2 0-1 0 0,-2 1 0 0 0,0-1 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 1-1 0 0,0-1 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 1 0 0,0-1 5 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 0-1 0 0,1 1 1 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,-2 0 1 0 0,2 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,-2-4-1912 0 0,3 0 782 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="19">1528 384 2759 0 0,'0'8'7334'0'0,"0"-7"-7111"0"0,10 7 2755 0 0,14 4-697 0 0,-8-9-1494 0 0,1-1 1 0 0,-1-1-1 0 0,1 0 0 0 0,32-3 0 0 0,77-8 888 0 0,287 18 938 0 0,-151 6-1589 0 0,84 7 224 0 0,-262-10-841 0 0,23 1 726 0 0,-31-12-667 0 0,-32-1 291 0 0,-44 1-775 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,1-1-1 0 0,-1 1 0 0 0,0 0 0 0 0,0 0 1 0 0,1-1-1 0 0,-1 1 0 0 0,0 0 0 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,0-1 1 0 0,0-2-1121 0 0,3-2-815 0 0</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="20">1516 343 5983 0 0,'-4'-1'8999'0'0,"80"-35"-3705"0"0,23-11-2774 0 0,-50 22-1544 0 0,74-43 554 0 0,-110 60-1438 0 0,0 1-1 0 0,22-9 1 0 0,-8 10-4106 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="21">1542 394 14599 0 0,'0'1'137'0'0,"-1"0"-1"0"0,1 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 1-1 0 0,0-1 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,1 0 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0-1 1 0 0,0 1-1 0 0,1 1 0 0 0,2 3 738 0 0,142 189 4499 0 0,-39-60-4084 0 0,-94-126-964 0 0,-13-8-390 0 0,1 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,0-1 1 0 0,1 1 0 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0-1 0 0 0,1 1 0 0 0,-1 0-1 0 0,0-1 1 0 0,1 0 0 0 0,1-3-1806 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="22">1 292 11519 0 0,'0'0'1040'0'0,"17"0"2082"0"0,96-7 1768 0 0,-57 5-3404 0 0,59 7-1 0 0,-78 1-896 0 0,-34-5-509 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 1 1 0 0,-1-1-1 0 0,1 1 1 0 0,0-1 0 0 0,4 4-1 0 0,-7-4-50 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 1 1 0 0,0-1-1 0 0,1 1 0 0 0,-1-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,0-1 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,0-1 1 0 0,-1 0-1 0 0,0 1 0 0 0,-13 15 510 0 0,12-13-464 0 0,-45 45 620 0 0,-50 48 18 0 0,4-12 79 0 0,87-76-713 0 0,10-5-920 0 0,14-6-4221 0 0,-7 0-3402 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="23">495 305 2303 0 0,'2'3'8567'0'0,"-2"-3"-8403"0"0,11-1 4812 0 0,13-4-2000 0 0,-22 4-2924 0 0,24-4 544 0 0,0 1 0 0 0,0 1 0 0 0,0 1 0 0 0,1 1 0 0 0,50 6 0 0 0,-68-4-521 0 0,0 0 0 0 0,0 1 0 0 0,-1 0 0 0 0,1 1 0 0 0,13 5 0 0 0,-21-8-35 0 0,1 1 0 0 0,0 0 0 0 0,-1 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 1 1 0 0,0-1 0 0 0,1 0 0 0 0,-1 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,-1 1 0 0 0,1-1-1 0 0,0 1 1 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1-1 0 0,1 0 1 0 0,-1-1 0 0 0,0 1 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,-1 0 0 0 0,1-1-1 0 0,-2 4 1 0 0,-2 4 183 0 0,0 0 0 0 0,0 0 1 0 0,-1-1-1 0 0,-1 1 0 0 0,-7 9 0 0 0,-37 38 337 0 0,15-19-275 0 0,-133 140 787 0 0,192-206-6956 0 0,-12 18 4232 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="24">849 553 6911 0 0,'0'0'252'0'0,"-1"-1"0"0"0,1 1-1 0 0,-1 0 1 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1-1-1 0 0,1 1 1 0 0,-1 0 0 0 0,1 0-1 0 0,-1-1 1 0 0,1 1 0 0 0,-1 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,1-1-1 0 0,0 1 1 0 0,-1-1 0 0 0,1 1-1 0 0,0-1 1 0 0,-1 0 0 0 0,-5-16 3062 0 0,5 11-2821 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,1-7 0 0 0,2-1-112 0 0,0 0 0 0 0,2 1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0 0 0 0 0,2 1 0 0 0,-1 0 0 0 0,1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0 1 0 0 0,0 1 0 0 0,19-14 0 0 0,-22 19-192 0 0,0-1-1 0 0,1 1 1 0 0,-1 1 0 0 0,1-1-1 0 0,13-3 1 0 0,-18 6-164 0 0,1 0 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,1 0 0 0 0,-1 0-1 0 0,1 1 1 0 0,-1-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,4 2 0 0 0,-5-1-12 0 0,0-1 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 1 0 0 0,1-1 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 1 1 0 0,1 0-1 0 0,-1-1 0 0 0,0 1 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 1 0 0,0-1-1 0 0,-1 1 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 4 0 0 0,-3 4 65 0 0,1 1 0 0 0,-1 0 0 0 0,-11 19 0 0 0,7-14-31 0 0,-17 35 10 0 0,7-16-9 0 0,-18 51-1 0 0,25-51-167 0 0,-9 47 0 0 0,17-68 81 0 0,1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,1 0 0 0 0,1 0 0 0 0,3 22 0 0 0,-4-34 29 0 0,0 0-1 0 0,1-1 1 0 0,-1 1-1 0 0,0 0 1 0 0,1-1 0 0 0,0 1-1 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 1 0 0,-1-1-1 0 0,1 1 1 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 1 0 0 0,0-1-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1-1 0 0 0,0 1-1 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 1 0 0,-1-1 0 0 0,1 0-1 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,0-1 1 0 0,1 1-1 0 0,2-2 3 0 0,-1 1-1 0 0,0 0 1 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,-1 1 1 0 0,1-1 0 0 0,-1 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,4-6-1 0 0,-5 5 46 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 1 0 0,-1 1-1 0 0,-1-10 0 0 0,1 8 125 0 0,0 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1-1 0 0,-1 0 1 0 0,1 1 0 0 0,-8-8 0 0 0,-10-9 442 0 0,-1 1 0 0 0,0 1-1 0 0,-48-30 1 0 0,68 49-611 0 0,1-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1-1 0 0,3-3-1037 0 0,9 4-1459 0 0,-2 0-4287 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="21">1542 394 14599 0 0,'0'1'137'0'0,"-1"0"-1"0"0,1 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 1-1 0 0,0-1 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,1 0 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0-1 1 0 0,0 1-1 0 0,1 1 0 0 0,2 3 738 0 0,142 189 4499 0 0,-39-60-4084 0 0,-94-126-964 0 0,-13-8-390 0 0,1 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,2 1 0 0 0,-2 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0-1 0 0 0,1 1 0 0 0,-1 0-1 0 0,0-1 1 0 0,1 0 0 0 0,1-3-1806 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="22">1 292 11519 0 0,'0'0'1040'0'0,"17"0"2082"0"0,96-7 1768 0 0,-57 5-3404 0 0,60 7-1 0 0,-80 1-896 0 0,-33-5-509 0 0,0-1 0 0 0,1 1-1 0 0,-2 0 1 0 0,1 0-1 0 0,0 1 1 0 0,-1-1-1 0 0,1 1 1 0 0,0-1 0 0 0,4 4-1 0 0,-7-4-50 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 1 1 0 0,0-1-1 0 0,1 1 0 0 0,-1-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,0-1 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,0-1 1 0 0,-1 0-1 0 0,0 1 0 0 0,-13 15 510 0 0,12-13-464 0 0,-45 45 620 0 0,-50 48 18 0 0,3-12 79 0 0,89-76-713 0 0,9-5-920 0 0,14-6-4221 0 0,-7 0-3402 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="23">495 305 2303 0 0,'2'3'8567'0'0,"-2"-3"-8403"0"0,11-1 4812 0 0,13-4-2000 0 0,-23 4-2924 0 0,26-4 544 0 0,-1 1 0 0 0,0 1 0 0 0,0 1 0 0 0,1 1 0 0 0,50 6 0 0 0,-68-4-521 0 0,0 0 0 0 0,0 1 0 0 0,-1 0 0 0 0,1 1 0 0 0,13 5 0 0 0,-21-8-35 0 0,1 1 0 0 0,0 0 0 0 0,-1 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 1 1 0 0,0-1 0 0 0,1 0 0 0 0,-1 0-1 0 0,0 1 1 0 0,-1-1 0 0 0,2 0 0 0 0,-1 1-1 0 0,0-1 1 0 0,-1 1 0 0 0,1-1-1 0 0,0 1 1 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1-1 0 0,1 0 1 0 0,-1-1 0 0 0,0 1 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,-1 0 0 0 0,1-1-1 0 0,-2 4 1 0 0,-3 4 183 0 0,2 0 0 0 0,-1 0 1 0 0,-1-1-1 0 0,-1 1 0 0 0,-7 9 0 0 0,-37 38 337 0 0,15-19-275 0 0,-133 140 787 0 0,192-206-6956 0 0,-12 18 4232 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="24">849 553 6911 0 0,'0'0'252'0'0,"-1"-1"0"0"0,1 1-1 0 0,-1 0 1 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1-1-1 0 0,1 1 1 0 0,-1 0 0 0 0,1 0-1 0 0,0-1 1 0 0,0 1 0 0 0,-2 0-1 0 0,2-1 1 0 0,-1 1 0 0 0,1-1-1 0 0,0 1 1 0 0,-1-1 0 0 0,1 1-1 0 0,0-1 1 0 0,-1 0 0 0 0,-5-16 3062 0 0,5 11-2821 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,1-7 0 0 0,2-1-112 0 0,0 0 0 0 0,2 1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0 0 0 0 0,3 1 0 0 0,-3 0 0 0 0,2 1 0 0 0,1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0 1 0 0 0,0 1 0 0 0,19-14 0 0 0,-22 19-192 0 0,0-1-1 0 0,1 1 1 0 0,-1 1 0 0 0,1-1-1 0 0,13-3 1 0 0,-18 6-164 0 0,1 0 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,1 0 0 0 0,-1 0-1 0 0,1 1 1 0 0,-1-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,4 2 0 0 0,-5-1-12 0 0,1-1 0 0 0,-3 0 1 0 0,2 0-1 0 0,-1 1 0 0 0,1-1 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 1 1 0 0,1 0-1 0 0,-1-1 0 0 0,0 1 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 1 0 0,-1-1-1 0 0,0 1 0 0 0,2 0 1 0 0,-2 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-2 4 0 0 0,-1 4 65 0 0,0 1 0 0 0,-1 0 0 0 0,-11 19 0 0 0,7-14-31 0 0,-17 35 10 0 0,6-16-9 0 0,-16 51-1 0 0,25-51-167 0 0,-11 47 0 0 0,18-68 81 0 0,1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,1 0 0 0 0,1 0 0 0 0,3 22 0 0 0,-4-34 29 0 0,0 0-1 0 0,1-1 1 0 0,-1 1-1 0 0,0 0 1 0 0,1-1 0 0 0,0 1-1 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 1 0 0,-1-1-1 0 0,1 1 1 0 0,-1-1 0 0 0,2 1-1 0 0,-1-1 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 1 0 0 0,0-1-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1-1 0 0 0,0 1-1 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 1 0 0,-1-1 0 0 0,1 0-1 0 0,0 1 1 0 0,-1-1-1 0 0,0 0 1 0 0,2 0-1 0 0,-1 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,0-1 1 0 0,1 1-1 0 0,2-2 3 0 0,-1 1-1 0 0,0 0 1 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,-1 1 1 0 0,1-1 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,1 0 1 0 0,3-6-1 0 0,-5 5 46 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 1 0 0,-1 1-1 0 0,-1-10 0 0 0,1 8 125 0 0,0 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1-1 0 0,-2 0 1 0 0,3 1 0 0 0,-9-8 0 0 0,-10-9 442 0 0,-1 1 0 0 0,0 1-1 0 0,-48-30 1 0 0,68 49-611 0 0,1-1 0 0 0,0 1-1 0 0,0-1 1 0 0,1 0 0 0 0,-2 0 0 0 0,1 1 0 0 0,0-1-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1-1 0 0,3-3-1037 0 0,9 4-1459 0 0,-2 0-4287 0 0</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -4717,21 +4713,21 @@
           <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2023-12-12T19:21:11.812"/>
+      <inkml:timestamp xml:id="ts0" timeString="2024-01-09T19:28:28.756"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.05" units="cm"/>
       <inkml:brushProperty name="height" value="0.05" units="cm"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">32 422 7831 0 0,'-2'-6'346'0'0,"1"4"751"0"0,1 0-1 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 1 0 0,0 0-1 0 0,0 1 0 0 0,-3-3 0 0 0,4 5-946 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 1 1 0 0,0-1 60 0 0,4 26 327 0 0,26 133 910 0 0,-28-130-1330 0 0,0 1 1 0 0,-2-1-1 0 0,-4 42 0 0 0,1-51-48 0 0,2-9 38 0 0,-1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,-8 22-1 0 0,10-33-93 0 0,1 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,-1 0-1 0 0,1 1 1 0 0,0-1-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 1-1 0 0,0-1 1 0 0,0 0-1 0 0,-1 1 1 0 0,1-1 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 1 1 0 0,-1-1 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,-1-1-1 0 0,1 1 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0-1-1 0 0,-1 1 1 0 0,1 0-1 0 0,0 0 1 0 0,0-1 0 0 0,-1 1-1 0 0,1 0 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,-1 0-1 0 0,1-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0-1 0 0 0,-10-24 340 0 0,7 7-287 0 0,-1 0 0 0 0,2 0 0 0 0,1-1 0 0 0,0 1 0 0 0,3-22 0 0 0,15-94-69 0 0,-10 83-31 0 0,-5 36 37 0 0,19-98-36 0 0,-18 100 25 0 0,1 0-1 0 0,1 0 1 0 0,0 1 0 0 0,0-1-1 0 0,1 1 1 0 0,11-15 0 0 0,-16 25 1 0 0,1 0-1 0 0,-1 1 1 0 0,0-1 0 0 0,0 1 0 0 0,1 0-1 0 0,-1-1 1 0 0,1 1 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 1-1 0 0,1-1 1 0 0,0 1 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,-1 1-1 0 0,1 0 1 0 0,0-1 0 0 0,2 3 0 0 0,2 0-15 0 0,-1 0 1 0 0,0 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,0 1 0 0 0,-1-1 1 0 0,1 1-1 0 0,6 8 1 0 0,-7-7 20 0 0,0 0-1 0 0,0-1 1 0 0,0 2 0 0 0,-1-1 0 0 0,0 0 0 0 0,2 9 0 0 0,-4-12 12 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-4 5 0 0 0,1 0 70 0 0,-1-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-2-1 0 0 0,1 1-1 0 0,-1-1 1 0 0,0-1 0 0 0,-10 7 0 0 0,-4 1 272 0 0,0-1-1 0 0,-27 10 1 0 0,41-19-323 0 0,0 0 0 0 0,0-1 0 0 0,0 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,-14 0 0 0 0,33-18-2590 0 0,-3 6-228 0 0,5-1-5707 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1">377 252 10591 0 0,'-1'1'238'0'0,"0"1"-1"0"0,0-1 0 0 0,0 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 1 0 0 0,1-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 1 0 0,0 2-1 0 0,7 32 4460 0 0,-3-21-4448 0 0,31 150 1976 0 0,8 36-1364 0 0,-42-192-803 0 0,-1-5-1 0 0,0-1 1 0 0,1 1-1 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,1-1 1 0 0,-1 0-1 0 0,0 1 1 0 0,1-1-1 0 0,2 4 0 0 0,-4-7-41 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0-1-1 0 0,4-13 315 0 0,-4 12-239 0 0,20-119 1634 0 0,-11 53-874 0 0,-3 34-576 0 0,24-132 636 0 0,-22 133-879 0 0,1 0 0 0 0,26-60 0 0 0,-35 92-150 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,0-1-1 0 0,-1 0 1 0 0,1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,2-1 0 0 0,4 2-1402 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2">758 662 16471 0 0,'-1'10'449'0'0,"0"-1"-1"0"0,0 1 1 0 0,1-1 0 0 0,0 1-1 0 0,2 14 1 0 0,-1-22-403 0 0,-1 0 0 0 0,1 0 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,1-1-1 0 0,-1 1 0 0 0,3 0 0 0 0,-1-1-40 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,-1-1 0 0 0,4-3 0 0 0,-2 2 55 0 0,-1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-2 0 0 0,-1 1 0 0 0,1 0 0 0 0,0-9 0 0 0,-1 12 36 0 0,-1 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-4 0 0 0 0,-4 0 483 0 0,0 0-1 0 0,1 0 0 0 0,-1 1 1 0 0,0 0-1 0 0,-14 3 0 0 0,-6-1-268 0 0,29-2-320 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,-1-1 0 0 0,0 0 1 0 0,3-2-2521 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3">1125 466 11975 0 0,'2'1'491'0'0,"0"0"1"0"0,-1 0-1 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,4 1 0 0 0,22 1 404 0 0,-25-2-690 0 0,6 0-125 0 0,0 0 0 0 0,0-1 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,1-1 1 0 0,-1 0-1 0 0,0 0 0 0 0,11-8 0 0 0,-6 3-223 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4">1043 237 17855 0 0,'0'0'76'0'0,"0"0"0"0"0,0 0 1 0 0,0 0-1 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,11 7 1595 0 0,16 3-432 0 0,-26-9-1155 0 0,9 1 6 0 0,0 0 0 0 0,0 0 0 0 0,0-1 1 0 0,1-1-1 0 0,-1 1 0 0 0,0-2 0 0 0,0 1 0 0 0,10-3 1 0 0,22-6-6888 0 0,-16 1-833 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5">1513 80 8751 0 0,'-5'-2'3135'0'0,"9"-1"422"0"0,11-2-949 0 0,-1 3-2172 0 0,0 0 0 0 0,1 2 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 2 0 0 0,0-1 0 0 0,1 2 0 0 0,-1 0 0 0 0,0 1 0 0 0,0 0 0 0 0,19 10 0 0 0,-25-11-380 0 0,-1 1-1 0 0,0 0 1 0 0,0 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0 0 0 0 0,7 10 0 0 0,-9-11-15 0 0,-1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 1 1 0 0,0 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,0 0 1 0 0,0 8-1 0 0,-1-7 7 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1-1 0 0 0,-2 1 1 0 0,-6 7-1 0 0,-3 3 95 0 0,-1 0-1 0 0,-27 22 1 0 0,28-30-102 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,-1-1 0 0 0,-17 6-1 0 0,-14 8 96 0 0,36-13-49 0 0,10-8-81 0 0,0 0-1 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 1 0 0,0 1-1 0 0,21 7 300 0 0,-17-7-296 0 0,8 1-245 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,0-2 0 0 0,0 1 0 0 0,0-1 0 0 0,16-10 0 0 0,-12 5-7953 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6">1915 13 11055 0 0,'5'7'6516'0'0,"-4"-7"-6191"0"0,10 5 2133 0 0,13 0-1133 0 0,-6-4-771 0 0,0-1-1 0 0,0 0 0 0 0,35-7 1 0 0,4 0 25 0 0,-37 5-263 0 0,1 2 0 0 0,27 2 0 0 0,-41-1-236 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,-1 0 0 0 0,1 0 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 1 1 0 0,-1 1-1 0 0,8 5 0 0 0,-13-8-62 0 0,0 0 0 0 0,0-1-1 0 0,-1 1 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,-2 1-1 0 0,-1 4 84 0 0,-1 0 0 0 0,1-1 0 0 0,-9 9 0 0 0,7-8-10 0 0,-30 37 529 0 0,-59 93-1 0 0,73-101-438 0 0,-34 41 1 0 0,43-64-159 0 0,12-11-28 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,1-1-46 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1-1-1 0 0,-1 1-58 0 0,9-21-3008 0 0,-1 8 1271 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="7">2418 0 1839 0 0,'22'7'10927'0'0,"2"-1"-5164"0"0,-16-4-5190 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 1 1 0 0,0 1 0 0 0,0-1-1 0 0,9 7 1 0 0,-16-9-520 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 1 0 0,0 2-1 0 0,0-2 9 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 1 0 0 0,-2 4 0 0 0,-1 0 44 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1-1 0 0,-11 9 1 0 0,14-12-88 0 0,-1 0-1 0 0,1-1 1 0 0,0 1 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,1 1 1 0 0,-3 3 0 0 0,4-6-21 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,1-1-1 0 0,1 2 0 0 0,10 5-201 0 0,24 13-1 0 0,-24-15 135 0 0,0 2 0 0 0,14 9 0 0 0,-22-13 68 0 0,-1 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,-1 0 1 0 0,1 1 0 0 0,0-1-1 0 0,-1 1 1 0 0,0 0-1 0 0,0-1 1 0 0,3 7-1 0 0,-4-5 41 0 0,0-1 1 0 0,0 1-1 0 0,-1 0 0 0 0,1-1 1 0 0,-1 1-1 0 0,0 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,-1-1 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0-1 0 0 0,-3 4 1 0 0,2-3 79 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 1 0 0,-1-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,0-1 1 0 0,-8 1-1 0 0,5-3 527 0 0,5 1-2227 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">32 422 7831 0 0,'-2'-6'346'0'0,"1"4"751"0"0,1 0-1 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 1 0 0,0 0-1 0 0,0 1 0 0 0,-3-3 0 0 0,4 5-946 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 1 1 0 0,0-1 60 0 0,4 26 327 0 0,26 133 910 0 0,-28-130-1330 0 0,0 1 1 0 0,-2-1-1 0 0,-4 42 0 0 0,1-51-48 0 0,2-9 38 0 0,-1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,-8 22-1 0 0,10-33-93 0 0,1 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,-1 0-1 0 0,1 1 1 0 0,0-1-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 1-1 0 0,0-1 1 0 0,0 0-1 0 0,-1 1 1 0 0,1-1 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 1 1 0 0,-1-1 0 0 0,1 0-1 0 0,0 0 1 0 0,-2 0-1 0 0,2 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,-1-1-1 0 0,1 1 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0-1-1 0 0,-1 1 1 0 0,1 0-1 0 0,0 0 1 0 0,0-1 0 0 0,-1 1-1 0 0,1 0 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,-1 0-1 0 0,1-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0-1 0 0 0,-10-24 340 0 0,7 7-287 0 0,-1 0 0 0 0,2 0 0 0 0,1-1 0 0 0,0 1 0 0 0,3-22 0 0 0,15-94-69 0 0,-10 83-31 0 0,-5 36 37 0 0,19-98-36 0 0,-18 100 25 0 0,1 0-1 0 0,1 0 1 0 0,0 1 0 0 0,0-1-1 0 0,1 1 1 0 0,11-15 0 0 0,-16 25 1 0 0,1 0-1 0 0,-1 1 1 0 0,0-1 0 0 0,0 1 0 0 0,1 0-1 0 0,-1-1 1 0 0,1 1 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,2 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,-1 1-1 0 0,1 0 1 0 0,0-1 0 0 0,2 3 0 0 0,2 0-15 0 0,-1 0 1 0 0,0 1-1 0 0,0-1 1 0 0,1 1-1 0 0,-1 1 0 0 0,-1-1 1 0 0,1 1-1 0 0,6 8 1 0 0,-7-7 20 0 0,0 0-1 0 0,0-1 1 0 0,0 2 0 0 0,-2-1 0 0 0,2 0 0 0 0,1 9 0 0 0,-4-12 12 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-5 5 0 0 0,3 0 70 0 0,-2-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1-1 0 0,-1-1 1 0 0,0-1 0 0 0,-10 7 0 0 0,-4 1 272 0 0,0-1-1 0 0,-28 10 1 0 0,43-19-323 0 0,-1 0 0 0 0,0-1 0 0 0,0 0 0 0 0,-2-1 1 0 0,3 1-1 0 0,-15 0 0 0 0,33-18-2590 0 0,-3 6-228 0 0,5-1-5707 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1">377 252 10591 0 0,'-1'1'238'0'0,"0"1"-1"0"0,0-1 0 0 0,-1 0 1 0 0,2 1-1 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 1 0 0,0 2-1 0 0,7 32 4460 0 0,-3-21-4448 0 0,31 150 1976 0 0,7 36-1364 0 0,-41-192-803 0 0,-1-5-1 0 0,0-1 1 0 0,2 1-1 0 0,-1-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,1-1 1 0 0,-1 0-1 0 0,0 1 1 0 0,1-1-1 0 0,2 4 0 0 0,-4-7-41 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0-1-1 0 0,4-13 315 0 0,-4 12-239 0 0,20-119 1634 0 0,-11 53-874 0 0,-3 34-576 0 0,24-132 636 0 0,-22 133-879 0 0,1 0 0 0 0,26-60 0 0 0,-35 92-150 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0 1 0 0 0,0-1-1 0 0,-1 0 1 0 0,2 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1-1 0 0,-1 0 1 0 0,4-1 0 0 0,3 2-1402 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2">758 662 16471 0 0,'-1'10'449'0'0,"0"-1"-1"0"0,0 1 1 0 0,1-1 0 0 0,0 1-1 0 0,2 14 1 0 0,-1-22-403 0 0,-1 0 0 0 0,1 0 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,1-1 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,4 0 0 0 0,-2-1-40 0 0,-2 0 0 0 0,3 0 0 0 0,-2-1 1 0 0,0 1-1 0 0,0-1 0 0 0,2 1 0 0 0,-2-1 0 0 0,-1 0 0 0 0,3-1 0 0 0,-2 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,2 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 0 0 0,-1-1 0 0 0,3-3 0 0 0,0 2 55 0 0,-2 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,-1 0 0 0 0,-1 0-1 0 0,1 1 1 0 0,1-2 0 0 0,-2 1 0 0 0,1 0 0 0 0,0-9 0 0 0,-1 12 36 0 0,-1 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,-1 0 0 0 0,1-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 1 0 0,-2 0-1 0 0,1 0 0 0 0,2 1 0 0 0,-2-1 0 0 0,1 0 0 0 0,-5 0 0 0 0,-2 0 483 0 0,-1 0-1 0 0,0 0 0 0 0,1 1 1 0 0,-1 0-1 0 0,-14 3 0 0 0,-6-1-268 0 0,29-2-320 0 0,-1 0-1 0 0,1 0 0 0 0,-2 0 0 0 0,2 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,-1-1 0 0 0,0 0 1 0 0,3-2-2521 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3">1125 466 11975 0 0,'1'1'491'0'0,"1"0"1"0"0,-1 0-1 0 0,1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,5 1 0 0 0,20 1 404 0 0,-23-2-690 0 0,4 0-125 0 0,2 0 0 0 0,-1-1 0 0 0,-1 0 0 0 0,0-1 0 0 0,2 0 0 0 0,-1 0 0 0 0,-2 0 0 0 0,2-1 0 0 0,0-1 1 0 0,-2 0-1 0 0,2 0 0 0 0,9-8 0 0 0,-4 3-223 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4">1042 237 17855 0 0,'0'0'76'0'0,"0"0"0"0"0,0 0 1 0 0,0 0-1 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,11 7 1595 0 0,16 3-432 0 0,-26-9-1155 0 0,9 1 6 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 1 0 0,1-1-1 0 0,-2 1 0 0 0,1-2 0 0 0,1 1 0 0 0,9-3 1 0 0,21-6-6888 0 0,-15 1-833 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5">1513 80 8751 0 0,'-6'-2'3135'0'0,"11"-1"422"0"0,10-2-949 0 0,-2 3-2172 0 0,1 0 0 0 0,1 2 0 0 0,-1 0 0 0 0,2 0 0 0 0,-2 2 0 0 0,-1-1 0 0 0,2 2 0 0 0,-1 0 0 0 0,0 1 0 0 0,1 0 0 0 0,17 10 0 0 0,-24-11-380 0 0,0 1-1 0 0,-2 0 1 0 0,2 1 0 0 0,-2 0 0 0 0,1 0 0 0 0,-2 0 0 0 0,2 1 0 0 0,-2 0 0 0 0,8 10 0 0 0,-8-11-15 0 0,-3 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,2 1 1 0 0,-2-1-1 0 0,-1 1 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,0 0 1 0 0,0 8-1 0 0,-1-7 7 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,1 0 1 0 0,-3 0-1 0 0,1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1-1 0 0 0,-1 1 1 0 0,-6 7-1 0 0,-3 3 95 0 0,0 0-1 0 0,-29 22 1 0 0,29-30-102 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-2-1 0 0 0,-18 6-1 0 0,-13 8 96 0 0,36-13-49 0 0,10-8-81 0 0,0 0-1 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 1 0 0,0 1-1 0 0,21 7 300 0 0,-17-7-296 0 0,8 1-245 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,0-2 0 0 0,0 1 0 0 0,1-1 0 0 0,14-10 0 0 0,-11 5-7953 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6">1915 13 11055 0 0,'4'7'6516'0'0,"-3"-7"-6191"0"0,10 5 2133 0 0,13 0-1133 0 0,-6-4-771 0 0,0-1-1 0 0,0 0 0 0 0,36-7 1 0 0,2 0 25 0 0,-36 5-263 0 0,2 2 0 0 0,26 2 0 0 0,-42-1-236 0 0,1 0 1 0 0,0 0-1 0 0,0 1 0 0 0,-1 0 0 0 0,1 0 1 0 0,0 1-1 0 0,-1-1 0 0 0,2 1 1 0 0,-3 1-1 0 0,9 5 0 0 0,-13-8-62 0 0,0 0 0 0 0,0-1-1 0 0,-1 1 1 0 0,1 0 0 0 0,-1 0 0 0 0,2 0-1 0 0,-1 0 1 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,-3 1-1 0 0,0 4 84 0 0,-1 0 0 0 0,1-1 0 0 0,-9 9 0 0 0,7-8-10 0 0,-30 37 529 0 0,-59 93-1 0 0,73-101-438 0 0,-33 41 1 0 0,42-64-159 0 0,12-11-28 0 0,0-1 0 0 0,-2 1 0 0 0,2-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,2-1-46 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,2-1-1 0 0,-2 1-58 0 0,8-21-3008 0 0,0 8 1271 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="7">2417 0 1839 0 0,'22'7'10927'0'0,"2"-1"-5164"0"0,-16-4-5190 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 1 1 0 0,0 1 0 0 0,0-1-1 0 0,9 7 1 0 0,-15-9-520 0 0,-2 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,2 0 0 0 0,-2 1 0 0 0,0-1 0 0 0,0 1 1 0 0,0 2-1 0 0,0-2 9 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 1 0 0,-2 1-1 0 0,1-1 0 0 0,0 1 0 0 0,-2 4 0 0 0,-1 0 44 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1-1 0 0,-11 9 1 0 0,15-12-88 0 0,-3 0-1 0 0,2-1 1 0 0,0 1 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,1 1 1 0 0,-3 3 0 0 0,4-6-21 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,2-1-1 0 0,-1 2 0 0 0,11 5-201 0 0,24 13-1 0 0,-24-15 135 0 0,1 2 0 0 0,12 9 0 0 0,-21-13 68 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 1 0 0 0,0-1-1 0 0,-1 1 1 0 0,0 0-1 0 0,0-1 1 0 0,3 7-1 0 0,-4-5 41 0 0,0-1 1 0 0,0 1-1 0 0,-1 0 0 0 0,1-1 1 0 0,-1 1-1 0 0,0 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,-1-1 1 0 0,0 1-1 0 0,-2-1 0 0 0,3 1 0 0 0,-2-1 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0-1 0 0 0,-3 4 1 0 0,2-3 79 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,1 0 1 0 0,-3-1-1 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-2-1 1 0 0,0 0-1 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,0-1 1 0 0,-8 1-1 0 0,5-3 527 0 0,5 1-2227 0 0</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -4755,19 +4751,19 @@
           <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2023-12-12T19:21:11.820"/>
+      <inkml:timestamp xml:id="ts0" timeString="2024-01-09T19:28:28.764"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.05" units="cm"/>
       <inkml:brushProperty name="height" value="0.05" units="cm"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">138 944 9127 0 0,'6'-13'5890'0'0,"-4"10"-5532"0"0,0 1 0 0 0,0 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,1 0 1 0 0,0 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,3 0 1 0 0,45-6 916 0 0,-44 6-1033 0 0,-2 0-165 0 0,239-15 2214 0 0,-199 15-1933 0 0,62-11-1 0 0,44-15 286 0 0,-108 18-517 0 0,-3 0 54 0 0,64-26 0 0 0,-24 7-19 0 0,-11 9-41 0 0,1 3-1 0 0,0 3 0 0 0,114-7 1 0 0,-144 15 19 0 0,0-1 1 0 0,69-21-1 0 0,-16 3 11 0 0,-23 11-32 0 0,88-3 1 0 0,-106 12-68 0 0,250-17 316 0 0,1 17 10 0 0,-72 10-251 0 0,135 6-135 0 0,-94-2 157 0 0,-260-10-64 0 0,-8 0-33 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 1-1 0 0,-1-1 1 0 0,8 3-1 0 0,-3-1 144 0 0,-8-6 67 0 0,-12-11-577 0 0,8 10-712 0 0,-7-9-7344 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1">113 254 10047 0 0,'2'3'4151'0'0,"11"21"-1186"0"0,-1 13-1651 0 0,-1 1 1 0 0,6 53-1 0 0,-14-77-1238 0 0,-1-6-52 0 0,-1 0 1 0 0,1 0-1 0 0,-2-1 0 0 0,1 17 0 0 0,-1-24-57 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,-2-3-1525 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2">0 354 13503 0 0,'44'3'5608'0'0,"1"3"-3598"0"0,41 4-820 0 0,-58-10-1269 0 0,0-1 1 0 0,-1-2-1 0 0,35-7 0 0 0,-38 5-838 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3">1242 6 5063 0 0,'-3'-4'3607'0'0,"2"4"-3246"0"0,1 0 0 0 0,0 0-1 0 0,-1-1 1 0 0,1 1 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1-1 0 0 0,-1 1-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,1 1 1 0 0,-1-1 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 1-51 0 0,0 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 2 0 0 0,-1 6 8 0 0,1 1 0 0 0,-2 15 0 0 0,3-22 166 0 0,-3 61-80 0 0,3 0-1 0 0,10 88 1 0 0,-9-146-488 0 0,-1-3-84 0 0,1 1-1 0 0,-1-1 1 0 0,1 1 0 0 0,-1-1-1 0 0,1 1 1 0 0,0-1 0 0 0,1 0-1 0 0,2 7 1 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4">1355 69 12895 0 0,'0'1'71'0'0,"-1"12"399"0"0,0 1 0 0 0,1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,3 15 0 0 0,-2-21-128 0 0,2 9 499 0 0,11 32 0 0 0,-13-44-738 0 0,0 0 1 0 0,1-1 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,7 4 1 0 0,-8-7-84 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,3-1 0 0 0,-1 0 10 0 0,-1 0 0 0 0,1 0-1 0 0,-1-1 1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,4-4-1 0 0,-1 1 51 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,4-11 0 0 0,-5 11 79 0 0,-1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1-11 0 0 0,-1 15-45 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0 1 1 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,-3-1 0 0 0,-71-16 1395 0 0,77 18-1539 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,5-2-3318 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5">1662 63 5063 0 0,'6'10'-222'0'0,"2"3"2536"0"0,1 0-1 0 0,0-1 1 0 0,19 21 0 0 0,-25-30-1777 0 0,0 0 0 0 0,0 0 1 0 0,1-1-1 0 0,-1 1 0 0 0,1-1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,7 2 0 0 0,-8-3-641 0 0,1-1 0 0 0,-1 1 1 0 0,0-1-1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,6-2 0 0 0,-7 2 186 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 1 0 0,0 0-1 0 0,-1-1 1 0 0,1 0-1 0 0,-1 1 1 0 0,0-1 0 0 0,1 0-1 0 0,-1 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0-4-1 0 0,-1 3 129 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,-4-3 0 0 0,1 1-3 0 0,0 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 1-1 0 0,-1 0 1 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,1 0-1 0 0,-1 1 1 0 0,-11 1 0 0 0,17-1-1206 0 0,6-2-862 0 0,2-3 373 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">138 943 9127 0 0,'6'-13'5890'0'0,"-4"10"-5532"0"0,0 1 0 0 0,-1 0 1 0 0,3 1-1 0 0,-2-1 0 0 0,1 0 1 0 0,0 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,3 0 1 0 0,45-6 916 0 0,-44 6-1033 0 0,-2 0-165 0 0,239-15 2214 0 0,-200 15-1933 0 0,63-11-1 0 0,45-15 286 0 0,-110 18-517 0 0,-1 0 54 0 0,63-25 0 0 0,-24 5-19 0 0,-11 10-41 0 0,1 3-1 0 0,0 3 0 0 0,113-7 1 0 0,-142 15 19 0 0,-1-1 1 0 0,68-21-1 0 0,-15 3 11 0 0,-23 11-32 0 0,88-3 1 0 0,-106 12-68 0 0,250-16 316 0 0,2 16 10 0 0,-74 10-251 0 0,137 5-135 0 0,-96-1 157 0 0,-259-10-64 0 0,-8 0-33 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 1-1 0 0,-1-1 1 0 0,9 3-1 0 0,-5-1 144 0 0,-7-6 67 0 0,-12-11-577 0 0,8 11-712 0 0,-7-10-7344 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1">113 254 10047 0 0,'1'3'4151'0'0,"13"21"-1186"0"0,-2 13-1651 0 0,-1 0 1 0 0,6 54-1 0 0,-14-77-1238 0 0,-1-6-52 0 0,-1 1 1 0 0,1-1-1 0 0,-2-1 0 0 0,1 17 0 0 0,-1-24-57 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,-2-3-1525 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2">0 354 13503 0 0,'43'2'5608'0'0,"3"4"-3598"0"0,40 4-820 0 0,-59-10-1269 0 0,2-1 1 0 0,-2-2-1 0 0,35-7 0 0 0,-39 6-838 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3">1241 6 5063 0 0,'-3'-4'3607'0'0,"2"4"-3246"0"0,1 0 0 0 0,0 0-1 0 0,-1-1 1 0 0,1 1 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1-1 0 0 0,-1 1-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,1 1 1 0 0,-1-1 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 1-51 0 0,0 0 1 0 0,-1 0-1 0 0,2 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,0 2 0 0 0,-2 6 8 0 0,1 1 0 0 0,-2 15 0 0 0,3-22 166 0 0,-3 60-80 0 0,3 2-1 0 0,9 87 1 0 0,-8-146-488 0 0,-1-3-84 0 0,1 0-1 0 0,-1 0 1 0 0,1 1 0 0 0,-1-1-1 0 0,1 1 1 0 0,0-1 0 0 0,2 0-1 0 0,1 7 1 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4">1355 69 12895 0 0,'0'1'71'0'0,"-1"12"399"0"0,0 1 0 0 0,1 0 0 0 0,0-2 0 0 0,1 2 0 0 0,3 16 0 0 0,-3-22-128 0 0,3 9 499 0 0,11 32 0 0 0,-13-44-738 0 0,0 0 1 0 0,2-1 0 0 0,-2 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,0 0 0 0 0,2 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 0-1 0 0,7 4 1 0 0,-8-7-84 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,4-1 0 0 0,-2 0 10 0 0,-2 0 0 0 0,2 0-1 0 0,0-1 1 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,5-4-1 0 0,-3 1 51 0 0,0-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,3-11 0 0 0,-3 11 79 0 0,-2 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0-12 0 0 0,0 16-45 0 0,0 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-2 0 0 0 0,2 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 0-1 0 0,0 1 1 0 0,-2-1 0 0 0,2 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,-4-1 0 0 0,-69-16 1395 0 0,76 18-1539 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,4-2-3318 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5">1661 63 5063 0 0,'7'10'-222'0'0,"0"3"2536"0"0,3 0-1 0 0,-2-1 1 0 0,21 20 0 0 0,-26-29-1777 0 0,0 0 0 0 0,-1 0 1 0 0,2-1-1 0 0,0 2 0 0 0,0-2 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,7 2 0 0 0,-8-3-641 0 0,1-1 0 0 0,0 1 1 0 0,-1-1-1 0 0,-1 0 0 0 0,2 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,4-2 0 0 0,-6 2 186 0 0,0-1 1 0 0,1 1-1 0 0,0-1 1 0 0,-1 1 0 0 0,0-1-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1-1-1 0 0,1 1 1 0 0,-1 0-1 0 0,-1-2 1 0 0,1 1-1 0 0,-1 1 1 0 0,0-1 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,2 0 1 0 0,-1-4-1 0 0,-1 3 129 0 0,0 0-1 0 0,-1 1 0 0 0,1-1 1 0 0,0 0-1 0 0,-2 0 0 0 0,1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,-1 0 1 0 0,2 1-1 0 0,-2-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,-1 0 1 0 0,1 0-1 0 0,-3-3 0 0 0,0 1-3 0 0,-1 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-2 0 0 0 0,1 0-1 0 0,1 1 1 0 0,-2 0 0 0 0,2 0 0 0 0,-2 0 0 0 0,0 1-1 0 0,1 0 1 0 0,-2 0 0 0 0,2 0 0 0 0,0 1 0 0 0,-1 0-1 0 0,1 1 1 0 0,-12 1 0 0 0,17-1-1206 0 0,5-2-862 0 0,4-3 373 0 0</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -4791,15 +4787,15 @@
           <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2023-12-12T19:21:11.826"/>
+      <inkml:timestamp xml:id="ts0" timeString="2024-01-09T19:28:28.770"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.05" units="cm"/>
       <inkml:brushProperty name="height" value="0.05" units="cm"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">52 7 5527 0 0,'2'-6'8846'0'0,"-1"22"-3605"0"0,0-7-6400 0 0,-3 27 2798 0 0,-8 46-1 0 0,5-47-965 0 0,-12 48 837 0 0,0-4-207 0 0,15-67-1165 0 0,1-1 0 0 0,0 1 0 0 0,1 0 0 0 0,2 20 0 0 0,-2-32-146 0 0,0 1-1 0 0,0-1 0 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 1 0 0,0 1-1 0 0,1-1 0 0 0,-1 0 1 0 0,0 0-1 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,0 0 0 0 0,1 0 0 0 0,0 0-119 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0-1-1 0 0,-1 1 1 0 0,1-1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,-1-1-1 0 0,1 1 1 0 0,0-2-1 0 0,19-25-4121 0 0,-13 16 2559 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1">231 199 4143 0 0,'2'21'1165'0'0,"10"30"7339"0"0,-7-31-8545 0 0,-2-6 474 0 0,0-2 66 0 0,0 0 0 0 0,0-1 1 0 0,1 1-1 0 0,9 17 0 0 0,-12-27-432 0 0,0 1-1 0 0,0-1 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 1 1 0 0,0-2-1 0 0,1 1 0 0 0,-1 0 0 0 0,1 0 1 0 0,-1-1-1 0 0,1 0 0 0 0,-1 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,4-1 0 0 0,0 0-25 0 0,0-1-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0-1-1 0 0,-1 0 1 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0-1-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 1 0 0,0 1-1 0 0,0-1 1 0 0,6-8-1 0 0,-6 7 114 0 0,0-1-1 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-2-13 1 0 0,1 18-33 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 0 0 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,-3 0 0 0 0,-5-1 299 0 0,0 1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,-13 2 0 0 0,-9 0-302 0 0,32-2-150 0 0,0 0-1 0 0,0 0 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1-1 0 0 0,1 1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 1 0 0,4-6-4802 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">52 7 5527 0 0,'2'-6'8846'0'0,"0"22"-3605"0"0,-2-7-6400 0 0,-2 27 2798 0 0,-8 46-1 0 0,5-47-965 0 0,-11 48 837 0 0,-2-4-207 0 0,17-67-1165 0 0,-1-1 0 0 0,1 1 0 0 0,1 0 0 0 0,3 20 0 0 0,-3-32-146 0 0,0 1-1 0 0,0-1 0 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 1 0 0,0 1-1 0 0,1-1 0 0 0,-1 0 1 0 0,0 0-1 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 1 0 0,2 0-1 0 0,-2 0 0 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 0 0 0,0 0-119 0 0,0 0-1 0 0,-1-1 1 0 0,2 1-1 0 0,-1 0 1 0 0,0-1-1 0 0,-1 1 1 0 0,1-1-1 0 0,-1 1 1 0 0,2-1-1 0 0,-1 1 1 0 0,-1-1-1 0 0,1 1 1 0 0,1-2-1 0 0,17-25-4121 0 0,-12 16 2559 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1">230 199 4143 0 0,'3'21'1165'0'0,"8"30"7339"0"0,-6-31-8545 0 0,-1-6 474 0 0,-1-2 66 0 0,1 0 0 0 0,-2-1 1 0 0,2 1-1 0 0,9 17 0 0 0,-12-27-432 0 0,0 1-1 0 0,0-1 0 0 0,1 0 1 0 0,-1 0-1 0 0,2 0 0 0 0,-3 0 0 0 0,2 0 1 0 0,1 0-1 0 0,-2-1 0 0 0,1 1 1 0 0,0 0-1 0 0,0-1 0 0 0,-1 0 1 0 0,2 0-1 0 0,0 0 0 0 0,-1 1 1 0 0,1-2-1 0 0,-1 1 0 0 0,-1 0 0 0 0,3 0 1 0 0,-3-1-1 0 0,3 0 0 0 0,-2 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,4-1 0 0 0,0 0-25 0 0,-1-1-1 0 0,2 0 1 0 0,-2 0-1 0 0,1 0 1 0 0,1-1-1 0 0,-2 0 1 0 0,-2 0 0 0 0,4 0-1 0 0,-2 0 1 0 0,0-1-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 1 0 0,1 1-1 0 0,-2-1 1 0 0,8-8-1 0 0,-8 7 114 0 0,1-1-1 0 0,-1 1 0 0 0,1-1 0 0 0,-2 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,-1-1 1 0 0,2 2-1 0 0,-2-1 0 0 0,0-1 0 0 0,-1 1 0 0 0,2 0 0 0 0,-4-13 1 0 0,2 18-33 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 1 0 0,-1 0-1 0 0,2 0 0 0 0,-1 0 0 0 0,-1 1 0 0 0,2-1 0 0 0,-2 0 0 0 0,0 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 0 0 0 0,0 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1 0 1 0 0,-2 0-1 0 0,1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,-3 0 0 0 0,-6-1 299 0 0,3 2 0 0 0,-3 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-13 1 0 0 0,-10 1-302 0 0,33-2-150 0 0,0 0-1 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1-1 0 0 0,1 1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 1 0 0,3-6-4802 0 0</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -4823,16 +4819,16 @@
           <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2023-12-12T19:21:11.828"/>
+      <inkml:timestamp xml:id="ts0" timeString="2024-01-09T19:28:28.772"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.05" units="cm"/>
       <inkml:brushProperty name="height" value="0.05" units="cm"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1322 715 6911 0 0,'-2'-8'10620'0'0,"-1"20"-5960"0"0,-3 23-716 0 0,0 42-3320 0 0,6-69-616 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1-1 0 0 0,5 11-1 0 0,-5-13-12 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-2 0 0 0,0 1 0 0 0,1 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,7 2 0 0 0,-6-3-8 0 0,0 0 0 0 0,0 0 1 0 0,0-1-1 0 0,1 1 0 0 0,-1-1 1 0 0,0-1-1 0 0,1 1 1 0 0,-1-1-1 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,-1-1 1 0 0,9-6-1 0 0,-10 7 36 0 0,0-1-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,0-1 1 0 0,-1 1 0 0 0,1 0-1 0 0,-1-1 1 0 0,0 0-1 0 0,0 1 1 0 0,-1-1 0 0 0,1 1-1 0 0,-1-1 1 0 0,0 0-1 0 0,-1-6 1 0 0,0 6 59 0 0,0 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,-1-1 1 0 0,0 1-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1-1-1 0 0,1 2 0 0 0,-6-7 0 0 0,-5-4 457 0 0,-20-16-1 0 0,17 16-128 0 0,6 5-281 0 0,1 1 0 0 0,-1 1-1 0 0,0 0 1 0 0,-1 0 0 0 0,0 1 0 0 0,0 1 0 0 0,0 0-1 0 0,-1 0 1 0 0,-20-5 0 0 0,19 5-315 0 0,12 5 115 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 1 0 0,-1 0-1 0 0,1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,6-6-1689 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1">6989 967 9671 0 0,'-1'9'10150'0'0,"-5"21"-7137"0"0,-1 3-2185 0 0,-6 40 34 0 0,2 1-1 0 0,-1 90 1 0 0,12-160-871 0 0,1 16-154 0 0,-1-19 152 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,2 0 0 0 0,-2-1-46 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1-1 0 0,1 0 1 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1-1 0 0,1 0 1 0 0,-1-1 0 0 0,0 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,1-1 0 0 0,7-14-2338 0 0,-7 15 2296 0 0,5-15-1829 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2">7244 1018 7831 0 0,'-7'27'3730'0'0,"-8"53"-1"0"0,12-42-2688 0 0,1 1 0 0 0,3 46 0 0 0,0-74-861 0 0,0 0 1 0 0,0 0-1 0 0,1 0 1 0 0,1 0 0 0 0,0 0-1 0 0,8 19 1 0 0,-10-27-162 0 0,0-1 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,0-1 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1-1 0 0,-1-1 1 0 0,1 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1-1 0 0,0-1 1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0-1 0 0 0,0 0 0 0 0,2 0 0 0 0,0-1 37 0 0,0 0 1 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 1-1 0 0,-1-2 1 0 0,0 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 1-1 0 0,1-2 1 0 0,-1 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 0-1 0 0,0 1 1 0 0,0-1 0 0 0,2-9 0 0 0,1-6 351 0 0,-1-1 0 0 0,0 0 0 0 0,0-40 0 0 0,-3 49-43 0 0,-1-1-1 0 0,-1 1 1 0 0,0 0 0 0 0,-1-1 0 0 0,-4-19-1 0 0,4 27-193 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 1 0 0,0-1-1 0 0,-1 1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 1 1 0 0,-8-5-1 0 0,5 4 9 0 0,-1 1-1 0 0,1 0 1 0 0,-1 0 0 0 0,-15-3 0 0 0,5 3-2429 0 0,32 5-6173 0 0,-2 0 499 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1322 715 6911 0 0,'-2'-8'10620'0'0,"-1"20"-5960"0"0,-3 23-716 0 0,0 42-3320 0 0,6-69-616 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1-1 0 0 0,5 11-1 0 0,-5-13-12 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-2 0 0 0,0 1 0 0 0,1 0 0 0 0,1-1 0 0 0,-3 1 0 0 0,2-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,7 2 0 0 0,-6-3-8 0 0,0 0 0 0 0,0 0 1 0 0,0-1-1 0 0,1 1 0 0 0,-1-1 1 0 0,0-1-1 0 0,1 1 1 0 0,-1-1-1 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,-1 0 1 0 0,2-1-1 0 0,-1 1 0 0 0,-1-1 1 0 0,9-6-1 0 0,-10 7 36 0 0,0-1-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,-1-1 1 0 0,1 1 0 0 0,0 0-1 0 0,-1-1 1 0 0,0 0-1 0 0,0 1 1 0 0,-1-1 0 0 0,1 1-1 0 0,-1-1 1 0 0,0 0-1 0 0,-1-6 1 0 0,0 6 59 0 0,0 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,-2-1 1 0 0,2 1-1 0 0,-2 0 0 0 0,1 0 1 0 0,-1-1-1 0 0,1 2 0 0 0,-6-7 0 0 0,-5-4 457 0 0,-20-16-1 0 0,17 16-128 0 0,6 5-281 0 0,1 1 0 0 0,-1 1-1 0 0,0 0 1 0 0,-1 0 0 0 0,0 1 0 0 0,0 1 0 0 0,0 0-1 0 0,-1 0 1 0 0,-20-5 0 0 0,19 5-315 0 0,12 5 115 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 1 0 0,-1 0-1 0 0,1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,6-6-1689 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1">6988 967 9671 0 0,'-1'9'10150'0'0,"-5"21"-7137"0"0,0 3-2185 0 0,-8 40 34 0 0,3 1-1 0 0,-1 90 1 0 0,12-160-871 0 0,1 16-154 0 0,-1-19 152 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,2 0 0 0 0,-2-1-46 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1-1 0 0,1 0 1 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0-1 0 0,2-1 1 0 0,-2 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,1-1 0 0 0,7-14-2338 0 0,-7 15 2296 0 0,6-15-1829 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2">7243 1018 7831 0 0,'-7'27'3730'0'0,"-8"53"-1"0"0,12-42-2688 0 0,1 1 0 0 0,3 46 0 0 0,0-74-861 0 0,1 0 1 0 0,-2 0-1 0 0,2 0 1 0 0,1 0 0 0 0,0 0-1 0 0,8 19 1 0 0,-10-27-162 0 0,0-1 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,0-1 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1-1 0 0,-1-1 1 0 0,1 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1-1 0 0,0-1 1 0 0,1 0 0 0 0,-3 0 0 0 0,2 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0-1 0 0 0,1 0 0 0 0,0 0 0 0 0,1-1 37 0 0,0 0 1 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 0 0 0 0,2 1-1 0 0,-3-2 1 0 0,1 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,0 0 0 0 0,1 1-1 0 0,0-2 1 0 0,-1 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 0-1 0 0,0 1 1 0 0,0-1 0 0 0,2-9 0 0 0,1-6 351 0 0,-1-1 0 0 0,0 0 0 0 0,0-40 0 0 0,-3 49-43 0 0,-1-1-1 0 0,-1 1 1 0 0,0 0 0 0 0,-1-1 0 0 0,-4-19-1 0 0,4 27-193 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 1 0 0,0-1-1 0 0,-1 1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 1 1 0 0,-7-5-1 0 0,3 4 9 0 0,0 1-1 0 0,1 0 1 0 0,-1 0 0 0 0,-15-3 0 0 0,5 3-2429 0 0,33 5-6173 0 0,-4 0 499 0 0</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -4856,21 +4852,21 @@
           <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2023-12-12T19:21:11.831"/>
+      <inkml:timestamp xml:id="ts0" timeString="2024-01-09T19:28:28.775"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.05" units="cm"/>
       <inkml:brushProperty name="height" value="0.05" units="cm"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">12439 1740 9671 0 0,'-10'9'727'0'0,"8"-7"-147"0"0,0-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 3 0 0 0,-8 16 781 0 0,2 1 1 0 0,1 1 0 0 0,-9 43 0 0 0,15-58-1317 0 0,0 0-1 0 0,0 0 1 0 0,1 0-1 0 0,0 1 1 0 0,0-1-1 0 0,1 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,1 0 0 0 0,0-1-1 0 0,0 1 1 0 0,7 12-1 0 0,-7-16-45 0 0,-1-1-1 0 0,1 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,1-1 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,1 0 0 0 0,3 0 1 0 0,-2-1 14 0 0,0 0 1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,8-9 0 0 0,-3 3 96 0 0,-2-1 0 0 0,1 1 1 0 0,-2-2-1 0 0,1 1 0 0 0,-2-1 0 0 0,1 0 0 0 0,-2-1 0 0 0,1 1 0 0 0,-2-1 1 0 0,0 0-1 0 0,0-1 0 0 0,-1 1 0 0 0,-1 0 0 0 0,0-1 0 0 0,-1 0 0 0 0,-1-18 0 0 0,0 29 16 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 1 0 0,-1 1-1 0 0,1-1 0 0 0,-1 1 1 0 0,-4-4-1 0 0,3 2 40 0 0,-1 1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-7-2 0 0 0,-6 0 151 0 0,0 0 0 0 0,0 2-1 0 0,-34-2 1 0 0,45 3-335 0 0,5 1-101 0 0,-1 1-144 0 0,1-1 0 0 0,-1-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1-1 0 0,1 1 1 0 0,-1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,-1-2 0 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1">6322 372 7367 0 0,'-15'-5'1902'0'0,"-23"-9"-1"0"0,27 9 212 0 0,-1 0 0 0 0,1 1-1 0 0,-1 1 1 0 0,-18-4 0 0 0,-6 3-1079 0 0,0 2 0 0 0,-53 3 0 0 0,65 1-698 0 0,0 1-1 0 0,0 1 1 0 0,1 1 0 0 0,-41 15 0 0 0,-192 87 1156 0 0,73-31-1148 0 0,41-16-192 0 0,75-31-87 0 0,1 3-1 0 0,-73 48 1 0 0,-108 100 34 0 0,132-94-62 0 0,61-48-18 0 0,-54 49 0 0 0,89-68-19 0 0,0 2 0 0 0,2 0 0 0 0,0 0 0 0 0,2 2 0 0 0,0 0 0 0 0,2 1 0 0 0,0 0 0 0 0,2 1 0 0 0,0 0 0 0 0,2 1 0 0 0,1 0 0 0 0,-7 37 0 0 0,12-44-24 0 0,1 0 1 0 0,1-1-1 0 0,1 1 1 0 0,0 0-1 0 0,1 0 1 0 0,1-1-1 0 0,1 1 0 0 0,1-1 1 0 0,0 1-1 0 0,1-1 1 0 0,1-1-1 0 0,14 29 0 0 0,22 39-72 0 0,32 58-52 0 0,-53-106 81 0 0,48 62 0 0 0,-22-47 1 0 0,72 64 1 0 0,-29-31 46 0 0,141 130-55 0 0,-176-171 59 0 0,2-1 1 0 0,89 49 0 0 0,348 154-50 0 0,-113-104 64 0 0,13-36 0 0 0,287 0 0 0 0,-417-79 37 0 0,-5-2-2 0 0,589 61 173 0 0,-284-51-61 0 0,348-26 174 0 0,-365-26-92 0 0,-311 8-107 0 0,236-24 123 0 0,-200-3-124 0 0,-180 22-86 0 0,297-67 182 0 0,-311 61-131 0 0,-1-3-1 0 0,-1-4 0 0 0,136-68 1 0 0,136-116 127 0 0,-253 145-174 0 0,150-94 122 0 0,-207 138-161 0 0,-1-1 0 0 0,-1-2 0 0 0,-1-2 0 0 0,-1-1 0 0 0,-2-2 0 0 0,-1-1 0 0 0,53-70 0 0 0,-49 53 114 0 0,55-101-1 0 0,-76 121-71 0 0,-2-1-1 0 0,0-1 0 0 0,-2 0 0 0 0,-1-1 0 0 0,6-43 1 0 0,-9 36-1 0 0,-3-1 1 0 0,-1 0 0 0 0,-1-1-1 0 0,-3 1 1 0 0,-1 0 0 0 0,-2 0 0 0 0,-1 1-1 0 0,-3 0 1 0 0,-1 0 0 0 0,-22-57-1 0 0,12 50 4 0 0,-2 0 0 0 0,-1 1 0 0 0,-3 1 0 0 0,-1 1-1 0 0,-2 1 1 0 0,-2 2 0 0 0,-2 1 0 0 0,-1 2 0 0 0,-64-53-1 0 0,-198-131 89 0 0,196 155-93 0 0,-118-57 1 0 0,135 84-6 0 0,0 4 0 0 0,-104-27 0 0 0,-180-27 36 0 0,300 73-66 0 0,-771-149 59 0 0,-115 30 0 0 0,311 80-64 0 0,549 48 0 0 0,-227-8 0 0 0,-49-3 0 0 0,-174-24 0 0 0,-99 21 75 0 0,205 46 75 0 0,402-24-130 0 0,-126 12 51 0 0,1 6-1 0 0,-167 45 0 0 0,257-44-363 0 0,2 4 1 0 0,0 2-1 0 0,-85 49 0 0 0,131-65-143 0 0,-46 27-2769 0 0,52-26 1841 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2">4222 1440 8751 0 0,'-4'-1'1148'0'0,"0"0"-1"0"0,0 0 0 0 0,0 0 1 0 0,0-1-1 0 0,-5-2 0 0 0,5 2-597 0 0,1 0 0 0 0,0-1 0 0 0,-1 1 1 0 0,1-1-1 0 0,0 0 0 0 0,1 1 0 0 0,-5-6 0 0 0,-5-6 1309 0 0,-10 3 288 0 0,10 3-1442 0 0,1 1 0 0 0,-25-12 0 0 0,9 6-107 0 0,11 4-288 0 0,0 1 1 0 0,-1 0-1 0 0,-1 2 0 0 0,1 0 1 0 0,-1 0-1 0 0,-25-3 0 0 0,-9 3 50 0 0,0 2 0 0 0,-69 4 0 0 0,-94-3 15 0 0,57-2-169 0 0,-373-12 194 0 0,495 13-359 0 0,-65-19-1 0 0,65 14 21 0 0,-61-8 0 0 0,19 9 1 0 0,-139-7-60 0 0,190 13-2 0 0,1 0 0 0 0,-31-8 0 0 0,-11-1 0 0 0,-192-11 0 0 0,133 23 0 0 0,45 2 0 0 0,71-4 0 0 0,0 0 0 0 0,-18-4 0 0 0,28 5 0 0 0,-9-2 0 0 0,3 0 0 0 0,1 1 0 0 0,-1 0 0 0 0,-8 0 0 0 0,14 1 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,0-1-1 0 0,3-8-25 0 0,11-11-42 0 0,-11 17 50 0 0,20-30-31 0 0,2 2 1 0 0,49-48-1 0 0,-57 64 31 0 0,1 0-1 0 0,0 1 1 0 0,1 1-1 0 0,0 1 1 0 0,1 1 0 0 0,26-11-1 0 0,-2 2 19 0 0,-25 11 0 0 0,0 1 0 0 0,41-12 0 0 0,-41 16 0 0 0,1 2 0 0 0,0 0 0 0 0,26 0 0 0 0,-47 2-88 0 0,-1 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,1 0 0 0 0,0-1-1 0 0,-1 0 1 0 0,1 1 0 0 0,0-1-1 0 0,-1 0 1 0 0,1 1 0 0 0,0-1 0 0 0,-2-1-1 0 0,2 0-43 0 0,0 2 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1-1 0 0,-1 1 1 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-3 0 0 0 0,-2 2-1532 0 0,1 0-51 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3">1454 1009 13015 0 0,'1'5'703'0'0,"0"0"0"0"0,0 1 0 0 0,1-1 0 0 0,0 0 0 0 0,4 7 0 0 0,-1 0 25 0 0,10 24 410 0 0,2 0 0 0 0,1-2 0 0 0,2 0 0 0 0,1-2 1 0 0,34 40-1 0 0,-45-60-791 0 0,1-1 1 0 0,1 0-1 0 0,0-1 1 0 0,20 13-1 0 0,-24-17-218 0 0,1-1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-2 0 0 0,1 1 0 0 0,-1-1 0 0 0,1-1 0 0 0,11 2 0 0 0,-20-3-269 0 0,1-1-1 0 0,-1 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 1 0 0,1 0-1 0 0,-1-1 1 0 0,0 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,2-2 0 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4">6 922 1839 0 0,'-2'3'1308'0'0,"2"0"0"0"0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,1 5 0 0 0,3 29 3136 0 0,-1-17-4116 0 0,7 64 1770 0 0,13 159 1167 0 0,-23-239-3225 0 0,0-1-20 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 1-1 0 0,1 1 1 0 0,-1-5-105 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,1-1-1 0 0,0-1 0 0 0,3-12-856 0 0,1-5-39 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5">175 963 10135 0 0,'1'1'229'0'0,"-1"0"0"0"0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0-1 0 0,0-1 1 0 0,1 2 0 0 0,24 10 2751 0 0,-24-11-3109 0 0,6 2 390 0 0,0 0-1 0 0,1-1 1 0 0,-1 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,1-2-1 0 0,-1 1 1 0 0,1-1-1 0 0,0 0 1 0 0,-1-1 0 0 0,1 0-1 0 0,16-4 1 0 0,2-4 157 0 0,0 0 0 0 0,40-21 0 0 0,-51 23-243 0 0,-4 1-77 0 0,1 0-1 0 0,0 1 1 0 0,16-3-1 0 0,-26 7-65 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 2 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 1 1 0 0,4 3 0 0 0,-5-3 32 0 0,-1 1-1 0 0,1 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 1 1 0 0,0-1-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1 5-1 0 0,-2 3 212 0 0,1 1-1 0 0,-1-1 0 0 0,-7 17 1 0 0,-4-1 238 0 0,0-1 0 0 0,-2 0 0 0 0,-36 46 0 0 0,-5 6 204 0 0,53-71-693 0 0,0 1 0 0 0,0-1 0 0 0,-5 13 0 0 0,9-20-29 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,0 0 0 0 0,7-3-869 0 0,7-9-1114 0 0,7-7-788 0 0,-6 7 913 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6">901 860 2303 0 0,'12'17'11658'0'0,"1"0"-5232"0"0,5 4-3428 0 0,-4-6-2552 0 0,21 18-1 0 0,-32-31-426 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,-1-1 0 0 0,0 1 0 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 0 0 0,1 3 0 0 0,-2-2 5 0 0,0 0-1 0 0,1 1 1 0 0,-2-1-1 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-2 7-1 0 0,-5 9 24 0 0,-4 17-19 0 0,11-34-27 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 5 0 0 0,0-6-6 0 0,0-1-1 0 0,-1 1 0 0 0,1 0 1 0 0,0-1-1 0 0,1 1 1 0 0,-1-1-1 0 0,0 1 1 0 0,0-1-1 0 0,1 1 1 0 0,-1-1-1 0 0,0 0 0 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,0-1 0 0 0,2 1 1 0 0,5 1-63 0 0,1 0 1 0 0,16 2 0 0 0,-20-4 62 0 0,-2 1 0 0 0,1-1-3 0 0,0 0 1 0 0,-1 1-1 0 0,1 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 1 0 0 0,1 0 1 0 0,5 2-1 0 0,-10-3 11 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1-1 0 0,-1 0 1 0 0,1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 1-1 0 0,-12 17 183 0 0,3-8 2 0 0,0-1 0 0 0,-1-1 0 0 0,1 1 1 0 0,-2-2-1 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 1 0 0,-1 0-1 0 0,1-1 0 0 0,-1 0 0 0 0,-17 3 0 0 0,17-6-639 0 0,6-1-2732 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="7">988 885 4607 0 0,'-38'17'10197'0'0,"-25"16"-2001"0"0,62-33-8127 0 0,1 0-1 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,-1 0 0 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 1 0 0,0 1-1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,0-1-1 0 0,-1 1 0 0 0,1 0 0 0 0,-1 0 1 0 0,1-1-1 0 0,-1 1 0 0 0,1 0 0 0 0,0-1 0 0 0,-1 1 1 0 0,1-1-1 0 0,0 1 0 0 0,-1 0 0 0 0,1-1 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 1 0 0,0-1-130 0 0,0 1 1 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1 0 0 0,0 0-1 0 0,0-1 1 0 0,1 1 0 0 0,-1 0 0 0 0,0-1-1 0 0,1 1 1 0 0,-1 0 0 0 0,1-1-1 0 0,0 1 1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0-1 0 0,1-1 1 0 0,4-4-2267 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">12438 1740 9671 0 0,'-10'9'727'0'0,"8"-7"-147"0"0,0-1 1 0 0,1 1-1 0 0,0 0 1 0 0,-2 0 0 0 0,1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 3 0 0 0,-8 16 781 0 0,2 1 1 0 0,2 1 0 0 0,-11 43 0 0 0,16-58-1317 0 0,0 0-1 0 0,1 0 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,1 0 0 0 0,0-1-1 0 0,0 1 1 0 0,7 12-1 0 0,-7-16-45 0 0,-1-1-1 0 0,1 1 0 0 0,1-1 1 0 0,-2 0-1 0 0,1 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,2-1 1 0 0,-3 0-1 0 0,2 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1-1 0 0 0,-2 1 1 0 0,1-1-1 0 0,0 0 0 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,1 0 0 0 0,3 0 1 0 0,-2-1 14 0 0,0 0 1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,8-9 0 0 0,-3 3 96 0 0,-2-1 0 0 0,1 1 1 0 0,-1-2-1 0 0,-1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-2-1 0 0 0,1 1 0 0 0,-2-1 1 0 0,0 0-1 0 0,0-1 0 0 0,-1 1 0 0 0,-1 0 0 0 0,0-1 0 0 0,-1 0 0 0 0,-1-18 0 0 0,0 29 16 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 1 0 0,-1 1-1 0 0,1-1 0 0 0,0 1 1 0 0,-6-4-1 0 0,4 2 40 0 0,-1 1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-9-2 0 0 0,-5 0 151 0 0,0 0 0 0 0,0 2-1 0 0,-33-2 1 0 0,43 3-335 0 0,6 1-101 0 0,-1 1-144 0 0,1-1 0 0 0,-1-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,-1-2 0 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1">6321 372 7367 0 0,'-15'-5'1902'0'0,"-23"-9"-1"0"0,28 9 212 0 0,-3 0 0 0 0,3 1-1 0 0,-2 1 1 0 0,-19-4 0 0 0,-5 3-1079 0 0,0 2 0 0 0,-52 3 0 0 0,63 1-698 0 0,1 1-1 0 0,1 1 1 0 0,0 1 0 0 0,-42 15 0 0 0,-191 87 1156 0 0,74-31-1148 0 0,40-16-192 0 0,75-31-87 0 0,1 3-1 0 0,-73 48 1 0 0,-109 100 34 0 0,133-94-62 0 0,61-48-18 0 0,-53 49 0 0 0,87-68-19 0 0,1 2 0 0 0,3 0 0 0 0,-1 0 0 0 0,2 2 0 0 0,0 0 0 0 0,1 1 0 0 0,2 0 0 0 0,1 1 0 0 0,-1 0 0 0 0,4 1 0 0 0,0 0 0 0 0,-7 37 0 0 0,12-44-24 0 0,0 0 1 0 0,2-1-1 0 0,1 1 1 0 0,0 0-1 0 0,1 0 1 0 0,2-1-1 0 0,0 1 0 0 0,1-1 1 0 0,-1 1-1 0 0,2-1 1 0 0,2-1-1 0 0,13 29 0 0 0,22 39-72 0 0,32 58-52 0 0,-54-106 81 0 0,50 62 0 0 0,-24-47 1 0 0,74 64 1 0 0,-30-31 46 0 0,141 130-55 0 0,-176-171 59 0 0,2-1 1 0 0,89 49 0 0 0,347 154-50 0 0,-111-104 64 0 0,12-36 0 0 0,286 0 0 0 0,-416-79 37 0 0,-5-2-2 0 0,589 61 173 0 0,-283-51-61 0 0,346-26 174 0 0,-363-26-92 0 0,-313 8-107 0 0,238-24 123 0 0,-202-3-124 0 0,-179 22-86 0 0,297-67 182 0 0,-311 61-131 0 0,-1-3-1 0 0,-1-4 0 0 0,136-68 1 0 0,136-116 127 0 0,-253 145-174 0 0,150-94 122 0 0,-207 138-161 0 0,-1-1 0 0 0,-1-2 0 0 0,-1-2 0 0 0,-1-1 0 0 0,-2-2 0 0 0,-1-1 0 0 0,53-70 0 0 0,-49 53 114 0 0,55-101-1 0 0,-76 121-71 0 0,-2-1-1 0 0,1-1 0 0 0,-4 0 0 0 0,1-1 0 0 0,4-43 1 0 0,-8 36-1 0 0,-3-1 1 0 0,-1 0 0 0 0,-1-1-1 0 0,-3 1 1 0 0,-1 0 0 0 0,-2 0 0 0 0,-1 1-1 0 0,-3 0 1 0 0,-1 0 0 0 0,-22-57-1 0 0,12 50 4 0 0,-2 0 0 0 0,-1 1 0 0 0,-2 1 0 0 0,-3 1-1 0 0,0 1 1 0 0,-4 2 0 0 0,-1 1 0 0 0,-1 2 0 0 0,-64-53-1 0 0,-198-131 89 0 0,196 155-93 0 0,-118-57 1 0 0,135 84-6 0 0,0 4 0 0 0,-104-27 0 0 0,-180-27 36 0 0,300 73-66 0 0,-771-149 59 0 0,-115 30 0 0 0,311 80-64 0 0,549 48 0 0 0,-226-8 0 0 0,-51-3 0 0 0,-173-24 0 0 0,-98 21 75 0 0,203 46 75 0 0,403-24-130 0 0,-125 12 51 0 0,-1 6-1 0 0,-165 45 0 0 0,256-44-363 0 0,1 4 1 0 0,2 2-1 0 0,-86 49 0 0 0,130-65-143 0 0,-44 27-2769 0 0,51-26 1841 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2">4222 1440 8751 0 0,'-4'-1'1148'0'0,"-1"0"-1"0"0,1 0 0 0 0,1 0 1 0 0,-1-1-1 0 0,-6-2 0 0 0,7 2-597 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 1 0 0,0-1-1 0 0,1 0 0 0 0,2 1 0 0 0,-6-6 0 0 0,-5-6 1309 0 0,-10 3 288 0 0,9 3-1442 0 0,3 1 0 0 0,-26-12 0 0 0,8 6-107 0 0,12 4-288 0 0,1 1 1 0 0,-2 0-1 0 0,-1 2 0 0 0,1 0 1 0 0,-1 0-1 0 0,-25-3 0 0 0,-9 3 50 0 0,0 2 0 0 0,-69 4 0 0 0,-94-3 15 0 0,57-2-169 0 0,-373-12 194 0 0,495 13-359 0 0,-65-19-1 0 0,65 14 21 0 0,-61-8 0 0 0,19 9 1 0 0,-139-7-60 0 0,189 13-2 0 0,3 0 0 0 0,-32-8 0 0 0,-12-1 0 0 0,-190-11 0 0 0,132 23 0 0 0,45 2 0 0 0,71-4 0 0 0,0 0 0 0 0,-18-4 0 0 0,28 5 0 0 0,-9-2 0 0 0,3 0 0 0 0,1 1 0 0 0,-1 0 0 0 0,-8 0 0 0 0,14 1 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,0-1-1 0 0,3-8-25 0 0,11-11-42 0 0,-11 17 50 0 0,20-30-31 0 0,1 2 1 0 0,50-48-1 0 0,-56 64 31 0 0,0 0-1 0 0,0 1 1 0 0,1 1-1 0 0,0 1 1 0 0,1 1 0 0 0,26-11-1 0 0,-2 2 19 0 0,-25 11 0 0 0,0 1 0 0 0,40-12 0 0 0,-40 16 0 0 0,1 2 0 0 0,1 0 0 0 0,25 0 0 0 0,-47 2-88 0 0,-1 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,1 0 0 0 0,0-1-1 0 0,-2 0 1 0 0,2 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,-2-1-1 0 0,2 0-43 0 0,0 2 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 0 0 0,-2-1 0 0 0,2 1 0 0 0,1-1-1 0 0,-2 1 1 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-4 0 0 0 0,0 2-1532 0 0,0 0-51 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3">1454 1009 13015 0 0,'1'5'703'0'0,"0"0"0"0"0,0 1 0 0 0,1-1 0 0 0,0 0 0 0 0,3 7 0 0 0,1 0 25 0 0,9 24 410 0 0,1 0 0 0 0,2-2 0 0 0,2 0 0 0 0,2-2 1 0 0,33 40-1 0 0,-45-60-791 0 0,1-1 1 0 0,1 0-1 0 0,0-1 1 0 0,20 13-1 0 0,-24-17-218 0 0,1-1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-2 0 0 0,1 1 0 0 0,-1-1 0 0 0,1-1 0 0 0,11 2 0 0 0,-20-3-269 0 0,1-1-1 0 0,-1 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0-1 1 0 0,1 1-1 0 0,0-1 1 0 0,-1 1-1 0 0,2-2 0 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4">6 922 1839 0 0,'-2'3'1308'0'0,"2"0"0"0"0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,1 5 0 0 0,3 29 3136 0 0,-1-17-4116 0 0,7 64 1770 0 0,13 159 1167 0 0,-23-239-3225 0 0,0-1-20 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 1-1 0 0,1 1 1 0 0,-2-5-105 0 0,2 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,1-1-1 0 0,0-1 0 0 0,3-12-856 0 0,1-5-39 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5">175 963 10135 0 0,'1'1'229'0'0,"-1"0"0"0"0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 1-1 0 0,0-1 1 0 0,2 0 0 0 0,-1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0-1 0 0,0-1 1 0 0,1 2 0 0 0,24 10 2751 0 0,-24-11-3109 0 0,6 2 390 0 0,0 0-1 0 0,1-1 1 0 0,0 0 0 0 0,-1-1-1 0 0,0 1 1 0 0,1-2-1 0 0,-1 1 1 0 0,1-1-1 0 0,0 0 1 0 0,-1-1 0 0 0,1 0-1 0 0,15-4 1 0 0,4-4 157 0 0,-1 0 0 0 0,40-21 0 0 0,-51 23-243 0 0,-5 1-77 0 0,3 0-1 0 0,-1 1 1 0 0,16-3-1 0 0,-26 7-65 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,-1 0 0 0 0,2 0 0 0 0,-1-1 0 0 0,0 2 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 1 1 0 0,4 3 0 0 0,-5-3 32 0 0,-1 1-1 0 0,1 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,-1 0-1 0 0,2-1 1 0 0,-1 1-1 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 1 1 0 0,0-1-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1 5-1 0 0,-3 3 212 0 0,3 1-1 0 0,-2-1 0 0 0,-7 17 1 0 0,-4-1 238 0 0,0-1 0 0 0,-2 0 0 0 0,-36 46 0 0 0,-6 6 204 0 0,55-71-693 0 0,-1 1 0 0 0,0-1 0 0 0,-5 13 0 0 0,9-20-29 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,0 0 0 0 0,7-3-869 0 0,7-9-1114 0 0,7-7-788 0 0,-7 7 913 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6">901 860 2303 0 0,'12'17'11658'0'0,"1"0"-5232"0"0,4 4-3428 0 0,-2-6-2552 0 0,20 18-1 0 0,-32-31-426 0 0,-1 0-1 0 0,-1 0 0 0 0,2 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,-1-1 0 0 0,0 1 0 0 0,1 0 1 0 0,-1-1-1 0 0,-1 1 0 0 0,3 3 0 0 0,-3-2 5 0 0,0 0-1 0 0,1 1 1 0 0,-2-1-1 0 0,1 0 1 0 0,0 0-1 0 0,-2 0 1 0 0,1 0-1 0 0,1 0 1 0 0,-3 7-1 0 0,-5 9 24 0 0,-4 17-19 0 0,11-34-27 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 5 0 0 0,0-6-6 0 0,0-1-1 0 0,-1 1 0 0 0,1 0 1 0 0,0-1-1 0 0,1 1 1 0 0,-2-1-1 0 0,1 1 1 0 0,1-1-1 0 0,0 1 1 0 0,-1-1-1 0 0,0 0 0 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,2-1 0 0 0,1 1 1 0 0,5 1-63 0 0,1 0 1 0 0,16 2 0 0 0,-20-4 62 0 0,-2 1 0 0 0,1-1-3 0 0,0 0 1 0 0,-1 1-1 0 0,1 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 1 0 0 0,1 0 1 0 0,5 2-1 0 0,-10-3 11 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1-1 0 0,-1 0 1 0 0,1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-2 1-1 0 0,-10 17 183 0 0,2-8 2 0 0,0-1 0 0 0,-1-1 0 0 0,1 1 1 0 0,-2-2-1 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 1 0 0,-1 0-1 0 0,1-1 0 0 0,-1 0 0 0 0,-18 3 0 0 0,19-6-639 0 0,5-1-2732 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="7">988 885 4607 0 0,'-38'17'10197'0'0,"-26"16"-2001"0"0,64-33-8127 0 0,0 0-1 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,-1 0 0 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 1 0 0,0 1-1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,0-1-1 0 0,-1 1 0 0 0,1 0 0 0 0,-1 0 1 0 0,1-1-1 0 0,-2 1 0 0 0,2 0 0 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,-1 0 0 0 0,1-1 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 1 0 0,0-1-130 0 0,0 1 1 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1 0 0 0,0 0-1 0 0,0-1 1 0 0,1 1 0 0 0,-1 0 0 0 0,0-1-1 0 0,1 1 1 0 0,-1 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,0 0 0 0 0,2 0 0 0 0,-1 0-1 0 0,1-1 1 0 0,4-4-2267 0 0</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -4890,14 +4886,14 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2023-12-12T19:21:10.262"/>
+      <inkml:timestamp xml:id="ts0" timeString="2024-01-09T19:28:26.486"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.035" units="cm"/>
       <inkml:brushProperty name="height" value="0.035" units="cm"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 10624,'0'0'4676,"0"2"-1278,1 0-1057,21 33-165,-9-5-1571,13 56 0,-5 33 112,-21-116-692,25 295 2476,-23 2 48,-2-175-1818,0-121-814,0 25-229,2-10-3090,-1-18 2917,-1-1 0,0 2-1,1-1 1,-1-1 0,1 1-1,0 0 1,-1 0 0,2 1-1,2 2-378</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 10624,'0'0'4676,"0"2"-1278,1 0-1057,21 34-165,-9-7-1571,13 57 0,-5 34 112,-21-117-692,25 294 2476,-23 2 48,-2-173-1818,0-122-814,0 25-229,1-10-3090,0-19 2917,-1 0 0,0 2-1,2-1 1,-2-1 0,1 1-1,0 0 1,-1 0 0,2 1-1,2 3-378</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -4917,14 +4913,14 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2023-12-12T19:21:10.263"/>
+      <inkml:timestamp xml:id="ts0" timeString="2024-01-09T19:28:26.487"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.035" units="cm"/>
       <inkml:brushProperty name="height" value="0.035" units="cm"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">5 0 13312,'-1'0'189,"1"0"0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 1,0 0-1,0 0 0,-1 0 0,1 0 0,0 0 0,0 0 0,-1 0 1,1 0-1,0 0 0,0 0 0,0 1 0,0-1 0,0 0 0,0 0 1,0 0-1,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,-1 0 1,1 1-1,0-1 0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 1,0 0-1,0 0 0,0 1 0,0-1 0,0 0 0,0 0 0,2 6 1473,0 0-977,5 29 1003,-3 0 1,-2 67 0,-15 9-1012,13-108-974,-1 7-2534,1-10 2654,0 0 1,0 1-1,0-1 1,0 0-1,0 1 1,0-1-1,1 0 1,-1 1-1,0-1 0,0 0 1,1 0-1,-1 1 1,0-1-1,0 0 1,0 1-1,1-1 1,-1 0-1,1 0 1,-1 1-1,0-1 0,1 0 1,0 1-1,4-1-863</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">5 0 13312,'-1'0'189,"1"0"0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 1,0 0-1,0 0 0,-1 0 0,1 0 0,0 0 0,0 0 0,-1 0 1,1 0-1,0 0 0,0 0 0,0 1 0,0-1 0,0 0 0,0 0 1,0 0-1,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,-1 0 1,1 1-1,0-1 0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 1,0 0-1,0 0 0,0 1 0,0-1 0,0 0 0,0 0 0,2 6 1473,0 0-977,5 29 1003,-3 0 1,-2 67 0,-15 8-1012,13-107-974,-1 7-2534,1-10 2654,0 0 1,0 1-1,0-1 1,0 0-1,0 1 1,0-1-1,1 0 1,-1 1-1,0-1 0,0 0 1,1 0-1,-1 1 1,0-1-1,0 0 1,0 2-1,1-2 1,-1 0-1,1 0 1,-1 1-1,0-1 0,1 0 1,-1 1-1,6-1-863</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -4944,14 +4940,14 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2023-12-12T19:21:10.260"/>
+      <inkml:timestamp xml:id="ts0" timeString="2024-01-09T19:28:26.484"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.035" units="cm"/>
       <inkml:brushProperty name="height" value="0.035" units="cm"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">239 0 10752,'0'0'306,"-1"0"1,1 0-1,-1 0 1,1 0 0,0 0-1,-1 0 1,1 0-1,-1 0 1,1 0 0,0 0-1,0 0 1,-1 0-1,0 0 1,1 1 0,0-1-1,0 0 1,-1 0 0,1 0-1,-1 1 1,-1 5 2435,2 69 1206,-20 98-861,-130 321-218,115-390-4949,34-100 1727,-1 2-1504,1 1 0,-2-1 0,-6 12 0,2-10 811</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">239 0 10752,'0'0'306,"-1"0"1,1 0-1,-2 0 1,2 0 0,0 0-1,-1 0 1,1 0-1,-1 0 1,1 0 0,0 0-1,0 0 1,-1 0-1,1 0 1,0 1 0,0-1-1,0 0 1,-1 0 0,1 0-1,-1 1 1,-1 5 2435,2 69 1206,-20 98-861,-130 321-218,115-389-4949,34-101 1727,-1 0-1504,1 3 0,-2-1 0,-6 13 0,2-11 811</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -4971,14 +4967,14 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2023-12-12T19:21:10.261"/>
+      <inkml:timestamp xml:id="ts0" timeString="2024-01-09T19:28:26.485"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.035" units="cm"/>
       <inkml:brushProperty name="height" value="0.035" units="cm"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 6 9984,'1'-1'309,"0"1"0,0-1 1,1 1-1,-1-1 0,0 1 0,0-1 1,0 1-1,1-1 0,-1 1 1,0 0-1,1 0 0,-1-1 0,0 1 1,3 0-1,0 0 144,0 0-1,0 1 1,0-1-1,0 1 1,3 1-1,0-1-70,1 2-1,0-1 1,-1 0-1,0 1 1,-1 0 0,2 0-1,-2 0 1,1 0-1,7 7 1,4 3 229,24 23 0,-32-26-492,-8-9-98,12 12 254,14 17 0,-24-26-220,-1 1-1,0-1 1,0 1-1,-1 0 1,1 0-1,-2 0 1,0 0-1,1 6 1,-1-3-62,-2 0-1,1 0 1,-2 1 0,1-1 0,-2-1 0,1 1 0,-2 0 0,-8 14 0,5-12-12,-1 0 1,-1-1 0,1 0-1,-2 0 1,0 0 0,-13 8 0,-3 0 124,-18 13 641,42-29-702,2 0-1,-2 0 1,2 0 0,-1 0 0,0 0 0,0 0-1,0-1 1,1 1 0,0 0 0,-1 1-1,0-2 1,1 1 0,0 2 0,0-2-19,0 0 1,0-1-1,0 1 1,0-1-1,1 1 1,-1 0-1,1 0 1,-1-1-1,0 1 1,1-1 0,0 1-1,-1 0 1,1-1-1,0 1 1,-1-1-1,1 1 1,0-1-1,0 0 1,0 1-1,1 0 1,5 2 66,1 0 0,-1-1 0,0 0 0,1 1-1,0-2 1,0 1 0,10 1 0,57 4-10,-64-6-178,92 2-3040,-100-3 3064,62-1-1102,0-1 538</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 6 9984,'1'-1'309,"0"1"0,0-1 1,1 1-1,-1-1 0,0 1 0,0-1 1,-1 1-1,3-1 0,-2 1 1,0 0-1,1 0 0,-1-1 0,0 1 1,3 0-1,0 0 144,0 0-1,0 1 1,0-1-1,0 1 1,3 1-1,0-1-70,1 2-1,0-1 1,-2 0-1,2 1 1,-2 0 0,2 0-1,-2 0 1,0 0-1,9 8 1,3 1 229,24 24 0,-32-26-492,-9-9-98,14 12 254,13 16 0,-24-24-220,-1 0-1,-1-1 1,1 1-1,0 0 1,0 0-1,-2 0 1,0 0-1,1 6 1,-1-3-62,-2 0-1,1 0 1,-2 1 0,1-1 0,-2-1 0,1 1 0,-3 0 0,-6 15 0,4-13-12,-1-2 1,-1 1 0,1 0-1,-2 1 1,0-1 0,-13 8 0,-3 0 124,-18 13 641,42-29-702,2 0-1,-2 0 1,2 0 0,-1 0 0,0 0 0,0 0-1,0-1 1,1 1 0,0 0 0,-1 1-1,0-2 1,1 1 0,0 2 0,0-2-19,0 0 1,0-1-1,0 1 1,0-1-1,1 1 1,-1 0-1,1 0 1,-1-1-1,0 1 1,1-1 0,0 1-1,-1 0 1,1-1-1,0 1 1,-1-1-1,1 1 1,0-1-1,0 0 1,0 1-1,0 0 1,7 2 66,0 0 0,-1 0 0,0-1 0,1 1-1,0-2 1,-1 1 0,11 1 0,58 4-10,-66-6-178,93 1-3040,-100-2 3064,62-1-1102,1 0 538</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -4998,7 +4994,7 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2023-12-12T19:21:10.266"/>
+      <inkml:timestamp xml:id="ts0" timeString="2024-01-09T19:28:26.490"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.05" units="cm"/>
@@ -5013,9 +5009,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -5053,7 +5049,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -5159,7 +5155,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -5301,14 +5297,14 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39F27F7E-EDCF-45C1-AE43-A2089A5EC6CB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08FB280C-ECB4-45CA-824F-897D28012714}">
   <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5321,13 +5317,10 @@
       <c r="E2" s="1"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A3" s="2">
-        <f>PV(10%,5,,100)</f>
-        <v>-62.092132305915499</v>
-      </c>
-      <c r="B3" t="str">
+      <c r="A3" s="2"/>
+      <c r="B3" t="e">
         <f ca="1">_xlfn.FORMULATEXT(A3)</f>
-        <v>=PV(10%,5,,100)</v>
+        <v>#N/A</v>
       </c>
       <c r="E3" s="1"/>
     </row>
@@ -5350,25 +5343,1178 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1508BF51-0F5E-4861-BD2A-72360AAE729C}">
-  <dimension ref="A1:M19"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1842974-CEFE-4FFD-A62F-114D3366EBE0}">
+  <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="20.265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.06640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A3" s="20"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20"/>
+      <c r="K3" s="20"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A4" s="20"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A5" s="20"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9BF7035-A988-4362-B55F-417A624D4DF1}">
+  <dimension ref="A1:K8"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="20.265625" customWidth="1"/>
+    <col min="3" max="3" width="11.19921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A3" s="20"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20"/>
+      <c r="K3" s="20"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A4" s="20"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A5" s="20"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7">
+        <f>12000/(6%-2%)</f>
+        <v>300000.00000000006</v>
+      </c>
+      <c r="D7" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(C7)</f>
+        <v>=12000/(6%-2%)</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="2">
+        <f>PV(6%,60-30,,C7)</f>
+        <v>-52233.03927319029</v>
+      </c>
+      <c r="D8" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(C8)</f>
+        <v>=PV(6%,60-30,,C7)</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3DD6788-52AA-4C59-AFB2-9ABD8958D709}">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="4" max="4" width="9.53125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A3" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="6"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A4" s="10">
+        <v>0</v>
+      </c>
+      <c r="B4" s="11">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" t="e">
+        <f ca="1">_xlfn.FORMULATEXT(D4)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A5" s="10">
+        <v>1</v>
+      </c>
+      <c r="B5" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A6" s="10">
+        <v>2</v>
+      </c>
+      <c r="B6" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A7" s="10">
+        <v>3</v>
+      </c>
+      <c r="B7" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A8" s="10">
+        <v>4</v>
+      </c>
+      <c r="B8" s="12">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A9" s="10">
+        <v>5</v>
+      </c>
+      <c r="B9" s="12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A10" s="10"/>
+      <c r="B10" s="11"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A11" s="10"/>
+      <c r="B11" s="11"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FE745C6-0592-4255-A467-D38AFADDAD70}">
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="3" max="3" width="9.19921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B3" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B4" s="10">
+        <v>0</v>
+      </c>
+      <c r="C4" s="11">
+        <v>-200</v>
+      </c>
+      <c r="E4" s="13"/>
+      <c r="F4" t="e">
+        <f ca="1">_xlfn.FORMULATEXT(E4)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B5" s="10">
+        <v>1</v>
+      </c>
+      <c r="C5" s="11">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B6" s="10">
+        <v>2</v>
+      </c>
+      <c r="C6" s="11">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B7" s="10">
+        <v>3</v>
+      </c>
+      <c r="C7" s="11">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D0141AE-43B7-4255-B10F-27874C1C5BE3}">
+  <dimension ref="A1:A15"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{173D033A-6307-4D52-BA81-EC59C137080C}">
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B3" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="6"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B4" s="10">
+        <v>0</v>
+      </c>
+      <c r="C4" s="11">
+        <v>100</v>
+      </c>
+      <c r="E4" s="2">
+        <f>100+NPV(10%,C5:C9)</f>
+        <v>236.47229759517165</v>
+      </c>
+      <c r="F4" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(E4)</f>
+        <v>=100+NPV(10%,C5:C9)</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B5" s="10">
+        <v>1</v>
+      </c>
+      <c r="C5" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B6" s="10">
+        <v>2</v>
+      </c>
+      <c r="C6" s="11">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B7" s="10">
+        <v>3</v>
+      </c>
+      <c r="C7" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B8" s="10">
+        <v>4</v>
+      </c>
+      <c r="C8" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A9" s="10"/>
+      <c r="B9" s="10">
+        <v>5</v>
+      </c>
+      <c r="C9" s="12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B17" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B18" s="10">
+        <v>0</v>
+      </c>
+      <c r="C18" s="11">
+        <v>-300</v>
+      </c>
+      <c r="E18" s="13">
+        <f>IRR(C18:C21)</f>
+        <v>0.14951246737419344</v>
+      </c>
+      <c r="F18" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(E18)</f>
+        <v>=IRR(C18:C21)</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B19" s="10">
+        <v>1</v>
+      </c>
+      <c r="C19" s="11">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B20" s="10">
+        <v>2</v>
+      </c>
+      <c r="C20" s="11">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B21" s="10">
+        <v>3</v>
+      </c>
+      <c r="C21" s="11">
+        <v>200</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65EA88EF-E456-4013-BEDB-A97FEB640DCC}">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A1" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A3" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="15">
+        <f>PV(5%,3,100)</f>
+        <v>-272.32480293704799</v>
+      </c>
+      <c r="C3" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(B3)</f>
+        <v>=PV(5%,3,100)</v>
+      </c>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A4" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="15">
+        <f>NPV(5%,G5:G7)</f>
+        <v>272.32480293704782</v>
+      </c>
+      <c r="C4" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(B4)</f>
+        <v>=NPV(5%,G5:G7)</v>
+      </c>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="17">
+        <v>0</v>
+      </c>
+      <c r="G4" s="18">
+        <v>-272.32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A5" s="14"/>
+      <c r="B5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="17">
+        <v>1</v>
+      </c>
+      <c r="G5" s="17">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A6" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="15">
+        <f>PMT(5%,3,-272.32)</f>
+        <v>99.998236320380641</v>
+      </c>
+      <c r="C6" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(B6)</f>
+        <v>=PMT(5%,3,-272.32)</v>
+      </c>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="17">
+        <v>2</v>
+      </c>
+      <c r="G6" s="17">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A7" s="14"/>
+      <c r="B7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="17">
+        <v>3</v>
+      </c>
+      <c r="G7" s="17">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A8" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="15">
+        <f>FV(5%,3,100)</f>
+        <v>-315.25000000000023</v>
+      </c>
+      <c r="C8" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(B8)</f>
+        <v>=FV(5%,3,100)</v>
+      </c>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A9" s="14"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A10" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="19">
+        <f>RATE(3,100,-272.32)</f>
+        <v>5.0009412473203507E-2</v>
+      </c>
+      <c r="C10" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(B10)</f>
+        <v>=RATE(3,100,-272.32)</v>
+      </c>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A11" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="19">
+        <f>IRR(G4:G7)</f>
+        <v>5.0009412471945902E-2</v>
+      </c>
+      <c r="C11" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(B11)</f>
+        <v>=IRR(G4:G7)</v>
+      </c>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A46C32CD-267D-48B3-9259-CAC015C4224D}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" t="e">
+        <f ca="1">_xlfn.FORMULATEXT(B5)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B6" s="5"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B7" s="5"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B8" s="6"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0458AEA8-8188-4E0E-B941-8519F7C12E7E}">
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A3" s="20"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="20"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A13" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A14" s="20"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A15" s="20"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A16" s="20"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I4"/>
+    <mergeCell ref="A13:I16"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52D2D9E6-33ED-4F4C-9640-8CE93970BAF6}">
+  <dimension ref="A1:I20"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="14.06640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A3" s="20"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="20"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="5">
+        <f>PV(5%,3,300)</f>
+        <v>-816.97440881114414</v>
+      </c>
+      <c r="C6" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(B6)</f>
+        <v>=PV(5%,3,300)</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="2">
+        <f>PV(5%,1,,B6)</f>
+        <v>778.07086553442298</v>
+      </c>
+      <c r="C7" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(B7)</f>
+        <v>=PV(5%,1,,B6)</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A13" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A14" s="20"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A15" s="20"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A16" s="20"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="5">
+        <f>-PV(10%,2,100)</f>
+        <v>173.55371900826461</v>
+      </c>
+      <c r="C18" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(B18)</f>
+        <v>=-PV(10%,2,100)</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="2">
+        <f>B18+B19</f>
+        <v>273.55371900826458</v>
+      </c>
+      <c r="C20" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(B20)</f>
+        <v>=B18+B19</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I4"/>
+    <mergeCell ref="A13:I16"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BFD6382-D205-4EAB-8D1D-6468E92D4081}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A3" s="2"/>
+      <c r="B3" t="e">
+        <f ca="1">_xlfn.FORMULATEXT(A3)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A46A343-B2E6-41DF-867E-26B5F826CA27}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A3" s="3"/>
+      <c r="B3" t="e">
+        <f ca="1">_xlfn.FORMULATEXT(A3)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C198BD5-E0D4-4212-BCD3-D09109DFC807}">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A3" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9A8381D-4E53-40B9-BE1D-782AEBBFD5A7}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A3" s="2">
+        <f>PV(8%,3,,300)</f>
+        <v>-238.14967230605089</v>
+      </c>
+      <c r="B3" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(A3)</f>
+        <v>=PV(8%,3,,300)</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{605939A8-10B1-461B-87BD-EE98CA82CBFF}">
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="5">
+        <f>PV(10%,3,100)</f>
+        <v>-248.68519909842246</v>
+      </c>
+      <c r="C7" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(B7)</f>
+        <v>=PV(10%,3,100)</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="5">
+        <f>FV(10%,3,100)</f>
+        <v>-331.0000000000004</v>
+      </c>
+      <c r="C8" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(B8)</f>
+        <v>=FV(10%,3,100)</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="5">
+        <f>PMT(10%,3,B7)</f>
+        <v>100.00000000000011</v>
+      </c>
+      <c r="C9" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(B9)</f>
+        <v>=PMT(10%,3,B7)</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="6">
+        <f>RATE(3,100,B7)</f>
+        <v>0.1</v>
+      </c>
+      <c r="C10" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(B10)</f>
+        <v>=RATE(3,100,B7)</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF5B5E4C-2C11-417E-9B70-1BCA56A356AF}">
+  <dimension ref="A1:M10"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="12.06640625" customWidth="1"/>
+    <col min="2" max="2" width="31.19921875" customWidth="1"/>
+    <col min="3" max="3" width="15.59765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
       <c r="I1" s="7"/>
       <c r="J1" s="7"/>
       <c r="K1" s="7"/>
@@ -5376,14 +6522,14 @@
       <c r="M1" s="7"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A2" s="21"/>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
       <c r="I2" s="7"/>
       <c r="J2" s="7"/>
       <c r="K2" s="7"/>
@@ -5391,14 +6537,14 @@
       <c r="M2" s="7"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A3" s="21"/>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
+      <c r="A3" s="20"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
       <c r="I3" s="7"/>
       <c r="J3" s="7"/>
       <c r="K3" s="7"/>
@@ -5406,14 +6552,14 @@
       <c r="M3" s="7"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A4" s="21"/>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
+      <c r="A4" s="20"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
       <c r="I4" s="7"/>
       <c r="J4" s="7"/>
       <c r="K4" s="7"/>
@@ -5421,14 +6567,14 @@
       <c r="M4" s="7"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A5" s="21"/>
-      <c r="B5" s="21"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21"/>
-      <c r="H5" s="21"/>
+      <c r="A5" s="20"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
       <c r="I5" s="7"/>
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
@@ -5450,1134 +6596,37 @@
       <c r="L6" s="7"/>
       <c r="M6" s="7"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7">
-        <f>60-25</f>
-        <v>35</v>
-      </c>
-      <c r="D7" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(C7)</f>
-        <v>=60-25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="9">
-        <f>PMT(6%,C7,,1000000)</f>
-        <v>-8973.8589796632659</v>
-      </c>
-      <c r="D8" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(C8)</f>
-        <v>=PMT(6%,C7,,1000000)</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A12" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="21"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="21"/>
-      <c r="K12" s="21"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A13" s="21"/>
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21"/>
-      <c r="K13" s="21"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A14" s="21"/>
-      <c r="B14" s="21"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="21"/>
-      <c r="J14" s="21"/>
-      <c r="K14" s="21"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A15" s="21"/>
-      <c r="B15" s="21"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="21"/>
-      <c r="K15" s="21"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A16" s="21"/>
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="21"/>
-      <c r="J16" s="21"/>
-      <c r="K16" s="21"/>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B18" t="s">
-        <v>14</v>
-      </c>
-      <c r="C18">
-        <f>12000/(6%-2%)</f>
-        <v>300000.00000000006</v>
-      </c>
-      <c r="D18" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(C18)</f>
-        <v>=12000/(6%-2%)</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B19" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="9">
-        <f>PV(6%,60-30,,C18)</f>
-        <v>-52233.03927319029</v>
-      </c>
-      <c r="D19" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(C19)</f>
-        <v>=PV(6%,60-30,,C18)</v>
-      </c>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="C10" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="1">
     <mergeCell ref="A1:H5"/>
-    <mergeCell ref="A12:K16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{192AC0C0-C9AD-42DF-B7CE-098DDBA25F5C}">
-  <dimension ref="A1:E11"/>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C48E662-5DB3-458E-96A1-61415DD2D0B8}">
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="4" max="4" width="9.53125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A3" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" s="6"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A4" s="11">
-        <v>0</v>
-      </c>
-      <c r="B4" s="12">
-        <v>0</v>
-      </c>
-      <c r="D4" s="9">
-        <f>NPV(10%,B5:B9)</f>
-        <v>123.56334328877183</v>
-      </c>
-      <c r="E4" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(D4)</f>
-        <v>=NPV(10%,B5:B9)</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A5" s="11">
-        <v>1</v>
-      </c>
-      <c r="B5" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A6" s="11">
-        <v>2</v>
-      </c>
-      <c r="B6" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A7" s="11">
-        <v>3</v>
-      </c>
-      <c r="B7" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A8" s="11">
-        <v>4</v>
-      </c>
-      <c r="B8" s="13">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A9" s="11">
-        <v>5</v>
-      </c>
-      <c r="B9" s="13">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A10" s="11"/>
-      <c r="B10" s="12"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A11" s="11"/>
-      <c r="B11" s="12"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B18EB6B-6A4B-4B3E-9941-EA32E1D89F55}">
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="3" max="3" width="9.19921875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B3" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B4" s="11">
-        <v>0</v>
-      </c>
-      <c r="C4" s="12">
-        <v>-200</v>
-      </c>
-      <c r="E4" s="14">
-        <f>IRR(C4:C7)</f>
-        <v>7.0715793648357117E-2</v>
-      </c>
-      <c r="F4" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(E4)</f>
-        <v>=IRR(C4:C7)</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B5" s="11">
-        <v>1</v>
-      </c>
-      <c r="C5" s="12">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B6" s="11">
-        <v>2</v>
-      </c>
-      <c r="C6" s="12">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B7" s="11">
-        <v>3</v>
-      </c>
-      <c r="C7" s="12">
-        <v>20</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6BD4509-448D-4E0A-BAAF-73391DD0050D}">
-  <dimension ref="A1:A15"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>21</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD0512CB-51C7-4334-983A-34A08F608B9E}">
-  <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B3" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="6"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B4" s="11">
-        <v>0</v>
-      </c>
-      <c r="C4" s="12">
-        <v>100</v>
-      </c>
-      <c r="E4" s="9">
-        <f>100+NPV(10%,C5:C9)</f>
-        <v>236.47229759517165</v>
-      </c>
-      <c r="F4" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(E4)</f>
-        <v>=100+NPV(10%,C5:C9)</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B5" s="11">
-        <v>1</v>
-      </c>
-      <c r="C5" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B6" s="11">
-        <v>2</v>
-      </c>
-      <c r="C6" s="12">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B7" s="11">
-        <v>3</v>
-      </c>
-      <c r="C7" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B8" s="11">
-        <v>4</v>
-      </c>
-      <c r="C8" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A9" s="11"/>
-      <c r="B9" s="11">
-        <v>5</v>
-      </c>
-      <c r="C9" s="13">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B17" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B18" s="11">
-        <v>0</v>
-      </c>
-      <c r="C18" s="12">
-        <v>-300</v>
-      </c>
-      <c r="E18" s="14">
-        <f>IRR(C18:C21)</f>
-        <v>0.14951246737419344</v>
-      </c>
-      <c r="F18" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(E18)</f>
-        <v>=IRR(C18:C21)</v>
-      </c>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B19" s="11">
-        <v>1</v>
-      </c>
-      <c r="C19" s="12">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B20" s="11">
-        <v>2</v>
-      </c>
-      <c r="C20" s="12">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B21" s="11">
-        <v>3</v>
-      </c>
-      <c r="C21" s="12">
-        <v>200</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38AB1A09-E8CC-48B7-B8CF-F7774090D606}">
-  <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A1" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A2" s="15"/>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A3" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="16">
-        <f>PV(5%,3,100)</f>
-        <v>-272.32480293704799</v>
-      </c>
-      <c r="C3" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(B3)</f>
-        <v>=PV(5%,3,100)</v>
-      </c>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="17" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A4" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="16">
-        <f>NPV(5%,G5:G7)</f>
-        <v>272.32480293704782</v>
-      </c>
-      <c r="C4" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(B4)</f>
-        <v>=NPV(5%,G5:G7)</v>
-      </c>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="18">
-        <v>0</v>
-      </c>
-      <c r="G4" s="19">
-        <v>-272.32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A5" s="15"/>
-      <c r="B5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="18">
-        <v>1</v>
-      </c>
-      <c r="G5" s="18">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A6" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="16">
-        <f>PMT(5%,3,-272.32)</f>
-        <v>99.998236320380641</v>
-      </c>
-      <c r="C6" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(B6)</f>
-        <v>=PMT(5%,3,-272.32)</v>
-      </c>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="18">
-        <v>2</v>
-      </c>
-      <c r="G6" s="18">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A7" s="15"/>
-      <c r="B7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="18">
-        <v>3</v>
-      </c>
-      <c r="G7" s="18">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A8" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="16">
-        <f>FV(5%,3,100)</f>
-        <v>-315.25000000000023</v>
-      </c>
-      <c r="C8" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(B8)</f>
-        <v>=FV(5%,3,100)</v>
-      </c>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A9" s="15"/>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A10" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="20">
-        <f>RATE(3,100,-272.32)</f>
-        <v>5.0009412473203507E-2</v>
-      </c>
-      <c r="C10" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(B10)</f>
-        <v>=RATE(3,100,-272.32)</v>
-      </c>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A11" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="20">
-        <f>IRR(G4:G7)</f>
-        <v>5.0009412471945902E-2</v>
-      </c>
-      <c r="C11" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(B11)</f>
-        <v>=IRR(G4:G7)</v>
-      </c>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA36BBD1-D8AF-4BD3-B85D-2FB6E38E6987}">
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="5">
-        <f>PV(10%,3,100,500)</f>
-        <v>-624.34259954921129</v>
-      </c>
-      <c r="C5" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(B5)</f>
-        <v>=PV(10%,3,100,500)</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B6" s="5"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B7" s="5"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B8" s="6"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF6D5298-036F-439A-A287-610975801704}">
-  <dimension ref="A1:I16"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData>
-    <row r="1" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A2" s="21"/>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A3" s="21"/>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A4" s="21"/>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A13" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A14" s="21"/>
-      <c r="B14" s="21"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="21"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A15" s="21"/>
-      <c r="B15" s="21"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A16" s="21"/>
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="21"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:I4"/>
-    <mergeCell ref="A13:I16"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06520E4B-C88E-4A99-A2B8-A732E23DFC3B}">
-  <dimension ref="A1:I22"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="14.06640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A1" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A2" s="21"/>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A3" s="21"/>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A4" s="21"/>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="5">
-        <f>PV(5%,3,300)</f>
-        <v>-816.97440881114414</v>
-      </c>
-      <c r="C6" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(B6)</f>
-        <v>=PV(5%,3,300)</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="2">
-        <f>PV(5%,1,,B6)</f>
-        <v>778.07086553442298</v>
-      </c>
-      <c r="C7" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(B7)</f>
-        <v>=PV(5%,1,,B6)</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A13" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A14" s="21"/>
-      <c r="B14" s="21"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="21"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A15" s="21"/>
-      <c r="B15" s="21"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A16" s="21"/>
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="21"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>30</v>
-      </c>
-      <c r="B18" s="5">
-        <f>-PV(10%,2,100)</f>
-        <v>173.55371900826461</v>
-      </c>
-      <c r="C18" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(B18)</f>
-        <v>=-PV(10%,2,100)</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
-        <v>31</v>
-      </c>
-      <c r="B19" s="5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="2">
-        <f>B18+B19</f>
-        <v>273.55371900826458</v>
-      </c>
-      <c r="C20" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(B20)</f>
-        <v>=B18+B19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="F22" t="s">
-        <v>32</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:I4"/>
-    <mergeCell ref="A13:I16"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{816F1BBD-12C4-4132-A007-46994421DAA9}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A3" s="2">
-        <f>FV(10%,5,,62.09)</f>
-        <v>-99.996565900000036</v>
-      </c>
-      <c r="B3" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(A3)</f>
-        <v>=FV(10%,5,,62.09)</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0BD5658-2A87-4877-A5A5-19294764CA7B}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A3" s="3">
-        <f>RATE(5,,-62.09,100)</f>
-        <v>0.10000755515027103</v>
-      </c>
-      <c r="B3" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(A3)</f>
-        <v>=RATE(5,,-62.09,100)</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC798F81-C0F8-49DB-85BE-FD215B8CD197}">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A3" s="4"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13D7F479-15E1-45BC-B943-7D2676585ACD}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A3" s="2">
-        <f>PV(8%,3,,300)</f>
-        <v>-238.14967230605089</v>
-      </c>
-      <c r="B3" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(A3)</f>
-        <v>=PV(8%,3,,300)</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6854D54A-747B-4709-B2AD-1310300780CD}">
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="5">
-        <f>PV(10%,3,100)</f>
-        <v>-248.68519909842246</v>
-      </c>
-      <c r="C7" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(B7)</f>
-        <v>=PV(10%,3,100)</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="5">
-        <f>FV(10%,3,100)</f>
-        <v>-331.0000000000004</v>
-      </c>
-      <c r="C8" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(B8)</f>
-        <v>=FV(10%,3,100)</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="5">
-        <f>PMT(10%,3,B7)</f>
-        <v>100.00000000000011</v>
-      </c>
-      <c r="C9" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(B9)</f>
-        <v>=PMT(10%,3,B7)</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="6">
-        <f>RATE(3,100,B7)</f>
-        <v>0.1</v>
-      </c>
-      <c r="C10" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(B10)</f>
-        <v>=RATE(3,100,B7)</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBE5520B-B915-4AE9-9055-F291F78A114D}">
-  <dimension ref="A1:M10"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="12.1328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.265625" customWidth="1"/>
+    <col min="3" max="3" width="10.796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
       <c r="I1" s="7"/>
       <c r="J1" s="7"/>
       <c r="K1" s="7"/>
@@ -6585,14 +6634,14 @@
       <c r="M1" s="7"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A2" s="21"/>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
       <c r="I2" s="7"/>
       <c r="J2" s="7"/>
       <c r="K2" s="7"/>
@@ -6600,14 +6649,14 @@
       <c r="M2" s="7"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A3" s="21"/>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
+      <c r="A3" s="20"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
       <c r="I3" s="7"/>
       <c r="J3" s="7"/>
       <c r="K3" s="7"/>
@@ -6615,14 +6664,14 @@
       <c r="M3" s="7"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A4" s="21"/>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
+      <c r="A4" s="20"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
       <c r="I4" s="7"/>
       <c r="J4" s="7"/>
       <c r="K4" s="7"/>
@@ -6630,14 +6679,14 @@
       <c r="M4" s="7"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A5" s="21"/>
-      <c r="B5" s="21"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21"/>
-      <c r="H5" s="21"/>
+      <c r="A5" s="20"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
       <c r="I5" s="7"/>
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
@@ -6659,8 +6708,31 @@
       <c r="L6" s="7"/>
       <c r="M6" s="7"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="C10" s="5"/>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <f>60-25</f>
+        <v>35</v>
+      </c>
+      <c r="D7" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(C7)</f>
+        <v>=60-25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="2">
+        <f>PMT(6%,C7,,1000000)</f>
+        <v>-8973.8589796632659</v>
+      </c>
+      <c r="D8" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(C8)</f>
+        <v>=PMT(6%,C7,,1000000)</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6670,113 +6742,27 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D115D9D-42BF-4FA9-AC85-8401715F2639}">
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E5A7A26-7CA9-41EF-92D3-1E3B768DE411}">
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="10.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.06640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A3" s="8">
-        <f>100/10%</f>
-        <v>1000</v>
-      </c>
-      <c r="B3" t="str">
+      <c r="A3" s="8"/>
+      <c r="B3" t="e">
         <f ca="1">_xlfn.FORMULATEXT(A3)</f>
-        <v>=100/10%</v>
+        <v>#N/A</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5C980E8-BCA5-4175-8837-BCCF08BC2E92}">
-  <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="3" max="3" width="12.1328125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A1" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A2" s="21"/>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A3" s="21"/>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="21"/>
-      <c r="K3" s="21"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A4" s="21"/>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="21"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A5" s="21"/>
-      <c r="B5" s="21"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21"/>
-      <c r="H5" s="21"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="21"/>
-      <c r="K5" s="21"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:K5"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>